--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA81445-66AA-4436-8BF0-DFE7A6BE6924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8D40CF-9715-4467-9C20-76336593EF18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="83">
   <si>
     <t>Commodities</t>
   </si>
@@ -10086,7 +10086,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68B577B-1347-43AB-A697-F4519763B965}">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -10760,6 +10760,666 @@
         <v>0</v>
       </c>
     </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>12</v>
+      </c>
+      <c r="B63" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>12</v>
+      </c>
+      <c r="B64" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>12</v>
+      </c>
+      <c r="B65" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>12</v>
+      </c>
+      <c r="B66" t="s">
+        <v>23</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>12</v>
+      </c>
+      <c r="B67" t="s">
+        <v>25</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>12</v>
+      </c>
+      <c r="B68" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>12</v>
+      </c>
+      <c r="B69" t="s">
+        <v>29</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>12</v>
+      </c>
+      <c r="B70" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>12</v>
+      </c>
+      <c r="B71" t="s">
+        <v>33</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>12</v>
+      </c>
+      <c r="B72" t="s">
+        <v>35</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>12</v>
+      </c>
+      <c r="B73" t="s">
+        <v>37</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>12</v>
+      </c>
+      <c r="B74" t="s">
+        <v>39</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>12</v>
+      </c>
+      <c r="B75" t="s">
+        <v>41</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>12</v>
+      </c>
+      <c r="B76" t="s">
+        <v>43</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>12</v>
+      </c>
+      <c r="B77" t="s">
+        <v>45</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>12</v>
+      </c>
+      <c r="B78" t="s">
+        <v>46</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>12</v>
+      </c>
+      <c r="B79" t="s">
+        <v>48</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>12</v>
+      </c>
+      <c r="B80" t="s">
+        <v>49</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>12</v>
+      </c>
+      <c r="B81" t="s">
+        <v>51</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>12</v>
+      </c>
+      <c r="B82" t="s">
+        <v>52</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>12</v>
+      </c>
+      <c r="B83" t="s">
+        <v>54</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>12</v>
+      </c>
+      <c r="B84" t="s">
+        <v>56</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>12</v>
+      </c>
+      <c r="B85" t="s">
+        <v>58</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>12</v>
+      </c>
+      <c r="B86" t="s">
+        <v>59</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>12</v>
+      </c>
+      <c r="B87" t="s">
+        <v>38</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>12</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>12</v>
+      </c>
+      <c r="B89" t="s">
+        <v>28</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>12</v>
+      </c>
+      <c r="B90" t="s">
+        <v>44</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>12</v>
+      </c>
+      <c r="B91" t="s">
+        <v>62</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92" t="s">
+        <v>22</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>12</v>
+      </c>
+      <c r="B93" t="s">
+        <v>63</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>12</v>
+      </c>
+      <c r="B94" t="s">
+        <v>66</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>12</v>
+      </c>
+      <c r="B95" t="s">
+        <v>24</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>12</v>
+      </c>
+      <c r="B96" t="s">
+        <v>18</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>12</v>
+      </c>
+      <c r="B97" t="s">
+        <v>42</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>12</v>
+      </c>
+      <c r="B98" t="s">
+        <v>30</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>12</v>
+      </c>
+      <c r="B99" t="s">
+        <v>64</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>12</v>
+      </c>
+      <c r="B100" t="s">
+        <v>67</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>12</v>
+      </c>
+      <c r="B101" t="s">
+        <v>68</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>12</v>
+      </c>
+      <c r="B102" t="s">
+        <v>70</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>12</v>
+      </c>
+      <c r="B103" t="s">
+        <v>71</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>12</v>
+      </c>
+      <c r="B104" t="s">
+        <v>20</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>12</v>
+      </c>
+      <c r="B105" t="s">
+        <v>53</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>12</v>
+      </c>
+      <c r="B106" t="s">
+        <v>26</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>12</v>
+      </c>
+      <c r="B107" t="s">
+        <v>75</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>12</v>
+      </c>
+      <c r="B108" t="s">
+        <v>34</v>
+      </c>
+      <c r="C108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>12</v>
+      </c>
+      <c r="B109" t="s">
+        <v>32</v>
+      </c>
+      <c r="C109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>12</v>
+      </c>
+      <c r="B110" t="s">
+        <v>60</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>12</v>
+      </c>
+      <c r="B111" t="s">
+        <v>74</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>12</v>
+      </c>
+      <c r="B112" t="s">
+        <v>55</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>12</v>
+      </c>
+      <c r="B113" t="s">
+        <v>77</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>12</v>
+      </c>
+      <c r="B114" t="s">
+        <v>36</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>12</v>
+      </c>
+      <c r="B115" t="s">
+        <v>50</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>12</v>
+      </c>
+      <c r="B116" t="s">
+        <v>40</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>12</v>
+      </c>
+      <c r="B117" t="s">
+        <v>57</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>12</v>
+      </c>
+      <c r="B118" t="s">
+        <v>47</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>12</v>
+      </c>
+      <c r="B119" t="s">
+        <v>78</v>
+      </c>
+      <c r="C119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>12</v>
+      </c>
+      <c r="B120" t="s">
+        <v>79</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>12</v>
+      </c>
+      <c r="B121" t="s">
+        <v>81</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF8D40CF-9715-4467-9C20-76336593EF18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2C3AFA-9616-498F-8081-1155D6067C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1414" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="81">
   <si>
     <t>Commodities</t>
   </si>
@@ -159,12 +159,6 @@
     <t>UK</t>
   </si>
   <si>
-    <t>DZ_Prod</t>
-  </si>
-  <si>
-    <t>DZ</t>
-  </si>
-  <si>
     <t>DK_Prod</t>
   </si>
   <si>
@@ -249,9 +243,6 @@
     <t>HU</t>
   </si>
   <si>
-    <t>SM</t>
-  </si>
-  <si>
     <t>RS</t>
   </si>
   <si>
@@ -289,6 +280,9 @@
   </si>
   <si>
     <t>IR</t>
+  </si>
+  <si>
+    <t>MA_Prod</t>
   </si>
 </sst>
 </file>
@@ -646,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0CB446-BDDD-415D-AF22-2CEB1FE45CA5}">
-  <dimension ref="A1:A61"/>
+  <dimension ref="A1:A60"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -716,67 +710,67 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.35">
@@ -796,12 +790,12 @@
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.35">
@@ -811,12 +805,12 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.35">
@@ -831,7 +825,7 @@
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.35">
@@ -841,27 +835,27 @@
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.35">
@@ -871,7 +865,7 @@
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.35">
@@ -881,7 +875,7 @@
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.35">
@@ -896,22 +890,22 @@
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
@@ -921,37 +915,32 @@
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -986,7 +975,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B138"/>
+  <dimension ref="A1:B140"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -1095,31 +1084,31 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
@@ -1127,15 +1116,15 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
         <v>28</v>
@@ -1143,15 +1132,15 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
         <v>30</v>
@@ -1159,31 +1148,31 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B22" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B25" t="s">
         <v>38</v>
@@ -1191,10 +1180,10 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
@@ -1210,7 +1199,7 @@
         <v>38</v>
       </c>
       <c r="B28" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
@@ -1234,7 +1223,7 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
@@ -1258,12 +1247,12 @@
         <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B35" t="s">
         <v>16</v>
@@ -1271,7 +1260,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B36" t="s">
         <v>28</v>
@@ -1279,23 +1268,23 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B37" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B38" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B39" t="s">
         <v>18</v>
@@ -1303,15 +1292,15 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B41" t="s">
         <v>30</v>
@@ -1319,31 +1308,31 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B45" t="s">
         <v>22</v>
@@ -1351,26 +1340,26 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
@@ -1378,7 +1367,7 @@
         <v>22</v>
       </c>
       <c r="B49" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
@@ -1386,7 +1375,7 @@
         <v>22</v>
       </c>
       <c r="B50" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
@@ -1394,55 +1383,55 @@
         <v>22</v>
       </c>
       <c r="B51" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="B52" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B53" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B55" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B56" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
@@ -1455,10 +1444,10 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
@@ -1466,7 +1455,7 @@
         <v>18</v>
       </c>
       <c r="B60" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
@@ -1474,60 +1463,60 @@
         <v>18</v>
       </c>
       <c r="B61" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="B62" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
+        <v>30</v>
+      </c>
+      <c r="B63" t="s">
         <v>42</v>
-      </c>
-      <c r="B63" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B65" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B66" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B68" t="s">
         <v>62</v>
@@ -1535,39 +1524,39 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B69" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B70" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B71" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B72" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B73" t="s">
         <v>67</v>
@@ -1575,103 +1564,103 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B74" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
+        <v>67</v>
+      </c>
+      <c r="B75" t="s">
         <v>68</v>
-      </c>
-      <c r="B75" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B77" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B78" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B79" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B80" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B81" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="B82" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="B83" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="B84" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B85" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B86" t="s">
         <v>71</v>
@@ -1679,314 +1668,314 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="B87" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
+        <v>26</v>
+      </c>
+      <c r="B88" t="s">
         <v>53</v>
-      </c>
-      <c r="B88" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
+        <v>72</v>
+      </c>
+      <c r="B89" t="s">
         <v>26</v>
-      </c>
-      <c r="B89" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="B90" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="B91" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="B92" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
+        <v>32</v>
+      </c>
+      <c r="B93" t="s">
         <v>34</v>
-      </c>
-      <c r="B93" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="B94" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="B95" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B96" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B97" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B98" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B99" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="B100" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B101" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="B102" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="B103" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="B104" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B105" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B106" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B107" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B108" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="B109" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B110" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B111" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="B112" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="B113" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B115" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B116" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="B117" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B118" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B119" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B120" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
+        <v>68</v>
+      </c>
+      <c r="B121" t="s">
         <v>70</v>
-      </c>
-      <c r="B121" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="B122" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="B123" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="B124" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B125" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
@@ -1994,79 +1983,79 @@
         <v>55</v>
       </c>
       <c r="B126" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="B127" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="B128" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="B129" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="B130" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B131" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B132" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B133" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B134" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B135" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
@@ -2074,23 +2063,39 @@
         <v>38</v>
       </c>
       <c r="B136" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="B137" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B138" t="s">
-        <v>28</v>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>72</v>
+      </c>
+      <c r="B139" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>77</v>
+      </c>
+      <c r="B140" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2100,7 +2105,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
-  <dimension ref="A1:I275"/>
+  <dimension ref="A1:I273"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -2485,10 +2490,10 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="D14">
         <v>500</v>
@@ -2514,10 +2519,10 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D15">
         <v>500</v>
@@ -2543,10 +2548,10 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D16">
         <v>500</v>
@@ -2572,7 +2577,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
@@ -2601,10 +2606,10 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D18">
         <v>500</v>
@@ -2630,7 +2635,7 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
         <v>28</v>
@@ -2659,10 +2664,10 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D20">
         <v>500</v>
@@ -2688,7 +2693,7 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
         <v>30</v>
@@ -2717,10 +2722,10 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D22">
         <v>500</v>
@@ -2746,10 +2751,10 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D23">
         <v>500</v>
@@ -2775,10 +2780,10 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D24">
         <v>500</v>
@@ -2804,7 +2809,7 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C25" t="s">
         <v>38</v>
@@ -2833,10 +2838,10 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C26" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D26">
         <v>500</v>
@@ -2894,7 +2899,7 @@
         <v>38</v>
       </c>
       <c r="C28" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D28">
         <v>500</v>
@@ -2981,7 +2986,7 @@
         <v>16</v>
       </c>
       <c r="C31" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D31">
         <v>500</v>
@@ -3068,7 +3073,7 @@
         <v>28</v>
       </c>
       <c r="C34" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D34">
         <v>500</v>
@@ -3094,7 +3099,7 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C35" t="s">
         <v>16</v>
@@ -3123,7 +3128,7 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
@@ -3152,10 +3157,10 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C37" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D37">
         <v>500</v>
@@ -3181,10 +3186,10 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D38">
         <v>500</v>
@@ -3210,7 +3215,7 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
@@ -3239,10 +3244,10 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C40" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D40">
         <v>500</v>
@@ -3268,7 +3273,7 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C41" t="s">
         <v>30</v>
@@ -3297,10 +3302,10 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C42" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D42">
         <v>500</v>
@@ -3326,10 +3331,10 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C43" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D43">
         <v>500</v>
@@ -3355,10 +3360,10 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C44" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D44">
         <v>500</v>
@@ -3384,7 +3389,7 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C45" t="s">
         <v>22</v>
@@ -3413,10 +3418,10 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C46" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D46">
         <v>500</v>
@@ -3442,10 +3447,10 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C47" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D47">
         <v>500</v>
@@ -3471,10 +3476,10 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C48" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D48">
         <v>500</v>
@@ -3503,7 +3508,7 @@
         <v>22</v>
       </c>
       <c r="C49" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D49">
         <v>500</v>
@@ -3532,7 +3537,7 @@
         <v>22</v>
       </c>
       <c r="C50" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D50">
         <v>500</v>
@@ -3561,7 +3566,7 @@
         <v>22</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D51">
         <v>500</v>
@@ -3587,10 +3592,10 @@
         <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="D52">
         <v>500</v>
@@ -3616,10 +3621,10 @@
         <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D53">
         <v>500</v>
@@ -3645,10 +3650,10 @@
         <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D54">
         <v>500</v>
@@ -3674,10 +3679,10 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C55" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D55">
         <v>500</v>
@@ -3703,10 +3708,10 @@
         <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C56" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D56">
         <v>500</v>
@@ -3732,10 +3737,10 @@
         <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="C57" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="D57">
         <v>500</v>
@@ -3790,10 +3795,10 @@
         <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C59" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="D59">
         <v>500</v>
@@ -3822,7 +3827,7 @@
         <v>18</v>
       </c>
       <c r="C60" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="D60">
         <v>500</v>
@@ -3851,7 +3856,7 @@
         <v>18</v>
       </c>
       <c r="C61" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="D61">
         <v>500</v>
@@ -3877,10 +3882,10 @@
         <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C62" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D62">
         <v>500</v>
@@ -3906,10 +3911,10 @@
         <v>11</v>
       </c>
       <c r="B63" t="s">
+        <v>30</v>
+      </c>
+      <c r="C63" t="s">
         <v>42</v>
-      </c>
-      <c r="C63" t="s">
-        <v>44</v>
       </c>
       <c r="D63">
         <v>500</v>
@@ -3935,10 +3940,10 @@
         <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="C64" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D64">
         <v>500</v>
@@ -3964,10 +3969,10 @@
         <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C65" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D65">
         <v>500</v>
@@ -3993,10 +3998,10 @@
         <v>11</v>
       </c>
       <c r="B66" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C66" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D66">
         <v>500</v>
@@ -4022,10 +4027,10 @@
         <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D67">
         <v>500</v>
@@ -4051,7 +4056,7 @@
         <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C68" t="s">
         <v>62</v>
@@ -4080,10 +4085,10 @@
         <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C69" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D69">
         <v>500</v>
@@ -4109,10 +4114,10 @@
         <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C70" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D70">
         <v>500</v>
@@ -4138,10 +4143,10 @@
         <v>11</v>
       </c>
       <c r="B71" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C71" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D71">
         <v>500</v>
@@ -4167,10 +4172,10 @@
         <v>11</v>
       </c>
       <c r="B72" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C72" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="D72">
         <v>500</v>
@@ -4196,7 +4201,7 @@
         <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C73" t="s">
         <v>67</v>
@@ -4225,10 +4230,10 @@
         <v>11</v>
       </c>
       <c r="B74" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C74" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="D74">
         <v>500</v>
@@ -4254,10 +4259,10 @@
         <v>11</v>
       </c>
       <c r="B75" t="s">
+        <v>67</v>
+      </c>
+      <c r="C75" t="s">
         <v>68</v>
-      </c>
-      <c r="C75" t="s">
-        <v>53</v>
       </c>
       <c r="D75">
         <v>500</v>
@@ -4283,10 +4288,10 @@
         <v>11</v>
       </c>
       <c r="B76" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C76" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D76">
         <v>500</v>
@@ -4312,10 +4317,10 @@
         <v>11</v>
       </c>
       <c r="B77" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C77" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D77">
         <v>500</v>
@@ -4341,10 +4346,10 @@
         <v>11</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C78" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="D78">
         <v>500</v>
@@ -4370,10 +4375,10 @@
         <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C79" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D79">
         <v>500</v>
@@ -4399,10 +4404,10 @@
         <v>11</v>
       </c>
       <c r="B80" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C80" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="D80">
         <v>500</v>
@@ -4428,10 +4433,10 @@
         <v>11</v>
       </c>
       <c r="B81" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C81" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="D81">
         <v>500</v>
@@ -4457,10 +4462,10 @@
         <v>11</v>
       </c>
       <c r="B82" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="C82" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="D82">
         <v>500</v>
@@ -4486,10 +4491,10 @@
         <v>11</v>
       </c>
       <c r="B83" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C83" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D83">
         <v>500</v>
@@ -4515,10 +4520,10 @@
         <v>11</v>
       </c>
       <c r="B84" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C84" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D84">
         <v>500</v>
@@ -4544,10 +4549,10 @@
         <v>11</v>
       </c>
       <c r="B85" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C85" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D85">
         <v>500</v>
@@ -4573,7 +4578,7 @@
         <v>11</v>
       </c>
       <c r="B86" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C86" t="s">
         <v>71</v>
@@ -4602,10 +4607,10 @@
         <v>11</v>
       </c>
       <c r="B87" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="C87" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D87">
         <v>500</v>
@@ -4631,10 +4636,10 @@
         <v>11</v>
       </c>
       <c r="B88" t="s">
+        <v>26</v>
+      </c>
+      <c r="C88" t="s">
         <v>53</v>
-      </c>
-      <c r="C88" t="s">
-        <v>74</v>
       </c>
       <c r="D88">
         <v>500</v>
@@ -4660,10 +4665,10 @@
         <v>11</v>
       </c>
       <c r="B89" t="s">
+        <v>72</v>
+      </c>
+      <c r="C89" t="s">
         <v>26</v>
-      </c>
-      <c r="C89" t="s">
-        <v>75</v>
       </c>
       <c r="D89">
         <v>500</v>
@@ -4689,10 +4694,10 @@
         <v>11</v>
       </c>
       <c r="B90" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="C90" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D90">
         <v>500</v>
@@ -4718,10 +4723,10 @@
         <v>11</v>
       </c>
       <c r="B91" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="C91" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D91">
         <v>500</v>
@@ -4747,10 +4752,10 @@
         <v>11</v>
       </c>
       <c r="B92" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="C92" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="D92">
         <v>500</v>
@@ -4776,10 +4781,10 @@
         <v>11</v>
       </c>
       <c r="B93" t="s">
+        <v>32</v>
+      </c>
+      <c r="C93" t="s">
         <v>34</v>
-      </c>
-      <c r="C93" t="s">
-        <v>18</v>
       </c>
       <c r="D93">
         <v>500</v>
@@ -4805,10 +4810,10 @@
         <v>11</v>
       </c>
       <c r="B94" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C94" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D94">
         <v>500</v>
@@ -4834,10 +4839,10 @@
         <v>11</v>
       </c>
       <c r="B95" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C95" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="D95">
         <v>500</v>
@@ -4863,10 +4868,10 @@
         <v>11</v>
       </c>
       <c r="B96" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C96" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="D96">
         <v>500</v>
@@ -4892,10 +4897,10 @@
         <v>11</v>
       </c>
       <c r="B97" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C97" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="D97">
         <v>500</v>
@@ -4921,10 +4926,10 @@
         <v>11</v>
       </c>
       <c r="B98" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C98" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D98">
         <v>500</v>
@@ -4950,10 +4955,10 @@
         <v>11</v>
       </c>
       <c r="B99" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C99" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D99">
         <v>500</v>
@@ -4979,10 +4984,10 @@
         <v>11</v>
       </c>
       <c r="B100" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C100" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="D100">
         <v>500</v>
@@ -5008,10 +5013,10 @@
         <v>11</v>
       </c>
       <c r="B101" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C101" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="D101">
         <v>500</v>
@@ -5037,10 +5042,10 @@
         <v>11</v>
       </c>
       <c r="B102" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="C102" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="D102">
         <v>500</v>
@@ -5066,10 +5071,10 @@
         <v>11</v>
       </c>
       <c r="B103" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C103" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D103">
         <v>500</v>
@@ -5095,10 +5100,10 @@
         <v>11</v>
       </c>
       <c r="B104" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="C104" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D104">
         <v>500</v>
@@ -5124,10 +5129,10 @@
         <v>11</v>
       </c>
       <c r="B105" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C105" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="D105">
         <v>500</v>
@@ -5153,10 +5158,10 @@
         <v>11</v>
       </c>
       <c r="B106" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C106" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D106">
         <v>500</v>
@@ -5182,10 +5187,10 @@
         <v>11</v>
       </c>
       <c r="B107" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C107" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D107">
         <v>500</v>
@@ -5211,10 +5216,10 @@
         <v>11</v>
       </c>
       <c r="B108" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C108" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D108">
         <v>500</v>
@@ -5240,10 +5245,10 @@
         <v>11</v>
       </c>
       <c r="B109" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="C109" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D109">
         <v>500</v>
@@ -5269,10 +5274,10 @@
         <v>11</v>
       </c>
       <c r="B110" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C110" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D110">
         <v>500</v>
@@ -5298,10 +5303,10 @@
         <v>11</v>
       </c>
       <c r="B111" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C111" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D111">
         <v>500</v>
@@ -5327,10 +5332,10 @@
         <v>11</v>
       </c>
       <c r="B112" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C112" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D112">
         <v>500</v>
@@ -5356,10 +5361,10 @@
         <v>11</v>
       </c>
       <c r="B113" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="C113" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D113">
         <v>500</v>
@@ -5385,10 +5390,10 @@
         <v>11</v>
       </c>
       <c r="B114" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="C114" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="D114">
         <v>500</v>
@@ -5414,10 +5419,10 @@
         <v>11</v>
       </c>
       <c r="B115" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C115" t="s">
-        <v>26</v>
+        <v>77</v>
       </c>
       <c r="D115">
         <v>500</v>
@@ -5443,10 +5448,10 @@
         <v>11</v>
       </c>
       <c r="B116" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C116" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D116">
         <v>500</v>
@@ -5472,10 +5477,10 @@
         <v>11</v>
       </c>
       <c r="B117" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="C117" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="D117">
         <v>500</v>
@@ -5501,10 +5506,10 @@
         <v>11</v>
       </c>
       <c r="B118" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C118" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="D118">
         <v>500</v>
@@ -5530,10 +5535,10 @@
         <v>11</v>
       </c>
       <c r="B119" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C119" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D119">
         <v>500</v>
@@ -5559,10 +5564,10 @@
         <v>11</v>
       </c>
       <c r="B120" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C120" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D120">
         <v>500</v>
@@ -5588,10 +5593,10 @@
         <v>11</v>
       </c>
       <c r="B121" t="s">
+        <v>68</v>
+      </c>
+      <c r="C121" t="s">
         <v>70</v>
-      </c>
-      <c r="C121" t="s">
-        <v>68</v>
       </c>
       <c r="D121">
         <v>500</v>
@@ -5617,10 +5622,10 @@
         <v>11</v>
       </c>
       <c r="B122" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="C122" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D122">
         <v>500</v>
@@ -5646,10 +5651,10 @@
         <v>11</v>
       </c>
       <c r="B123" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C123" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D123">
         <v>500</v>
@@ -5675,10 +5680,10 @@
         <v>11</v>
       </c>
       <c r="B124" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C124" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D124">
         <v>500</v>
@@ -5704,10 +5709,10 @@
         <v>11</v>
       </c>
       <c r="B125" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C125" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="D125">
         <v>500</v>
@@ -5736,7 +5741,7 @@
         <v>55</v>
       </c>
       <c r="C126" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="D126">
         <v>500</v>
@@ -5762,10 +5767,10 @@
         <v>11</v>
       </c>
       <c r="B127" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C127" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D127">
         <v>500</v>
@@ -5791,10 +5796,10 @@
         <v>11</v>
       </c>
       <c r="B128" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="C128" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D128">
         <v>500</v>
@@ -5820,10 +5825,10 @@
         <v>11</v>
       </c>
       <c r="B129" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="C129" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D129">
         <v>500</v>
@@ -5849,10 +5854,10 @@
         <v>11</v>
       </c>
       <c r="B130" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="C130" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D130">
         <v>500</v>
@@ -5878,10 +5883,10 @@
         <v>11</v>
       </c>
       <c r="B131" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C131" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="D131">
         <v>500</v>
@@ -5907,10 +5912,10 @@
         <v>11</v>
       </c>
       <c r="B132" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C132" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D132">
         <v>500</v>
@@ -5936,10 +5941,10 @@
         <v>11</v>
       </c>
       <c r="B133" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C133" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D133">
         <v>500</v>
@@ -5965,10 +5970,10 @@
         <v>11</v>
       </c>
       <c r="B134" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C134" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="D134">
         <v>500</v>
@@ -5994,10 +5999,10 @@
         <v>11</v>
       </c>
       <c r="B135" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C135" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D135">
         <v>500</v>
@@ -6026,7 +6031,7 @@
         <v>38</v>
       </c>
       <c r="C136" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="D136">
         <v>500</v>
@@ -6052,10 +6057,10 @@
         <v>11</v>
       </c>
       <c r="B137" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="C137" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D137">
         <v>500</v>
@@ -6081,10 +6086,10 @@
         <v>11</v>
       </c>
       <c r="B138" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C138" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="D138">
         <v>500</v>
@@ -6110,10 +6115,10 @@
         <v>12</v>
       </c>
       <c r="B139" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C139" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D139">
         <v>500</v>
@@ -6139,10 +6144,10 @@
         <v>12</v>
       </c>
       <c r="B140" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C140" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D140">
         <v>500</v>
@@ -6168,10 +6173,10 @@
         <v>12</v>
       </c>
       <c r="B141" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C141" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D141">
         <v>500</v>
@@ -6197,10 +6202,10 @@
         <v>12</v>
       </c>
       <c r="B142" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C142" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D142">
         <v>500</v>
@@ -6226,10 +6231,10 @@
         <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C143" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D143">
         <v>500</v>
@@ -6255,10 +6260,10 @@
         <v>12</v>
       </c>
       <c r="B144" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C144" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D144">
         <v>500</v>
@@ -6284,10 +6289,10 @@
         <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C145" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D145">
         <v>500</v>
@@ -6313,10 +6318,10 @@
         <v>12</v>
       </c>
       <c r="B146" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C146" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D146">
         <v>500</v>
@@ -6342,10 +6347,10 @@
         <v>12</v>
       </c>
       <c r="B147" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C147" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D147">
         <v>500</v>
@@ -6371,10 +6376,10 @@
         <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C148" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D148">
         <v>500</v>
@@ -6400,10 +6405,10 @@
         <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="C149" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="D149">
         <v>500</v>
@@ -6429,10 +6434,10 @@
         <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C150" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D150">
         <v>500</v>
@@ -6458,10 +6463,10 @@
         <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C151" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D151">
         <v>500</v>
@@ -6487,10 +6492,10 @@
         <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C152" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D152">
         <v>500</v>
@@ -6516,10 +6521,10 @@
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C153" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D153">
         <v>500</v>
@@ -6545,10 +6550,10 @@
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C154" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D154">
         <v>500</v>
@@ -6574,10 +6579,10 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C155" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D155">
         <v>500</v>
@@ -6603,10 +6608,10 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C156" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D156">
         <v>500</v>
@@ -6632,10 +6637,10 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C157" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D157">
         <v>500</v>
@@ -6661,10 +6666,10 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C158" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="D158">
         <v>500</v>
@@ -6690,10 +6695,10 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C159" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D159">
         <v>500</v>
@@ -6719,10 +6724,10 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C160" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D160">
         <v>500</v>
@@ -6748,10 +6753,10 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C161" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D161">
         <v>500</v>
@@ -6777,10 +6782,10 @@
         <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="C162" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D162">
         <v>500</v>
@@ -6806,10 +6811,10 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
+        <v>38</v>
+      </c>
+      <c r="C163" t="s">
         <v>59</v>
-      </c>
-      <c r="C163" t="s">
-        <v>60</v>
       </c>
       <c r="D163">
         <v>500</v>
@@ -6835,10 +6840,10 @@
         <v>12</v>
       </c>
       <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="s">
         <v>38</v>
-      </c>
-      <c r="C164" t="s">
-        <v>16</v>
       </c>
       <c r="D164">
         <v>500</v>
@@ -6864,10 +6869,10 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="C165" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="D165">
         <v>500</v>
@@ -6896,7 +6901,7 @@
         <v>16</v>
       </c>
       <c r="C166" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D166">
         <v>500</v>
@@ -6925,7 +6930,7 @@
         <v>16</v>
       </c>
       <c r="C167" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D167">
         <v>500</v>
@@ -6951,10 +6956,10 @@
         <v>12</v>
       </c>
       <c r="B168" t="s">
+        <v>28</v>
+      </c>
+      <c r="C168" t="s">
         <v>16</v>
-      </c>
-      <c r="C168" t="s">
-        <v>44</v>
       </c>
       <c r="D168">
         <v>500</v>
@@ -6980,10 +6985,10 @@
         <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C169" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D169">
         <v>500</v>
@@ -7009,7 +7014,7 @@
         <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C170" t="s">
         <v>16</v>
@@ -7038,10 +7043,10 @@
         <v>12</v>
       </c>
       <c r="B171" t="s">
+        <v>42</v>
+      </c>
+      <c r="C171" t="s">
         <v>28</v>
-      </c>
-      <c r="C171" t="s">
-        <v>44</v>
       </c>
       <c r="D171">
         <v>500</v>
@@ -7067,10 +7072,10 @@
         <v>12</v>
       </c>
       <c r="B172" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C172" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="D172">
         <v>500</v>
@@ -7096,10 +7101,10 @@
         <v>12</v>
       </c>
       <c r="B173" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C173" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="D173">
         <v>500</v>
@@ -7125,10 +7130,10 @@
         <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C174" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="D174">
         <v>500</v>
@@ -7154,10 +7159,10 @@
         <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C175" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D175">
         <v>500</v>
@@ -7183,10 +7188,10 @@
         <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C176" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D176">
         <v>500</v>
@@ -7212,10 +7217,10 @@
         <v>12</v>
       </c>
       <c r="B177" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C177" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D177">
         <v>500</v>
@@ -7241,10 +7246,10 @@
         <v>12</v>
       </c>
       <c r="B178" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C178" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="D178">
         <v>500</v>
@@ -7270,10 +7275,10 @@
         <v>12</v>
       </c>
       <c r="B179" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C179" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D179">
         <v>500</v>
@@ -7299,10 +7304,10 @@
         <v>12</v>
       </c>
       <c r="B180" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C180" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="D180">
         <v>500</v>
@@ -7328,10 +7333,10 @@
         <v>12</v>
       </c>
       <c r="B181" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C181" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
       <c r="D181">
         <v>500</v>
@@ -7357,10 +7362,10 @@
         <v>12</v>
       </c>
       <c r="B182" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C182" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="D182">
         <v>500</v>
@@ -7386,7 +7391,7 @@
         <v>12</v>
       </c>
       <c r="B183" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C183" t="s">
         <v>66</v>
@@ -7415,10 +7420,10 @@
         <v>12</v>
       </c>
       <c r="B184" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="C184" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D184">
         <v>500</v>
@@ -7444,10 +7449,10 @@
         <v>12</v>
       </c>
       <c r="B185" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="C185" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D185">
         <v>500</v>
@@ -7476,7 +7481,7 @@
         <v>22</v>
       </c>
       <c r="C186" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D186">
         <v>500</v>
@@ -7502,10 +7507,10 @@
         <v>12</v>
       </c>
       <c r="B187" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="C187" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="D187">
         <v>500</v>
@@ -7531,10 +7536,10 @@
         <v>12</v>
       </c>
       <c r="B188" t="s">
+        <v>61</v>
+      </c>
+      <c r="C188" t="s">
         <v>22</v>
-      </c>
-      <c r="C188" t="s">
-        <v>66</v>
       </c>
       <c r="D188">
         <v>500</v>
@@ -7560,10 +7565,10 @@
         <v>12</v>
       </c>
       <c r="B189" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="C189" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="D189">
         <v>500</v>
@@ -7589,10 +7594,10 @@
         <v>12</v>
       </c>
       <c r="B190" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C190" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D190">
         <v>500</v>
@@ -7618,10 +7623,10 @@
         <v>12</v>
       </c>
       <c r="B191" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C191" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D191">
         <v>500</v>
@@ -7647,10 +7652,10 @@
         <v>12</v>
       </c>
       <c r="B192" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="C192" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="D192">
         <v>500</v>
@@ -7676,10 +7681,10 @@
         <v>12</v>
       </c>
       <c r="B193" t="s">
+        <v>24</v>
+      </c>
+      <c r="C193" t="s">
         <v>66</v>
-      </c>
-      <c r="C193" t="s">
-        <v>22</v>
       </c>
       <c r="D193">
         <v>500</v>
@@ -7705,10 +7710,10 @@
         <v>12</v>
       </c>
       <c r="B194" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="C194" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D194">
         <v>500</v>
@@ -7734,10 +7739,10 @@
         <v>12</v>
       </c>
       <c r="B195" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C195" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D195">
         <v>500</v>
@@ -7763,10 +7768,10 @@
         <v>12</v>
       </c>
       <c r="B196" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C196" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="D196">
         <v>500</v>
@@ -7792,10 +7797,10 @@
         <v>12</v>
       </c>
       <c r="B197" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C197" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="D197">
         <v>500</v>
@@ -7821,10 +7826,10 @@
         <v>12</v>
       </c>
       <c r="B198" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C198" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="D198">
         <v>500</v>
@@ -7850,10 +7855,10 @@
         <v>12</v>
       </c>
       <c r="B199" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="C199" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D199">
         <v>500</v>
@@ -7879,10 +7884,10 @@
         <v>12</v>
       </c>
       <c r="B200" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="C200" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D200">
         <v>500</v>
@@ -7908,10 +7913,10 @@
         <v>12</v>
       </c>
       <c r="B201" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="C201" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="D201">
         <v>500</v>
@@ -7937,10 +7942,10 @@
         <v>12</v>
       </c>
       <c r="B202" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C202" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="D202">
         <v>500</v>
@@ -7966,10 +7971,10 @@
         <v>12</v>
       </c>
       <c r="B203" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C203" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="D203">
         <v>500</v>
@@ -7995,10 +8000,10 @@
         <v>12</v>
       </c>
       <c r="B204" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C204" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D204">
         <v>500</v>
@@ -8024,10 +8029,10 @@
         <v>12</v>
       </c>
       <c r="B205" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C205" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D205">
         <v>500</v>
@@ -8053,10 +8058,10 @@
         <v>12</v>
       </c>
       <c r="B206" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C206" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="D206">
         <v>500</v>
@@ -8082,10 +8087,10 @@
         <v>12</v>
       </c>
       <c r="B207" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C207" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D207">
         <v>500</v>
@@ -8111,10 +8116,10 @@
         <v>12</v>
       </c>
       <c r="B208" t="s">
+        <v>66</v>
+      </c>
+      <c r="C208" t="s">
         <v>67</v>
-      </c>
-      <c r="C208" t="s">
-        <v>60</v>
       </c>
       <c r="D208">
         <v>500</v>
@@ -8140,10 +8145,10 @@
         <v>12</v>
       </c>
       <c r="B209" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C209" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="D209">
         <v>500</v>
@@ -8169,10 +8174,10 @@
         <v>12</v>
       </c>
       <c r="B210" t="s">
+        <v>67</v>
+      </c>
+      <c r="C210" t="s">
         <v>68</v>
-      </c>
-      <c r="C210" t="s">
-        <v>67</v>
       </c>
       <c r="D210">
         <v>500</v>
@@ -8198,10 +8203,10 @@
         <v>12</v>
       </c>
       <c r="B211" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C211" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D211">
         <v>500</v>
@@ -8230,7 +8235,7 @@
         <v>68</v>
       </c>
       <c r="C212" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D212">
         <v>500</v>
@@ -8256,10 +8261,10 @@
         <v>12</v>
       </c>
       <c r="B213" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C213" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="D213">
         <v>500</v>
@@ -8285,10 +8290,10 @@
         <v>12</v>
       </c>
       <c r="B214" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C214" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="D214">
         <v>500</v>
@@ -8314,7 +8319,7 @@
         <v>12</v>
       </c>
       <c r="B215" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C215" t="s">
         <v>70</v>
@@ -8343,10 +8348,10 @@
         <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C216" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D216">
         <v>500</v>
@@ -8372,10 +8377,10 @@
         <v>12</v>
       </c>
       <c r="B217" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="C217" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="D217">
         <v>500</v>
@@ -8401,10 +8406,10 @@
         <v>12</v>
       </c>
       <c r="B218" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C218" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D218">
         <v>500</v>
@@ -8430,10 +8435,10 @@
         <v>12</v>
       </c>
       <c r="B219" t="s">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="C219" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="D219">
         <v>500</v>
@@ -8459,10 +8464,10 @@
         <v>12</v>
       </c>
       <c r="B220" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C220" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D220">
         <v>500</v>
@@ -8488,10 +8493,10 @@
         <v>12</v>
       </c>
       <c r="B221" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C221" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="D221">
         <v>500</v>
@@ -8517,10 +8522,10 @@
         <v>12</v>
       </c>
       <c r="B222" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="C222" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D222">
         <v>500</v>
@@ -8546,10 +8551,10 @@
         <v>12</v>
       </c>
       <c r="B223" t="s">
+        <v>26</v>
+      </c>
+      <c r="C223" t="s">
         <v>53</v>
-      </c>
-      <c r="C223" t="s">
-        <v>71</v>
       </c>
       <c r="D223">
         <v>500</v>
@@ -8575,10 +8580,10 @@
         <v>12</v>
       </c>
       <c r="B224" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="C224" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="D224">
         <v>500</v>
@@ -8604,10 +8609,10 @@
         <v>12</v>
       </c>
       <c r="B225" t="s">
+        <v>72</v>
+      </c>
+      <c r="C225" t="s">
         <v>53</v>
-      </c>
-      <c r="C225" t="s">
-        <v>74</v>
       </c>
       <c r="D225">
         <v>500</v>
@@ -8633,10 +8638,10 @@
         <v>12</v>
       </c>
       <c r="B226" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C226" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="D226">
         <v>500</v>
@@ -8662,10 +8667,10 @@
         <v>12</v>
       </c>
       <c r="B227" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C227" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="D227">
         <v>500</v>
@@ -8691,10 +8696,10 @@
         <v>12</v>
       </c>
       <c r="B228" t="s">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="C228" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D228">
         <v>500</v>
@@ -8720,10 +8725,10 @@
         <v>12</v>
       </c>
       <c r="B229" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="C229" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="D229">
         <v>500</v>
@@ -8749,10 +8754,10 @@
         <v>12</v>
       </c>
       <c r="B230" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C230" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="D230">
         <v>500</v>
@@ -8778,10 +8783,10 @@
         <v>12</v>
       </c>
       <c r="B231" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C231" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="D231">
         <v>500</v>
@@ -8807,10 +8812,10 @@
         <v>12</v>
       </c>
       <c r="B232" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C232" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="D232">
         <v>500</v>
@@ -8836,10 +8841,10 @@
         <v>12</v>
       </c>
       <c r="B233" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C233" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="D233">
         <v>500</v>
@@ -8865,10 +8870,10 @@
         <v>12</v>
       </c>
       <c r="B234" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C234" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="D234">
         <v>500</v>
@@ -8894,10 +8899,10 @@
         <v>12</v>
       </c>
       <c r="B235" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C235" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D235">
         <v>500</v>
@@ -8923,10 +8928,10 @@
         <v>12</v>
       </c>
       <c r="B236" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C236" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="D236">
         <v>500</v>
@@ -8955,7 +8960,7 @@
         <v>74</v>
       </c>
       <c r="C237" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="D237">
         <v>500</v>
@@ -8981,10 +8986,10 @@
         <v>12</v>
       </c>
       <c r="B238" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C238" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="D238">
         <v>500</v>
@@ -9010,10 +9015,10 @@
         <v>12</v>
       </c>
       <c r="B239" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C239" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="D239">
         <v>500</v>
@@ -9039,10 +9044,10 @@
         <v>12</v>
       </c>
       <c r="B240" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C240" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="D240">
         <v>500</v>
@@ -9068,10 +9073,10 @@
         <v>12</v>
       </c>
       <c r="B241" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="C241" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D241">
         <v>500</v>
@@ -9097,10 +9102,10 @@
         <v>12</v>
       </c>
       <c r="B242" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C242" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="D242">
         <v>500</v>
@@ -9126,10 +9131,10 @@
         <v>12</v>
       </c>
       <c r="B243" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C243" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D243">
         <v>500</v>
@@ -9155,10 +9160,10 @@
         <v>12</v>
       </c>
       <c r="B244" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="C244" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D244">
         <v>500</v>
@@ -9184,10 +9189,10 @@
         <v>12</v>
       </c>
       <c r="B245" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C245" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D245">
         <v>500</v>
@@ -9213,10 +9218,10 @@
         <v>12</v>
       </c>
       <c r="B246" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C246" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D246">
         <v>500</v>
@@ -9242,10 +9247,10 @@
         <v>12</v>
       </c>
       <c r="B247" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="C247" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D247">
         <v>500</v>
@@ -9271,10 +9276,10 @@
         <v>12</v>
       </c>
       <c r="B248" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="C248" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D248">
         <v>500</v>
@@ -9300,10 +9305,10 @@
         <v>12</v>
       </c>
       <c r="B249" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C249" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="D249">
         <v>500</v>
@@ -9329,10 +9334,10 @@
         <v>12</v>
       </c>
       <c r="B250" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C250" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="D250">
         <v>500</v>
@@ -9358,7 +9363,7 @@
         <v>12</v>
       </c>
       <c r="B251" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="C251" t="s">
         <v>30</v>
@@ -9387,10 +9392,10 @@
         <v>12</v>
       </c>
       <c r="B252" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="C252" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="D252">
         <v>500</v>
@@ -9416,10 +9421,10 @@
         <v>12</v>
       </c>
       <c r="B253" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C253" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D253">
         <v>500</v>
@@ -9445,10 +9450,10 @@
         <v>12</v>
       </c>
       <c r="B254" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C254" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="D254">
         <v>500</v>
@@ -9474,10 +9479,10 @@
         <v>12</v>
       </c>
       <c r="B255" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C255" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="D255">
         <v>500</v>
@@ -9503,10 +9508,10 @@
         <v>12</v>
       </c>
       <c r="B256" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C256" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D256">
         <v>500</v>
@@ -9532,7 +9537,7 @@
         <v>12</v>
       </c>
       <c r="B257" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C257" t="s">
         <v>68</v>
@@ -9561,10 +9566,10 @@
         <v>12</v>
       </c>
       <c r="B258" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C258" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D258">
         <v>500</v>
@@ -9590,10 +9595,10 @@
         <v>12</v>
       </c>
       <c r="B259" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C259" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D259">
         <v>500</v>
@@ -9619,10 +9624,10 @@
         <v>12</v>
       </c>
       <c r="B260" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="C260" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="D260">
         <v>500</v>
@@ -9648,10 +9653,10 @@
         <v>12</v>
       </c>
       <c r="B261" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C261" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="D261">
         <v>500</v>
@@ -9677,10 +9682,10 @@
         <v>12</v>
       </c>
       <c r="B262" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="C262" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="D262">
         <v>500</v>
@@ -9706,10 +9711,10 @@
         <v>12</v>
       </c>
       <c r="B263" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C263" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="D263">
         <v>500</v>
@@ -9735,10 +9740,10 @@
         <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C264" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D264">
         <v>500</v>
@@ -9764,10 +9769,10 @@
         <v>12</v>
       </c>
       <c r="B265" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C265" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D265">
         <v>500</v>
@@ -9793,10 +9798,10 @@
         <v>12</v>
       </c>
       <c r="B266" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="C266" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D266">
         <v>500</v>
@@ -9822,10 +9827,10 @@
         <v>12</v>
       </c>
       <c r="B267" t="s">
-        <v>81</v>
+        <v>48</v>
       </c>
       <c r="C267" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D267">
         <v>500</v>
@@ -9851,10 +9856,10 @@
         <v>12</v>
       </c>
       <c r="B268" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C268" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D268">
         <v>500</v>
@@ -9880,10 +9885,10 @@
         <v>12</v>
       </c>
       <c r="B269" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C269" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="D269">
         <v>500</v>
@@ -9909,7 +9914,7 @@
         <v>12</v>
       </c>
       <c r="B270" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C270" t="s">
         <v>16</v>
@@ -9938,10 +9943,10 @@
         <v>12</v>
       </c>
       <c r="B271" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C271" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D271">
         <v>500</v>
@@ -9967,10 +9972,10 @@
         <v>12</v>
       </c>
       <c r="B272" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="C272" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D272">
         <v>500</v>
@@ -9996,10 +10001,10 @@
         <v>12</v>
       </c>
       <c r="B273" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C273" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D273">
         <v>500</v>
@@ -10017,64 +10022,6 @@
         <v>0</v>
       </c>
       <c r="I273">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A274" t="s">
-        <v>12</v>
-      </c>
-      <c r="B274" t="s">
-        <v>38</v>
-      </c>
-      <c r="C274" t="s">
-        <v>16</v>
-      </c>
-      <c r="D274">
-        <v>500</v>
-      </c>
-      <c r="E274">
-        <v>500</v>
-      </c>
-      <c r="F274">
-        <v>1</v>
-      </c>
-      <c r="G274">
-        <v>5</v>
-      </c>
-      <c r="H274">
-        <v>0</v>
-      </c>
-      <c r="I274">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A275" t="s">
-        <v>12</v>
-      </c>
-      <c r="B275" t="s">
-        <v>38</v>
-      </c>
-      <c r="C275" t="s">
-        <v>28</v>
-      </c>
-      <c r="D275">
-        <v>500</v>
-      </c>
-      <c r="E275">
-        <v>500</v>
-      </c>
-      <c r="F275">
-        <v>1</v>
-      </c>
-      <c r="G275">
-        <v>5</v>
-      </c>
-      <c r="H275">
-        <v>0</v>
-      </c>
-      <c r="I275">
         <v>1</v>
       </c>
     </row>
@@ -10086,7 +10033,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68B577B-1347-43AB-A697-F4519763B965}">
-  <dimension ref="A1:C121"/>
+  <dimension ref="A1:C123"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -10237,7 +10184,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="C14">
         <v>100</v>
@@ -10248,7 +10195,7 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -10259,7 +10206,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C16">
         <v>100</v>
@@ -10270,7 +10217,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C17">
         <v>100</v>
@@ -10281,7 +10228,7 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -10292,7 +10239,7 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -10303,7 +10250,7 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -10314,7 +10261,7 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C21">
         <v>100</v>
@@ -10325,7 +10272,7 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -10336,7 +10283,7 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C23">
         <v>100</v>
@@ -10347,7 +10294,7 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C24">
         <v>100</v>
@@ -10358,7 +10305,7 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C25">
         <v>100</v>
@@ -10369,7 +10316,7 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -10413,7 +10360,7 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C30">
         <v>-100</v>
@@ -10424,7 +10371,7 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C31">
         <v>-100</v>
@@ -10446,7 +10393,7 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C33">
         <v>-100</v>
@@ -10457,7 +10404,7 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C34">
         <v>-100</v>
@@ -10490,7 +10437,7 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C37">
         <v>-100</v>
@@ -10512,7 +10459,7 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C39">
         <v>-100</v>
@@ -10523,7 +10470,7 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C40">
         <v>-100</v>
@@ -10534,7 +10481,7 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C41">
         <v>-100</v>
@@ -10545,7 +10492,7 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C42">
         <v>-100</v>
@@ -10556,7 +10503,7 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C43">
         <v>-100</v>
@@ -10578,7 +10525,7 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C45">
         <v>-100</v>
@@ -10600,7 +10547,7 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C47">
         <v>-100</v>
@@ -10633,7 +10580,7 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C50">
         <v>-100</v>
@@ -10644,7 +10591,7 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C51">
         <v>-100</v>
@@ -10655,7 +10602,7 @@
         <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C52">
         <v>-100</v>
@@ -10666,7 +10613,7 @@
         <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C53">
         <v>-100</v>
@@ -10688,7 +10635,7 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C55">
         <v>-100</v>
@@ -10699,7 +10646,7 @@
         <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -10710,7 +10657,7 @@
         <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -10721,7 +10668,7 @@
         <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -10732,7 +10679,7 @@
         <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -10743,7 +10690,7 @@
         <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -10754,7 +10701,7 @@
         <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -10897,7 +10844,7 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -10908,7 +10855,7 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -10919,7 +10866,7 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -10930,7 +10877,7 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -10941,7 +10888,7 @@
         <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -10952,7 +10899,7 @@
         <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -10963,7 +10910,7 @@
         <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -10974,7 +10921,7 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -10985,7 +10932,7 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -10996,7 +10943,7 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -11007,7 +10954,7 @@
         <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -11018,7 +10965,7 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -11029,7 +10976,7 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -11073,7 +11020,7 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -11084,7 +11031,7 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -11106,7 +11053,7 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -11117,7 +11064,7 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -11150,7 +11097,7 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -11172,7 +11119,7 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -11183,7 +11130,7 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -11194,7 +11141,7 @@
         <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -11205,7 +11152,7 @@
         <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -11216,7 +11163,7 @@
         <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -11238,7 +11185,7 @@
         <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -11260,7 +11207,7 @@
         <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -11293,7 +11240,7 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -11304,7 +11251,7 @@
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -11315,7 +11262,7 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -11326,7 +11273,7 @@
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -11348,7 +11295,7 @@
         <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -11359,7 +11306,7 @@
         <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -11370,7 +11317,7 @@
         <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -11381,7 +11328,7 @@
         <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -11392,7 +11339,7 @@
         <v>12</v>
       </c>
       <c r="B119" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -11403,7 +11350,7 @@
         <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -11414,9 +11361,31 @@
         <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>11</v>
+      </c>
+      <c r="B122" t="s">
+        <v>69</v>
+      </c>
+      <c r="C122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>12</v>
+      </c>
+      <c r="B123" t="s">
+        <v>69</v>
+      </c>
+      <c r="C123">
         <v>0</v>
       </c>
     </row>

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2C3AFA-9616-498F-8081-1155D6067C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD0EFF4-3304-4C53-8C27-D82BD6D5F307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="81">
   <si>
     <t>Commodities</t>
   </si>
@@ -975,7 +975,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B140"/>
+  <dimension ref="A1:B139"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -2084,17 +2084,9 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B139" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
-        <v>77</v>
-      </c>
-      <c r="B140" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2105,7 +2097,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
-  <dimension ref="A1:I273"/>
+  <dimension ref="A1:I277"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -10022,6 +10014,122 @@
         <v>0</v>
       </c>
       <c r="I273">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>11</v>
+      </c>
+      <c r="B274" t="s">
+        <v>77</v>
+      </c>
+      <c r="C274" t="s">
+        <v>20</v>
+      </c>
+      <c r="D274">
+        <v>500</v>
+      </c>
+      <c r="E274">
+        <v>500</v>
+      </c>
+      <c r="F274">
+        <v>1</v>
+      </c>
+      <c r="G274">
+        <v>5</v>
+      </c>
+      <c r="H274">
+        <v>0</v>
+      </c>
+      <c r="I274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>12</v>
+      </c>
+      <c r="B275" t="s">
+        <v>77</v>
+      </c>
+      <c r="C275" t="s">
+        <v>20</v>
+      </c>
+      <c r="D275">
+        <v>500</v>
+      </c>
+      <c r="E275">
+        <v>500</v>
+      </c>
+      <c r="F275">
+        <v>1</v>
+      </c>
+      <c r="G275">
+        <v>5</v>
+      </c>
+      <c r="H275">
+        <v>0</v>
+      </c>
+      <c r="I275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>12</v>
+      </c>
+      <c r="B276" t="s">
+        <v>15</v>
+      </c>
+      <c r="C276" t="s">
+        <v>16</v>
+      </c>
+      <c r="D276">
+        <v>500</v>
+      </c>
+      <c r="E276">
+        <v>500</v>
+      </c>
+      <c r="F276">
+        <v>10000</v>
+      </c>
+      <c r="G276">
+        <v>5</v>
+      </c>
+      <c r="H276">
+        <v>0</v>
+      </c>
+      <c r="I276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>12</v>
+      </c>
+      <c r="B277" t="s">
+        <v>17</v>
+      </c>
+      <c r="C277" t="s">
+        <v>18</v>
+      </c>
+      <c r="D277">
+        <v>500</v>
+      </c>
+      <c r="E277">
+        <v>500</v>
+      </c>
+      <c r="F277">
+        <v>10000</v>
+      </c>
+      <c r="G277">
+        <v>5</v>
+      </c>
+      <c r="H277">
+        <v>0</v>
+      </c>
+      <c r="I277">
         <v>1</v>
       </c>
     </row>

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BD0EFF4-3304-4C53-8C27-D82BD6D5F307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAE517D-064C-4547-8345-FC6B9ABED5F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="82">
   <si>
     <t>Commodities</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t>MA_Prod</t>
+  </si>
+  <si>
+    <t>SE</t>
   </si>
 </sst>
 </file>
@@ -640,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0CB446-BDDD-415D-AF22-2CEB1FE45CA5}">
-  <dimension ref="A1:A60"/>
+  <dimension ref="A1:A61"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -941,6 +944,11 @@
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>76</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -975,7 +983,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B139"/>
+  <dimension ref="A1:B140"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -2088,6 +2096,14 @@
       </c>
       <c r="B139" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>53</v>
+      </c>
+      <c r="B140" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2140,16 +2156,16 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>500</v>
+        <v>111.378</v>
       </c>
       <c r="E2">
-        <v>500</v>
+        <v>111.378</v>
       </c>
       <c r="F2">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -2169,16 +2185,16 @@
         <v>18</v>
       </c>
       <c r="D3">
-        <v>500</v>
+        <v>322.40999999999997</v>
       </c>
       <c r="E3">
-        <v>500</v>
+        <v>322.40999999999997</v>
       </c>
       <c r="F3">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -2198,16 +2214,16 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>500</v>
+        <v>73.274999999999991</v>
       </c>
       <c r="E4">
-        <v>500</v>
+        <v>73.274999999999991</v>
       </c>
       <c r="F4">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -2227,16 +2243,16 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>500</v>
+        <v>155.83149999999998</v>
       </c>
       <c r="E5">
-        <v>500</v>
+        <v>155.83149999999998</v>
       </c>
       <c r="F5">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -2256,16 +2272,16 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>500</v>
+        <v>25.402000000000001</v>
       </c>
       <c r="E6">
-        <v>500</v>
+        <v>25.402000000000001</v>
       </c>
       <c r="F6">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -2285,16 +2301,16 @@
         <v>26</v>
       </c>
       <c r="D7">
-        <v>500</v>
+        <v>39.08</v>
       </c>
       <c r="E7">
-        <v>500</v>
+        <v>39.08</v>
       </c>
       <c r="F7">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -2314,16 +2330,16 @@
         <v>28</v>
       </c>
       <c r="D8">
-        <v>500</v>
+        <v>122.125</v>
       </c>
       <c r="E8">
-        <v>500</v>
+        <v>122.125</v>
       </c>
       <c r="F8">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -2343,16 +2359,16 @@
         <v>30</v>
       </c>
       <c r="D9">
-        <v>500</v>
+        <v>60.573999999999998</v>
       </c>
       <c r="E9">
-        <v>500</v>
+        <v>60.573999999999998</v>
       </c>
       <c r="F9">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -2372,16 +2388,16 @@
         <v>32</v>
       </c>
       <c r="D10">
-        <v>500</v>
+        <v>74.251999999999995</v>
       </c>
       <c r="E10">
-        <v>500</v>
+        <v>74.251999999999995</v>
       </c>
       <c r="F10">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -2401,16 +2417,16 @@
         <v>34</v>
       </c>
       <c r="D11">
-        <v>500</v>
+        <v>655.56699999999989</v>
       </c>
       <c r="E11">
-        <v>500</v>
+        <v>655.56699999999989</v>
       </c>
       <c r="F11">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H11">
         <v>0</v>
@@ -2430,16 +2446,16 @@
         <v>36</v>
       </c>
       <c r="D12">
-        <v>500</v>
+        <v>425.97199999999998</v>
       </c>
       <c r="E12">
-        <v>500</v>
+        <v>425.97199999999998</v>
       </c>
       <c r="F12">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="G12">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -2459,16 +2475,16 @@
         <v>38</v>
       </c>
       <c r="D13">
-        <v>500</v>
+        <v>510.97099999999995</v>
       </c>
       <c r="E13">
-        <v>500</v>
+        <v>510.97099999999995</v>
       </c>
       <c r="F13">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -2488,16 +2504,16 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E14">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F14">
         <v>1</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2517,16 +2533,16 @@
         <v>40</v>
       </c>
       <c r="D15">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E15">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F15">
         <v>1</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -2546,16 +2562,16 @@
         <v>42</v>
       </c>
       <c r="D16">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E16">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F16">
         <v>1</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -2575,16 +2591,16 @@
         <v>22</v>
       </c>
       <c r="D17">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E17">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F17">
         <v>1</v>
       </c>
       <c r="G17">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -2604,16 +2620,16 @@
         <v>45</v>
       </c>
       <c r="D18">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E18">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F18">
         <v>1</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -2633,16 +2649,16 @@
         <v>28</v>
       </c>
       <c r="D19">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E19">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -2662,16 +2678,16 @@
         <v>48</v>
       </c>
       <c r="D20">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E20">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -2691,16 +2707,16 @@
         <v>30</v>
       </c>
       <c r="D21">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E21">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F21">
         <v>1</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -2720,16 +2736,16 @@
         <v>51</v>
       </c>
       <c r="D22">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E22">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -2749,16 +2765,16 @@
         <v>53</v>
       </c>
       <c r="D23">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E23">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="G23">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -2778,16 +2794,16 @@
         <v>55</v>
       </c>
       <c r="D24">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E24">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F24">
         <v>1</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -2807,16 +2823,16 @@
         <v>38</v>
       </c>
       <c r="D25">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E25">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F25">
         <v>1</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -2836,16 +2852,16 @@
         <v>58</v>
       </c>
       <c r="D26">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E26">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F26">
         <v>1</v>
       </c>
       <c r="G26">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -2865,16 +2881,16 @@
         <v>16</v>
       </c>
       <c r="D27">
-        <v>500</v>
+        <v>237.87050000000002</v>
       </c>
       <c r="E27">
-        <v>500</v>
+        <v>237.87050000000002</v>
       </c>
       <c r="F27">
         <v>1</v>
       </c>
       <c r="G27">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -2894,16 +2910,16 @@
         <v>59</v>
       </c>
       <c r="D28">
-        <v>500</v>
+        <v>141.21850000000001</v>
       </c>
       <c r="E28">
-        <v>500</v>
+        <v>141.21850000000001</v>
       </c>
       <c r="F28">
         <v>1</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H28">
         <v>0</v>
@@ -2923,16 +2939,16 @@
         <v>38</v>
       </c>
       <c r="D29">
-        <v>500</v>
+        <v>293.24099999999999</v>
       </c>
       <c r="E29">
-        <v>500</v>
+        <v>293.24099999999999</v>
       </c>
       <c r="F29">
         <v>1</v>
       </c>
       <c r="G29">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -2952,16 +2968,16 @@
         <v>28</v>
       </c>
       <c r="D30">
-        <v>500</v>
+        <v>120.88800000000001</v>
       </c>
       <c r="E30">
-        <v>500</v>
+        <v>120.88800000000001</v>
       </c>
       <c r="F30">
         <v>1</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H30">
         <v>0</v>
@@ -2981,16 +2997,16 @@
         <v>42</v>
       </c>
       <c r="D31">
-        <v>500</v>
+        <v>117.81104999999999</v>
       </c>
       <c r="E31">
-        <v>500</v>
+        <v>117.81104999999999</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -3010,16 +3026,16 @@
         <v>18</v>
       </c>
       <c r="D32">
-        <v>500</v>
+        <v>317.55</v>
       </c>
       <c r="E32">
-        <v>500</v>
+        <v>317.55</v>
       </c>
       <c r="F32">
         <v>1</v>
       </c>
       <c r="G32">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -3039,16 +3055,16 @@
         <v>16</v>
       </c>
       <c r="D33">
-        <v>500</v>
+        <v>509.97800000000001</v>
       </c>
       <c r="E33">
-        <v>500</v>
+        <v>509.97800000000001</v>
       </c>
       <c r="F33">
         <v>1</v>
       </c>
       <c r="G33">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -3068,16 +3084,16 @@
         <v>42</v>
       </c>
       <c r="D34">
-        <v>500</v>
+        <v>702.90714500000001</v>
       </c>
       <c r="E34">
-        <v>500</v>
+        <v>702.90714500000001</v>
       </c>
       <c r="F34">
         <v>1</v>
       </c>
       <c r="G34">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H34">
         <v>0</v>
@@ -3097,16 +3113,16 @@
         <v>16</v>
       </c>
       <c r="D35">
-        <v>500</v>
+        <v>144.59475</v>
       </c>
       <c r="E35">
-        <v>500</v>
+        <v>144.59475</v>
       </c>
       <c r="F35">
         <v>1</v>
       </c>
       <c r="G35">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H35">
         <v>0</v>
@@ -3126,16 +3142,16 @@
         <v>28</v>
       </c>
       <c r="D36">
-        <v>500</v>
+        <v>594.33059500000013</v>
       </c>
       <c r="E36">
-        <v>500</v>
+        <v>594.33059500000013</v>
       </c>
       <c r="F36">
         <v>1</v>
       </c>
       <c r="G36">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H36">
         <v>0</v>
@@ -3155,16 +3171,16 @@
         <v>60</v>
       </c>
       <c r="D37">
-        <v>500</v>
+        <v>125.65051999999997</v>
       </c>
       <c r="E37">
-        <v>500</v>
+        <v>125.65051999999997</v>
       </c>
       <c r="F37">
         <v>1</v>
       </c>
       <c r="G37">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -3184,16 +3200,16 @@
         <v>61</v>
       </c>
       <c r="D38">
-        <v>500</v>
+        <v>119.72</v>
       </c>
       <c r="E38">
-        <v>500</v>
+        <v>119.72</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
       <c r="G38">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H38">
         <v>0</v>
@@ -3213,16 +3229,16 @@
         <v>18</v>
       </c>
       <c r="D39">
-        <v>500</v>
+        <v>224.00633999999999</v>
       </c>
       <c r="E39">
-        <v>500</v>
+        <v>224.00633999999999</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H39">
         <v>0</v>
@@ -3242,16 +3258,16 @@
         <v>40</v>
       </c>
       <c r="D40">
-        <v>500</v>
+        <v>49.680879999999995</v>
       </c>
       <c r="E40">
-        <v>500</v>
+        <v>49.680879999999995</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="G40">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -3271,16 +3287,16 @@
         <v>30</v>
       </c>
       <c r="D41">
-        <v>500</v>
+        <v>85.227500000000006</v>
       </c>
       <c r="E41">
-        <v>500</v>
+        <v>85.227500000000006</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="G41">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -3300,16 +3316,16 @@
         <v>62</v>
       </c>
       <c r="D42">
-        <v>500</v>
+        <v>658.37605000000008</v>
       </c>
       <c r="E42">
-        <v>500</v>
+        <v>658.37605000000008</v>
       </c>
       <c r="F42">
         <v>1</v>
       </c>
       <c r="G42">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H42">
         <v>0</v>
@@ -3329,16 +3345,16 @@
         <v>63</v>
       </c>
       <c r="D43">
-        <v>500</v>
+        <v>9.7491500000000002</v>
       </c>
       <c r="E43">
-        <v>500</v>
+        <v>9.7491500000000002</v>
       </c>
       <c r="F43">
         <v>1</v>
       </c>
       <c r="G43">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H43">
         <v>0</v>
@@ -3358,16 +3374,16 @@
         <v>42</v>
       </c>
       <c r="D44">
-        <v>500</v>
+        <v>124.08832</v>
       </c>
       <c r="E44">
-        <v>500</v>
+        <v>124.08832</v>
       </c>
       <c r="F44">
         <v>1</v>
       </c>
       <c r="G44">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H44">
         <v>0</v>
@@ -3387,16 +3403,16 @@
         <v>22</v>
       </c>
       <c r="D45">
-        <v>500</v>
+        <v>419.75</v>
       </c>
       <c r="E45">
-        <v>500</v>
+        <v>419.75</v>
       </c>
       <c r="F45">
         <v>1</v>
       </c>
       <c r="G45">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H45">
         <v>0</v>
@@ -3416,16 +3432,16 @@
         <v>64</v>
       </c>
       <c r="D46">
-        <v>500</v>
+        <v>41.0625</v>
       </c>
       <c r="E46">
-        <v>500</v>
+        <v>41.0625</v>
       </c>
       <c r="F46">
         <v>1</v>
       </c>
       <c r="G46">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -3445,16 +3461,16 @@
         <v>65</v>
       </c>
       <c r="D47">
-        <v>500</v>
+        <v>89.972499999999997</v>
       </c>
       <c r="E47">
-        <v>500</v>
+        <v>89.972499999999997</v>
       </c>
       <c r="F47">
         <v>1</v>
       </c>
       <c r="G47">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H47">
         <v>0</v>
@@ -3474,16 +3490,16 @@
         <v>66</v>
       </c>
       <c r="D48">
-        <v>500</v>
+        <v>55.881500000000003</v>
       </c>
       <c r="E48">
-        <v>500</v>
+        <v>55.881500000000003</v>
       </c>
       <c r="F48">
         <v>1</v>
       </c>
       <c r="G48">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -3503,16 +3519,16 @@
         <v>60</v>
       </c>
       <c r="D49">
-        <v>500</v>
+        <v>70.627499999999998</v>
       </c>
       <c r="E49">
-        <v>500</v>
+        <v>70.627499999999998</v>
       </c>
       <c r="F49">
         <v>1</v>
       </c>
       <c r="G49">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -3532,16 +3548,16 @@
         <v>61</v>
       </c>
       <c r="D50">
-        <v>500</v>
+        <v>157.46100000000001</v>
       </c>
       <c r="E50">
-        <v>500</v>
+        <v>157.46100000000001</v>
       </c>
       <c r="F50">
         <v>1</v>
       </c>
       <c r="G50">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -3561,16 +3577,16 @@
         <v>64</v>
       </c>
       <c r="D51">
-        <v>500</v>
+        <v>10.4025</v>
       </c>
       <c r="E51">
-        <v>500</v>
+        <v>10.4025</v>
       </c>
       <c r="F51">
         <v>1</v>
       </c>
       <c r="G51">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -3590,16 +3606,16 @@
         <v>42</v>
       </c>
       <c r="D52">
-        <v>500</v>
+        <v>63.07200000000001</v>
       </c>
       <c r="E52">
-        <v>500</v>
+        <v>63.07200000000001</v>
       </c>
       <c r="F52">
         <v>1</v>
       </c>
       <c r="G52">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -3619,16 +3635,16 @@
         <v>22</v>
       </c>
       <c r="D53">
-        <v>500</v>
+        <v>233.74600000000001</v>
       </c>
       <c r="E53">
-        <v>500</v>
+        <v>233.74600000000001</v>
       </c>
       <c r="F53">
         <v>1</v>
       </c>
       <c r="G53">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -3648,16 +3664,16 @@
         <v>18</v>
       </c>
       <c r="D54">
-        <v>500</v>
+        <v>36.5</v>
       </c>
       <c r="E54">
-        <v>500</v>
+        <v>36.5</v>
       </c>
       <c r="F54">
         <v>1</v>
       </c>
       <c r="G54">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H54">
         <v>0</v>
@@ -3677,16 +3693,16 @@
         <v>22</v>
       </c>
       <c r="D55">
-        <v>500</v>
+        <v>7.8475000000000001</v>
       </c>
       <c r="E55">
-        <v>500</v>
+        <v>7.8475000000000001</v>
       </c>
       <c r="F55">
         <v>1</v>
       </c>
       <c r="G55">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -3706,16 +3722,16 @@
         <v>24</v>
       </c>
       <c r="D56">
-        <v>500</v>
+        <v>19.6005</v>
       </c>
       <c r="E56">
-        <v>500</v>
+        <v>19.6005</v>
       </c>
       <c r="F56">
         <v>1</v>
       </c>
       <c r="G56">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -3735,16 +3751,16 @@
         <v>64</v>
       </c>
       <c r="D57">
-        <v>500</v>
+        <v>2.8105000000000002</v>
       </c>
       <c r="E57">
-        <v>500</v>
+        <v>2.8105000000000002</v>
       </c>
       <c r="F57">
         <v>1</v>
       </c>
       <c r="G57">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -3764,16 +3780,16 @@
         <v>66</v>
       </c>
       <c r="D58">
-        <v>500</v>
+        <v>17.72805</v>
       </c>
       <c r="E58">
-        <v>500</v>
+        <v>17.72805</v>
       </c>
       <c r="F58">
         <v>1</v>
       </c>
       <c r="G58">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -3793,16 +3809,16 @@
         <v>16</v>
       </c>
       <c r="D59">
-        <v>500</v>
+        <v>98.55</v>
       </c>
       <c r="E59">
-        <v>500</v>
+        <v>98.55</v>
       </c>
       <c r="F59">
         <v>1</v>
       </c>
       <c r="G59">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -3822,16 +3838,16 @@
         <v>61</v>
       </c>
       <c r="D60">
-        <v>500</v>
+        <v>81.394999999999996</v>
       </c>
       <c r="E60">
-        <v>500</v>
+        <v>81.394999999999996</v>
       </c>
       <c r="F60">
         <v>1</v>
       </c>
       <c r="G60">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -3851,16 +3867,16 @@
         <v>34</v>
       </c>
       <c r="D61">
-        <v>500</v>
+        <v>60.068779999999997</v>
       </c>
       <c r="E61">
-        <v>500</v>
+        <v>60.068779999999997</v>
       </c>
       <c r="F61">
         <v>1</v>
       </c>
       <c r="G61">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -3880,16 +3896,16 @@
         <v>42</v>
       </c>
       <c r="D62">
-        <v>500</v>
+        <v>1.5034349999999999</v>
       </c>
       <c r="E62">
-        <v>500</v>
+        <v>1.5034349999999999</v>
       </c>
       <c r="F62">
         <v>1</v>
       </c>
       <c r="G62">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H62">
         <v>0</v>
@@ -3909,16 +3925,16 @@
         <v>42</v>
       </c>
       <c r="D63">
-        <v>500</v>
+        <v>340.03399999999999</v>
       </c>
       <c r="E63">
-        <v>500</v>
+        <v>340.03399999999999</v>
       </c>
       <c r="F63">
         <v>1</v>
       </c>
       <c r="G63">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H63">
         <v>0</v>
@@ -3938,16 +3954,16 @@
         <v>42</v>
       </c>
       <c r="D64">
-        <v>500</v>
+        <v>449.59203500000001</v>
       </c>
       <c r="E64">
-        <v>500</v>
+        <v>449.59203500000001</v>
       </c>
       <c r="F64">
         <v>1</v>
       </c>
       <c r="G64">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -3967,16 +3983,16 @@
         <v>30</v>
       </c>
       <c r="D65">
-        <v>500</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="E65">
-        <v>500</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="F65">
         <v>1</v>
       </c>
       <c r="G65">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -3996,16 +4012,16 @@
         <v>65</v>
       </c>
       <c r="D66">
-        <v>500</v>
+        <v>454.93600000000004</v>
       </c>
       <c r="E66">
-        <v>500</v>
+        <v>454.93600000000004</v>
       </c>
       <c r="F66">
         <v>1</v>
       </c>
       <c r="G66">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -4025,16 +4041,16 @@
         <v>60</v>
       </c>
       <c r="D67">
-        <v>500</v>
+        <v>573.19600000000003</v>
       </c>
       <c r="E67">
-        <v>500</v>
+        <v>573.19600000000003</v>
       </c>
       <c r="F67">
         <v>1</v>
       </c>
       <c r="G67">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H67">
         <v>0</v>
@@ -4054,16 +4070,16 @@
         <v>62</v>
       </c>
       <c r="D68">
-        <v>500</v>
+        <v>167.024</v>
       </c>
       <c r="E68">
-        <v>500</v>
+        <v>167.024</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="G68">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -4083,16 +4099,16 @@
         <v>66</v>
       </c>
       <c r="D69">
-        <v>500</v>
+        <v>47.048499999999997</v>
       </c>
       <c r="E69">
-        <v>500</v>
+        <v>47.048499999999997</v>
       </c>
       <c r="F69">
         <v>1</v>
       </c>
       <c r="G69">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H69">
         <v>0</v>
@@ -4112,16 +4128,16 @@
         <v>58</v>
       </c>
       <c r="D70">
-        <v>500</v>
+        <v>151.84</v>
       </c>
       <c r="E70">
-        <v>500</v>
+        <v>151.84</v>
       </c>
       <c r="F70">
         <v>1</v>
       </c>
       <c r="G70">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H70">
         <v>0</v>
@@ -4141,16 +4157,16 @@
         <v>24</v>
       </c>
       <c r="D71">
-        <v>500</v>
+        <v>28.251000000000005</v>
       </c>
       <c r="E71">
-        <v>500</v>
+        <v>28.251000000000005</v>
       </c>
       <c r="F71">
         <v>1</v>
       </c>
       <c r="G71">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H71">
         <v>0</v>
@@ -4170,16 +4186,16 @@
         <v>65</v>
       </c>
       <c r="D72">
-        <v>500</v>
+        <v>18.572295</v>
       </c>
       <c r="E72">
-        <v>500</v>
+        <v>18.572295</v>
       </c>
       <c r="F72">
         <v>1</v>
       </c>
       <c r="G72">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H72">
         <v>0</v>
@@ -4199,16 +4215,16 @@
         <v>67</v>
       </c>
       <c r="D73">
-        <v>500</v>
+        <v>51.83</v>
       </c>
       <c r="E73">
-        <v>500</v>
+        <v>51.83</v>
       </c>
       <c r="F73">
         <v>1</v>
       </c>
       <c r="G73">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H73">
         <v>0</v>
@@ -4228,16 +4244,16 @@
         <v>51</v>
       </c>
       <c r="D74">
-        <v>500</v>
+        <v>28.287500000000001</v>
       </c>
       <c r="E74">
-        <v>500</v>
+        <v>28.287500000000001</v>
       </c>
       <c r="F74">
         <v>1</v>
       </c>
       <c r="G74">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H74">
         <v>0</v>
@@ -4257,16 +4273,16 @@
         <v>68</v>
       </c>
       <c r="D75">
-        <v>500</v>
+        <v>122.3699</v>
       </c>
       <c r="E75">
-        <v>500</v>
+        <v>122.3699</v>
       </c>
       <c r="F75">
         <v>1</v>
       </c>
       <c r="G75">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H75">
         <v>0</v>
@@ -4286,16 +4302,16 @@
         <v>69</v>
       </c>
       <c r="D76">
-        <v>500</v>
+        <v>6.5626999999999995</v>
       </c>
       <c r="E76">
-        <v>500</v>
+        <v>6.5626999999999995</v>
       </c>
       <c r="F76">
         <v>1</v>
       </c>
       <c r="G76">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H76">
         <v>0</v>
@@ -4315,16 +4331,16 @@
         <v>67</v>
       </c>
       <c r="D77">
-        <v>500</v>
+        <v>145.31745000000001</v>
       </c>
       <c r="E77">
-        <v>500</v>
+        <v>145.31745000000001</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H77">
         <v>0</v>
@@ -4344,16 +4360,16 @@
         <v>20</v>
       </c>
       <c r="D78">
-        <v>500</v>
+        <v>42.997</v>
       </c>
       <c r="E78">
-        <v>500</v>
+        <v>42.997</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="G78">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H78">
         <v>0</v>
@@ -4373,16 +4389,16 @@
         <v>51</v>
       </c>
       <c r="D79">
-        <v>500</v>
+        <v>54.074750000000002</v>
       </c>
       <c r="E79">
-        <v>500</v>
+        <v>54.074750000000002</v>
       </c>
       <c r="F79">
         <v>1</v>
       </c>
       <c r="G79">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H79">
         <v>0</v>
@@ -4402,16 +4418,16 @@
         <v>70</v>
       </c>
       <c r="D80">
-        <v>500</v>
+        <v>9.9936999999999987</v>
       </c>
       <c r="E80">
-        <v>500</v>
+        <v>9.9936999999999987</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="G80">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H80">
         <v>0</v>
@@ -4431,16 +4447,16 @@
         <v>36</v>
       </c>
       <c r="D81">
-        <v>500</v>
+        <v>181.46340000000004</v>
       </c>
       <c r="E81">
-        <v>500</v>
+        <v>181.46340000000004</v>
       </c>
       <c r="F81">
         <v>1</v>
       </c>
       <c r="G81">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H81">
         <v>0</v>
@@ -4460,16 +4476,16 @@
         <v>68</v>
       </c>
       <c r="D82">
-        <v>500</v>
+        <v>23.659299999999998</v>
       </c>
       <c r="E82">
-        <v>500</v>
+        <v>23.659299999999998</v>
       </c>
       <c r="F82">
         <v>1</v>
       </c>
       <c r="G82">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H82">
         <v>0</v>
@@ -4489,16 +4505,16 @@
         <v>66</v>
       </c>
       <c r="D83">
-        <v>500</v>
+        <v>18.359500000000001</v>
       </c>
       <c r="E83">
-        <v>500</v>
+        <v>18.359500000000001</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="G83">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H83">
         <v>0</v>
@@ -4518,16 +4534,16 @@
         <v>68</v>
       </c>
       <c r="D84">
-        <v>500</v>
+        <v>294.09875000000005</v>
       </c>
       <c r="E84">
-        <v>500</v>
+        <v>294.09875000000005</v>
       </c>
       <c r="F84">
         <v>1</v>
       </c>
       <c r="G84">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H84">
         <v>0</v>
@@ -4547,16 +4563,16 @@
         <v>58</v>
       </c>
       <c r="D85">
-        <v>500</v>
+        <v>44.603000000000002</v>
       </c>
       <c r="E85">
-        <v>500</v>
+        <v>44.603000000000002</v>
       </c>
       <c r="F85">
         <v>1</v>
       </c>
       <c r="G85">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H85">
         <v>0</v>
@@ -4576,16 +4592,16 @@
         <v>71</v>
       </c>
       <c r="D86">
-        <v>500</v>
+        <v>5.8765000000000009</v>
       </c>
       <c r="E86">
-        <v>500</v>
+        <v>5.8765000000000009</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
       <c r="G86">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H86">
         <v>0</v>
@@ -4605,16 +4621,16 @@
         <v>72</v>
       </c>
       <c r="D87">
-        <v>500</v>
+        <v>24.673999999999996</v>
       </c>
       <c r="E87">
-        <v>500</v>
+        <v>24.673999999999996</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="G87">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H87">
         <v>0</v>
@@ -4634,16 +4650,16 @@
         <v>53</v>
       </c>
       <c r="D88">
-        <v>500</v>
+        <v>41.683</v>
       </c>
       <c r="E88">
-        <v>500</v>
+        <v>41.683</v>
       </c>
       <c r="F88">
         <v>1</v>
       </c>
       <c r="G88">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H88">
         <v>0</v>
@@ -4663,16 +4679,16 @@
         <v>26</v>
       </c>
       <c r="D89">
-        <v>500</v>
+        <v>23.761499999999998</v>
       </c>
       <c r="E89">
-        <v>500</v>
+        <v>23.761499999999998</v>
       </c>
       <c r="F89">
         <v>1</v>
       </c>
       <c r="G89">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H89">
         <v>0</v>
@@ -4692,16 +4708,16 @@
         <v>53</v>
       </c>
       <c r="D90">
-        <v>500</v>
+        <v>31.024999999999999</v>
       </c>
       <c r="E90">
-        <v>500</v>
+        <v>31.024999999999999</v>
       </c>
       <c r="F90">
         <v>1</v>
       </c>
       <c r="G90">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H90">
         <v>0</v>
@@ -4721,16 +4737,16 @@
         <v>18</v>
       </c>
       <c r="D91">
-        <v>500</v>
+        <v>81.906000000000006</v>
       </c>
       <c r="E91">
-        <v>500</v>
+        <v>81.906000000000006</v>
       </c>
       <c r="F91">
         <v>1</v>
       </c>
       <c r="G91">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H91">
         <v>0</v>
@@ -4750,16 +4766,16 @@
         <v>32</v>
       </c>
       <c r="D92">
-        <v>500</v>
+        <v>52.56</v>
       </c>
       <c r="E92">
-        <v>500</v>
+        <v>52.56</v>
       </c>
       <c r="F92">
         <v>1</v>
       </c>
       <c r="G92">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -4779,16 +4795,16 @@
         <v>34</v>
       </c>
       <c r="D93">
-        <v>500</v>
+        <v>29.2</v>
       </c>
       <c r="E93">
-        <v>500</v>
+        <v>29.2</v>
       </c>
       <c r="F93">
         <v>1</v>
       </c>
       <c r="G93">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H93">
         <v>0</v>
@@ -4808,16 +4824,16 @@
         <v>30</v>
       </c>
       <c r="D94">
-        <v>500</v>
+        <v>49.494</v>
       </c>
       <c r="E94">
-        <v>500</v>
+        <v>49.494</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
       <c r="G94">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H94">
         <v>0</v>
@@ -4837,16 +4853,16 @@
         <v>65</v>
       </c>
       <c r="D95">
-        <v>500</v>
+        <v>831.32399999999996</v>
       </c>
       <c r="E95">
-        <v>500</v>
+        <v>831.32399999999996</v>
       </c>
       <c r="F95">
         <v>1</v>
       </c>
       <c r="G95">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H95">
         <v>0</v>
@@ -4866,16 +4882,16 @@
         <v>66</v>
       </c>
       <c r="D96">
-        <v>500</v>
+        <v>188.19399999999999</v>
       </c>
       <c r="E96">
-        <v>500</v>
+        <v>188.19399999999999</v>
       </c>
       <c r="F96">
         <v>1</v>
       </c>
       <c r="G96">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H96">
         <v>0</v>
@@ -4895,16 +4911,16 @@
         <v>51</v>
       </c>
       <c r="D97">
-        <v>500</v>
+        <v>424.64100000000008</v>
       </c>
       <c r="E97">
-        <v>500</v>
+        <v>424.64100000000008</v>
       </c>
       <c r="F97">
         <v>1</v>
       </c>
       <c r="G97">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H97">
         <v>0</v>
@@ -4924,16 +4940,16 @@
         <v>51</v>
       </c>
       <c r="D98">
-        <v>500</v>
+        <v>0.80300000000000016</v>
       </c>
       <c r="E98">
-        <v>500</v>
+        <v>0.80300000000000016</v>
       </c>
       <c r="F98">
         <v>1</v>
       </c>
       <c r="G98">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H98">
         <v>0</v>
@@ -4953,16 +4969,16 @@
         <v>42</v>
       </c>
       <c r="D99">
-        <v>500</v>
+        <v>635.83000000000004</v>
       </c>
       <c r="E99">
-        <v>500</v>
+        <v>635.83000000000004</v>
       </c>
       <c r="F99">
         <v>1</v>
       </c>
       <c r="G99">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H99">
         <v>0</v>
@@ -4982,16 +4998,16 @@
         <v>72</v>
       </c>
       <c r="D100">
-        <v>500</v>
+        <v>61.32</v>
       </c>
       <c r="E100">
-        <v>500</v>
+        <v>61.32</v>
       </c>
       <c r="F100">
         <v>1</v>
       </c>
       <c r="G100">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H100">
         <v>0</v>
@@ -5011,16 +5027,16 @@
         <v>73</v>
       </c>
       <c r="D101">
-        <v>500</v>
+        <v>80.3</v>
       </c>
       <c r="E101">
-        <v>500</v>
+        <v>80.3</v>
       </c>
       <c r="F101">
         <v>1</v>
       </c>
       <c r="G101">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H101">
         <v>0</v>
@@ -5040,16 +5056,16 @@
         <v>22</v>
       </c>
       <c r="D102">
-        <v>500</v>
+        <v>177.79150000000001</v>
       </c>
       <c r="E102">
-        <v>500</v>
+        <v>177.79150000000001</v>
       </c>
       <c r="F102">
         <v>1</v>
       </c>
       <c r="G102">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H102">
         <v>0</v>
@@ -5069,16 +5085,16 @@
         <v>68</v>
       </c>
       <c r="D103">
-        <v>500</v>
+        <v>210.25094999999999</v>
       </c>
       <c r="E103">
-        <v>500</v>
+        <v>210.25094999999999</v>
       </c>
       <c r="F103">
         <v>1</v>
       </c>
       <c r="G103">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H103">
         <v>0</v>
@@ -5098,16 +5114,16 @@
         <v>20</v>
       </c>
       <c r="D104">
-        <v>500</v>
+        <v>145.489</v>
       </c>
       <c r="E104">
-        <v>500</v>
+        <v>145.489</v>
       </c>
       <c r="F104">
         <v>1</v>
       </c>
       <c r="G104">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H104">
         <v>0</v>
@@ -5127,16 +5143,16 @@
         <v>38</v>
       </c>
       <c r="D105">
-        <v>500</v>
+        <v>547.17150000000004</v>
       </c>
       <c r="E105">
-        <v>500</v>
+        <v>547.17150000000004</v>
       </c>
       <c r="F105">
         <v>1</v>
       </c>
       <c r="G105">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H105">
         <v>0</v>
@@ -5156,16 +5172,16 @@
         <v>16</v>
       </c>
       <c r="D106">
-        <v>500</v>
+        <v>178.12</v>
       </c>
       <c r="E106">
-        <v>500</v>
+        <v>178.12</v>
       </c>
       <c r="F106">
         <v>1</v>
       </c>
       <c r="G106">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H106">
         <v>0</v>
@@ -5185,16 +5201,16 @@
         <v>42</v>
       </c>
       <c r="D107">
-        <v>500</v>
+        <v>806.85586000000001</v>
       </c>
       <c r="E107">
-        <v>500</v>
+        <v>806.85586000000001</v>
       </c>
       <c r="F107">
         <v>1</v>
       </c>
       <c r="G107">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -5214,16 +5230,16 @@
         <v>18</v>
       </c>
       <c r="D108">
-        <v>500</v>
+        <v>208.05</v>
       </c>
       <c r="E108">
-        <v>500</v>
+        <v>208.05</v>
       </c>
       <c r="F108">
         <v>1</v>
       </c>
       <c r="G108">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H108">
         <v>0</v>
@@ -5243,16 +5259,16 @@
         <v>34</v>
       </c>
       <c r="D109">
-        <v>500</v>
+        <v>267.07049999999998</v>
       </c>
       <c r="E109">
-        <v>500</v>
+        <v>267.07049999999998</v>
       </c>
       <c r="F109">
         <v>1</v>
       </c>
       <c r="G109">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -5272,16 +5288,16 @@
         <v>22</v>
       </c>
       <c r="D110">
-        <v>500</v>
+        <v>415.40649999999994</v>
       </c>
       <c r="E110">
-        <v>500</v>
+        <v>415.40649999999994</v>
       </c>
       <c r="F110">
         <v>1</v>
       </c>
       <c r="G110">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -5301,16 +5317,16 @@
         <v>22</v>
       </c>
       <c r="D111">
-        <v>500</v>
+        <v>173.667</v>
       </c>
       <c r="E111">
-        <v>500</v>
+        <v>173.667</v>
       </c>
       <c r="F111">
         <v>1</v>
       </c>
       <c r="G111">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H111">
         <v>0</v>
@@ -5330,16 +5346,16 @@
         <v>30</v>
       </c>
       <c r="D112">
-        <v>500</v>
+        <v>439.27749999999992</v>
       </c>
       <c r="E112">
-        <v>500</v>
+        <v>439.27749999999992</v>
       </c>
       <c r="F112">
         <v>1</v>
       </c>
       <c r="G112">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H112">
         <v>0</v>
@@ -5359,16 +5375,16 @@
         <v>26</v>
       </c>
       <c r="D113">
-        <v>500</v>
+        <v>118.77099999999999</v>
       </c>
       <c r="E113">
-        <v>500</v>
+        <v>118.77099999999999</v>
       </c>
       <c r="F113">
         <v>1</v>
       </c>
       <c r="G113">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H113">
         <v>0</v>
@@ -5388,16 +5404,16 @@
         <v>58</v>
       </c>
       <c r="D114">
-        <v>500</v>
+        <v>486.91</v>
       </c>
       <c r="E114">
-        <v>500</v>
+        <v>118.77099999999999</v>
       </c>
       <c r="F114">
         <v>1</v>
       </c>
       <c r="G114">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H114">
         <v>0</v>
@@ -5417,16 +5433,16 @@
         <v>77</v>
       </c>
       <c r="D115">
-        <v>500</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="E115">
-        <v>500</v>
+        <v>118.77099999999999</v>
       </c>
       <c r="F115">
         <v>1</v>
       </c>
       <c r="G115">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H115">
         <v>0</v>
@@ -5446,7 +5462,7 @@
         <v>30</v>
       </c>
       <c r="D116">
-        <v>500</v>
+        <v>49.494</v>
       </c>
       <c r="E116">
         <v>500</v>
@@ -5455,7 +5471,7 @@
         <v>1</v>
       </c>
       <c r="G116">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H116">
         <v>0</v>
@@ -5475,7 +5491,7 @@
         <v>65</v>
       </c>
       <c r="D117">
-        <v>500</v>
+        <v>816.06700000000012</v>
       </c>
       <c r="E117">
         <v>500</v>
@@ -5484,7 +5500,7 @@
         <v>1</v>
       </c>
       <c r="G117">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H117">
         <v>0</v>
@@ -5504,7 +5520,7 @@
         <v>66</v>
       </c>
       <c r="D118">
-        <v>500</v>
+        <v>188.88749999999999</v>
       </c>
       <c r="E118">
         <v>500</v>
@@ -5513,7 +5529,7 @@
         <v>1</v>
       </c>
       <c r="G118">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H118">
         <v>0</v>
@@ -5533,7 +5549,7 @@
         <v>66</v>
       </c>
       <c r="D119">
-        <v>500</v>
+        <v>89.716999999999999</v>
       </c>
       <c r="E119">
         <v>500</v>
@@ -5542,7 +5558,7 @@
         <v>1</v>
       </c>
       <c r="G119">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H119">
         <v>0</v>
@@ -5562,7 +5578,7 @@
         <v>67</v>
       </c>
       <c r="D120">
-        <v>500</v>
+        <v>170.63749999999999</v>
       </c>
       <c r="E120">
         <v>500</v>
@@ -5571,7 +5587,7 @@
         <v>1</v>
       </c>
       <c r="G120">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H120">
         <v>0</v>
@@ -5591,7 +5607,7 @@
         <v>70</v>
       </c>
       <c r="D121">
-        <v>500</v>
+        <v>12.1837</v>
       </c>
       <c r="E121">
         <v>500</v>
@@ -5600,7 +5616,7 @@
         <v>1</v>
       </c>
       <c r="G121">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H121">
         <v>0</v>
@@ -5620,7 +5636,7 @@
         <v>68</v>
       </c>
       <c r="D122">
-        <v>500</v>
+        <v>256.15699999999998</v>
       </c>
       <c r="E122">
         <v>500</v>
@@ -5629,7 +5645,7 @@
         <v>1</v>
       </c>
       <c r="G122">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H122">
         <v>0</v>
@@ -5649,7 +5665,7 @@
         <v>72</v>
       </c>
       <c r="D123">
-        <v>500</v>
+        <v>61.32</v>
       </c>
       <c r="E123">
         <v>500</v>
@@ -5658,7 +5674,7 @@
         <v>1</v>
       </c>
       <c r="G123">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H123">
         <v>0</v>
@@ -5678,7 +5694,7 @@
         <v>73</v>
       </c>
       <c r="D124">
-        <v>500</v>
+        <v>80.3</v>
       </c>
       <c r="E124">
         <v>500</v>
@@ -5687,7 +5703,7 @@
         <v>1</v>
       </c>
       <c r="G124">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H124">
         <v>0</v>
@@ -5707,7 +5723,7 @@
         <v>22</v>
       </c>
       <c r="D125">
-        <v>500</v>
+        <v>180.20050000000001</v>
       </c>
       <c r="E125">
         <v>500</v>
@@ -5716,7 +5732,7 @@
         <v>1</v>
       </c>
       <c r="G125">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H125">
         <v>0</v>
@@ -5736,7 +5752,7 @@
         <v>22</v>
       </c>
       <c r="D126">
-        <v>500</v>
+        <v>421.21</v>
       </c>
       <c r="E126">
         <v>500</v>
@@ -5745,7 +5761,7 @@
         <v>1</v>
       </c>
       <c r="G126">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H126">
         <v>0</v>
@@ -5765,7 +5781,7 @@
         <v>34</v>
       </c>
       <c r="D127">
-        <v>500</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="E127">
         <v>500</v>
@@ -5774,7 +5790,7 @@
         <v>1</v>
       </c>
       <c r="G127">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H127">
         <v>0</v>
@@ -5794,7 +5810,7 @@
         <v>34</v>
       </c>
       <c r="D128">
-        <v>500</v>
+        <v>161.62200000000001</v>
       </c>
       <c r="E128">
         <v>500</v>
@@ -5803,7 +5819,7 @@
         <v>1</v>
       </c>
       <c r="G128">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H128">
         <v>0</v>
@@ -5823,7 +5839,7 @@
         <v>42</v>
       </c>
       <c r="D129">
-        <v>500</v>
+        <v>455.15499999999997</v>
       </c>
       <c r="E129">
         <v>500</v>
@@ -5832,7 +5848,7 @@
         <v>1</v>
       </c>
       <c r="G129">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H129">
         <v>0</v>
@@ -5852,7 +5868,7 @@
         <v>28</v>
       </c>
       <c r="D130">
-        <v>500</v>
+        <v>351.714</v>
       </c>
       <c r="E130">
         <v>500</v>
@@ -5861,7 +5877,7 @@
         <v>1</v>
       </c>
       <c r="G130">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H130">
         <v>0</v>
@@ -5881,7 +5897,7 @@
         <v>16</v>
       </c>
       <c r="D131">
-        <v>500</v>
+        <v>167.75399999999999</v>
       </c>
       <c r="E131">
         <v>500</v>
@@ -5890,7 +5906,7 @@
         <v>1</v>
       </c>
       <c r="G131">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H131">
         <v>0</v>
@@ -5910,7 +5926,7 @@
         <v>18</v>
       </c>
       <c r="D132">
-        <v>500</v>
+        <v>207.5025</v>
       </c>
       <c r="E132">
         <v>500</v>
@@ -5919,7 +5935,7 @@
         <v>1</v>
       </c>
       <c r="G132">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H132">
         <v>0</v>
@@ -5939,7 +5955,7 @@
         <v>38</v>
       </c>
       <c r="D133">
-        <v>500</v>
+        <v>513.19000000000005</v>
       </c>
       <c r="E133">
         <v>500</v>
@@ -5948,7 +5964,7 @@
         <v>1</v>
       </c>
       <c r="G133">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H133">
         <v>0</v>
@@ -5968,7 +5984,7 @@
         <v>79</v>
       </c>
       <c r="D134">
-        <v>500</v>
+        <v>140.52500000000001</v>
       </c>
       <c r="E134">
         <v>500</v>
@@ -5977,7 +5993,7 @@
         <v>1</v>
       </c>
       <c r="G134">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H134">
         <v>0</v>
@@ -5997,7 +6013,7 @@
         <v>16</v>
       </c>
       <c r="D135">
-        <v>500</v>
+        <v>82.927999999999997</v>
       </c>
       <c r="E135">
         <v>500</v>
@@ -6006,7 +6022,7 @@
         <v>1</v>
       </c>
       <c r="G135">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H135">
         <v>0</v>
@@ -6026,7 +6042,7 @@
         <v>28</v>
       </c>
       <c r="D136">
-        <v>500</v>
+        <v>67.451999999999998</v>
       </c>
       <c r="E136">
         <v>500</v>
@@ -6035,7 +6051,7 @@
         <v>1</v>
       </c>
       <c r="G136">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H136">
         <v>0</v>
@@ -6055,16 +6071,16 @@
         <v>22</v>
       </c>
       <c r="D137">
-        <v>500</v>
+        <v>395</v>
       </c>
       <c r="E137">
-        <v>500</v>
+        <v>395</v>
       </c>
       <c r="F137">
         <v>1</v>
       </c>
       <c r="G137">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H137">
         <v>0</v>
@@ -6084,16 +6100,16 @@
         <v>74</v>
       </c>
       <c r="D138">
-        <v>500</v>
+        <v>395</v>
       </c>
       <c r="E138">
-        <v>500</v>
+        <v>395</v>
       </c>
       <c r="F138">
         <v>1</v>
       </c>
       <c r="G138">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H138">
         <v>0</v>
@@ -6104,25 +6120,25 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B139" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="C139" t="s">
         <v>20</v>
       </c>
       <c r="D139">
-        <v>500</v>
+        <v>395</v>
       </c>
       <c r="E139">
-        <v>500</v>
+        <v>395</v>
       </c>
       <c r="F139">
         <v>1</v>
       </c>
       <c r="G139">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H139">
         <v>0</v>
@@ -6136,10 +6152,10 @@
         <v>12</v>
       </c>
       <c r="B140" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C140" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D140">
         <v>500</v>
@@ -6151,10 +6167,10 @@
         <v>1</v>
       </c>
       <c r="G140">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H140">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I140">
         <v>1</v>
@@ -6165,10 +6181,10 @@
         <v>12</v>
       </c>
       <c r="B141" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C141" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D141">
         <v>500</v>
@@ -6180,10 +6196,10 @@
         <v>1</v>
       </c>
       <c r="G141">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H141">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I141">
         <v>1</v>
@@ -6194,10 +6210,10 @@
         <v>12</v>
       </c>
       <c r="B142" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C142" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D142">
         <v>500</v>
@@ -6209,10 +6225,10 @@
         <v>1</v>
       </c>
       <c r="G142">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H142">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I142">
         <v>1</v>
@@ -6223,10 +6239,10 @@
         <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C143" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D143">
         <v>500</v>
@@ -6238,10 +6254,10 @@
         <v>1</v>
       </c>
       <c r="G143">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I143">
         <v>1</v>
@@ -6252,10 +6268,10 @@
         <v>12</v>
       </c>
       <c r="B144" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C144" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D144">
         <v>500</v>
@@ -6267,10 +6283,10 @@
         <v>1</v>
       </c>
       <c r="G144">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H144">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I144">
         <v>1</v>
@@ -6281,10 +6297,10 @@
         <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C145" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D145">
         <v>500</v>
@@ -6296,10 +6312,10 @@
         <v>1</v>
       </c>
       <c r="G145">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I145">
         <v>1</v>
@@ -6310,10 +6326,10 @@
         <v>12</v>
       </c>
       <c r="B146" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C146" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D146">
         <v>500</v>
@@ -6325,10 +6341,10 @@
         <v>1</v>
       </c>
       <c r="G146">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H146">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I146">
         <v>1</v>
@@ -6339,10 +6355,10 @@
         <v>12</v>
       </c>
       <c r="B147" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C147" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D147">
         <v>500</v>
@@ -6354,10 +6370,10 @@
         <v>1</v>
       </c>
       <c r="G147">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I147">
         <v>1</v>
@@ -6368,10 +6384,10 @@
         <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C148" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D148">
         <v>500</v>
@@ -6383,10 +6399,10 @@
         <v>1</v>
       </c>
       <c r="G148">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H148">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I148">
         <v>1</v>
@@ -6397,10 +6413,10 @@
         <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="C149" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="D149">
         <v>500</v>
@@ -6412,10 +6428,10 @@
         <v>1</v>
       </c>
       <c r="G149">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H149">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I149">
         <v>1</v>
@@ -6426,10 +6442,10 @@
         <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C150" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D150">
         <v>500</v>
@@ -6441,10 +6457,10 @@
         <v>1</v>
       </c>
       <c r="G150">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H150">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I150">
         <v>1</v>
@@ -6455,10 +6471,10 @@
         <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C151" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D151">
         <v>500</v>
@@ -6470,10 +6486,10 @@
         <v>1</v>
       </c>
       <c r="G151">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H151">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I151">
         <v>1</v>
@@ -6484,10 +6500,10 @@
         <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="C152" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="D152">
         <v>500</v>
@@ -6499,10 +6515,10 @@
         <v>1</v>
       </c>
       <c r="G152">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H152">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I152">
         <v>1</v>
@@ -6513,10 +6529,10 @@
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C153" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D153">
         <v>500</v>
@@ -6528,10 +6544,10 @@
         <v>1</v>
       </c>
       <c r="G153">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H153">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I153">
         <v>1</v>
@@ -6542,10 +6558,10 @@
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C154" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D154">
         <v>500</v>
@@ -6557,10 +6573,10 @@
         <v>1</v>
       </c>
       <c r="G154">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H154">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I154">
         <v>1</v>
@@ -6571,10 +6587,10 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C155" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="D155">
         <v>500</v>
@@ -6586,10 +6602,10 @@
         <v>1</v>
       </c>
       <c r="G155">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H155">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I155">
         <v>1</v>
@@ -6600,10 +6616,10 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C156" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D156">
         <v>500</v>
@@ -6615,10 +6631,10 @@
         <v>1</v>
       </c>
       <c r="G156">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I156">
         <v>1</v>
@@ -6629,10 +6645,10 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C157" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="D157">
         <v>500</v>
@@ -6644,10 +6660,10 @@
         <v>1</v>
       </c>
       <c r="G157">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H157">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I157">
         <v>1</v>
@@ -6658,10 +6674,10 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C158" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D158">
         <v>500</v>
@@ -6673,10 +6689,10 @@
         <v>1</v>
       </c>
       <c r="G158">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H158">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I158">
         <v>1</v>
@@ -6687,10 +6703,10 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C159" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="D159">
         <v>500</v>
@@ -6702,10 +6718,10 @@
         <v>1</v>
       </c>
       <c r="G159">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H159">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I159">
         <v>1</v>
@@ -6716,10 +6732,10 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C160" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D160">
         <v>500</v>
@@ -6731,10 +6747,10 @@
         <v>1</v>
       </c>
       <c r="G160">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H160">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I160">
         <v>1</v>
@@ -6745,10 +6761,10 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C161" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D161">
         <v>500</v>
@@ -6760,10 +6776,10 @@
         <v>1</v>
       </c>
       <c r="G161">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H161">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I161">
         <v>1</v>
@@ -6774,10 +6790,10 @@
         <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C162" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="D162">
         <v>500</v>
@@ -6789,10 +6805,10 @@
         <v>1</v>
       </c>
       <c r="G162">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H162">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I162">
         <v>1</v>
@@ -6803,11 +6819,11 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
+        <v>56</v>
+      </c>
+      <c r="C163" t="s">
         <v>38</v>
       </c>
-      <c r="C163" t="s">
-        <v>59</v>
-      </c>
       <c r="D163">
         <v>500</v>
       </c>
@@ -6818,10 +6834,10 @@
         <v>1</v>
       </c>
       <c r="G163">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H163">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I163">
         <v>1</v>
@@ -6832,10 +6848,10 @@
         <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="C164" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D164">
         <v>500</v>
@@ -6847,10 +6863,10 @@
         <v>1</v>
       </c>
       <c r="G164">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H164">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I164">
         <v>1</v>
@@ -6861,11 +6877,11 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
+        <v>38</v>
+      </c>
+      <c r="C165" t="s">
         <v>16</v>
       </c>
-      <c r="C165" t="s">
-        <v>28</v>
-      </c>
       <c r="D165">
         <v>500</v>
       </c>
@@ -6876,10 +6892,10 @@
         <v>1</v>
       </c>
       <c r="G165">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H165">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I165">
         <v>1</v>
@@ -6890,10 +6906,10 @@
         <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C166" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D166">
         <v>500</v>
@@ -6905,10 +6921,10 @@
         <v>1</v>
       </c>
       <c r="G166">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H166">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I166">
         <v>1</v>
@@ -6922,7 +6938,7 @@
         <v>16</v>
       </c>
       <c r="C167" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D167">
         <v>500</v>
@@ -6934,10 +6950,10 @@
         <v>1</v>
       </c>
       <c r="G167">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H167">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I167">
         <v>1</v>
@@ -6948,11 +6964,11 @@
         <v>12</v>
       </c>
       <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="s">
         <v>28</v>
       </c>
-      <c r="C168" t="s">
-        <v>16</v>
-      </c>
       <c r="D168">
         <v>500</v>
       </c>
@@ -6963,10 +6979,10 @@
         <v>1</v>
       </c>
       <c r="G168">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H168">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I168">
         <v>1</v>
@@ -6977,7 +6993,7 @@
         <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C169" t="s">
         <v>42</v>
@@ -6992,10 +7008,10 @@
         <v>1</v>
       </c>
       <c r="G169">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H169">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I169">
         <v>1</v>
@@ -7006,10 +7022,10 @@
         <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C170" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D170">
         <v>500</v>
@@ -7021,10 +7037,10 @@
         <v>1</v>
       </c>
       <c r="G170">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H170">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I170">
         <v>1</v>
@@ -7035,10 +7051,10 @@
         <v>12</v>
       </c>
       <c r="B171" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C171" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D171">
         <v>500</v>
@@ -7050,10 +7066,10 @@
         <v>1</v>
       </c>
       <c r="G171">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H171">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I171">
         <v>1</v>
@@ -7064,11 +7080,11 @@
         <v>12</v>
       </c>
       <c r="B172" t="s">
+        <v>28</v>
+      </c>
+      <c r="C172" t="s">
         <v>42</v>
       </c>
-      <c r="C172" t="s">
-        <v>60</v>
-      </c>
       <c r="D172">
         <v>500</v>
       </c>
@@ -7079,10 +7095,10 @@
         <v>1</v>
       </c>
       <c r="G172">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H172">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I172">
         <v>1</v>
@@ -7096,7 +7112,7 @@
         <v>42</v>
       </c>
       <c r="C173" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="D173">
         <v>500</v>
@@ -7108,10 +7124,10 @@
         <v>1</v>
       </c>
       <c r="G173">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H173">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I173">
         <v>1</v>
@@ -7125,7 +7141,7 @@
         <v>42</v>
       </c>
       <c r="C174" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D174">
         <v>500</v>
@@ -7137,10 +7153,10 @@
         <v>1</v>
       </c>
       <c r="G174">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H174">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I174">
         <v>1</v>
@@ -7154,7 +7170,7 @@
         <v>42</v>
       </c>
       <c r="C175" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D175">
         <v>500</v>
@@ -7166,10 +7182,10 @@
         <v>1</v>
       </c>
       <c r="G175">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H175">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I175">
         <v>1</v>
@@ -7183,7 +7199,7 @@
         <v>42</v>
       </c>
       <c r="C176" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="D176">
         <v>500</v>
@@ -7195,10 +7211,10 @@
         <v>1</v>
       </c>
       <c r="G176">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H176">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I176">
         <v>1</v>
@@ -7212,7 +7228,7 @@
         <v>42</v>
       </c>
       <c r="C177" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="D177">
         <v>500</v>
@@ -7224,10 +7240,10 @@
         <v>1</v>
       </c>
       <c r="G177">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H177">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I177">
         <v>1</v>
@@ -7241,7 +7257,7 @@
         <v>42</v>
       </c>
       <c r="C178" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="D178">
         <v>500</v>
@@ -7253,10 +7269,10 @@
         <v>1</v>
       </c>
       <c r="G178">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H178">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I178">
         <v>1</v>
@@ -7267,10 +7283,10 @@
         <v>12</v>
       </c>
       <c r="B179" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C179" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D179">
         <v>500</v>
@@ -7282,10 +7298,10 @@
         <v>1</v>
       </c>
       <c r="G179">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H179">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I179">
         <v>1</v>
@@ -7296,10 +7312,10 @@
         <v>12</v>
       </c>
       <c r="B180" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C180" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="D180">
         <v>500</v>
@@ -7311,10 +7327,10 @@
         <v>1</v>
       </c>
       <c r="G180">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H180">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I180">
         <v>1</v>
@@ -7325,10 +7341,10 @@
         <v>12</v>
       </c>
       <c r="B181" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C181" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D181">
         <v>500</v>
@@ -7340,10 +7356,10 @@
         <v>1</v>
       </c>
       <c r="G181">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H181">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I181">
         <v>1</v>
@@ -7357,7 +7373,7 @@
         <v>60</v>
       </c>
       <c r="C182" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="D182">
         <v>500</v>
@@ -7369,10 +7385,10 @@
         <v>1</v>
       </c>
       <c r="G182">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H182">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I182">
         <v>1</v>
@@ -7386,7 +7402,7 @@
         <v>60</v>
       </c>
       <c r="C183" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D183">
         <v>500</v>
@@ -7398,10 +7414,10 @@
         <v>1</v>
       </c>
       <c r="G183">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H183">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I183">
         <v>1</v>
@@ -7412,10 +7428,10 @@
         <v>12</v>
       </c>
       <c r="B184" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C184" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D184">
         <v>500</v>
@@ -7427,10 +7443,10 @@
         <v>1</v>
       </c>
       <c r="G184">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H184">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I184">
         <v>1</v>
@@ -7441,10 +7457,10 @@
         <v>12</v>
       </c>
       <c r="B185" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C185" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D185">
         <v>500</v>
@@ -7456,10 +7472,10 @@
         <v>1</v>
       </c>
       <c r="G185">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H185">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I185">
         <v>1</v>
@@ -7470,10 +7486,10 @@
         <v>12</v>
       </c>
       <c r="B186" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C186" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D186">
         <v>500</v>
@@ -7485,10 +7501,10 @@
         <v>1</v>
       </c>
       <c r="G186">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H186">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I186">
         <v>1</v>
@@ -7499,10 +7515,10 @@
         <v>12</v>
       </c>
       <c r="B187" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C187" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D187">
         <v>500</v>
@@ -7514,10 +7530,10 @@
         <v>1</v>
       </c>
       <c r="G187">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H187">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I187">
         <v>1</v>
@@ -7528,11 +7544,11 @@
         <v>12</v>
       </c>
       <c r="B188" t="s">
+        <v>22</v>
+      </c>
+      <c r="C188" t="s">
         <v>61</v>
       </c>
-      <c r="C188" t="s">
-        <v>22</v>
-      </c>
       <c r="D188">
         <v>500</v>
       </c>
@@ -7543,10 +7559,10 @@
         <v>1</v>
       </c>
       <c r="G188">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H188">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I188">
         <v>1</v>
@@ -7557,10 +7573,10 @@
         <v>12</v>
       </c>
       <c r="B189" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C189" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="D189">
         <v>500</v>
@@ -7572,10 +7588,10 @@
         <v>1</v>
       </c>
       <c r="G189">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H189">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I189">
         <v>1</v>
@@ -7586,10 +7602,10 @@
         <v>12</v>
       </c>
       <c r="B190" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C190" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D190">
         <v>500</v>
@@ -7601,10 +7617,10 @@
         <v>1</v>
       </c>
       <c r="G190">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H190">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I190">
         <v>1</v>
@@ -7615,10 +7631,10 @@
         <v>12</v>
       </c>
       <c r="B191" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C191" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D191">
         <v>500</v>
@@ -7630,10 +7646,10 @@
         <v>1</v>
       </c>
       <c r="G191">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H191">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I191">
         <v>1</v>
@@ -7644,10 +7660,10 @@
         <v>12</v>
       </c>
       <c r="B192" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C192" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="D192">
         <v>500</v>
@@ -7659,10 +7675,10 @@
         <v>1</v>
       </c>
       <c r="G192">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H192">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I192">
         <v>1</v>
@@ -7673,10 +7689,10 @@
         <v>12</v>
       </c>
       <c r="B193" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="C193" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D193">
         <v>500</v>
@@ -7688,10 +7704,10 @@
         <v>1</v>
       </c>
       <c r="G193">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H193">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I193">
         <v>1</v>
@@ -7702,10 +7718,10 @@
         <v>12</v>
       </c>
       <c r="B194" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="C194" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D194">
         <v>500</v>
@@ -7717,10 +7733,10 @@
         <v>1</v>
       </c>
       <c r="G194">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H194">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I194">
         <v>1</v>
@@ -7731,10 +7747,10 @@
         <v>12</v>
       </c>
       <c r="B195" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C195" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D195">
         <v>500</v>
@@ -7746,10 +7762,10 @@
         <v>1</v>
       </c>
       <c r="G195">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H195">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I195">
         <v>1</v>
@@ -7760,10 +7776,10 @@
         <v>12</v>
       </c>
       <c r="B196" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C196" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="D196">
         <v>500</v>
@@ -7775,10 +7791,10 @@
         <v>1</v>
       </c>
       <c r="G196">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H196">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I196">
         <v>1</v>
@@ -7789,10 +7805,10 @@
         <v>12</v>
       </c>
       <c r="B197" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C197" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D197">
         <v>500</v>
@@ -7804,10 +7820,10 @@
         <v>1</v>
       </c>
       <c r="G197">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H197">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I197">
         <v>1</v>
@@ -7818,10 +7834,10 @@
         <v>12</v>
       </c>
       <c r="B198" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C198" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D198">
         <v>500</v>
@@ -7833,10 +7849,10 @@
         <v>1</v>
       </c>
       <c r="G198">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H198">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I198">
         <v>1</v>
@@ -7847,10 +7863,10 @@
         <v>12</v>
       </c>
       <c r="B199" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="C199" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D199">
         <v>500</v>
@@ -7862,10 +7878,10 @@
         <v>1</v>
       </c>
       <c r="G199">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H199">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I199">
         <v>1</v>
@@ -7876,10 +7892,10 @@
         <v>12</v>
       </c>
       <c r="B200" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="C200" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D200">
         <v>500</v>
@@ -7891,10 +7907,10 @@
         <v>1</v>
       </c>
       <c r="G200">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H200">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I200">
         <v>1</v>
@@ -7905,10 +7921,10 @@
         <v>12</v>
       </c>
       <c r="B201" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="C201" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="D201">
         <v>500</v>
@@ -7920,10 +7936,10 @@
         <v>1</v>
       </c>
       <c r="G201">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H201">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I201">
         <v>1</v>
@@ -7934,10 +7950,10 @@
         <v>12</v>
       </c>
       <c r="B202" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C202" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="D202">
         <v>500</v>
@@ -7949,10 +7965,10 @@
         <v>1</v>
       </c>
       <c r="G202">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H202">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I202">
         <v>1</v>
@@ -7963,10 +7979,10 @@
         <v>12</v>
       </c>
       <c r="B203" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C203" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="D203">
         <v>500</v>
@@ -7978,10 +7994,10 @@
         <v>1</v>
       </c>
       <c r="G203">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H203">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I203">
         <v>1</v>
@@ -7992,11 +8008,11 @@
         <v>12</v>
       </c>
       <c r="B204" t="s">
+        <v>62</v>
+      </c>
+      <c r="C204" t="s">
         <v>65</v>
       </c>
-      <c r="C204" t="s">
-        <v>66</v>
-      </c>
       <c r="D204">
         <v>500</v>
       </c>
@@ -8007,10 +8023,10 @@
         <v>1</v>
       </c>
       <c r="G204">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H204">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I204">
         <v>1</v>
@@ -8024,7 +8040,7 @@
         <v>65</v>
       </c>
       <c r="C205" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D205">
         <v>500</v>
@@ -8036,10 +8052,10 @@
         <v>1</v>
       </c>
       <c r="G205">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H205">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I205">
         <v>1</v>
@@ -8050,10 +8066,10 @@
         <v>12</v>
       </c>
       <c r="B206" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C206" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D206">
         <v>500</v>
@@ -8065,10 +8081,10 @@
         <v>1</v>
       </c>
       <c r="G206">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H206">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I206">
         <v>1</v>
@@ -8079,11 +8095,11 @@
         <v>12</v>
       </c>
       <c r="B207" t="s">
+        <v>65</v>
+      </c>
+      <c r="C207" t="s">
         <v>66</v>
       </c>
-      <c r="C207" t="s">
-        <v>65</v>
-      </c>
       <c r="D207">
         <v>500</v>
       </c>
@@ -8094,10 +8110,10 @@
         <v>1</v>
       </c>
       <c r="G207">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H207">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I207">
         <v>1</v>
@@ -8108,10 +8124,10 @@
         <v>12</v>
       </c>
       <c r="B208" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C208" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D208">
         <v>500</v>
@@ -8123,10 +8139,10 @@
         <v>1</v>
       </c>
       <c r="G208">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H208">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I208">
         <v>1</v>
@@ -8140,7 +8156,7 @@
         <v>66</v>
       </c>
       <c r="C209" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="D209">
         <v>500</v>
@@ -8152,10 +8168,10 @@
         <v>1</v>
       </c>
       <c r="G209">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H209">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I209">
         <v>1</v>
@@ -8166,10 +8182,10 @@
         <v>12</v>
       </c>
       <c r="B210" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C210" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D210">
         <v>500</v>
@@ -8181,10 +8197,10 @@
         <v>1</v>
       </c>
       <c r="G210">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H210">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I210">
         <v>1</v>
@@ -8195,11 +8211,11 @@
         <v>12</v>
       </c>
       <c r="B211" t="s">
+        <v>66</v>
+      </c>
+      <c r="C211" t="s">
         <v>67</v>
       </c>
-      <c r="C211" t="s">
-        <v>69</v>
-      </c>
       <c r="D211">
         <v>500</v>
       </c>
@@ -8210,10 +8226,10 @@
         <v>1</v>
       </c>
       <c r="G211">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H211">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I211">
         <v>1</v>
@@ -8224,10 +8240,10 @@
         <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C212" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="D212">
         <v>500</v>
@@ -8239,10 +8255,10 @@
         <v>1</v>
       </c>
       <c r="G212">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H212">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I212">
         <v>1</v>
@@ -8253,11 +8269,11 @@
         <v>12</v>
       </c>
       <c r="B213" t="s">
+        <v>67</v>
+      </c>
+      <c r="C213" t="s">
         <v>68</v>
       </c>
-      <c r="C213" t="s">
-        <v>20</v>
-      </c>
       <c r="D213">
         <v>500</v>
       </c>
@@ -8268,10 +8284,10 @@
         <v>1</v>
       </c>
       <c r="G213">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H213">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I213">
         <v>1</v>
@@ -8282,10 +8298,10 @@
         <v>12</v>
       </c>
       <c r="B214" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C214" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="D214">
         <v>500</v>
@@ -8297,10 +8313,10 @@
         <v>1</v>
       </c>
       <c r="G214">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H214">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I214">
         <v>1</v>
@@ -8314,7 +8330,7 @@
         <v>68</v>
       </c>
       <c r="C215" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D215">
         <v>500</v>
@@ -8326,10 +8342,10 @@
         <v>1</v>
       </c>
       <c r="G215">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H215">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I215">
         <v>1</v>
@@ -8343,7 +8359,7 @@
         <v>68</v>
       </c>
       <c r="C216" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D216">
         <v>500</v>
@@ -8355,10 +8371,10 @@
         <v>1</v>
       </c>
       <c r="G216">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H216">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I216">
         <v>1</v>
@@ -8369,10 +8385,10 @@
         <v>12</v>
       </c>
       <c r="B217" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="C217" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D217">
         <v>500</v>
@@ -8384,10 +8400,10 @@
         <v>1</v>
       </c>
       <c r="G217">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H217">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I217">
         <v>1</v>
@@ -8398,10 +8414,10 @@
         <v>12</v>
       </c>
       <c r="B218" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C218" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D218">
         <v>500</v>
@@ -8413,10 +8429,10 @@
         <v>1</v>
       </c>
       <c r="G218">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H218">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I218">
         <v>1</v>
@@ -8427,10 +8443,10 @@
         <v>12</v>
       </c>
       <c r="B219" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="C219" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="D219">
         <v>500</v>
@@ -8442,10 +8458,10 @@
         <v>1</v>
       </c>
       <c r="G219">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H219">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I219">
         <v>1</v>
@@ -8456,10 +8472,10 @@
         <v>12</v>
       </c>
       <c r="B220" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="C220" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D220">
         <v>500</v>
@@ -8471,10 +8487,10 @@
         <v>1</v>
       </c>
       <c r="G220">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H220">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I220">
         <v>1</v>
@@ -8488,7 +8504,7 @@
         <v>51</v>
       </c>
       <c r="C221" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D221">
         <v>500</v>
@@ -8500,10 +8516,10 @@
         <v>1</v>
       </c>
       <c r="G221">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H221">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I221">
         <v>1</v>
@@ -8514,10 +8530,10 @@
         <v>12</v>
       </c>
       <c r="B222" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C222" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D222">
         <v>500</v>
@@ -8529,10 +8545,10 @@
         <v>1</v>
       </c>
       <c r="G222">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H222">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I222">
         <v>1</v>
@@ -8543,10 +8559,10 @@
         <v>12</v>
       </c>
       <c r="B223" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C223" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D223">
         <v>500</v>
@@ -8558,10 +8574,10 @@
         <v>1</v>
       </c>
       <c r="G223">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H223">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I223">
         <v>1</v>
@@ -8572,10 +8588,10 @@
         <v>12</v>
       </c>
       <c r="B224" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C224" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="D224">
         <v>500</v>
@@ -8587,10 +8603,10 @@
         <v>1</v>
       </c>
       <c r="G224">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H224">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I224">
         <v>1</v>
@@ -8601,11 +8617,11 @@
         <v>12</v>
       </c>
       <c r="B225" t="s">
+        <v>26</v>
+      </c>
+      <c r="C225" t="s">
         <v>72</v>
       </c>
-      <c r="C225" t="s">
-        <v>53</v>
-      </c>
       <c r="D225">
         <v>500</v>
       </c>
@@ -8616,10 +8632,10 @@
         <v>1</v>
       </c>
       <c r="G225">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H225">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I225">
         <v>1</v>
@@ -8630,10 +8646,10 @@
         <v>12</v>
       </c>
       <c r="B226" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C226" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D226">
         <v>500</v>
@@ -8645,10 +8661,10 @@
         <v>1</v>
       </c>
       <c r="G226">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H226">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I226">
         <v>1</v>
@@ -8659,10 +8675,10 @@
         <v>12</v>
       </c>
       <c r="B227" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C227" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D227">
         <v>500</v>
@@ -8674,10 +8690,10 @@
         <v>1</v>
       </c>
       <c r="G227">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H227">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I227">
         <v>1</v>
@@ -8688,10 +8704,10 @@
         <v>12</v>
       </c>
       <c r="B228" t="s">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="C228" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="D228">
         <v>500</v>
@@ -8703,10 +8719,10 @@
         <v>1</v>
       </c>
       <c r="G228">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H228">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I228">
         <v>1</v>
@@ -8717,10 +8733,10 @@
         <v>12</v>
       </c>
       <c r="B229" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C229" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D229">
         <v>500</v>
@@ -8732,10 +8748,10 @@
         <v>1</v>
       </c>
       <c r="G229">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H229">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I229">
         <v>1</v>
@@ -8746,10 +8762,10 @@
         <v>12</v>
       </c>
       <c r="B230" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="C230" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="D230">
         <v>500</v>
@@ -8761,10 +8777,10 @@
         <v>1</v>
       </c>
       <c r="G230">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H230">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I230">
         <v>1</v>
@@ -8775,10 +8791,10 @@
         <v>12</v>
       </c>
       <c r="B231" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C231" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="D231">
         <v>500</v>
@@ -8790,10 +8806,10 @@
         <v>1</v>
       </c>
       <c r="G231">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H231">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I231">
         <v>1</v>
@@ -8807,7 +8823,7 @@
         <v>58</v>
       </c>
       <c r="C232" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="D232">
         <v>500</v>
@@ -8819,10 +8835,10 @@
         <v>1</v>
       </c>
       <c r="G232">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H232">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I232">
         <v>1</v>
@@ -8833,10 +8849,10 @@
         <v>12</v>
       </c>
       <c r="B233" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C233" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="D233">
         <v>500</v>
@@ -8848,10 +8864,10 @@
         <v>1</v>
       </c>
       <c r="G233">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H233">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I233">
         <v>1</v>
@@ -8862,10 +8878,10 @@
         <v>12</v>
       </c>
       <c r="B234" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C234" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D234">
         <v>500</v>
@@ -8877,10 +8893,10 @@
         <v>1</v>
       </c>
       <c r="G234">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H234">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I234">
         <v>1</v>
@@ -8891,10 +8907,10 @@
         <v>12</v>
       </c>
       <c r="B235" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C235" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="D235">
         <v>500</v>
@@ -8906,10 +8922,10 @@
         <v>1</v>
       </c>
       <c r="G235">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H235">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I235">
         <v>1</v>
@@ -8920,10 +8936,10 @@
         <v>12</v>
       </c>
       <c r="B236" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C236" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="D236">
         <v>500</v>
@@ -8935,10 +8951,10 @@
         <v>1</v>
       </c>
       <c r="G236">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H236">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I236">
         <v>1</v>
@@ -8949,10 +8965,10 @@
         <v>12</v>
       </c>
       <c r="B237" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C237" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D237">
         <v>500</v>
@@ -8964,10 +8980,10 @@
         <v>1</v>
       </c>
       <c r="G237">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H237">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I237">
         <v>1</v>
@@ -8978,10 +8994,10 @@
         <v>12</v>
       </c>
       <c r="B238" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C238" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D238">
         <v>500</v>
@@ -8993,10 +9009,10 @@
         <v>1</v>
       </c>
       <c r="G238">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H238">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I238">
         <v>1</v>
@@ -9007,10 +9023,10 @@
         <v>12</v>
       </c>
       <c r="B239" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C239" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="D239">
         <v>500</v>
@@ -9022,10 +9038,10 @@
         <v>1</v>
       </c>
       <c r="G239">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H239">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I239">
         <v>1</v>
@@ -9036,10 +9052,10 @@
         <v>12</v>
       </c>
       <c r="B240" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="C240" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D240">
         <v>500</v>
@@ -9051,10 +9067,10 @@
         <v>1</v>
       </c>
       <c r="G240">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H240">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I240">
         <v>1</v>
@@ -9065,10 +9081,10 @@
         <v>12</v>
       </c>
       <c r="B241" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C241" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="D241">
         <v>500</v>
@@ -9080,10 +9096,10 @@
         <v>1</v>
       </c>
       <c r="G241">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H241">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I241">
         <v>1</v>
@@ -9094,10 +9110,10 @@
         <v>12</v>
       </c>
       <c r="B242" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C242" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D242">
         <v>500</v>
@@ -9109,10 +9125,10 @@
         <v>1</v>
       </c>
       <c r="G242">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H242">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I242">
         <v>1</v>
@@ -9126,7 +9142,7 @@
         <v>48</v>
       </c>
       <c r="C243" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D243">
         <v>500</v>
@@ -9138,10 +9154,10 @@
         <v>1</v>
       </c>
       <c r="G243">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H243">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I243">
         <v>1</v>
@@ -9152,10 +9168,10 @@
         <v>12</v>
       </c>
       <c r="B244" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C244" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D244">
         <v>500</v>
@@ -9167,10 +9183,10 @@
         <v>1</v>
       </c>
       <c r="G244">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H244">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I244">
         <v>1</v>
@@ -9181,10 +9197,10 @@
         <v>12</v>
       </c>
       <c r="B245" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C245" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D245">
         <v>500</v>
@@ -9196,10 +9212,10 @@
         <v>1</v>
       </c>
       <c r="G245">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H245">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I245">
         <v>1</v>
@@ -9210,10 +9226,10 @@
         <v>12</v>
       </c>
       <c r="B246" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C246" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D246">
         <v>500</v>
@@ -9225,10 +9241,10 @@
         <v>1</v>
       </c>
       <c r="G246">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H246">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I246">
         <v>1</v>
@@ -9239,10 +9255,10 @@
         <v>12</v>
       </c>
       <c r="B247" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C247" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D247">
         <v>500</v>
@@ -9254,10 +9270,10 @@
         <v>1</v>
       </c>
       <c r="G247">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H247">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I247">
         <v>1</v>
@@ -9268,10 +9284,10 @@
         <v>12</v>
       </c>
       <c r="B248" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C248" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D248">
         <v>500</v>
@@ -9283,10 +9299,10 @@
         <v>1</v>
       </c>
       <c r="G248">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H248">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I248">
         <v>1</v>
@@ -9297,10 +9313,10 @@
         <v>12</v>
       </c>
       <c r="B249" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C249" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="D249">
         <v>500</v>
@@ -9312,10 +9328,10 @@
         <v>1</v>
       </c>
       <c r="G249">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H249">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I249">
         <v>1</v>
@@ -9326,10 +9342,10 @@
         <v>12</v>
       </c>
       <c r="B250" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C250" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="D250">
         <v>500</v>
@@ -9341,10 +9357,10 @@
         <v>1</v>
       </c>
       <c r="G250">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H250">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I250">
         <v>1</v>
@@ -9355,10 +9371,10 @@
         <v>12</v>
       </c>
       <c r="B251" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="C251" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D251">
         <v>500</v>
@@ -9370,10 +9386,10 @@
         <v>1</v>
       </c>
       <c r="G251">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H251">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I251">
         <v>1</v>
@@ -9384,11 +9400,11 @@
         <v>12</v>
       </c>
       <c r="B252" t="s">
+        <v>53</v>
+      </c>
+      <c r="C252" t="s">
         <v>58</v>
       </c>
-      <c r="C252" t="s">
-        <v>65</v>
-      </c>
       <c r="D252">
         <v>500</v>
       </c>
@@ -9399,10 +9415,10 @@
         <v>1</v>
       </c>
       <c r="G252">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H252">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I252">
         <v>1</v>
@@ -9413,10 +9429,10 @@
         <v>12</v>
       </c>
       <c r="B253" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C253" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="D253">
         <v>500</v>
@@ -9428,10 +9444,10 @@
         <v>1</v>
       </c>
       <c r="G253">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H253">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I253">
         <v>1</v>
@@ -9442,10 +9458,10 @@
         <v>12</v>
       </c>
       <c r="B254" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C254" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="D254">
         <v>500</v>
@@ -9457,10 +9473,10 @@
         <v>1</v>
       </c>
       <c r="G254">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H254">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I254">
         <v>1</v>
@@ -9471,10 +9487,10 @@
         <v>12</v>
       </c>
       <c r="B255" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C255" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D255">
         <v>500</v>
@@ -9486,10 +9502,10 @@
         <v>1</v>
       </c>
       <c r="G255">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H255">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I255">
         <v>1</v>
@@ -9500,10 +9516,10 @@
         <v>12</v>
       </c>
       <c r="B256" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C256" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D256">
         <v>500</v>
@@ -9515,10 +9531,10 @@
         <v>1</v>
       </c>
       <c r="G256">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H256">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I256">
         <v>1</v>
@@ -9529,10 +9545,10 @@
         <v>12</v>
       </c>
       <c r="B257" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="C257" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D257">
         <v>500</v>
@@ -9544,10 +9560,10 @@
         <v>1</v>
       </c>
       <c r="G257">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H257">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I257">
         <v>1</v>
@@ -9558,10 +9574,10 @@
         <v>12</v>
       </c>
       <c r="B258" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C258" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D258">
         <v>500</v>
@@ -9573,10 +9589,10 @@
         <v>1</v>
       </c>
       <c r="G258">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H258">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I258">
         <v>1</v>
@@ -9587,10 +9603,10 @@
         <v>12</v>
       </c>
       <c r="B259" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C259" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D259">
         <v>500</v>
@@ -9602,10 +9618,10 @@
         <v>1</v>
       </c>
       <c r="G259">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H259">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I259">
         <v>1</v>
@@ -9616,10 +9632,10 @@
         <v>12</v>
       </c>
       <c r="B260" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C260" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D260">
         <v>500</v>
@@ -9631,10 +9647,10 @@
         <v>1</v>
       </c>
       <c r="G260">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H260">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I260">
         <v>1</v>
@@ -9645,10 +9661,10 @@
         <v>12</v>
       </c>
       <c r="B261" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C261" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="D261">
         <v>500</v>
@@ -9660,10 +9676,10 @@
         <v>1</v>
       </c>
       <c r="G261">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H261">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I261">
         <v>1</v>
@@ -9674,10 +9690,10 @@
         <v>12</v>
       </c>
       <c r="B262" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C262" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="D262">
         <v>500</v>
@@ -9689,10 +9705,10 @@
         <v>1</v>
       </c>
       <c r="G262">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H262">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I262">
         <v>1</v>
@@ -9703,10 +9719,10 @@
         <v>12</v>
       </c>
       <c r="B263" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="C263" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D263">
         <v>500</v>
@@ -9718,10 +9734,10 @@
         <v>1</v>
       </c>
       <c r="G263">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H263">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I263">
         <v>1</v>
@@ -9732,10 +9748,10 @@
         <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C264" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D264">
         <v>500</v>
@@ -9747,10 +9763,10 @@
         <v>1</v>
       </c>
       <c r="G264">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H264">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I264">
         <v>1</v>
@@ -9761,10 +9777,10 @@
         <v>12</v>
       </c>
       <c r="B265" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="C265" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D265">
         <v>500</v>
@@ -9776,10 +9792,10 @@
         <v>1</v>
       </c>
       <c r="G265">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H265">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I265">
         <v>1</v>
@@ -9790,10 +9806,10 @@
         <v>12</v>
       </c>
       <c r="B266" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="C266" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D266">
         <v>500</v>
@@ -9805,10 +9821,10 @@
         <v>1</v>
       </c>
       <c r="G266">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H266">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I266">
         <v>1</v>
@@ -9822,7 +9838,7 @@
         <v>48</v>
       </c>
       <c r="C267" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D267">
         <v>500</v>
@@ -9834,10 +9850,10 @@
         <v>1</v>
       </c>
       <c r="G267">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H267">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I267">
         <v>1</v>
@@ -9851,7 +9867,7 @@
         <v>48</v>
       </c>
       <c r="C268" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D268">
         <v>500</v>
@@ -9863,10 +9879,10 @@
         <v>1</v>
       </c>
       <c r="G268">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H268">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I268">
         <v>1</v>
@@ -9877,10 +9893,10 @@
         <v>12</v>
       </c>
       <c r="B269" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C269" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="D269">
         <v>500</v>
@@ -9892,10 +9908,10 @@
         <v>1</v>
       </c>
       <c r="G269">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H269">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I269">
         <v>1</v>
@@ -9906,10 +9922,10 @@
         <v>12</v>
       </c>
       <c r="B270" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C270" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D270">
         <v>500</v>
@@ -9921,10 +9937,10 @@
         <v>1</v>
       </c>
       <c r="G270">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H270">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I270">
         <v>1</v>
@@ -9935,11 +9951,11 @@
         <v>12</v>
       </c>
       <c r="B271" t="s">
+        <v>48</v>
+      </c>
+      <c r="C271" t="s">
         <v>38</v>
       </c>
-      <c r="C271" t="s">
-        <v>28</v>
-      </c>
       <c r="D271">
         <v>500</v>
       </c>
@@ -9950,10 +9966,10 @@
         <v>1</v>
       </c>
       <c r="G271">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H271">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I271">
         <v>1</v>
@@ -9964,10 +9980,10 @@
         <v>12</v>
       </c>
       <c r="B272" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="C272" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="D272">
         <v>500</v>
@@ -9979,10 +9995,10 @@
         <v>1</v>
       </c>
       <c r="G272">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H272">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I272">
         <v>1</v>
@@ -9993,10 +10009,10 @@
         <v>12</v>
       </c>
       <c r="B273" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C273" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="D273">
         <v>500</v>
@@ -10008,10 +10024,10 @@
         <v>1</v>
       </c>
       <c r="G273">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H273">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I273">
         <v>1</v>
@@ -10019,13 +10035,13 @@
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B274" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="C274" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D274">
         <v>500</v>
@@ -10037,10 +10053,10 @@
         <v>1</v>
       </c>
       <c r="G274">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H274">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I274">
         <v>1</v>
@@ -10051,10 +10067,10 @@
         <v>12</v>
       </c>
       <c r="B275" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C275" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D275">
         <v>500</v>
@@ -10066,10 +10082,10 @@
         <v>1</v>
       </c>
       <c r="G275">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H275">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I275">
         <v>1</v>
@@ -10080,10 +10096,10 @@
         <v>12</v>
       </c>
       <c r="B276" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C276" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="D276">
         <v>500</v>
@@ -10092,13 +10108,13 @@
         <v>500</v>
       </c>
       <c r="F276">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="G276">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H276">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I276">
         <v>1</v>
@@ -10109,10 +10125,10 @@
         <v>12</v>
       </c>
       <c r="B277" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="C277" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D277">
         <v>500</v>
@@ -10121,13 +10137,13 @@
         <v>500</v>
       </c>
       <c r="F277">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="G277">
-        <v>5</v>
+        <v>10000000</v>
       </c>
       <c r="H277">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I277">
         <v>1</v>
@@ -10141,7 +10157,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68B577B-1347-43AB-A697-F4519763B965}">
-  <dimension ref="A1:C123"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -10163,7 +10179,7 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -10174,7 +10190,7 @@
         <v>17</v>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -10185,7 +10201,7 @@
         <v>19</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -10196,7 +10212,7 @@
         <v>21</v>
       </c>
       <c r="C5">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -10207,7 +10223,7 @@
         <v>23</v>
       </c>
       <c r="C6">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -10218,7 +10234,7 @@
         <v>25</v>
       </c>
       <c r="C7">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -10229,7 +10245,7 @@
         <v>27</v>
       </c>
       <c r="C8">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -10240,7 +10256,7 @@
         <v>29</v>
       </c>
       <c r="C9">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -10251,7 +10267,7 @@
         <v>31</v>
       </c>
       <c r="C10">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -10262,7 +10278,7 @@
         <v>33</v>
       </c>
       <c r="C11">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -10273,7 +10289,7 @@
         <v>35</v>
       </c>
       <c r="C12">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -10284,7 +10300,7 @@
         <v>37</v>
       </c>
       <c r="C13">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
@@ -10295,7 +10311,7 @@
         <v>80</v>
       </c>
       <c r="C14">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -10306,7 +10322,7 @@
         <v>39</v>
       </c>
       <c r="C15">
-        <v>100</v>
+        <v>13.677999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -10317,7 +10333,7 @@
         <v>41</v>
       </c>
       <c r="C16">
-        <v>100</v>
+        <v>43.964999999999996</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -10328,7 +10344,7 @@
         <v>43</v>
       </c>
       <c r="C17">
-        <v>100</v>
+        <v>38.102999999999994</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -10339,7 +10355,7 @@
         <v>44</v>
       </c>
       <c r="C18">
-        <v>100</v>
+        <v>129.941</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
@@ -10350,7 +10366,7 @@
         <v>46</v>
       </c>
       <c r="C19">
-        <v>100</v>
+        <v>195.39999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -10361,7 +10377,7 @@
         <v>47</v>
       </c>
       <c r="C20">
-        <v>100</v>
+        <v>1089.355</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -10372,7 +10388,7 @@
         <v>49</v>
       </c>
       <c r="C21">
-        <v>100</v>
+        <v>38.102999999999994</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -10383,7 +10399,7 @@
         <v>50</v>
       </c>
       <c r="C22">
-        <v>100</v>
+        <v>84.998999999999995</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -10394,7 +10410,7 @@
         <v>52</v>
       </c>
       <c r="C23">
-        <v>100</v>
+        <v>6238.1449999999995</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -10405,7 +10421,7 @@
         <v>54</v>
       </c>
       <c r="C24">
-        <v>100</v>
+        <v>18.562999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -10416,7 +10432,7 @@
         <v>56</v>
       </c>
       <c r="C25">
-        <v>100</v>
+        <v>385.91499999999996</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -10427,7 +10443,7 @@
         <v>57</v>
       </c>
       <c r="C26">
-        <v>100</v>
+        <v>185.63</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -10438,7 +10454,7 @@
         <v>38</v>
       </c>
       <c r="C27">
-        <v>-100</v>
+        <v>-708.32499999999993</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
@@ -10449,7 +10465,7 @@
         <v>16</v>
       </c>
       <c r="C28">
-        <v>-100</v>
+        <v>-166.09</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
@@ -10460,7 +10476,7 @@
         <v>28</v>
       </c>
       <c r="C29">
-        <v>-100</v>
+        <v>-357.58199999999999</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -10471,7 +10487,7 @@
         <v>42</v>
       </c>
       <c r="C30">
-        <v>-100</v>
+        <v>-845.10500000000002</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
@@ -10482,7 +10498,7 @@
         <v>60</v>
       </c>
       <c r="C31">
-        <v>-100</v>
+        <v>-83.045000000000002</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
@@ -10493,10 +10509,10 @@
         <v>22</v>
       </c>
       <c r="C32">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-661.42899999999997</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -10504,10 +10520,10 @@
         <v>61</v>
       </c>
       <c r="C33">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-31.263999999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -10515,10 +10531,10 @@
         <v>64</v>
       </c>
       <c r="C34">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -10526,10 +10542,10 @@
         <v>24</v>
       </c>
       <c r="C35">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -10537,10 +10553,10 @@
         <v>18</v>
       </c>
       <c r="C36">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-397.63900000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -10551,7 +10567,7 @@
         <v>-100</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>11</v>
       </c>
@@ -10559,10 +10575,16 @@
         <v>30</v>
       </c>
       <c r="C38">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-211.03200000000001</v>
+      </c>
+      <c r="F38" t="s">
+        <v>81</v>
+      </c>
+      <c r="G38">
+        <v>-10.747</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>11</v>
       </c>
@@ -10570,10 +10592,16 @@
         <v>62</v>
       </c>
       <c r="C39">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-83.045000000000002</v>
+      </c>
+      <c r="F39" t="s">
+        <v>77</v>
+      </c>
+      <c r="G39">
+        <v>-453.32799999999997</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>11</v>
       </c>
@@ -10581,10 +10609,10 @@
         <v>65</v>
       </c>
       <c r="C40">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>11</v>
       </c>
@@ -10592,10 +10620,10 @@
         <v>66</v>
       </c>
       <c r="C41">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-99.653999999999982</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>11</v>
       </c>
@@ -10603,73 +10631,73 @@
         <v>67</v>
       </c>
       <c r="C42">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>11</v>
       </c>
       <c r="B43" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43">
+        <v>-19.54</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" t="s">
         <v>68</v>
       </c>
-      <c r="C43">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>11</v>
-      </c>
-      <c r="B44" t="s">
+      <c r="C44">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" t="s">
         <v>20</v>
       </c>
-      <c r="C44">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>11</v>
-      </c>
-      <c r="B45" t="s">
+      <c r="C45">
+        <v>-55.689</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" t="s">
         <v>51</v>
       </c>
-      <c r="C45">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>11</v>
-      </c>
-      <c r="B46" t="s">
+      <c r="C46">
+        <v>-110.401</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" t="s">
         <v>26</v>
       </c>
-      <c r="C46">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>11</v>
-      </c>
-      <c r="B47" t="s">
+      <c r="C47">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48" t="s">
         <v>72</v>
       </c>
-      <c r="C47">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>11</v>
-      </c>
-      <c r="B48" t="s">
-        <v>34</v>
-      </c>
       <c r="C48">
-        <v>-100</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
@@ -10677,10 +10705,10 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C49">
-        <v>-100</v>
+        <v>-316.54799999999994</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
@@ -10688,10 +10716,10 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C50">
-        <v>-100</v>
+        <v>-58.62</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
@@ -10699,10 +10727,10 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C51">
-        <v>-100</v>
+        <v>-286.26099999999997</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
@@ -10710,10 +10738,10 @@
         <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C52">
-        <v>-100</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
@@ -10721,10 +10749,10 @@
         <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C53">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
@@ -10732,7 +10760,7 @@
         <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -10743,10 +10771,10 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C55">
-        <v>-100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
@@ -10754,10 +10782,10 @@
         <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>-42.988</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
@@ -10765,7 +10793,7 @@
         <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -10776,7 +10804,7 @@
         <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -10787,7 +10815,7 @@
         <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -10798,7 +10826,7 @@
         <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -10809,7 +10837,7 @@
         <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -10817,10 +10845,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -10831,7 +10859,7 @@
         <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -10842,7 +10870,7 @@
         <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -10853,7 +10881,7 @@
         <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -10864,7 +10892,7 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -10875,7 +10903,7 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -10886,7 +10914,7 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -10897,7 +10925,7 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -10908,7 +10936,7 @@
         <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -10919,7 +10947,7 @@
         <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -10930,7 +10958,7 @@
         <v>12</v>
       </c>
       <c r="B72" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -10941,7 +10969,7 @@
         <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -10952,7 +10980,7 @@
         <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -10963,7 +10991,7 @@
         <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -10974,7 +11002,7 @@
         <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -10985,7 +11013,7 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -10996,7 +11024,7 @@
         <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -11007,7 +11035,7 @@
         <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -11018,7 +11046,7 @@
         <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -11029,7 +11057,7 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -11040,7 +11068,7 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -11051,7 +11079,7 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -11062,7 +11090,7 @@
         <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -11073,7 +11101,7 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -11084,7 +11112,7 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -11095,7 +11123,7 @@
         <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -11106,7 +11134,7 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -11117,7 +11145,7 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -11128,7 +11156,7 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -11139,7 +11167,7 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -11150,7 +11178,7 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -11161,7 +11189,7 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -11172,7 +11200,7 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -11183,7 +11211,7 @@
         <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -11194,7 +11222,7 @@
         <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -11205,7 +11233,7 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -11216,7 +11244,7 @@
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -11227,7 +11255,7 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -11238,7 +11266,7 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -11249,7 +11277,7 @@
         <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -11260,7 +11288,7 @@
         <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -11271,7 +11299,7 @@
         <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -11282,7 +11310,7 @@
         <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -11293,7 +11321,7 @@
         <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -11304,7 +11332,7 @@
         <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -11315,7 +11343,7 @@
         <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -11326,7 +11354,7 @@
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -11337,7 +11365,7 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -11348,7 +11376,7 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -11359,7 +11387,7 @@
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -11370,7 +11398,7 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -11381,7 +11409,7 @@
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -11392,7 +11420,7 @@
         <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -11403,7 +11431,7 @@
         <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -11414,7 +11442,7 @@
         <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -11425,7 +11453,7 @@
         <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -11436,7 +11464,7 @@
         <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -11447,7 +11475,7 @@
         <v>12</v>
       </c>
       <c r="B119" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -11458,7 +11486,7 @@
         <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -11469,7 +11497,7 @@
         <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -11477,10 +11505,10 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -11488,12 +11516,34 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B123" t="s">
         <v>69</v>
       </c>
       <c r="C123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>12</v>
+      </c>
+      <c r="B124" t="s">
+        <v>69</v>
+      </c>
+      <c r="C124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>12</v>
+      </c>
+      <c r="B125" t="s">
+        <v>73</v>
+      </c>
+      <c r="C125">
         <v>0</v>
       </c>
     </row>

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAE517D-064C-4547-8345-FC6B9ABED5F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FE2CB3-5DD6-49BE-895E-56F8D0BC7B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="82">
   <si>
     <t>Commodities</t>
   </si>
@@ -983,7 +983,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B140"/>
+  <dimension ref="A1:B138"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -1972,15 +1972,15 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B124" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B125" t="s">
         <v>22</v>
@@ -1988,15 +1988,15 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="B126" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B127" t="s">
         <v>34</v>
@@ -2004,10 +2004,10 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="B128" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
@@ -2015,7 +2015,7 @@
         <v>48</v>
       </c>
       <c r="B129" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
@@ -2023,7 +2023,7 @@
         <v>48</v>
       </c>
       <c r="B130" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
@@ -2031,7 +2031,7 @@
         <v>48</v>
       </c>
       <c r="B131" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
@@ -2039,15 +2039,15 @@
         <v>48</v>
       </c>
       <c r="B132" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B133" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
@@ -2055,7 +2055,7 @@
         <v>38</v>
       </c>
       <c r="B134" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
@@ -2063,47 +2063,31 @@
         <v>38</v>
       </c>
       <c r="B135" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="B136" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
+        <v>20</v>
+      </c>
+      <c r="B137" t="s">
         <v>74</v>
-      </c>
-      <c r="B137" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
+        <v>77</v>
+      </c>
+      <c r="B138" t="s">
         <v>20</v>
-      </c>
-      <c r="B138" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
-        <v>77</v>
-      </c>
-      <c r="B139" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
-        <v>53</v>
-      </c>
-      <c r="B140" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -2113,7 +2097,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
-  <dimension ref="A1:I277"/>
+  <dimension ref="A1:I275"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -5688,13 +5672,13 @@
         <v>11</v>
       </c>
       <c r="B124" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C124" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="D124">
-        <v>80.3</v>
+        <v>180.20050000000001</v>
       </c>
       <c r="E124">
         <v>500</v>
@@ -5717,13 +5701,13 @@
         <v>11</v>
       </c>
       <c r="B125" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C125" t="s">
         <v>22</v>
       </c>
       <c r="D125">
-        <v>180.20050000000001</v>
+        <v>421.21</v>
       </c>
       <c r="E125">
         <v>500</v>
@@ -5746,13 +5730,13 @@
         <v>11</v>
       </c>
       <c r="B126" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="C126" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D126">
-        <v>421.21</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="E126">
         <v>500</v>
@@ -5775,13 +5759,13 @@
         <v>11</v>
       </c>
       <c r="B127" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C127" t="s">
         <v>34</v>
       </c>
       <c r="D127">
-        <v>123.04150000000001</v>
+        <v>161.62200000000001</v>
       </c>
       <c r="E127">
         <v>500</v>
@@ -5804,13 +5788,13 @@
         <v>11</v>
       </c>
       <c r="B128" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C128" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D128">
-        <v>161.62200000000001</v>
+        <v>455.15499999999997</v>
       </c>
       <c r="E128">
         <v>500</v>
@@ -5836,10 +5820,10 @@
         <v>48</v>
       </c>
       <c r="C129" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D129">
-        <v>455.15499999999997</v>
+        <v>351.714</v>
       </c>
       <c r="E129">
         <v>500</v>
@@ -5865,10 +5849,10 @@
         <v>48</v>
       </c>
       <c r="C130" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D130">
-        <v>351.714</v>
+        <v>167.75399999999999</v>
       </c>
       <c r="E130">
         <v>500</v>
@@ -5894,10 +5878,10 @@
         <v>48</v>
       </c>
       <c r="C131" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D131">
-        <v>167.75399999999999</v>
+        <v>207.5025</v>
       </c>
       <c r="E131">
         <v>500</v>
@@ -5923,10 +5907,10 @@
         <v>48</v>
       </c>
       <c r="C132" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D132">
-        <v>207.5025</v>
+        <v>513.19000000000005</v>
       </c>
       <c r="E132">
         <v>500</v>
@@ -5949,13 +5933,13 @@
         <v>11</v>
       </c>
       <c r="B133" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C133" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="D133">
-        <v>513.19000000000005</v>
+        <v>140.52500000000001</v>
       </c>
       <c r="E133">
         <v>500</v>
@@ -5981,10 +5965,10 @@
         <v>38</v>
       </c>
       <c r="C134" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="D134">
-        <v>140.52500000000001</v>
+        <v>82.927999999999997</v>
       </c>
       <c r="E134">
         <v>500</v>
@@ -6010,10 +5994,10 @@
         <v>38</v>
       </c>
       <c r="C135" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D135">
-        <v>82.927999999999997</v>
+        <v>67.451999999999998</v>
       </c>
       <c r="E135">
         <v>500</v>
@@ -6036,16 +6020,16 @@
         <v>11</v>
       </c>
       <c r="B136" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="C136" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D136">
-        <v>67.451999999999998</v>
+        <v>395</v>
       </c>
       <c r="E136">
-        <v>500</v>
+        <v>395</v>
       </c>
       <c r="F136">
         <v>1</v>
@@ -6065,10 +6049,10 @@
         <v>11</v>
       </c>
       <c r="B137" t="s">
+        <v>20</v>
+      </c>
+      <c r="C137" t="s">
         <v>74</v>
-      </c>
-      <c r="C137" t="s">
-        <v>22</v>
       </c>
       <c r="D137">
         <v>395</v>
@@ -6094,10 +6078,10 @@
         <v>11</v>
       </c>
       <c r="B138" t="s">
+        <v>77</v>
+      </c>
+      <c r="C138" t="s">
         <v>20</v>
-      </c>
-      <c r="C138" t="s">
-        <v>74</v>
       </c>
       <c r="D138">
         <v>395</v>
@@ -6120,19 +6104,19 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B139" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="C139" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D139">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="E139">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="F139">
         <v>1</v>
@@ -6141,7 +6125,7 @@
         <v>10000000</v>
       </c>
       <c r="H139">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I139">
         <v>1</v>
@@ -6152,10 +6136,10 @@
         <v>12</v>
       </c>
       <c r="B140" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C140" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D140">
         <v>500</v>
@@ -6181,10 +6165,10 @@
         <v>12</v>
       </c>
       <c r="B141" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C141" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D141">
         <v>500</v>
@@ -6210,10 +6194,10 @@
         <v>12</v>
       </c>
       <c r="B142" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C142" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D142">
         <v>500</v>
@@ -6239,10 +6223,10 @@
         <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C143" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D143">
         <v>500</v>
@@ -6268,10 +6252,10 @@
         <v>12</v>
       </c>
       <c r="B144" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C144" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D144">
         <v>500</v>
@@ -6297,10 +6281,10 @@
         <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C145" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D145">
         <v>500</v>
@@ -6326,10 +6310,10 @@
         <v>12</v>
       </c>
       <c r="B146" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C146" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D146">
         <v>500</v>
@@ -6355,10 +6339,10 @@
         <v>12</v>
       </c>
       <c r="B147" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C147" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D147">
         <v>500</v>
@@ -6384,10 +6368,10 @@
         <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C148" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D148">
         <v>500</v>
@@ -6413,10 +6397,10 @@
         <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C149" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D149">
         <v>500</v>
@@ -6442,10 +6426,10 @@
         <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C150" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D150">
         <v>500</v>
@@ -6471,10 +6455,10 @@
         <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>37</v>
+        <v>80</v>
       </c>
       <c r="C151" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="D151">
         <v>500</v>
@@ -6500,10 +6484,10 @@
         <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="C152" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="D152">
         <v>500</v>
@@ -6529,10 +6513,10 @@
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C153" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D153">
         <v>500</v>
@@ -6558,10 +6542,10 @@
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C154" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D154">
         <v>500</v>
@@ -6587,10 +6571,10 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C155" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="D155">
         <v>500</v>
@@ -6616,10 +6600,10 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C156" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D156">
         <v>500</v>
@@ -6645,10 +6629,10 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C157" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D157">
         <v>500</v>
@@ -6674,10 +6658,10 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C158" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D158">
         <v>500</v>
@@ -6703,10 +6687,10 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C159" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="D159">
         <v>500</v>
@@ -6732,10 +6716,10 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C160" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D160">
         <v>500</v>
@@ -6761,10 +6745,10 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C161" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D161">
         <v>500</v>
@@ -6790,10 +6774,10 @@
         <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C162" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D162">
         <v>500</v>
@@ -6819,10 +6803,10 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C163" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D163">
         <v>500</v>
@@ -6848,10 +6832,10 @@
         <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="C164" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="D164">
         <v>500</v>
@@ -6880,7 +6864,7 @@
         <v>38</v>
       </c>
       <c r="C165" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D165">
         <v>500</v>
@@ -6906,10 +6890,10 @@
         <v>12</v>
       </c>
       <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="s">
         <v>38</v>
-      </c>
-      <c r="C166" t="s">
-        <v>59</v>
       </c>
       <c r="D166">
         <v>500</v>
@@ -6938,7 +6922,7 @@
         <v>16</v>
       </c>
       <c r="C167" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D167">
         <v>500</v>
@@ -6967,7 +6951,7 @@
         <v>16</v>
       </c>
       <c r="C168" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D168">
         <v>500</v>
@@ -6996,7 +6980,7 @@
         <v>16</v>
       </c>
       <c r="C169" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D169">
         <v>500</v>
@@ -7022,10 +7006,10 @@
         <v>12</v>
       </c>
       <c r="B170" t="s">
+        <v>28</v>
+      </c>
+      <c r="C170" t="s">
         <v>16</v>
-      </c>
-      <c r="C170" t="s">
-        <v>18</v>
       </c>
       <c r="D170">
         <v>500</v>
@@ -7054,7 +7038,7 @@
         <v>28</v>
       </c>
       <c r="C171" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="D171">
         <v>500</v>
@@ -7080,10 +7064,10 @@
         <v>12</v>
       </c>
       <c r="B172" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C172" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D172">
         <v>500</v>
@@ -7112,7 +7096,7 @@
         <v>42</v>
       </c>
       <c r="C173" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D173">
         <v>500</v>
@@ -7141,7 +7125,7 @@
         <v>42</v>
       </c>
       <c r="C174" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="D174">
         <v>500</v>
@@ -7170,7 +7154,7 @@
         <v>42</v>
       </c>
       <c r="C175" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D175">
         <v>500</v>
@@ -7199,7 +7183,7 @@
         <v>42</v>
       </c>
       <c r="C176" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D176">
         <v>500</v>
@@ -7228,7 +7212,7 @@
         <v>42</v>
       </c>
       <c r="C177" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D177">
         <v>500</v>
@@ -7257,7 +7241,7 @@
         <v>42</v>
       </c>
       <c r="C178" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D178">
         <v>500</v>
@@ -7286,7 +7270,7 @@
         <v>42</v>
       </c>
       <c r="C179" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="D179">
         <v>500</v>
@@ -7315,7 +7299,7 @@
         <v>42</v>
       </c>
       <c r="C180" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D180">
         <v>500</v>
@@ -7341,10 +7325,10 @@
         <v>12</v>
       </c>
       <c r="B181" t="s">
+        <v>60</v>
+      </c>
+      <c r="C181" t="s">
         <v>42</v>
-      </c>
-      <c r="C181" t="s">
-        <v>63</v>
       </c>
       <c r="D181">
         <v>500</v>
@@ -7373,7 +7357,7 @@
         <v>60</v>
       </c>
       <c r="C182" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D182">
         <v>500</v>
@@ -7402,7 +7386,7 @@
         <v>60</v>
       </c>
       <c r="C183" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="D183">
         <v>500</v>
@@ -7431,7 +7415,7 @@
         <v>60</v>
       </c>
       <c r="C184" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D184">
         <v>500</v>
@@ -7460,7 +7444,7 @@
         <v>60</v>
       </c>
       <c r="C185" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D185">
         <v>500</v>
@@ -7486,10 +7470,10 @@
         <v>12</v>
       </c>
       <c r="B186" t="s">
+        <v>22</v>
+      </c>
+      <c r="C186" t="s">
         <v>60</v>
-      </c>
-      <c r="C186" t="s">
-        <v>66</v>
       </c>
       <c r="D186">
         <v>500</v>
@@ -7518,7 +7502,7 @@
         <v>22</v>
       </c>
       <c r="C187" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D187">
         <v>500</v>
@@ -7547,7 +7531,7 @@
         <v>22</v>
       </c>
       <c r="C188" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D188">
         <v>500</v>
@@ -7573,10 +7557,10 @@
         <v>12</v>
       </c>
       <c r="B189" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="C189" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D189">
         <v>500</v>
@@ -7605,7 +7589,7 @@
         <v>61</v>
       </c>
       <c r="C190" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D190">
         <v>500</v>
@@ -7634,7 +7618,7 @@
         <v>61</v>
       </c>
       <c r="C191" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D191">
         <v>500</v>
@@ -7660,10 +7644,10 @@
         <v>12</v>
       </c>
       <c r="B192" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C192" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D192">
         <v>500</v>
@@ -7692,7 +7676,7 @@
         <v>64</v>
       </c>
       <c r="C193" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D193">
         <v>500</v>
@@ -7718,10 +7702,10 @@
         <v>12</v>
       </c>
       <c r="B194" t="s">
+        <v>24</v>
+      </c>
+      <c r="C194" t="s">
         <v>64</v>
-      </c>
-      <c r="C194" t="s">
-        <v>24</v>
       </c>
       <c r="D194">
         <v>500</v>
@@ -7750,7 +7734,7 @@
         <v>24</v>
       </c>
       <c r="C195" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D195">
         <v>500</v>
@@ -7776,10 +7760,10 @@
         <v>12</v>
       </c>
       <c r="B196" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C196" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="D196">
         <v>500</v>
@@ -7808,7 +7792,7 @@
         <v>18</v>
       </c>
       <c r="C197" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="D197">
         <v>500</v>
@@ -7837,7 +7821,7 @@
         <v>18</v>
       </c>
       <c r="C198" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D198">
         <v>500</v>
@@ -7863,10 +7847,10 @@
         <v>12</v>
       </c>
       <c r="B199" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C199" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D199">
         <v>500</v>
@@ -7892,7 +7876,7 @@
         <v>12</v>
       </c>
       <c r="B200" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C200" t="s">
         <v>42</v>
@@ -7921,7 +7905,7 @@
         <v>12</v>
       </c>
       <c r="B201" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="C201" t="s">
         <v>42</v>
@@ -7953,7 +7937,7 @@
         <v>62</v>
       </c>
       <c r="C202" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D202">
         <v>500</v>
@@ -7982,7 +7966,7 @@
         <v>62</v>
       </c>
       <c r="C203" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D203">
         <v>500</v>
@@ -8008,10 +7992,10 @@
         <v>12</v>
       </c>
       <c r="B204" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C204" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D204">
         <v>500</v>
@@ -8040,7 +8024,7 @@
         <v>65</v>
       </c>
       <c r="C205" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D205">
         <v>500</v>
@@ -8069,7 +8053,7 @@
         <v>65</v>
       </c>
       <c r="C206" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D206">
         <v>500</v>
@@ -8098,7 +8082,7 @@
         <v>65</v>
       </c>
       <c r="C207" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D207">
         <v>500</v>
@@ -8124,10 +8108,10 @@
         <v>12</v>
       </c>
       <c r="B208" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C208" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D208">
         <v>500</v>
@@ -8156,7 +8140,7 @@
         <v>66</v>
       </c>
       <c r="C209" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="D209">
         <v>500</v>
@@ -8185,7 +8169,7 @@
         <v>66</v>
       </c>
       <c r="C210" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D210">
         <v>500</v>
@@ -8214,7 +8198,7 @@
         <v>66</v>
       </c>
       <c r="C211" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="D211">
         <v>500</v>
@@ -8240,10 +8224,10 @@
         <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C212" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D212">
         <v>500</v>
@@ -8272,7 +8256,7 @@
         <v>67</v>
       </c>
       <c r="C213" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D213">
         <v>500</v>
@@ -8298,10 +8282,10 @@
         <v>12</v>
       </c>
       <c r="B214" t="s">
+        <v>68</v>
+      </c>
+      <c r="C214" t="s">
         <v>67</v>
-      </c>
-      <c r="C214" t="s">
-        <v>69</v>
       </c>
       <c r="D214">
         <v>500</v>
@@ -8330,7 +8314,7 @@
         <v>68</v>
       </c>
       <c r="C215" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D215">
         <v>500</v>
@@ -8359,7 +8343,7 @@
         <v>68</v>
       </c>
       <c r="C216" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D216">
         <v>500</v>
@@ -8388,7 +8372,7 @@
         <v>68</v>
       </c>
       <c r="C217" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D217">
         <v>500</v>
@@ -8417,7 +8401,7 @@
         <v>68</v>
       </c>
       <c r="C218" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="D218">
         <v>500</v>
@@ -8443,10 +8427,10 @@
         <v>12</v>
       </c>
       <c r="B219" t="s">
+        <v>20</v>
+      </c>
+      <c r="C219" t="s">
         <v>68</v>
-      </c>
-      <c r="C219" t="s">
-        <v>36</v>
       </c>
       <c r="D219">
         <v>500</v>
@@ -8472,10 +8456,10 @@
         <v>12</v>
       </c>
       <c r="B220" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C220" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D220">
         <v>500</v>
@@ -8504,7 +8488,7 @@
         <v>51</v>
       </c>
       <c r="C221" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D221">
         <v>500</v>
@@ -8533,7 +8517,7 @@
         <v>51</v>
       </c>
       <c r="C222" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D222">
         <v>500</v>
@@ -8562,7 +8546,7 @@
         <v>51</v>
       </c>
       <c r="C223" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D223">
         <v>500</v>
@@ -8588,10 +8572,10 @@
         <v>12</v>
       </c>
       <c r="B224" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C224" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D224">
         <v>500</v>
@@ -8620,7 +8604,7 @@
         <v>26</v>
       </c>
       <c r="C225" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="D225">
         <v>500</v>
@@ -8646,10 +8630,10 @@
         <v>12</v>
       </c>
       <c r="B226" t="s">
+        <v>72</v>
+      </c>
+      <c r="C226" t="s">
         <v>26</v>
-      </c>
-      <c r="C226" t="s">
-        <v>53</v>
       </c>
       <c r="D226">
         <v>500</v>
@@ -8678,7 +8662,7 @@
         <v>72</v>
       </c>
       <c r="C227" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D227">
         <v>500</v>
@@ -8704,10 +8688,10 @@
         <v>12</v>
       </c>
       <c r="B228" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="C228" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D228">
         <v>500</v>
@@ -8736,7 +8720,7 @@
         <v>34</v>
       </c>
       <c r="C229" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D229">
         <v>500</v>
@@ -8762,10 +8746,10 @@
         <v>12</v>
       </c>
       <c r="B230" t="s">
+        <v>32</v>
+      </c>
+      <c r="C230" t="s">
         <v>34</v>
-      </c>
-      <c r="C230" t="s">
-        <v>32</v>
       </c>
       <c r="D230">
         <v>500</v>
@@ -8791,10 +8775,10 @@
         <v>12</v>
       </c>
       <c r="B231" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C231" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D231">
         <v>500</v>
@@ -8823,7 +8807,7 @@
         <v>58</v>
       </c>
       <c r="C232" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D232">
         <v>500</v>
@@ -8852,7 +8836,7 @@
         <v>58</v>
       </c>
       <c r="C233" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D233">
         <v>500</v>
@@ -8881,7 +8865,7 @@
         <v>58</v>
       </c>
       <c r="C234" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="D234">
         <v>500</v>
@@ -8907,7 +8891,7 @@
         <v>12</v>
       </c>
       <c r="B235" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="C235" t="s">
         <v>51</v>
@@ -8936,10 +8920,10 @@
         <v>12</v>
       </c>
       <c r="B236" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C236" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D236">
         <v>500</v>
@@ -8968,7 +8952,7 @@
         <v>53</v>
       </c>
       <c r="C237" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D237">
         <v>500</v>
@@ -8997,7 +8981,7 @@
         <v>53</v>
       </c>
       <c r="C238" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D238">
         <v>500</v>
@@ -9023,10 +9007,10 @@
         <v>12</v>
       </c>
       <c r="B239" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="C239" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="D239">
         <v>500</v>
@@ -9052,10 +9036,10 @@
         <v>12</v>
       </c>
       <c r="B240" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="C240" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D240">
         <v>500</v>
@@ -9084,7 +9068,7 @@
         <v>36</v>
       </c>
       <c r="C241" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="D241">
         <v>500</v>
@@ -9110,10 +9094,10 @@
         <v>12</v>
       </c>
       <c r="B242" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C242" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D242">
         <v>500</v>
@@ -9142,7 +9126,7 @@
         <v>48</v>
       </c>
       <c r="C243" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D243">
         <v>500</v>
@@ -9171,7 +9155,7 @@
         <v>48</v>
       </c>
       <c r="C244" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="D244">
         <v>500</v>
@@ -9200,7 +9184,7 @@
         <v>48</v>
       </c>
       <c r="C245" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D245">
         <v>500</v>
@@ -9226,10 +9210,10 @@
         <v>12</v>
       </c>
       <c r="B246" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="C246" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D246">
         <v>500</v>
@@ -9255,10 +9239,10 @@
         <v>12</v>
       </c>
       <c r="B247" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="C247" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D247">
         <v>500</v>
@@ -9284,7 +9268,7 @@
         <v>12</v>
       </c>
       <c r="B248" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C248" t="s">
         <v>22</v>
@@ -9313,10 +9297,10 @@
         <v>12</v>
       </c>
       <c r="B249" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C249" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D249">
         <v>500</v>
@@ -9345,7 +9329,7 @@
         <v>75</v>
       </c>
       <c r="C250" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D250">
         <v>500</v>
@@ -9371,10 +9355,10 @@
         <v>12</v>
       </c>
       <c r="B251" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="C251" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="D251">
         <v>500</v>
@@ -9400,10 +9384,10 @@
         <v>12</v>
       </c>
       <c r="B252" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C252" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D252">
         <v>500</v>
@@ -9429,10 +9413,10 @@
         <v>12</v>
       </c>
       <c r="B253" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C253" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="D253">
         <v>500</v>
@@ -9461,7 +9445,7 @@
         <v>58</v>
       </c>
       <c r="C254" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D254">
         <v>500</v>
@@ -9490,7 +9474,7 @@
         <v>58</v>
       </c>
       <c r="C255" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D255">
         <v>500</v>
@@ -9516,7 +9500,7 @@
         <v>12</v>
       </c>
       <c r="B256" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C256" t="s">
         <v>66</v>
@@ -9545,10 +9529,10 @@
         <v>12</v>
       </c>
       <c r="B257" t="s">
+        <v>68</v>
+      </c>
+      <c r="C257" t="s">
         <v>67</v>
-      </c>
-      <c r="C257" t="s">
-        <v>66</v>
       </c>
       <c r="D257">
         <v>500</v>
@@ -9577,7 +9561,7 @@
         <v>68</v>
       </c>
       <c r="C258" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D258">
         <v>500</v>
@@ -9603,10 +9587,10 @@
         <v>12</v>
       </c>
       <c r="B259" t="s">
+        <v>36</v>
+      </c>
+      <c r="C259" t="s">
         <v>68</v>
-      </c>
-      <c r="C259" t="s">
-        <v>70</v>
       </c>
       <c r="D259">
         <v>500</v>
@@ -9632,10 +9616,10 @@
         <v>12</v>
       </c>
       <c r="B260" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C260" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D260">
         <v>500</v>
@@ -9661,10 +9645,10 @@
         <v>12</v>
       </c>
       <c r="B261" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C261" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="D261">
         <v>500</v>
@@ -9690,10 +9674,10 @@
         <v>12</v>
       </c>
       <c r="B262" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C262" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="D262">
         <v>500</v>
@@ -9719,10 +9703,10 @@
         <v>12</v>
       </c>
       <c r="B263" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C263" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D263">
         <v>500</v>
@@ -9748,10 +9732,10 @@
         <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C264" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D264">
         <v>500</v>
@@ -9777,10 +9761,10 @@
         <v>12</v>
       </c>
       <c r="B265" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="C265" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D265">
         <v>500</v>
@@ -9806,10 +9790,10 @@
         <v>12</v>
       </c>
       <c r="B266" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C266" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D266">
         <v>500</v>
@@ -9838,7 +9822,7 @@
         <v>48</v>
       </c>
       <c r="C267" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D267">
         <v>500</v>
@@ -9867,7 +9851,7 @@
         <v>48</v>
       </c>
       <c r="C268" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D268">
         <v>500</v>
@@ -9896,7 +9880,7 @@
         <v>48</v>
       </c>
       <c r="C269" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D269">
         <v>500</v>
@@ -9922,10 +9906,10 @@
         <v>12</v>
       </c>
       <c r="B270" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C270" t="s">
-        <v>18</v>
+        <v>79</v>
       </c>
       <c r="D270">
         <v>500</v>
@@ -9951,10 +9935,10 @@
         <v>12</v>
       </c>
       <c r="B271" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C271" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D271">
         <v>500</v>
@@ -9983,7 +9967,7 @@
         <v>38</v>
       </c>
       <c r="C272" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="D272">
         <v>500</v>
@@ -10009,10 +9993,10 @@
         <v>12</v>
       </c>
       <c r="B273" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="C273" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D273">
         <v>500</v>
@@ -10038,10 +10022,10 @@
         <v>12</v>
       </c>
       <c r="B274" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C274" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="D274">
         <v>500</v>
@@ -10067,10 +10051,10 @@
         <v>12</v>
       </c>
       <c r="B275" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C275" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D275">
         <v>500</v>
@@ -10088,64 +10072,6 @@
         <v>1000</v>
       </c>
       <c r="I275">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A276" t="s">
-        <v>12</v>
-      </c>
-      <c r="B276" t="s">
-        <v>20</v>
-      </c>
-      <c r="C276" t="s">
-        <v>74</v>
-      </c>
-      <c r="D276">
-        <v>500</v>
-      </c>
-      <c r="E276">
-        <v>500</v>
-      </c>
-      <c r="F276">
-        <v>1</v>
-      </c>
-      <c r="G276">
-        <v>10000000</v>
-      </c>
-      <c r="H276">
-        <v>1000</v>
-      </c>
-      <c r="I276">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A277" t="s">
-        <v>12</v>
-      </c>
-      <c r="B277" t="s">
-        <v>77</v>
-      </c>
-      <c r="C277" t="s">
-        <v>20</v>
-      </c>
-      <c r="D277">
-        <v>500</v>
-      </c>
-      <c r="E277">
-        <v>500</v>
-      </c>
-      <c r="F277">
-        <v>1</v>
-      </c>
-      <c r="G277">
-        <v>10000000</v>
-      </c>
-      <c r="H277">
-        <v>1000</v>
-      </c>
-      <c r="I277">
         <v>1</v>
       </c>
     </row>

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FE2CB3-5DD6-49BE-895E-56F8D0BC7B55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F33ECF1-A089-4749-A056-AEFBEFD9B9AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F33ECF1-A089-4749-A056-AEFBEFD9B9AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0496360A-C275-4DAC-8138-12AE6D08D54C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1424" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="99">
   <si>
     <t>Commodities</t>
   </si>
@@ -286,6 +286,57 @@
   </si>
   <si>
     <t>SE</t>
+  </si>
+  <si>
+    <t>AL_Prod</t>
+  </si>
+  <si>
+    <t>DZ_Prod</t>
+  </si>
+  <si>
+    <t>DZ</t>
+  </si>
+  <si>
+    <t>AT_Prod</t>
+  </si>
+  <si>
+    <t>BE_Prod</t>
+  </si>
+  <si>
+    <t>BG_Prod</t>
+  </si>
+  <si>
+    <t>HR_Prod</t>
+  </si>
+  <si>
+    <t>CZ_Prod</t>
+  </si>
+  <si>
+    <t>FR_Prod</t>
+  </si>
+  <si>
+    <t>GR_Prod</t>
+  </si>
+  <si>
+    <t>HU_Prod</t>
+  </si>
+  <si>
+    <t>IE_Prod</t>
+  </si>
+  <si>
+    <t>RS_Prod</t>
+  </si>
+  <si>
+    <t>SK_Prod</t>
+  </si>
+  <si>
+    <t>SI_Prod</t>
+  </si>
+  <si>
+    <t>TR_Prod</t>
+  </si>
+  <si>
+    <t>ES_Prod</t>
   </si>
 </sst>
 </file>
@@ -643,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0CB446-BDDD-415D-AF22-2CEB1FE45CA5}">
-  <dimension ref="A1:A61"/>
+  <dimension ref="A1:A78"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -949,6 +1000,91 @@
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -983,7 +1119,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B138"/>
+  <dimension ref="A1:B154"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -1988,7 +2124,7 @@
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B126" t="s">
         <v>34</v>
@@ -2088,6 +2224,134 @@
       </c>
       <c r="B138" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>82</v>
+      </c>
+      <c r="B139" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>83</v>
+      </c>
+      <c r="B140" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>85</v>
+      </c>
+      <c r="B141" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>86</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>87</v>
+      </c>
+      <c r="B143" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>88</v>
+      </c>
+      <c r="B144" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>89</v>
+      </c>
+      <c r="B145" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>90</v>
+      </c>
+      <c r="B146" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>91</v>
+      </c>
+      <c r="B147" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>92</v>
+      </c>
+      <c r="B148" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>93</v>
+      </c>
+      <c r="B149" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>94</v>
+      </c>
+      <c r="B150" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>95</v>
+      </c>
+      <c r="B151" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>96</v>
+      </c>
+      <c r="B152" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>97</v>
+      </c>
+      <c r="B153" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>98</v>
+      </c>
+      <c r="B154" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -10083,7 +10347,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68B577B-1347-43AB-A697-F4519763B965}">
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -10245,10 +10509,10 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>82</v>
       </c>
       <c r="C15">
-        <v>13.677999999999999</v>
+        <v>0.55586415</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -10256,10 +10520,10 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="C16">
-        <v>43.964999999999996</v>
+        <v>796.255</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -10267,10 +10531,10 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="C17">
-        <v>38.102999999999994</v>
+        <v>7.5617455199999997</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -10278,10 +10542,10 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="C18">
-        <v>129.941</v>
+        <v>5.7643000000000007E-2</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
@@ -10289,10 +10553,10 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="C19">
-        <v>195.39999999999998</v>
+        <v>0.53100926999999998</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -10300,10 +10564,10 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="C20">
-        <v>1089.355</v>
+        <v>8.6795214499999993</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -10311,10 +10575,10 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="C21">
-        <v>38.102999999999994</v>
+        <v>1.9156527500000002</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -10322,10 +10586,10 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="C22">
-        <v>84.998999999999995</v>
+        <v>0.16949973000000002</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -10333,10 +10597,10 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="C23">
-        <v>6238.1449999999995</v>
+        <v>6.3309600000000021E-2</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -10344,10 +10608,10 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="C24">
-        <v>18.562999999999999</v>
+        <v>16.46245</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -10355,10 +10619,10 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="C25">
-        <v>385.91499999999996</v>
+        <v>19.829690269999997</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -10366,10 +10630,10 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="C26">
-        <v>185.63</v>
+        <v>3.9959299999999995</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -10377,10 +10641,10 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="C27">
-        <v>-708.32499999999993</v>
+        <v>0.6516687699999999</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
@@ -10388,10 +10652,10 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="C28">
-        <v>-166.09</v>
+        <v>5.2113180000000002E-2</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
@@ -10399,10 +10663,10 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="C29">
-        <v>-357.58199999999999</v>
+        <v>4.2744726999999996</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -10410,10 +10674,10 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="C30">
-        <v>-845.10500000000002</v>
+        <v>0.44941999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
@@ -10421,10 +10685,10 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="C31">
-        <v>-83.045000000000002</v>
+        <v>13.947075569999997</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
@@ -10432,426 +10696,426 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32">
+        <v>47.618979999999993</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33">
+        <v>38.415639999999996</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" t="s">
+        <v>44</v>
+      </c>
+      <c r="C34">
+        <v>129.941</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35">
+        <v>234.14902171</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36">
+        <v>1135.3337630899998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37">
+        <v>54.642437600000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38">
+        <v>88.09608999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39">
+        <v>6238.1449999999995</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40">
+        <v>18.562999999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41">
+        <v>320.81311303999996</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" t="s">
+        <v>57</v>
+      </c>
+      <c r="C42">
+        <v>190.67131999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43">
+        <v>-708.32499999999993</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44">
+        <v>-166.09</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" t="s">
+        <v>28</v>
+      </c>
+      <c r="C45">
+        <v>-357.58199999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" t="s">
+        <v>42</v>
+      </c>
+      <c r="C46">
+        <v>-845.10500000000002</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47">
+        <v>-83.045000000000002</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48" t="s">
         <v>22</v>
       </c>
-      <c r="C32">
+      <c r="C48">
         <v>-661.42899999999997</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>11</v>
-      </c>
-      <c r="B33" t="s">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49" t="s">
         <v>61</v>
       </c>
-      <c r="C33">
+      <c r="C49">
         <v>-31.263999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>11</v>
-      </c>
-      <c r="B34" t="s">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" t="s">
         <v>64</v>
       </c>
-      <c r="C34">
+      <c r="C50">
         <v>-30</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>11</v>
-      </c>
-      <c r="B35" t="s">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" t="s">
         <v>24</v>
       </c>
-      <c r="C35">
+      <c r="C51">
         <v>-50</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>11</v>
-      </c>
-      <c r="B36" t="s">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" t="s">
         <v>18</v>
       </c>
-      <c r="C36">
+      <c r="C52">
         <v>-397.63900000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>11</v>
-      </c>
-      <c r="B37" t="s">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53" t="s">
         <v>40</v>
       </c>
-      <c r="C37">
+      <c r="C53">
         <v>-100</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>11</v>
-      </c>
-      <c r="B38" t="s">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" t="s">
         <v>30</v>
       </c>
-      <c r="C38">
+      <c r="C54">
         <v>-211.03200000000001</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F54" t="s">
         <v>81</v>
       </c>
-      <c r="G38">
+      <c r="G54">
         <v>-10.747</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>11</v>
-      </c>
-      <c r="B39" t="s">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>11</v>
+      </c>
+      <c r="B55" t="s">
         <v>62</v>
       </c>
-      <c r="C39">
+      <c r="C55">
         <v>-83.045000000000002</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F55" t="s">
         <v>77</v>
       </c>
-      <c r="G39">
+      <c r="G55">
         <v>-453.32799999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>11</v>
-      </c>
-      <c r="B40" t="s">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" t="s">
         <v>65</v>
       </c>
-      <c r="C40">
+      <c r="C56">
         <v>-30</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>11</v>
-      </c>
-      <c r="B41" t="s">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" t="s">
         <v>66</v>
       </c>
-      <c r="C41">
+      <c r="C57">
         <v>-99.653999999999982</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>11</v>
-      </c>
-      <c r="B42" t="s">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" t="s">
         <v>67</v>
       </c>
-      <c r="C42">
+      <c r="C58">
         <v>-30</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>11</v>
-      </c>
-      <c r="B43" t="s">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" t="s">
         <v>73</v>
       </c>
-      <c r="C43">
+      <c r="C59">
         <v>-19.54</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>11</v>
-      </c>
-      <c r="B44" t="s">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" t="s">
         <v>68</v>
       </c>
-      <c r="C44">
+      <c r="C60">
         <v>-50</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>11</v>
-      </c>
-      <c r="B45" t="s">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61" t="s">
         <v>20</v>
       </c>
-      <c r="C45">
+      <c r="C61">
         <v>-55.689</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>11</v>
-      </c>
-      <c r="B46" t="s">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" t="s">
         <v>51</v>
       </c>
-      <c r="C46">
+      <c r="C62">
         <v>-110.401</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>11</v>
-      </c>
-      <c r="B47" t="s">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" t="s">
         <v>26</v>
       </c>
-      <c r="C47">
+      <c r="C63">
         <v>-20</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>11</v>
-      </c>
-      <c r="B48" t="s">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>11</v>
+      </c>
+      <c r="B64" t="s">
         <v>72</v>
       </c>
-      <c r="C48">
+      <c r="C64">
         <v>-20</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>11</v>
-      </c>
-      <c r="B49" t="s">
-        <v>34</v>
-      </c>
-      <c r="C49">
-        <v>-316.54799999999994</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>11</v>
-      </c>
-      <c r="B50" t="s">
-        <v>32</v>
-      </c>
-      <c r="C50">
-        <v>-58.62</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>11</v>
-      </c>
-      <c r="B51" t="s">
-        <v>58</v>
-      </c>
-      <c r="C51">
-        <v>-286.26099999999997</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>11</v>
-      </c>
-      <c r="B52" t="s">
-        <v>71</v>
-      </c>
-      <c r="C52">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>11</v>
-      </c>
-      <c r="B53" t="s">
-        <v>53</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>11</v>
-      </c>
-      <c r="B54" t="s">
-        <v>74</v>
-      </c>
-      <c r="C54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>11</v>
-      </c>
-      <c r="B55" t="s">
-        <v>36</v>
-      </c>
-      <c r="C55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>11</v>
-      </c>
-      <c r="B56" t="s">
-        <v>48</v>
-      </c>
-      <c r="C56">
-        <v>-42.988</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>11</v>
-      </c>
-      <c r="B57" t="s">
-        <v>78</v>
-      </c>
-      <c r="C57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>11</v>
-      </c>
-      <c r="B58" t="s">
-        <v>55</v>
-      </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>11</v>
-      </c>
-      <c r="B59" t="s">
-        <v>45</v>
-      </c>
-      <c r="C59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>11</v>
-      </c>
-      <c r="B60" t="s">
-        <v>75</v>
-      </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>11</v>
-      </c>
-      <c r="B61" t="s">
-        <v>76</v>
-      </c>
-      <c r="C61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>11</v>
-      </c>
-      <c r="B62" t="s">
-        <v>78</v>
-      </c>
-      <c r="C62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>12</v>
-      </c>
-      <c r="B63" t="s">
-        <v>15</v>
-      </c>
-      <c r="C63">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>12</v>
-      </c>
-      <c r="B64" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64">
-        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>-316.54799999999994</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B66" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>-58.62</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>-286.26099999999997</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -10859,10 +11123,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -10870,10 +11134,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B71" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -10881,21 +11145,21 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B72" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>-42.988</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -10903,10 +11167,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B74" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -10914,10 +11178,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -10925,10 +11189,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B76" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -10936,10 +11200,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B77" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -10947,10 +11211,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B78" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -10961,7 +11225,7 @@
         <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -10972,7 +11236,7 @@
         <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -10983,7 +11247,7 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -10994,7 +11258,7 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -11005,7 +11269,7 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -11016,7 +11280,7 @@
         <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -11027,7 +11291,7 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -11038,7 +11302,7 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -11049,7 +11313,7 @@
         <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -11060,7 +11324,7 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -11071,7 +11335,7 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -11082,7 +11346,7 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -11093,7 +11357,7 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -11104,7 +11368,7 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>60</v>
+        <v>39</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -11115,7 +11379,7 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -11126,7 +11390,7 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -11137,7 +11401,7 @@
         <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -11148,7 +11412,7 @@
         <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -11159,7 +11423,7 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -11170,7 +11434,7 @@
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -11181,7 +11445,7 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -11192,7 +11456,7 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -11203,7 +11467,7 @@
         <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -11214,7 +11478,7 @@
         <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -11225,7 +11489,7 @@
         <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -11236,7 +11500,7 @@
         <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -11247,7 +11511,7 @@
         <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -11258,7 +11522,7 @@
         <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -11269,7 +11533,7 @@
         <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -11280,7 +11544,7 @@
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -11291,7 +11555,7 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -11302,7 +11566,7 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -11313,7 +11577,7 @@
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -11324,7 +11588,7 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -11335,7 +11599,7 @@
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -11346,7 +11610,7 @@
         <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -11357,7 +11621,7 @@
         <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -11368,7 +11632,7 @@
         <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -11379,7 +11643,7 @@
         <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -11390,7 +11654,7 @@
         <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -11401,7 +11665,7 @@
         <v>12</v>
       </c>
       <c r="B119" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -11412,7 +11676,7 @@
         <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -11423,7 +11687,7 @@
         <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -11434,7 +11698,7 @@
         <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -11442,10 +11706,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B123" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -11456,7 +11720,7 @@
         <v>12</v>
       </c>
       <c r="B124" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -11467,9 +11731,361 @@
         <v>12</v>
       </c>
       <c r="B125" t="s">
+        <v>34</v>
+      </c>
+      <c r="C125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>12</v>
+      </c>
+      <c r="B126" t="s">
+        <v>32</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>12</v>
+      </c>
+      <c r="B127" t="s">
+        <v>58</v>
+      </c>
+      <c r="C127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>12</v>
+      </c>
+      <c r="B128" t="s">
+        <v>71</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>12</v>
+      </c>
+      <c r="B129" t="s">
+        <v>53</v>
+      </c>
+      <c r="C129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>12</v>
+      </c>
+      <c r="B130" t="s">
+        <v>74</v>
+      </c>
+      <c r="C130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>12</v>
+      </c>
+      <c r="B131" t="s">
+        <v>36</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>12</v>
+      </c>
+      <c r="B132" t="s">
+        <v>48</v>
+      </c>
+      <c r="C132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>12</v>
+      </c>
+      <c r="B133" t="s">
+        <v>78</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>12</v>
+      </c>
+      <c r="B134" t="s">
+        <v>55</v>
+      </c>
+      <c r="C134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>12</v>
+      </c>
+      <c r="B135" t="s">
+        <v>45</v>
+      </c>
+      <c r="C135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>12</v>
+      </c>
+      <c r="B136" t="s">
+        <v>75</v>
+      </c>
+      <c r="C136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>12</v>
+      </c>
+      <c r="B137" t="s">
+        <v>76</v>
+      </c>
+      <c r="C137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>12</v>
+      </c>
+      <c r="B138" t="s">
+        <v>78</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>11</v>
+      </c>
+      <c r="B139" t="s">
+        <v>69</v>
+      </c>
+      <c r="C139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>12</v>
+      </c>
+      <c r="B140" t="s">
+        <v>69</v>
+      </c>
+      <c r="C140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>12</v>
+      </c>
+      <c r="B141" t="s">
         <v>73</v>
       </c>
-      <c r="C125">
+      <c r="C141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>12</v>
+      </c>
+      <c r="B142" t="s">
+        <v>82</v>
+      </c>
+      <c r="C142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>12</v>
+      </c>
+      <c r="B143" t="s">
+        <v>83</v>
+      </c>
+      <c r="C143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>12</v>
+      </c>
+      <c r="B144" t="s">
+        <v>85</v>
+      </c>
+      <c r="C144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>12</v>
+      </c>
+      <c r="B145" t="s">
+        <v>86</v>
+      </c>
+      <c r="C145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>12</v>
+      </c>
+      <c r="B146" t="s">
+        <v>87</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>12</v>
+      </c>
+      <c r="B147" t="s">
+        <v>88</v>
+      </c>
+      <c r="C147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>12</v>
+      </c>
+      <c r="B148" t="s">
+        <v>89</v>
+      </c>
+      <c r="C148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>12</v>
+      </c>
+      <c r="B149" t="s">
+        <v>90</v>
+      </c>
+      <c r="C149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>12</v>
+      </c>
+      <c r="B150" t="s">
+        <v>91</v>
+      </c>
+      <c r="C150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>12</v>
+      </c>
+      <c r="B151" t="s">
+        <v>92</v>
+      </c>
+      <c r="C151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>12</v>
+      </c>
+      <c r="B152" t="s">
+        <v>93</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>12</v>
+      </c>
+      <c r="B153" t="s">
+        <v>94</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>12</v>
+      </c>
+      <c r="B154" t="s">
+        <v>95</v>
+      </c>
+      <c r="C154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>12</v>
+      </c>
+      <c r="B155" t="s">
+        <v>96</v>
+      </c>
+      <c r="C155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>12</v>
+      </c>
+      <c r="B156" t="s">
+        <v>97</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>12</v>
+      </c>
+      <c r="B157" t="s">
+        <v>98</v>
+      </c>
+      <c r="C157">
         <v>0</v>
       </c>
     </row>

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0496360A-C275-4DAC-8138-12AE6D08D54C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6584178-130D-4F54-9B44-93BAE78B7206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="99">
   <si>
     <t>Commodities</t>
   </si>
@@ -2361,7 +2361,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
-  <dimension ref="A1:I275"/>
+  <dimension ref="A1:I307"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -2746,10 +2746,10 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D14">
         <v>10000</v>
@@ -2758,7 +2758,7 @@
         <v>10000</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G14">
         <v>10000000</v>
@@ -2775,10 +2775,10 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="D15">
         <v>10000</v>
@@ -2787,7 +2787,7 @@
         <v>10000</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G15">
         <v>10000000</v>
@@ -2804,10 +2804,10 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D16">
         <v>10000</v>
@@ -2816,7 +2816,7 @@
         <v>10000</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G16">
         <v>10000000</v>
@@ -2833,10 +2833,10 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D17">
         <v>10000</v>
@@ -2845,7 +2845,7 @@
         <v>10000</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G17">
         <v>10000000</v>
@@ -2862,10 +2862,10 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="D18">
         <v>10000</v>
@@ -2874,7 +2874,7 @@
         <v>10000</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G18">
         <v>10000000</v>
@@ -2891,10 +2891,10 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D19">
         <v>10000</v>
@@ -2903,7 +2903,7 @@
         <v>10000</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G19">
         <v>10000000</v>
@@ -2920,10 +2920,10 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="D20">
         <v>10000</v>
@@ -2932,7 +2932,7 @@
         <v>10000</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G20">
         <v>10000000</v>
@@ -2949,10 +2949,10 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D21">
         <v>10000</v>
@@ -2961,7 +2961,7 @@
         <v>10000</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G21">
         <v>10000000</v>
@@ -2978,10 +2978,10 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="D22">
         <v>10000</v>
@@ -2990,7 +2990,7 @@
         <v>10000</v>
       </c>
       <c r="F22">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G22">
         <v>10000000</v>
@@ -3007,10 +3007,10 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D23">
         <v>10000</v>
@@ -3019,7 +3019,7 @@
         <v>10000</v>
       </c>
       <c r="F23">
-        <v>10000</v>
+        <v>100</v>
       </c>
       <c r="G23">
         <v>10000000</v>
@@ -3036,10 +3036,10 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D24">
         <v>10000</v>
@@ -3048,7 +3048,7 @@
         <v>10000</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G24">
         <v>10000000</v>
@@ -3065,10 +3065,10 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D25">
         <v>10000</v>
@@ -3077,7 +3077,7 @@
         <v>10000</v>
       </c>
       <c r="F25">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G25">
         <v>10000000</v>
@@ -3094,10 +3094,10 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D26">
         <v>10000</v>
@@ -3106,7 +3106,7 @@
         <v>10000</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G26">
         <v>10000000</v>
@@ -3123,19 +3123,19 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="D27">
-        <v>237.87050000000002</v>
+        <v>10000</v>
       </c>
       <c r="E27">
-        <v>237.87050000000002</v>
+        <v>10000</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G27">
         <v>10000000</v>
@@ -3152,19 +3152,19 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D28">
-        <v>141.21850000000001</v>
+        <v>10000</v>
       </c>
       <c r="E28">
-        <v>141.21850000000001</v>
+        <v>10000</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G28">
         <v>10000000</v>
@@ -3181,19 +3181,19 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D29">
-        <v>293.24099999999999</v>
+        <v>10000</v>
       </c>
       <c r="E29">
-        <v>293.24099999999999</v>
+        <v>10000</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G29">
         <v>10000000</v>
@@ -3210,16 +3210,16 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="D30">
-        <v>120.88800000000001</v>
+        <v>10000</v>
       </c>
       <c r="E30">
-        <v>120.88800000000001</v>
+        <v>10000</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -3239,16 +3239,16 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C31" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D31">
-        <v>117.81104999999999</v>
+        <v>10000</v>
       </c>
       <c r="E31">
-        <v>117.81104999999999</v>
+        <v>10000</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -3268,16 +3268,16 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C32" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D32">
-        <v>317.55</v>
+        <v>10000</v>
       </c>
       <c r="E32">
-        <v>317.55</v>
+        <v>10000</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -3297,16 +3297,16 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C33" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D33">
-        <v>509.97800000000001</v>
+        <v>10000</v>
       </c>
       <c r="E33">
-        <v>509.97800000000001</v>
+        <v>10000</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -3326,16 +3326,16 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D34">
-        <v>702.90714500000001</v>
+        <v>10000</v>
       </c>
       <c r="E34">
-        <v>702.90714500000001</v>
+        <v>10000</v>
       </c>
       <c r="F34">
         <v>1</v>
@@ -3355,16 +3355,16 @@
         <v>11</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C35" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D35">
-        <v>144.59475</v>
+        <v>10000</v>
       </c>
       <c r="E35">
-        <v>144.59475</v>
+        <v>10000</v>
       </c>
       <c r="F35">
         <v>1</v>
@@ -3384,16 +3384,16 @@
         <v>11</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D36">
-        <v>594.33059500000013</v>
+        <v>10000</v>
       </c>
       <c r="E36">
-        <v>594.33059500000013</v>
+        <v>10000</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -3413,16 +3413,16 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D37">
-        <v>125.65051999999997</v>
+        <v>10000</v>
       </c>
       <c r="E37">
-        <v>125.65051999999997</v>
+        <v>10000</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -3442,16 +3442,16 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D38">
-        <v>119.72</v>
+        <v>10000</v>
       </c>
       <c r="E38">
-        <v>119.72</v>
+        <v>10000</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -3471,19 +3471,19 @@
         <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D39">
-        <v>224.00633999999999</v>
+        <v>10000</v>
       </c>
       <c r="E39">
-        <v>224.00633999999999</v>
+        <v>10000</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="G39">
         <v>10000000</v>
@@ -3500,16 +3500,16 @@
         <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C40" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D40">
-        <v>49.680879999999995</v>
+        <v>10000</v>
       </c>
       <c r="E40">
-        <v>49.680879999999995</v>
+        <v>10000</v>
       </c>
       <c r="F40">
         <v>1</v>
@@ -3529,16 +3529,16 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C41" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D41">
-        <v>85.227500000000006</v>
+        <v>10000</v>
       </c>
       <c r="E41">
-        <v>85.227500000000006</v>
+        <v>10000</v>
       </c>
       <c r="F41">
         <v>1</v>
@@ -3558,16 +3558,16 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C42" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D42">
-        <v>658.37605000000008</v>
+        <v>10000</v>
       </c>
       <c r="E42">
-        <v>658.37605000000008</v>
+        <v>10000</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -3587,16 +3587,16 @@
         <v>11</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C43" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="D43">
-        <v>9.7491500000000002</v>
+        <v>237.87050000000002</v>
       </c>
       <c r="E43">
-        <v>9.7491500000000002</v>
+        <v>237.87050000000002</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -3616,16 +3616,16 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="C44" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D44">
-        <v>124.08832</v>
+        <v>141.21850000000001</v>
       </c>
       <c r="E44">
-        <v>124.08832</v>
+        <v>141.21850000000001</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -3645,16 +3645,16 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="C45" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D45">
-        <v>419.75</v>
+        <v>293.24099999999999</v>
       </c>
       <c r="E45">
-        <v>419.75</v>
+        <v>293.24099999999999</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -3674,16 +3674,16 @@
         <v>11</v>
       </c>
       <c r="B46" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="C46" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="D46">
-        <v>41.0625</v>
+        <v>120.88800000000001</v>
       </c>
       <c r="E46">
-        <v>41.0625</v>
+        <v>120.88800000000001</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -3703,16 +3703,16 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="C47" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="D47">
-        <v>89.972499999999997</v>
+        <v>117.81104999999999</v>
       </c>
       <c r="E47">
-        <v>89.972499999999997</v>
+        <v>117.81104999999999</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -3732,16 +3732,16 @@
         <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="C48" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="D48">
-        <v>55.881500000000003</v>
+        <v>317.55</v>
       </c>
       <c r="E48">
-        <v>55.881500000000003</v>
+        <v>317.55</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -3761,16 +3761,16 @@
         <v>11</v>
       </c>
       <c r="B49" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C49" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="D49">
-        <v>70.627499999999998</v>
+        <v>509.97800000000001</v>
       </c>
       <c r="E49">
-        <v>70.627499999999998</v>
+        <v>509.97800000000001</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -3790,16 +3790,16 @@
         <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C50" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D50">
-        <v>157.46100000000001</v>
+        <v>702.90714500000001</v>
       </c>
       <c r="E50">
-        <v>157.46100000000001</v>
+        <v>702.90714500000001</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -3819,16 +3819,16 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C51" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="D51">
-        <v>10.4025</v>
+        <v>144.59475</v>
       </c>
       <c r="E51">
-        <v>10.4025</v>
+        <v>144.59475</v>
       </c>
       <c r="F51">
         <v>1</v>
@@ -3848,16 +3848,16 @@
         <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C52" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D52">
-        <v>63.07200000000001</v>
+        <v>594.33059500000013</v>
       </c>
       <c r="E52">
-        <v>63.07200000000001</v>
+        <v>594.33059500000013</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -3877,16 +3877,16 @@
         <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C53" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D53">
-        <v>233.74600000000001</v>
+        <v>125.65051999999997</v>
       </c>
       <c r="E53">
-        <v>233.74600000000001</v>
+        <v>125.65051999999997</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -3906,16 +3906,16 @@
         <v>11</v>
       </c>
       <c r="B54" t="s">
+        <v>42</v>
+      </c>
+      <c r="C54" t="s">
         <v>61</v>
       </c>
-      <c r="C54" t="s">
-        <v>18</v>
-      </c>
       <c r="D54">
-        <v>36.5</v>
+        <v>119.72</v>
       </c>
       <c r="E54">
-        <v>36.5</v>
+        <v>119.72</v>
       </c>
       <c r="F54">
         <v>1</v>
@@ -3935,16 +3935,16 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="C55" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D55">
-        <v>7.8475000000000001</v>
+        <v>224.00633999999999</v>
       </c>
       <c r="E55">
-        <v>7.8475000000000001</v>
+        <v>224.00633999999999</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -3964,16 +3964,16 @@
         <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="C56" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D56">
-        <v>19.6005</v>
+        <v>49.680879999999995</v>
       </c>
       <c r="E56">
-        <v>19.6005</v>
+        <v>49.680879999999995</v>
       </c>
       <c r="F56">
         <v>1</v>
@@ -3993,16 +3993,16 @@
         <v>11</v>
       </c>
       <c r="B57" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C57" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="D57">
-        <v>2.8105000000000002</v>
+        <v>85.227500000000006</v>
       </c>
       <c r="E57">
-        <v>2.8105000000000002</v>
+        <v>85.227500000000006</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -4022,16 +4022,16 @@
         <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C58" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D58">
-        <v>17.72805</v>
+        <v>658.37605000000008</v>
       </c>
       <c r="E58">
-        <v>17.72805</v>
+        <v>658.37605000000008</v>
       </c>
       <c r="F58">
         <v>1</v>
@@ -4051,16 +4051,16 @@
         <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C59" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="D59">
-        <v>98.55</v>
+        <v>9.7491500000000002</v>
       </c>
       <c r="E59">
-        <v>98.55</v>
+        <v>9.7491500000000002</v>
       </c>
       <c r="F59">
         <v>1</v>
@@ -4080,16 +4080,16 @@
         <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="C60" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D60">
-        <v>81.394999999999996</v>
+        <v>124.08832</v>
       </c>
       <c r="E60">
-        <v>81.394999999999996</v>
+        <v>124.08832</v>
       </c>
       <c r="F60">
         <v>1</v>
@@ -4109,16 +4109,16 @@
         <v>11</v>
       </c>
       <c r="B61" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="C61" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D61">
-        <v>60.068779999999997</v>
+        <v>419.75</v>
       </c>
       <c r="E61">
-        <v>60.068779999999997</v>
+        <v>419.75</v>
       </c>
       <c r="F61">
         <v>1</v>
@@ -4138,16 +4138,16 @@
         <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D62">
-        <v>1.5034349999999999</v>
+        <v>41.0625</v>
       </c>
       <c r="E62">
-        <v>1.5034349999999999</v>
+        <v>41.0625</v>
       </c>
       <c r="F62">
         <v>1</v>
@@ -4167,16 +4167,16 @@
         <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C63" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D63">
-        <v>340.03399999999999</v>
+        <v>89.972499999999997</v>
       </c>
       <c r="E63">
-        <v>340.03399999999999</v>
+        <v>89.972499999999997</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -4196,16 +4196,16 @@
         <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C64" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D64">
-        <v>449.59203500000001</v>
+        <v>55.881500000000003</v>
       </c>
       <c r="E64">
-        <v>449.59203500000001</v>
+        <v>55.881500000000003</v>
       </c>
       <c r="F64">
         <v>1</v>
@@ -4225,16 +4225,16 @@
         <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="C65" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D65">
-        <v>10.220000000000001</v>
+        <v>70.627499999999998</v>
       </c>
       <c r="E65">
-        <v>10.220000000000001</v>
+        <v>70.627499999999998</v>
       </c>
       <c r="F65">
         <v>1</v>
@@ -4254,16 +4254,16 @@
         <v>11</v>
       </c>
       <c r="B66" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="C66" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D66">
-        <v>454.93600000000004</v>
+        <v>157.46100000000001</v>
       </c>
       <c r="E66">
-        <v>454.93600000000004</v>
+        <v>157.46100000000001</v>
       </c>
       <c r="F66">
         <v>1</v>
@@ -4283,16 +4283,16 @@
         <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="C67" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D67">
-        <v>573.19600000000003</v>
+        <v>10.4025</v>
       </c>
       <c r="E67">
-        <v>573.19600000000003</v>
+        <v>10.4025</v>
       </c>
       <c r="F67">
         <v>1</v>
@@ -4312,16 +4312,16 @@
         <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C68" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D68">
-        <v>167.024</v>
+        <v>63.07200000000001</v>
       </c>
       <c r="E68">
-        <v>167.024</v>
+        <v>63.07200000000001</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -4341,16 +4341,16 @@
         <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C69" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D69">
-        <v>47.048499999999997</v>
+        <v>233.74600000000001</v>
       </c>
       <c r="E69">
-        <v>47.048499999999997</v>
+        <v>233.74600000000001</v>
       </c>
       <c r="F69">
         <v>1</v>
@@ -4370,16 +4370,16 @@
         <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C70" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="D70">
-        <v>151.84</v>
+        <v>36.5</v>
       </c>
       <c r="E70">
-        <v>151.84</v>
+        <v>36.5</v>
       </c>
       <c r="F70">
         <v>1</v>
@@ -4399,16 +4399,16 @@
         <v>11</v>
       </c>
       <c r="B71" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C71" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D71">
-        <v>28.251000000000005</v>
+        <v>7.8475000000000001</v>
       </c>
       <c r="E71">
-        <v>28.251000000000005</v>
+        <v>7.8475000000000001</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -4428,16 +4428,16 @@
         <v>11</v>
       </c>
       <c r="B72" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C72" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="D72">
-        <v>18.572295</v>
+        <v>19.6005</v>
       </c>
       <c r="E72">
-        <v>18.572295</v>
+        <v>19.6005</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -4457,16 +4457,16 @@
         <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="C73" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D73">
-        <v>51.83</v>
+        <v>2.8105000000000002</v>
       </c>
       <c r="E73">
-        <v>51.83</v>
+        <v>2.8105000000000002</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -4486,16 +4486,16 @@
         <v>11</v>
       </c>
       <c r="B74" t="s">
+        <v>24</v>
+      </c>
+      <c r="C74" t="s">
         <v>66</v>
       </c>
-      <c r="C74" t="s">
-        <v>51</v>
-      </c>
       <c r="D74">
-        <v>28.287500000000001</v>
+        <v>17.72805</v>
       </c>
       <c r="E74">
-        <v>28.287500000000001</v>
+        <v>17.72805</v>
       </c>
       <c r="F74">
         <v>1</v>
@@ -4515,16 +4515,16 @@
         <v>11</v>
       </c>
       <c r="B75" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="C75" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="D75">
-        <v>122.3699</v>
+        <v>98.55</v>
       </c>
       <c r="E75">
-        <v>122.3699</v>
+        <v>98.55</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -4544,16 +4544,16 @@
         <v>11</v>
       </c>
       <c r="B76" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="C76" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D76">
-        <v>6.5626999999999995</v>
+        <v>81.394999999999996</v>
       </c>
       <c r="E76">
-        <v>6.5626999999999995</v>
+        <v>81.394999999999996</v>
       </c>
       <c r="F76">
         <v>1</v>
@@ -4573,16 +4573,16 @@
         <v>11</v>
       </c>
       <c r="B77" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="C77" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="D77">
-        <v>145.31745000000001</v>
+        <v>60.068779999999997</v>
       </c>
       <c r="E77">
-        <v>145.31745000000001</v>
+        <v>60.068779999999997</v>
       </c>
       <c r="F77">
         <v>1</v>
@@ -4602,16 +4602,16 @@
         <v>11</v>
       </c>
       <c r="B78" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C78" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="D78">
-        <v>42.997</v>
+        <v>1.5034349999999999</v>
       </c>
       <c r="E78">
-        <v>42.997</v>
+        <v>1.5034349999999999</v>
       </c>
       <c r="F78">
         <v>1</v>
@@ -4631,16 +4631,16 @@
         <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C79" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D79">
-        <v>54.074750000000002</v>
+        <v>340.03399999999999</v>
       </c>
       <c r="E79">
-        <v>54.074750000000002</v>
+        <v>340.03399999999999</v>
       </c>
       <c r="F79">
         <v>1</v>
@@ -4660,16 +4660,16 @@
         <v>11</v>
       </c>
       <c r="B80" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C80" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="D80">
-        <v>9.9936999999999987</v>
+        <v>449.59203500000001</v>
       </c>
       <c r="E80">
-        <v>9.9936999999999987</v>
+        <v>449.59203500000001</v>
       </c>
       <c r="F80">
         <v>1</v>
@@ -4689,16 +4689,16 @@
         <v>11</v>
       </c>
       <c r="B81" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C81" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D81">
-        <v>181.46340000000004</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="E81">
-        <v>181.46340000000004</v>
+        <v>10.220000000000001</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -4718,16 +4718,16 @@
         <v>11</v>
       </c>
       <c r="B82" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C82" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D82">
-        <v>23.659299999999998</v>
+        <v>454.93600000000004</v>
       </c>
       <c r="E82">
-        <v>23.659299999999998</v>
+        <v>454.93600000000004</v>
       </c>
       <c r="F82">
         <v>1</v>
@@ -4747,16 +4747,16 @@
         <v>11</v>
       </c>
       <c r="B83" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C83" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D83">
-        <v>18.359500000000001</v>
+        <v>573.19600000000003</v>
       </c>
       <c r="E83">
-        <v>18.359500000000001</v>
+        <v>573.19600000000003</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -4776,16 +4776,16 @@
         <v>11</v>
       </c>
       <c r="B84" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C84" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D84">
-        <v>294.09875000000005</v>
+        <v>167.024</v>
       </c>
       <c r="E84">
-        <v>294.09875000000005</v>
+        <v>167.024</v>
       </c>
       <c r="F84">
         <v>1</v>
@@ -4805,16 +4805,16 @@
         <v>11</v>
       </c>
       <c r="B85" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C85" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D85">
-        <v>44.603000000000002</v>
+        <v>47.048499999999997</v>
       </c>
       <c r="E85">
-        <v>44.603000000000002</v>
+        <v>47.048499999999997</v>
       </c>
       <c r="F85">
         <v>1</v>
@@ -4834,16 +4834,16 @@
         <v>11</v>
       </c>
       <c r="B86" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C86" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D86">
-        <v>5.8765000000000009</v>
+        <v>151.84</v>
       </c>
       <c r="E86">
-        <v>5.8765000000000009</v>
+        <v>151.84</v>
       </c>
       <c r="F86">
         <v>1</v>
@@ -4863,16 +4863,16 @@
         <v>11</v>
       </c>
       <c r="B87" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="C87" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="D87">
-        <v>24.673999999999996</v>
+        <v>28.251000000000005</v>
       </c>
       <c r="E87">
-        <v>24.673999999999996</v>
+        <v>28.251000000000005</v>
       </c>
       <c r="F87">
         <v>1</v>
@@ -4892,16 +4892,16 @@
         <v>11</v>
       </c>
       <c r="B88" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="C88" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D88">
-        <v>41.683</v>
+        <v>18.572295</v>
       </c>
       <c r="E88">
-        <v>41.683</v>
+        <v>18.572295</v>
       </c>
       <c r="F88">
         <v>1</v>
@@ -4921,16 +4921,16 @@
         <v>11</v>
       </c>
       <c r="B89" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C89" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="D89">
-        <v>23.761499999999998</v>
+        <v>51.83</v>
       </c>
       <c r="E89">
-        <v>23.761499999999998</v>
+        <v>51.83</v>
       </c>
       <c r="F89">
         <v>1</v>
@@ -4950,16 +4950,16 @@
         <v>11</v>
       </c>
       <c r="B90" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C90" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D90">
-        <v>31.024999999999999</v>
+        <v>28.287500000000001</v>
       </c>
       <c r="E90">
-        <v>31.024999999999999</v>
+        <v>28.287500000000001</v>
       </c>
       <c r="F90">
         <v>1</v>
@@ -4979,16 +4979,16 @@
         <v>11</v>
       </c>
       <c r="B91" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C91" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="D91">
-        <v>81.906000000000006</v>
+        <v>122.3699</v>
       </c>
       <c r="E91">
-        <v>81.906000000000006</v>
+        <v>122.3699</v>
       </c>
       <c r="F91">
         <v>1</v>
@@ -5008,16 +5008,16 @@
         <v>11</v>
       </c>
       <c r="B92" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C92" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="D92">
-        <v>52.56</v>
+        <v>6.5626999999999995</v>
       </c>
       <c r="E92">
-        <v>52.56</v>
+        <v>6.5626999999999995</v>
       </c>
       <c r="F92">
         <v>1</v>
@@ -5037,16 +5037,16 @@
         <v>11</v>
       </c>
       <c r="B93" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="C93" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D93">
-        <v>29.2</v>
+        <v>145.31745000000001</v>
       </c>
       <c r="E93">
-        <v>29.2</v>
+        <v>145.31745000000001</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -5066,16 +5066,16 @@
         <v>11</v>
       </c>
       <c r="B94" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C94" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D94">
-        <v>49.494</v>
+        <v>42.997</v>
       </c>
       <c r="E94">
-        <v>49.494</v>
+        <v>42.997</v>
       </c>
       <c r="F94">
         <v>1</v>
@@ -5095,16 +5095,16 @@
         <v>11</v>
       </c>
       <c r="B95" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C95" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D95">
-        <v>831.32399999999996</v>
+        <v>54.074750000000002</v>
       </c>
       <c r="E95">
-        <v>831.32399999999996</v>
+        <v>54.074750000000002</v>
       </c>
       <c r="F95">
         <v>1</v>
@@ -5124,16 +5124,16 @@
         <v>11</v>
       </c>
       <c r="B96" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C96" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D96">
-        <v>188.19399999999999</v>
+        <v>9.9936999999999987</v>
       </c>
       <c r="E96">
-        <v>188.19399999999999</v>
+        <v>9.9936999999999987</v>
       </c>
       <c r="F96">
         <v>1</v>
@@ -5153,16 +5153,16 @@
         <v>11</v>
       </c>
       <c r="B97" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C97" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="D97">
-        <v>424.64100000000008</v>
+        <v>181.46340000000004</v>
       </c>
       <c r="E97">
-        <v>424.64100000000008</v>
+        <v>181.46340000000004</v>
       </c>
       <c r="F97">
         <v>1</v>
@@ -5182,16 +5182,16 @@
         <v>11</v>
       </c>
       <c r="B98" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="C98" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D98">
-        <v>0.80300000000000016</v>
+        <v>23.659299999999998</v>
       </c>
       <c r="E98">
-        <v>0.80300000000000016</v>
+        <v>23.659299999999998</v>
       </c>
       <c r="F98">
         <v>1</v>
@@ -5211,16 +5211,16 @@
         <v>11</v>
       </c>
       <c r="B99" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C99" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D99">
-        <v>635.83000000000004</v>
+        <v>18.359500000000001</v>
       </c>
       <c r="E99">
-        <v>635.83000000000004</v>
+        <v>18.359500000000001</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -5240,16 +5240,16 @@
         <v>11</v>
       </c>
       <c r="B100" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C100" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D100">
-        <v>61.32</v>
+        <v>294.09875000000005</v>
       </c>
       <c r="E100">
-        <v>61.32</v>
+        <v>294.09875000000005</v>
       </c>
       <c r="F100">
         <v>1</v>
@@ -5269,16 +5269,16 @@
         <v>11</v>
       </c>
       <c r="B101" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C101" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D101">
-        <v>80.3</v>
+        <v>44.603000000000002</v>
       </c>
       <c r="E101">
-        <v>80.3</v>
+        <v>44.603000000000002</v>
       </c>
       <c r="F101">
         <v>1</v>
@@ -5298,16 +5298,16 @@
         <v>11</v>
       </c>
       <c r="B102" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="C102" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="D102">
-        <v>177.79150000000001</v>
+        <v>5.8765000000000009</v>
       </c>
       <c r="E102">
-        <v>177.79150000000001</v>
+        <v>5.8765000000000009</v>
       </c>
       <c r="F102">
         <v>1</v>
@@ -5327,16 +5327,16 @@
         <v>11</v>
       </c>
       <c r="B103" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C103" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D103">
-        <v>210.25094999999999</v>
+        <v>24.673999999999996</v>
       </c>
       <c r="E103">
-        <v>210.25094999999999</v>
+        <v>24.673999999999996</v>
       </c>
       <c r="F103">
         <v>1</v>
@@ -5356,16 +5356,16 @@
         <v>11</v>
       </c>
       <c r="B104" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C104" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D104">
-        <v>145.489</v>
+        <v>41.683</v>
       </c>
       <c r="E104">
-        <v>145.489</v>
+        <v>41.683</v>
       </c>
       <c r="F104">
         <v>1</v>
@@ -5385,16 +5385,16 @@
         <v>11</v>
       </c>
       <c r="B105" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C105" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D105">
-        <v>547.17150000000004</v>
+        <v>23.761499999999998</v>
       </c>
       <c r="E105">
-        <v>547.17150000000004</v>
+        <v>23.761499999999998</v>
       </c>
       <c r="F105">
         <v>1</v>
@@ -5414,16 +5414,16 @@
         <v>11</v>
       </c>
       <c r="B106" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C106" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="D106">
-        <v>178.12</v>
+        <v>31.024999999999999</v>
       </c>
       <c r="E106">
-        <v>178.12</v>
+        <v>31.024999999999999</v>
       </c>
       <c r="F106">
         <v>1</v>
@@ -5443,16 +5443,16 @@
         <v>11</v>
       </c>
       <c r="B107" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C107" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D107">
-        <v>806.85586000000001</v>
+        <v>81.906000000000006</v>
       </c>
       <c r="E107">
-        <v>806.85586000000001</v>
+        <v>81.906000000000006</v>
       </c>
       <c r="F107">
         <v>1</v>
@@ -5472,16 +5472,16 @@
         <v>11</v>
       </c>
       <c r="B108" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C108" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D108">
-        <v>208.05</v>
+        <v>52.56</v>
       </c>
       <c r="E108">
-        <v>208.05</v>
+        <v>52.56</v>
       </c>
       <c r="F108">
         <v>1</v>
@@ -5501,16 +5501,16 @@
         <v>11</v>
       </c>
       <c r="B109" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="C109" t="s">
         <v>34</v>
       </c>
       <c r="D109">
-        <v>267.07049999999998</v>
+        <v>29.2</v>
       </c>
       <c r="E109">
-        <v>267.07049999999998</v>
+        <v>29.2</v>
       </c>
       <c r="F109">
         <v>1</v>
@@ -5530,16 +5530,16 @@
         <v>11</v>
       </c>
       <c r="B110" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C110" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D110">
-        <v>415.40649999999994</v>
+        <v>49.494</v>
       </c>
       <c r="E110">
-        <v>415.40649999999994</v>
+        <v>49.494</v>
       </c>
       <c r="F110">
         <v>1</v>
@@ -5559,16 +5559,16 @@
         <v>11</v>
       </c>
       <c r="B111" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C111" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="D111">
-        <v>173.667</v>
+        <v>831.32399999999996</v>
       </c>
       <c r="E111">
-        <v>173.667</v>
+        <v>831.32399999999996</v>
       </c>
       <c r="F111">
         <v>1</v>
@@ -5588,16 +5588,16 @@
         <v>11</v>
       </c>
       <c r="B112" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="C112" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="D112">
-        <v>439.27749999999992</v>
+        <v>188.19399999999999</v>
       </c>
       <c r="E112">
-        <v>439.27749999999992</v>
+        <v>188.19399999999999</v>
       </c>
       <c r="F112">
         <v>1</v>
@@ -5617,16 +5617,16 @@
         <v>11</v>
       </c>
       <c r="B113" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="C113" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="D113">
-        <v>118.77099999999999</v>
+        <v>424.64100000000008</v>
       </c>
       <c r="E113">
-        <v>118.77099999999999</v>
+        <v>424.64100000000008</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -5646,16 +5646,16 @@
         <v>11</v>
       </c>
       <c r="B114" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C114" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D114">
-        <v>486.91</v>
+        <v>0.80300000000000016</v>
       </c>
       <c r="E114">
-        <v>118.77099999999999</v>
+        <v>0.80300000000000016</v>
       </c>
       <c r="F114">
         <v>1</v>
@@ -5675,16 +5675,16 @@
         <v>11</v>
       </c>
       <c r="B115" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="C115" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="D115">
-        <v>144.17500000000001</v>
+        <v>635.83000000000004</v>
       </c>
       <c r="E115">
-        <v>118.77099999999999</v>
+        <v>635.83000000000004</v>
       </c>
       <c r="F115">
         <v>1</v>
@@ -5704,16 +5704,16 @@
         <v>11</v>
       </c>
       <c r="B116" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C116" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="D116">
-        <v>49.494</v>
+        <v>61.32</v>
       </c>
       <c r="E116">
-        <v>500</v>
+        <v>61.32</v>
       </c>
       <c r="F116">
         <v>1</v>
@@ -5733,16 +5733,16 @@
         <v>11</v>
       </c>
       <c r="B117" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C117" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D117">
-        <v>816.06700000000012</v>
+        <v>80.3</v>
       </c>
       <c r="E117">
-        <v>500</v>
+        <v>80.3</v>
       </c>
       <c r="F117">
         <v>1</v>
@@ -5762,16 +5762,16 @@
         <v>11</v>
       </c>
       <c r="B118" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C118" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D118">
-        <v>188.88749999999999</v>
+        <v>177.79150000000001</v>
       </c>
       <c r="E118">
-        <v>500</v>
+        <v>177.79150000000001</v>
       </c>
       <c r="F118">
         <v>1</v>
@@ -5791,16 +5791,16 @@
         <v>11</v>
       </c>
       <c r="B119" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="C119" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D119">
-        <v>89.716999999999999</v>
+        <v>210.25094999999999</v>
       </c>
       <c r="E119">
-        <v>500</v>
+        <v>210.25094999999999</v>
       </c>
       <c r="F119">
         <v>1</v>
@@ -5820,16 +5820,16 @@
         <v>11</v>
       </c>
       <c r="B120" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="C120" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D120">
-        <v>170.63749999999999</v>
+        <v>145.489</v>
       </c>
       <c r="E120">
-        <v>500</v>
+        <v>145.489</v>
       </c>
       <c r="F120">
         <v>1</v>
@@ -5849,16 +5849,16 @@
         <v>11</v>
       </c>
       <c r="B121" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="C121" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="D121">
-        <v>12.1837</v>
+        <v>547.17150000000004</v>
       </c>
       <c r="E121">
-        <v>500</v>
+        <v>547.17150000000004</v>
       </c>
       <c r="F121">
         <v>1</v>
@@ -5878,16 +5878,16 @@
         <v>11</v>
       </c>
       <c r="B122" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C122" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="D122">
-        <v>256.15699999999998</v>
+        <v>178.12</v>
       </c>
       <c r="E122">
-        <v>500</v>
+        <v>178.12</v>
       </c>
       <c r="F122">
         <v>1</v>
@@ -5907,16 +5907,16 @@
         <v>11</v>
       </c>
       <c r="B123" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C123" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="D123">
-        <v>61.32</v>
+        <v>806.85586000000001</v>
       </c>
       <c r="E123">
-        <v>500</v>
+        <v>806.85586000000001</v>
       </c>
       <c r="F123">
         <v>1</v>
@@ -5936,16 +5936,16 @@
         <v>11</v>
       </c>
       <c r="B124" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C124" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D124">
-        <v>180.20050000000001</v>
+        <v>208.05</v>
       </c>
       <c r="E124">
-        <v>500</v>
+        <v>208.05</v>
       </c>
       <c r="F124">
         <v>1</v>
@@ -5965,16 +5965,16 @@
         <v>11</v>
       </c>
       <c r="B125" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C125" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D125">
-        <v>421.21</v>
+        <v>267.07049999999998</v>
       </c>
       <c r="E125">
-        <v>500</v>
+        <v>267.07049999999998</v>
       </c>
       <c r="F125">
         <v>1</v>
@@ -5994,16 +5994,16 @@
         <v>11</v>
       </c>
       <c r="B126" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C126" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D126">
-        <v>123.04150000000001</v>
+        <v>415.40649999999994</v>
       </c>
       <c r="E126">
-        <v>500</v>
+        <v>415.40649999999994</v>
       </c>
       <c r="F126">
         <v>1</v>
@@ -6023,16 +6023,16 @@
         <v>11</v>
       </c>
       <c r="B127" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="C127" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D127">
-        <v>161.62200000000001</v>
+        <v>173.667</v>
       </c>
       <c r="E127">
-        <v>500</v>
+        <v>173.667</v>
       </c>
       <c r="F127">
         <v>1</v>
@@ -6052,16 +6052,16 @@
         <v>11</v>
       </c>
       <c r="B128" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="C128" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D128">
-        <v>455.15499999999997</v>
+        <v>439.27749999999992</v>
       </c>
       <c r="E128">
-        <v>500</v>
+        <v>439.27749999999992</v>
       </c>
       <c r="F128">
         <v>1</v>
@@ -6081,16 +6081,16 @@
         <v>11</v>
       </c>
       <c r="B129" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="C129" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D129">
-        <v>351.714</v>
+        <v>118.77099999999999</v>
       </c>
       <c r="E129">
-        <v>500</v>
+        <v>118.77099999999999</v>
       </c>
       <c r="F129">
         <v>1</v>
@@ -6110,16 +6110,16 @@
         <v>11</v>
       </c>
       <c r="B130" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C130" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D130">
-        <v>167.75399999999999</v>
+        <v>486.91</v>
       </c>
       <c r="E130">
-        <v>500</v>
+        <v>118.77099999999999</v>
       </c>
       <c r="F130">
         <v>1</v>
@@ -6139,16 +6139,16 @@
         <v>11</v>
       </c>
       <c r="B131" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="C131" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="D131">
-        <v>207.5025</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="E131">
-        <v>500</v>
+        <v>118.77099999999999</v>
       </c>
       <c r="F131">
         <v>1</v>
@@ -6168,13 +6168,13 @@
         <v>11</v>
       </c>
       <c r="B132" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C132" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D132">
-        <v>513.19000000000005</v>
+        <v>49.494</v>
       </c>
       <c r="E132">
         <v>500</v>
@@ -6197,13 +6197,13 @@
         <v>11</v>
       </c>
       <c r="B133" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C133" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D133">
-        <v>140.52500000000001</v>
+        <v>816.06700000000012</v>
       </c>
       <c r="E133">
         <v>500</v>
@@ -6226,13 +6226,13 @@
         <v>11</v>
       </c>
       <c r="B134" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C134" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="D134">
-        <v>82.927999999999997</v>
+        <v>188.88749999999999</v>
       </c>
       <c r="E134">
         <v>500</v>
@@ -6255,13 +6255,13 @@
         <v>11</v>
       </c>
       <c r="B135" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="C135" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="D135">
-        <v>67.451999999999998</v>
+        <v>89.716999999999999</v>
       </c>
       <c r="E135">
         <v>500</v>
@@ -6284,16 +6284,16 @@
         <v>11</v>
       </c>
       <c r="B136" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C136" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="D136">
-        <v>395</v>
+        <v>170.63749999999999</v>
       </c>
       <c r="E136">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="F136">
         <v>1</v>
@@ -6313,16 +6313,16 @@
         <v>11</v>
       </c>
       <c r="B137" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="C137" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D137">
-        <v>395</v>
+        <v>12.1837</v>
       </c>
       <c r="E137">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="F137">
         <v>1</v>
@@ -6342,16 +6342,16 @@
         <v>11</v>
       </c>
       <c r="B138" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="C138" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D138">
-        <v>395</v>
+        <v>256.15699999999998</v>
       </c>
       <c r="E138">
-        <v>395</v>
+        <v>500</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -6368,16 +6368,16 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B139" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="C139" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="D139">
-        <v>500</v>
+        <v>61.32</v>
       </c>
       <c r="E139">
         <v>500</v>
@@ -6389,7 +6389,7 @@
         <v>10000000</v>
       </c>
       <c r="H139">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I139">
         <v>1</v>
@@ -6397,16 +6397,16 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B140" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="C140" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D140">
-        <v>500</v>
+        <v>180.20050000000001</v>
       </c>
       <c r="E140">
         <v>500</v>
@@ -6418,7 +6418,7 @@
         <v>10000000</v>
       </c>
       <c r="H140">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I140">
         <v>1</v>
@@ -6426,16 +6426,16 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B141" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="C141" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D141">
-        <v>500</v>
+        <v>421.21</v>
       </c>
       <c r="E141">
         <v>500</v>
@@ -6447,7 +6447,7 @@
         <v>10000000</v>
       </c>
       <c r="H141">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I141">
         <v>1</v>
@@ -6455,16 +6455,16 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B142" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="C142" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D142">
-        <v>500</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="E142">
         <v>500</v>
@@ -6476,7 +6476,7 @@
         <v>10000000</v>
       </c>
       <c r="H142">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I142">
         <v>1</v>
@@ -6484,16 +6484,16 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B143" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="C143" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D143">
-        <v>500</v>
+        <v>161.62200000000001</v>
       </c>
       <c r="E143">
         <v>500</v>
@@ -6505,7 +6505,7 @@
         <v>10000000</v>
       </c>
       <c r="H143">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I143">
         <v>1</v>
@@ -6513,16 +6513,16 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B144" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C144" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D144">
-        <v>500</v>
+        <v>455.15499999999997</v>
       </c>
       <c r="E144">
         <v>500</v>
@@ -6534,7 +6534,7 @@
         <v>10000000</v>
       </c>
       <c r="H144">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I144">
         <v>1</v>
@@ -6542,16 +6542,16 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B145" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C145" t="s">
         <v>28</v>
       </c>
       <c r="D145">
-        <v>500</v>
+        <v>351.714</v>
       </c>
       <c r="E145">
         <v>500</v>
@@ -6563,7 +6563,7 @@
         <v>10000000</v>
       </c>
       <c r="H145">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I145">
         <v>1</v>
@@ -6571,16 +6571,16 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B146" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C146" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D146">
-        <v>500</v>
+        <v>167.75399999999999</v>
       </c>
       <c r="E146">
         <v>500</v>
@@ -6592,7 +6592,7 @@
         <v>10000000</v>
       </c>
       <c r="H146">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I146">
         <v>1</v>
@@ -6600,16 +6600,16 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B147" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C147" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D147">
-        <v>500</v>
+        <v>207.5025</v>
       </c>
       <c r="E147">
         <v>500</v>
@@ -6621,7 +6621,7 @@
         <v>10000000</v>
       </c>
       <c r="H147">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I147">
         <v>1</v>
@@ -6629,16 +6629,16 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B148" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C148" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D148">
-        <v>500</v>
+        <v>513.19000000000005</v>
       </c>
       <c r="E148">
         <v>500</v>
@@ -6650,7 +6650,7 @@
         <v>10000000</v>
       </c>
       <c r="H148">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I148">
         <v>1</v>
@@ -6658,16 +6658,16 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B149" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C149" t="s">
-        <v>36</v>
+        <v>79</v>
       </c>
       <c r="D149">
-        <v>500</v>
+        <v>140.52500000000001</v>
       </c>
       <c r="E149">
         <v>500</v>
@@ -6679,7 +6679,7 @@
         <v>10000000</v>
       </c>
       <c r="H149">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I149">
         <v>1</v>
@@ -6687,16 +6687,16 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B150" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C150" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D150">
-        <v>500</v>
+        <v>82.927999999999997</v>
       </c>
       <c r="E150">
         <v>500</v>
@@ -6708,7 +6708,7 @@
         <v>10000000</v>
       </c>
       <c r="H150">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I150">
         <v>1</v>
@@ -6716,16 +6716,16 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B151" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="C151" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="D151">
-        <v>500</v>
+        <v>67.451999999999998</v>
       </c>
       <c r="E151">
         <v>500</v>
@@ -6737,7 +6737,7 @@
         <v>10000000</v>
       </c>
       <c r="H151">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I151">
         <v>1</v>
@@ -6745,19 +6745,19 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B152" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="C152" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D152">
-        <v>500</v>
+        <v>395</v>
       </c>
       <c r="E152">
-        <v>500</v>
+        <v>395</v>
       </c>
       <c r="F152">
         <v>1</v>
@@ -6766,7 +6766,7 @@
         <v>10000000</v>
       </c>
       <c r="H152">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I152">
         <v>1</v>
@@ -6774,19 +6774,19 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B153" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C153" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="D153">
-        <v>500</v>
+        <v>395</v>
       </c>
       <c r="E153">
-        <v>500</v>
+        <v>395</v>
       </c>
       <c r="F153">
         <v>1</v>
@@ -6795,7 +6795,7 @@
         <v>10000000</v>
       </c>
       <c r="H153">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I153">
         <v>1</v>
@@ -6803,19 +6803,19 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B154" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="C154" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D154">
-        <v>500</v>
+        <v>395</v>
       </c>
       <c r="E154">
-        <v>500</v>
+        <v>395</v>
       </c>
       <c r="F154">
         <v>1</v>
@@ -6824,7 +6824,7 @@
         <v>10000000</v>
       </c>
       <c r="H154">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I154">
         <v>1</v>
@@ -6835,10 +6835,10 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="C155" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="D155">
         <v>500</v>
@@ -6864,10 +6864,10 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="C156" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D156">
         <v>500</v>
@@ -6893,10 +6893,10 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="C157" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D157">
         <v>500</v>
@@ -6922,10 +6922,10 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="C158" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D158">
         <v>500</v>
@@ -6951,10 +6951,10 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="C159" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="D159">
         <v>500</v>
@@ -6980,10 +6980,10 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C160" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="D160">
         <v>500</v>
@@ -7009,10 +7009,10 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="C161" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="D161">
         <v>500</v>
@@ -7038,10 +7038,10 @@
         <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="C162" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D162">
         <v>500</v>
@@ -7067,10 +7067,10 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C163" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="D163">
         <v>500</v>
@@ -7096,10 +7096,10 @@
         <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C164" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D164">
         <v>500</v>
@@ -7125,10 +7125,10 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C165" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D165">
         <v>500</v>
@@ -7154,7 +7154,7 @@
         <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C166" t="s">
         <v>38</v>
@@ -7183,10 +7183,10 @@
         <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="C167" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="D167">
         <v>500</v>
@@ -7212,10 +7212,10 @@
         <v>12</v>
       </c>
       <c r="B168" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C168" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D168">
         <v>500</v>
@@ -7241,10 +7241,10 @@
         <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C169" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D169">
         <v>500</v>
@@ -7270,10 +7270,10 @@
         <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C170" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D170">
         <v>500</v>
@@ -7299,10 +7299,10 @@
         <v>12</v>
       </c>
       <c r="B171" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C171" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D171">
         <v>500</v>
@@ -7328,10 +7328,10 @@
         <v>12</v>
       </c>
       <c r="B172" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C172" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D172">
         <v>500</v>
@@ -7357,10 +7357,10 @@
         <v>12</v>
       </c>
       <c r="B173" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C173" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D173">
         <v>500</v>
@@ -7386,10 +7386,10 @@
         <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C174" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D174">
         <v>500</v>
@@ -7415,10 +7415,10 @@
         <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C175" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D175">
         <v>500</v>
@@ -7444,10 +7444,10 @@
         <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C176" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D176">
         <v>500</v>
@@ -7473,10 +7473,10 @@
         <v>12</v>
       </c>
       <c r="B177" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="C177" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D177">
         <v>500</v>
@@ -7502,10 +7502,10 @@
         <v>12</v>
       </c>
       <c r="B178" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C178" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D178">
         <v>500</v>
@@ -7531,10 +7531,10 @@
         <v>12</v>
       </c>
       <c r="B179" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C179" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D179">
         <v>500</v>
@@ -7560,10 +7560,10 @@
         <v>12</v>
       </c>
       <c r="B180" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C180" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="D180">
         <v>500</v>
@@ -7589,10 +7589,10 @@
         <v>12</v>
       </c>
       <c r="B181" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="C181" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="D181">
         <v>500</v>
@@ -7618,10 +7618,10 @@
         <v>12</v>
       </c>
       <c r="B182" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="C182" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D182">
         <v>500</v>
@@ -7647,10 +7647,10 @@
         <v>12</v>
       </c>
       <c r="B183" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="C183" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="D183">
         <v>500</v>
@@ -7676,10 +7676,10 @@
         <v>12</v>
       </c>
       <c r="B184" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="C184" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="D184">
         <v>500</v>
@@ -7705,10 +7705,10 @@
         <v>12</v>
       </c>
       <c r="B185" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="C185" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="D185">
         <v>500</v>
@@ -7734,10 +7734,10 @@
         <v>12</v>
       </c>
       <c r="B186" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C186" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="D186">
         <v>500</v>
@@ -7763,10 +7763,10 @@
         <v>12</v>
       </c>
       <c r="B187" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C187" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D187">
         <v>500</v>
@@ -7792,10 +7792,10 @@
         <v>12</v>
       </c>
       <c r="B188" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C188" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="D188">
         <v>500</v>
@@ -7821,10 +7821,10 @@
         <v>12</v>
       </c>
       <c r="B189" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C189" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D189">
         <v>500</v>
@@ -7850,10 +7850,10 @@
         <v>12</v>
       </c>
       <c r="B190" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C190" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="D190">
         <v>500</v>
@@ -7879,10 +7879,10 @@
         <v>12</v>
       </c>
       <c r="B191" t="s">
+        <v>42</v>
+      </c>
+      <c r="C191" t="s">
         <v>61</v>
-      </c>
-      <c r="C191" t="s">
-        <v>18</v>
       </c>
       <c r="D191">
         <v>500</v>
@@ -7908,10 +7908,10 @@
         <v>12</v>
       </c>
       <c r="B192" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="C192" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D192">
         <v>500</v>
@@ -7937,10 +7937,10 @@
         <v>12</v>
       </c>
       <c r="B193" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="C193" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D193">
         <v>500</v>
@@ -7966,10 +7966,10 @@
         <v>12</v>
       </c>
       <c r="B194" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C194" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="D194">
         <v>500</v>
@@ -7995,10 +7995,10 @@
         <v>12</v>
       </c>
       <c r="B195" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C195" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D195">
         <v>500</v>
@@ -8024,10 +8024,10 @@
         <v>12</v>
       </c>
       <c r="B196" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C196" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="D196">
         <v>500</v>
@@ -8053,10 +8053,10 @@
         <v>12</v>
       </c>
       <c r="B197" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="C197" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="D197">
         <v>500</v>
@@ -8082,10 +8082,10 @@
         <v>12</v>
       </c>
       <c r="B198" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="C198" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D198">
         <v>500</v>
@@ -8111,10 +8111,10 @@
         <v>12</v>
       </c>
       <c r="B199" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C199" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D199">
         <v>500</v>
@@ -8140,10 +8140,10 @@
         <v>12</v>
       </c>
       <c r="B200" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C200" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D200">
         <v>500</v>
@@ -8169,10 +8169,10 @@
         <v>12</v>
       </c>
       <c r="B201" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C201" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D201">
         <v>500</v>
@@ -8198,10 +8198,10 @@
         <v>12</v>
       </c>
       <c r="B202" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="C202" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D202">
         <v>500</v>
@@ -8227,10 +8227,10 @@
         <v>12</v>
       </c>
       <c r="B203" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="C203" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D203">
         <v>500</v>
@@ -8256,10 +8256,10 @@
         <v>12</v>
       </c>
       <c r="B204" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="C204" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D204">
         <v>500</v>
@@ -8285,10 +8285,10 @@
         <v>12</v>
       </c>
       <c r="B205" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C205" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="D205">
         <v>500</v>
@@ -8314,10 +8314,10 @@
         <v>12</v>
       </c>
       <c r="B206" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C206" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D206">
         <v>500</v>
@@ -8343,10 +8343,10 @@
         <v>12</v>
       </c>
       <c r="B207" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C207" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="D207">
         <v>500</v>
@@ -8372,10 +8372,10 @@
         <v>12</v>
       </c>
       <c r="B208" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C208" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D208">
         <v>500</v>
@@ -8401,10 +8401,10 @@
         <v>12</v>
       </c>
       <c r="B209" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C209" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="D209">
         <v>500</v>
@@ -8430,10 +8430,10 @@
         <v>12</v>
       </c>
       <c r="B210" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="C210" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D210">
         <v>500</v>
@@ -8459,10 +8459,10 @@
         <v>12</v>
       </c>
       <c r="B211" t="s">
+        <v>24</v>
+      </c>
+      <c r="C211" t="s">
         <v>66</v>
-      </c>
-      <c r="C211" t="s">
-        <v>51</v>
       </c>
       <c r="D211">
         <v>500</v>
@@ -8488,10 +8488,10 @@
         <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="C212" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="D212">
         <v>500</v>
@@ -8517,10 +8517,10 @@
         <v>12</v>
       </c>
       <c r="B213" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="C213" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D213">
         <v>500</v>
@@ -8546,10 +8546,10 @@
         <v>12</v>
       </c>
       <c r="B214" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="C214" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="D214">
         <v>500</v>
@@ -8575,10 +8575,10 @@
         <v>12</v>
       </c>
       <c r="B215" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="C215" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="D215">
         <v>500</v>
@@ -8604,10 +8604,10 @@
         <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="C216" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D216">
         <v>500</v>
@@ -8633,10 +8633,10 @@
         <v>12</v>
       </c>
       <c r="B217" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C217" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="D217">
         <v>500</v>
@@ -8662,10 +8662,10 @@
         <v>12</v>
       </c>
       <c r="B218" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C218" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D218">
         <v>500</v>
@@ -8691,10 +8691,10 @@
         <v>12</v>
       </c>
       <c r="B219" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C219" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D219">
         <v>500</v>
@@ -8720,10 +8720,10 @@
         <v>12</v>
       </c>
       <c r="B220" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C220" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D220">
         <v>500</v>
@@ -8749,10 +8749,10 @@
         <v>12</v>
       </c>
       <c r="B221" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C221" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D221">
         <v>500</v>
@@ -8778,10 +8778,10 @@
         <v>12</v>
       </c>
       <c r="B222" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C222" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D222">
         <v>500</v>
@@ -8807,10 +8807,10 @@
         <v>12</v>
       </c>
       <c r="B223" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="C223" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D223">
         <v>500</v>
@@ -8836,10 +8836,10 @@
         <v>12</v>
       </c>
       <c r="B224" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="C224" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="D224">
         <v>500</v>
@@ -8865,10 +8865,10 @@
         <v>12</v>
       </c>
       <c r="B225" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="C225" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D225">
         <v>500</v>
@@ -8894,10 +8894,10 @@
         <v>12</v>
       </c>
       <c r="B226" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C226" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="D226">
         <v>500</v>
@@ -8923,10 +8923,10 @@
         <v>12</v>
       </c>
       <c r="B227" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C227" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D227">
         <v>500</v>
@@ -8952,10 +8952,10 @@
         <v>12</v>
       </c>
       <c r="B228" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C228" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="D228">
         <v>500</v>
@@ -8981,10 +8981,10 @@
         <v>12</v>
       </c>
       <c r="B229" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="C229" t="s">
-        <v>32</v>
+        <v>69</v>
       </c>
       <c r="D229">
         <v>500</v>
@@ -9010,10 +9010,10 @@
         <v>12</v>
       </c>
       <c r="B230" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="C230" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="D230">
         <v>500</v>
@@ -9039,10 +9039,10 @@
         <v>12</v>
       </c>
       <c r="B231" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C231" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D231">
         <v>500</v>
@@ -9068,10 +9068,10 @@
         <v>12</v>
       </c>
       <c r="B232" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C232" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="D232">
         <v>500</v>
@@ -9097,10 +9097,10 @@
         <v>12</v>
       </c>
       <c r="B233" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C233" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D233">
         <v>500</v>
@@ -9126,10 +9126,10 @@
         <v>12</v>
       </c>
       <c r="B234" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C234" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="D234">
         <v>500</v>
@@ -9155,10 +9155,10 @@
         <v>12</v>
       </c>
       <c r="B235" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="C235" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D235">
         <v>500</v>
@@ -9184,10 +9184,10 @@
         <v>12</v>
       </c>
       <c r="B236" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C236" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D236">
         <v>500</v>
@@ -9213,10 +9213,10 @@
         <v>12</v>
       </c>
       <c r="B237" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C237" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D237">
         <v>500</v>
@@ -9242,10 +9242,10 @@
         <v>12</v>
       </c>
       <c r="B238" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C238" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D238">
         <v>500</v>
@@ -9271,10 +9271,10 @@
         <v>12</v>
       </c>
       <c r="B239" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="C239" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="D239">
         <v>500</v>
@@ -9300,10 +9300,10 @@
         <v>12</v>
       </c>
       <c r="B240" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C240" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D240">
         <v>500</v>
@@ -9329,10 +9329,10 @@
         <v>12</v>
       </c>
       <c r="B241" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C241" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="D241">
         <v>500</v>
@@ -9358,10 +9358,10 @@
         <v>12</v>
       </c>
       <c r="B242" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C242" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D242">
         <v>500</v>
@@ -9387,10 +9387,10 @@
         <v>12</v>
       </c>
       <c r="B243" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C243" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="D243">
         <v>500</v>
@@ -9416,10 +9416,10 @@
         <v>12</v>
       </c>
       <c r="B244" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C244" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D244">
         <v>500</v>
@@ -9445,10 +9445,10 @@
         <v>12</v>
       </c>
       <c r="B245" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C245" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D245">
         <v>500</v>
@@ -9474,7 +9474,7 @@
         <v>12</v>
       </c>
       <c r="B246" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="C246" t="s">
         <v>34</v>
@@ -9503,10 +9503,10 @@
         <v>12</v>
       </c>
       <c r="B247" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C247" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D247">
         <v>500</v>
@@ -9532,10 +9532,10 @@
         <v>12</v>
       </c>
       <c r="B248" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C248" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="D248">
         <v>500</v>
@@ -9561,10 +9561,10 @@
         <v>12</v>
       </c>
       <c r="B249" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="C249" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="D249">
         <v>500</v>
@@ -9590,10 +9590,10 @@
         <v>12</v>
       </c>
       <c r="B250" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="C250" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="D250">
         <v>500</v>
@@ -9619,10 +9619,10 @@
         <v>12</v>
       </c>
       <c r="B251" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C251" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D251">
         <v>500</v>
@@ -9648,10 +9648,10 @@
         <v>12</v>
       </c>
       <c r="B252" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="C252" t="s">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="D252">
         <v>500</v>
@@ -9677,10 +9677,10 @@
         <v>12</v>
       </c>
       <c r="B253" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C253" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="D253">
         <v>500</v>
@@ -9706,10 +9706,10 @@
         <v>12</v>
       </c>
       <c r="B254" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C254" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D254">
         <v>500</v>
@@ -9735,10 +9735,10 @@
         <v>12</v>
       </c>
       <c r="B255" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C255" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D255">
         <v>500</v>
@@ -9764,10 +9764,10 @@
         <v>12</v>
       </c>
       <c r="B256" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="C256" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D256">
         <v>500</v>
@@ -9793,10 +9793,10 @@
         <v>12</v>
       </c>
       <c r="B257" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="C257" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D257">
         <v>500</v>
@@ -9822,10 +9822,10 @@
         <v>12</v>
       </c>
       <c r="B258" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="C258" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="D258">
         <v>500</v>
@@ -9851,10 +9851,10 @@
         <v>12</v>
       </c>
       <c r="B259" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C259" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="D259">
         <v>500</v>
@@ -9880,10 +9880,10 @@
         <v>12</v>
       </c>
       <c r="B260" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C260" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="D260">
         <v>500</v>
@@ -9909,10 +9909,10 @@
         <v>12</v>
       </c>
       <c r="B261" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C261" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D261">
         <v>500</v>
@@ -9938,10 +9938,10 @@
         <v>12</v>
       </c>
       <c r="B262" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C262" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D262">
         <v>500</v>
@@ -9967,10 +9967,10 @@
         <v>12</v>
       </c>
       <c r="B263" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="C263" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D263">
         <v>500</v>
@@ -9996,10 +9996,10 @@
         <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="C264" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D264">
         <v>500</v>
@@ -10025,10 +10025,10 @@
         <v>12</v>
       </c>
       <c r="B265" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="C265" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D265">
         <v>500</v>
@@ -10054,10 +10054,10 @@
         <v>12</v>
       </c>
       <c r="B266" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="C266" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D266">
         <v>500</v>
@@ -10083,10 +10083,10 @@
         <v>12</v>
       </c>
       <c r="B267" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C267" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D267">
         <v>500</v>
@@ -10112,10 +10112,10 @@
         <v>12</v>
       </c>
       <c r="B268" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="C268" t="s">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="D268">
         <v>500</v>
@@ -10141,10 +10141,10 @@
         <v>12</v>
       </c>
       <c r="B269" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C269" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D269">
         <v>500</v>
@@ -10170,10 +10170,10 @@
         <v>12</v>
       </c>
       <c r="B270" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C270" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D270">
         <v>500</v>
@@ -10199,10 +10199,10 @@
         <v>12</v>
       </c>
       <c r="B271" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C271" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="D271">
         <v>500</v>
@@ -10228,10 +10228,10 @@
         <v>12</v>
       </c>
       <c r="B272" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="C272" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="D272">
         <v>500</v>
@@ -10257,10 +10257,10 @@
         <v>12</v>
       </c>
       <c r="B273" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C273" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="D273">
         <v>500</v>
@@ -10286,10 +10286,10 @@
         <v>12</v>
       </c>
       <c r="B274" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="C274" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D274">
         <v>500</v>
@@ -10315,27 +10315,955 @@
         <v>12</v>
       </c>
       <c r="B275" t="s">
+        <v>36</v>
+      </c>
+      <c r="C275" t="s">
+        <v>68</v>
+      </c>
+      <c r="D275">
+        <v>500</v>
+      </c>
+      <c r="E275">
+        <v>500</v>
+      </c>
+      <c r="F275">
+        <v>1</v>
+      </c>
+      <c r="G275">
+        <v>10000000</v>
+      </c>
+      <c r="H275">
+        <v>1000</v>
+      </c>
+      <c r="I275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>12</v>
+      </c>
+      <c r="B276" t="s">
+        <v>53</v>
+      </c>
+      <c r="C276" t="s">
+        <v>72</v>
+      </c>
+      <c r="D276">
+        <v>500</v>
+      </c>
+      <c r="E276">
+        <v>500</v>
+      </c>
+      <c r="F276">
+        <v>1</v>
+      </c>
+      <c r="G276">
+        <v>10000000</v>
+      </c>
+      <c r="H276">
+        <v>1000</v>
+      </c>
+      <c r="I276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>12</v>
+      </c>
+      <c r="B277" t="s">
+        <v>45</v>
+      </c>
+      <c r="C277" t="s">
+        <v>22</v>
+      </c>
+      <c r="D277">
+        <v>500</v>
+      </c>
+      <c r="E277">
+        <v>500</v>
+      </c>
+      <c r="F277">
+        <v>1</v>
+      </c>
+      <c r="G277">
+        <v>10000000</v>
+      </c>
+      <c r="H277">
+        <v>1000</v>
+      </c>
+      <c r="I277">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>12</v>
+      </c>
+      <c r="B278" t="s">
+        <v>55</v>
+      </c>
+      <c r="C278" t="s">
+        <v>22</v>
+      </c>
+      <c r="D278">
+        <v>500</v>
+      </c>
+      <c r="E278">
+        <v>500</v>
+      </c>
+      <c r="F278">
+        <v>1</v>
+      </c>
+      <c r="G278">
+        <v>10000000</v>
+      </c>
+      <c r="H278">
+        <v>1000</v>
+      </c>
+      <c r="I278">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
+        <v>12</v>
+      </c>
+      <c r="B279" t="s">
+        <v>84</v>
+      </c>
+      <c r="C279" t="s">
+        <v>34</v>
+      </c>
+      <c r="D279">
+        <v>500</v>
+      </c>
+      <c r="E279">
+        <v>500</v>
+      </c>
+      <c r="F279">
+        <v>1</v>
+      </c>
+      <c r="G279">
+        <v>10000000</v>
+      </c>
+      <c r="H279">
+        <v>1000</v>
+      </c>
+      <c r="I279">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
+        <v>12</v>
+      </c>
+      <c r="B280" t="s">
+        <v>78</v>
+      </c>
+      <c r="C280" t="s">
+        <v>34</v>
+      </c>
+      <c r="D280">
+        <v>500</v>
+      </c>
+      <c r="E280">
+        <v>500</v>
+      </c>
+      <c r="F280">
+        <v>1</v>
+      </c>
+      <c r="G280">
+        <v>10000000</v>
+      </c>
+      <c r="H280">
+        <v>1000</v>
+      </c>
+      <c r="I280">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>12</v>
+      </c>
+      <c r="B281" t="s">
+        <v>48</v>
+      </c>
+      <c r="C281" t="s">
+        <v>42</v>
+      </c>
+      <c r="D281">
+        <v>500</v>
+      </c>
+      <c r="E281">
+        <v>500</v>
+      </c>
+      <c r="F281">
+        <v>1</v>
+      </c>
+      <c r="G281">
+        <v>10000000</v>
+      </c>
+      <c r="H281">
+        <v>1000</v>
+      </c>
+      <c r="I281">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>12</v>
+      </c>
+      <c r="B282" t="s">
+        <v>48</v>
+      </c>
+      <c r="C282" t="s">
+        <v>28</v>
+      </c>
+      <c r="D282">
+        <v>500</v>
+      </c>
+      <c r="E282">
+        <v>500</v>
+      </c>
+      <c r="F282">
+        <v>1</v>
+      </c>
+      <c r="G282">
+        <v>10000000</v>
+      </c>
+      <c r="H282">
+        <v>1000</v>
+      </c>
+      <c r="I282">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>12</v>
+      </c>
+      <c r="B283" t="s">
+        <v>48</v>
+      </c>
+      <c r="C283" t="s">
+        <v>16</v>
+      </c>
+      <c r="D283">
+        <v>500</v>
+      </c>
+      <c r="E283">
+        <v>500</v>
+      </c>
+      <c r="F283">
+        <v>1</v>
+      </c>
+      <c r="G283">
+        <v>10000000</v>
+      </c>
+      <c r="H283">
+        <v>1000</v>
+      </c>
+      <c r="I283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>12</v>
+      </c>
+      <c r="B284" t="s">
+        <v>48</v>
+      </c>
+      <c r="C284" t="s">
+        <v>18</v>
+      </c>
+      <c r="D284">
+        <v>500</v>
+      </c>
+      <c r="E284">
+        <v>500</v>
+      </c>
+      <c r="F284">
+        <v>1</v>
+      </c>
+      <c r="G284">
+        <v>10000000</v>
+      </c>
+      <c r="H284">
+        <v>1000</v>
+      </c>
+      <c r="I284">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>12</v>
+      </c>
+      <c r="B285" t="s">
+        <v>48</v>
+      </c>
+      <c r="C285" t="s">
+        <v>38</v>
+      </c>
+      <c r="D285">
+        <v>500</v>
+      </c>
+      <c r="E285">
+        <v>500</v>
+      </c>
+      <c r="F285">
+        <v>1</v>
+      </c>
+      <c r="G285">
+        <v>10000000</v>
+      </c>
+      <c r="H285">
+        <v>1000</v>
+      </c>
+      <c r="I285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>12</v>
+      </c>
+      <c r="B286" t="s">
+        <v>38</v>
+      </c>
+      <c r="C286" t="s">
+        <v>79</v>
+      </c>
+      <c r="D286">
+        <v>500</v>
+      </c>
+      <c r="E286">
+        <v>500</v>
+      </c>
+      <c r="F286">
+        <v>1</v>
+      </c>
+      <c r="G286">
+        <v>10000000</v>
+      </c>
+      <c r="H286">
+        <v>1000</v>
+      </c>
+      <c r="I286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>12</v>
+      </c>
+      <c r="B287" t="s">
+        <v>38</v>
+      </c>
+      <c r="C287" t="s">
+        <v>16</v>
+      </c>
+      <c r="D287">
+        <v>500</v>
+      </c>
+      <c r="E287">
+        <v>500</v>
+      </c>
+      <c r="F287">
+        <v>1</v>
+      </c>
+      <c r="G287">
+        <v>10000000</v>
+      </c>
+      <c r="H287">
+        <v>1000</v>
+      </c>
+      <c r="I287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>12</v>
+      </c>
+      <c r="B288" t="s">
+        <v>38</v>
+      </c>
+      <c r="C288" t="s">
+        <v>28</v>
+      </c>
+      <c r="D288">
+        <v>500</v>
+      </c>
+      <c r="E288">
+        <v>500</v>
+      </c>
+      <c r="F288">
+        <v>1</v>
+      </c>
+      <c r="G288">
+        <v>10000000</v>
+      </c>
+      <c r="H288">
+        <v>1000</v>
+      </c>
+      <c r="I288">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>12</v>
+      </c>
+      <c r="B289" t="s">
+        <v>74</v>
+      </c>
+      <c r="C289" t="s">
+        <v>22</v>
+      </c>
+      <c r="D289">
+        <v>500</v>
+      </c>
+      <c r="E289">
+        <v>500</v>
+      </c>
+      <c r="F289">
+        <v>1</v>
+      </c>
+      <c r="G289">
+        <v>10000000</v>
+      </c>
+      <c r="H289">
+        <v>1000</v>
+      </c>
+      <c r="I289">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>12</v>
+      </c>
+      <c r="B290" t="s">
+        <v>20</v>
+      </c>
+      <c r="C290" t="s">
+        <v>74</v>
+      </c>
+      <c r="D290">
+        <v>500</v>
+      </c>
+      <c r="E290">
+        <v>500</v>
+      </c>
+      <c r="F290">
+        <v>1</v>
+      </c>
+      <c r="G290">
+        <v>10000000</v>
+      </c>
+      <c r="H290">
+        <v>1000</v>
+      </c>
+      <c r="I290">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>12</v>
+      </c>
+      <c r="B291" t="s">
         <v>77</v>
       </c>
-      <c r="C275" t="s">
+      <c r="C291" t="s">
         <v>20</v>
       </c>
-      <c r="D275">
-        <v>500</v>
-      </c>
-      <c r="E275">
-        <v>500</v>
-      </c>
-      <c r="F275">
-        <v>1</v>
-      </c>
-      <c r="G275">
-        <v>10000000</v>
-      </c>
-      <c r="H275">
-        <v>1000</v>
-      </c>
-      <c r="I275">
+      <c r="D291">
+        <v>500</v>
+      </c>
+      <c r="E291">
+        <v>500</v>
+      </c>
+      <c r="F291">
+        <v>1</v>
+      </c>
+      <c r="G291">
+        <v>10000000</v>
+      </c>
+      <c r="H291">
+        <v>1000</v>
+      </c>
+      <c r="I291">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>12</v>
+      </c>
+      <c r="B292" t="s">
+        <v>82</v>
+      </c>
+      <c r="C292" t="s">
+        <v>74</v>
+      </c>
+      <c r="D292">
+        <v>10000</v>
+      </c>
+      <c r="E292">
+        <v>10000</v>
+      </c>
+      <c r="F292">
+        <v>100</v>
+      </c>
+      <c r="G292">
+        <v>10000000</v>
+      </c>
+      <c r="H292">
+        <v>1000</v>
+      </c>
+      <c r="I292">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>12</v>
+      </c>
+      <c r="B293" t="s">
+        <v>83</v>
+      </c>
+      <c r="C293" t="s">
+        <v>84</v>
+      </c>
+      <c r="D293">
+        <v>10000</v>
+      </c>
+      <c r="E293">
+        <v>10000</v>
+      </c>
+      <c r="F293">
+        <v>100</v>
+      </c>
+      <c r="G293">
+        <v>10000000</v>
+      </c>
+      <c r="H293">
+        <v>1000</v>
+      </c>
+      <c r="I293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>12</v>
+      </c>
+      <c r="B294" t="s">
+        <v>85</v>
+      </c>
+      <c r="C294" t="s">
+        <v>60</v>
+      </c>
+      <c r="D294">
+        <v>10000</v>
+      </c>
+      <c r="E294">
+        <v>10000</v>
+      </c>
+      <c r="F294">
+        <v>100</v>
+      </c>
+      <c r="G294">
+        <v>10000000</v>
+      </c>
+      <c r="H294">
+        <v>1000</v>
+      </c>
+      <c r="I294">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>12</v>
+      </c>
+      <c r="B295" t="s">
+        <v>86</v>
+      </c>
+      <c r="C295" t="s">
+        <v>16</v>
+      </c>
+      <c r="D295">
+        <v>10000</v>
+      </c>
+      <c r="E295">
+        <v>10000</v>
+      </c>
+      <c r="F295">
+        <v>100</v>
+      </c>
+      <c r="G295">
+        <v>10000000</v>
+      </c>
+      <c r="H295">
+        <v>1000</v>
+      </c>
+      <c r="I295">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>12</v>
+      </c>
+      <c r="B296" t="s">
+        <v>87</v>
+      </c>
+      <c r="C296" t="s">
+        <v>68</v>
+      </c>
+      <c r="D296">
+        <v>10000</v>
+      </c>
+      <c r="E296">
+        <v>10000</v>
+      </c>
+      <c r="F296">
+        <v>100</v>
+      </c>
+      <c r="G296">
+        <v>10000000</v>
+      </c>
+      <c r="H296">
+        <v>1000</v>
+      </c>
+      <c r="I296">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>12</v>
+      </c>
+      <c r="B297" t="s">
+        <v>88</v>
+      </c>
+      <c r="C297" t="s">
+        <v>24</v>
+      </c>
+      <c r="D297">
+        <v>10000</v>
+      </c>
+      <c r="E297">
+        <v>10000</v>
+      </c>
+      <c r="F297">
+        <v>100</v>
+      </c>
+      <c r="G297">
+        <v>10000000</v>
+      </c>
+      <c r="H297">
+        <v>1000</v>
+      </c>
+      <c r="I297">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>12</v>
+      </c>
+      <c r="B298" t="s">
+        <v>89</v>
+      </c>
+      <c r="C298" t="s">
+        <v>62</v>
+      </c>
+      <c r="D298">
+        <v>10000</v>
+      </c>
+      <c r="E298">
+        <v>10000</v>
+      </c>
+      <c r="F298">
+        <v>100</v>
+      </c>
+      <c r="G298">
+        <v>10000000</v>
+      </c>
+      <c r="H298">
+        <v>1000</v>
+      </c>
+      <c r="I298">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>12</v>
+      </c>
+      <c r="B299" t="s">
+        <v>90</v>
+      </c>
+      <c r="C299" t="s">
+        <v>18</v>
+      </c>
+      <c r="D299">
+        <v>10000</v>
+      </c>
+      <c r="E299">
+        <v>10000</v>
+      </c>
+      <c r="F299">
+        <v>100</v>
+      </c>
+      <c r="G299">
+        <v>10000000</v>
+      </c>
+      <c r="H299">
+        <v>1000</v>
+      </c>
+      <c r="I299">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>12</v>
+      </c>
+      <c r="B300" t="s">
+        <v>91</v>
+      </c>
+      <c r="C300" t="s">
+        <v>20</v>
+      </c>
+      <c r="D300">
+        <v>10000</v>
+      </c>
+      <c r="E300">
+        <v>10000</v>
+      </c>
+      <c r="F300">
+        <v>100</v>
+      </c>
+      <c r="G300">
+        <v>10000000</v>
+      </c>
+      <c r="H300">
+        <v>1000</v>
+      </c>
+      <c r="I300">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>12</v>
+      </c>
+      <c r="B301" t="s">
+        <v>92</v>
+      </c>
+      <c r="C301" t="s">
+        <v>66</v>
+      </c>
+      <c r="D301">
+        <v>10000</v>
+      </c>
+      <c r="E301">
+        <v>10000</v>
+      </c>
+      <c r="F301">
+        <v>100</v>
+      </c>
+      <c r="G301">
+        <v>10000000</v>
+      </c>
+      <c r="H301">
+        <v>1000</v>
+      </c>
+      <c r="I301">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
+        <v>12</v>
+      </c>
+      <c r="B302" t="s">
+        <v>93</v>
+      </c>
+      <c r="C302" t="s">
+        <v>59</v>
+      </c>
+      <c r="D302">
+        <v>10000</v>
+      </c>
+      <c r="E302">
+        <v>10000</v>
+      </c>
+      <c r="F302">
+        <v>100</v>
+      </c>
+      <c r="G302">
+        <v>10000000</v>
+      </c>
+      <c r="H302">
+        <v>1000</v>
+      </c>
+      <c r="I302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>12</v>
+      </c>
+      <c r="B303" t="s">
+        <v>94</v>
+      </c>
+      <c r="C303" t="s">
+        <v>67</v>
+      </c>
+      <c r="D303">
+        <v>10000</v>
+      </c>
+      <c r="E303">
+        <v>10000</v>
+      </c>
+      <c r="F303">
+        <v>100</v>
+      </c>
+      <c r="G303">
+        <v>10000000</v>
+      </c>
+      <c r="H303">
+        <v>1000</v>
+      </c>
+      <c r="I303">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>12</v>
+      </c>
+      <c r="B304" t="s">
+        <v>95</v>
+      </c>
+      <c r="C304" t="s">
+        <v>65</v>
+      </c>
+      <c r="D304">
+        <v>10000</v>
+      </c>
+      <c r="E304">
+        <v>10000</v>
+      </c>
+      <c r="F304">
+        <v>100</v>
+      </c>
+      <c r="G304">
+        <v>10000000</v>
+      </c>
+      <c r="H304">
+        <v>1000</v>
+      </c>
+      <c r="I304">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>12</v>
+      </c>
+      <c r="B305" t="s">
+        <v>96</v>
+      </c>
+      <c r="C305" t="s">
+        <v>64</v>
+      </c>
+      <c r="D305">
+        <v>10000</v>
+      </c>
+      <c r="E305">
+        <v>10000</v>
+      </c>
+      <c r="F305">
+        <v>100</v>
+      </c>
+      <c r="G305">
+        <v>10000000</v>
+      </c>
+      <c r="H305">
+        <v>1000</v>
+      </c>
+      <c r="I305">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>12</v>
+      </c>
+      <c r="B306" t="s">
+        <v>97</v>
+      </c>
+      <c r="C306" t="s">
+        <v>36</v>
+      </c>
+      <c r="D306">
+        <v>10000</v>
+      </c>
+      <c r="E306">
+        <v>10000</v>
+      </c>
+      <c r="F306">
+        <v>100</v>
+      </c>
+      <c r="G306">
+        <v>10000000</v>
+      </c>
+      <c r="H306">
+        <v>1000</v>
+      </c>
+      <c r="I306">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>12</v>
+      </c>
+      <c r="B307" t="s">
+        <v>98</v>
+      </c>
+      <c r="C307" t="s">
+        <v>34</v>
+      </c>
+      <c r="D307">
+        <v>10000</v>
+      </c>
+      <c r="E307">
+        <v>10000</v>
+      </c>
+      <c r="F307">
+        <v>100</v>
+      </c>
+      <c r="G307">
+        <v>10000000</v>
+      </c>
+      <c r="H307">
+        <v>1000</v>
+      </c>
+      <c r="I307">
         <v>1</v>
       </c>
     </row>
@@ -10347,7 +11275,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68B577B-1347-43AB-A697-F4519763B965}">
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -12089,6 +13017,28 @@
         <v>0</v>
       </c>
     </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>11</v>
+      </c>
+      <c r="B158" t="s">
+        <v>84</v>
+      </c>
+      <c r="C158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>12</v>
+      </c>
+      <c r="B159" t="s">
+        <v>84</v>
+      </c>
+      <c r="C159">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6584178-130D-4F54-9B44-93BAE78B7206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D090723C-22A6-4BFE-BF9A-F2325F44EED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="99">
   <si>
     <t>Commodities</t>
   </si>
@@ -1119,7 +1119,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B154"/>
+  <dimension ref="A1:B155"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -2352,6 +2352,14 @@
       </c>
       <c r="B154" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>84</v>
+      </c>
+      <c r="B155" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2361,7 +2369,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
-  <dimension ref="A1:I307"/>
+  <dimension ref="A1:I309"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -6119,7 +6127,7 @@
         <v>486.91</v>
       </c>
       <c r="E130">
-        <v>118.77099999999999</v>
+        <v>486.91</v>
       </c>
       <c r="F130">
         <v>1</v>
@@ -6148,7 +6156,7 @@
         <v>144.17500000000001</v>
       </c>
       <c r="E131">
-        <v>118.77099999999999</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="F131">
         <v>1</v>
@@ -6177,7 +6185,7 @@
         <v>49.494</v>
       </c>
       <c r="E132">
-        <v>500</v>
+        <v>49.494</v>
       </c>
       <c r="F132">
         <v>1</v>
@@ -6206,7 +6214,7 @@
         <v>816.06700000000012</v>
       </c>
       <c r="E133">
-        <v>500</v>
+        <v>816.06700000000012</v>
       </c>
       <c r="F133">
         <v>1</v>
@@ -6235,7 +6243,7 @@
         <v>188.88749999999999</v>
       </c>
       <c r="E134">
-        <v>500</v>
+        <v>188.88749999999999</v>
       </c>
       <c r="F134">
         <v>1</v>
@@ -6264,7 +6272,7 @@
         <v>89.716999999999999</v>
       </c>
       <c r="E135">
-        <v>500</v>
+        <v>89.716999999999999</v>
       </c>
       <c r="F135">
         <v>1</v>
@@ -6293,7 +6301,7 @@
         <v>170.63749999999999</v>
       </c>
       <c r="E136">
-        <v>500</v>
+        <v>170.63749999999999</v>
       </c>
       <c r="F136">
         <v>1</v>
@@ -6322,7 +6330,7 @@
         <v>12.1837</v>
       </c>
       <c r="E137">
-        <v>500</v>
+        <v>12.1837</v>
       </c>
       <c r="F137">
         <v>1</v>
@@ -6351,7 +6359,7 @@
         <v>256.15699999999998</v>
       </c>
       <c r="E138">
-        <v>500</v>
+        <v>256.15699999999998</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -6380,7 +6388,7 @@
         <v>61.32</v>
       </c>
       <c r="E139">
-        <v>500</v>
+        <v>61.32</v>
       </c>
       <c r="F139">
         <v>1</v>
@@ -6409,7 +6417,7 @@
         <v>180.20050000000001</v>
       </c>
       <c r="E140">
-        <v>500</v>
+        <v>180.20050000000001</v>
       </c>
       <c r="F140">
         <v>1</v>
@@ -6438,7 +6446,7 @@
         <v>421.21</v>
       </c>
       <c r="E141">
-        <v>500</v>
+        <v>421.21</v>
       </c>
       <c r="F141">
         <v>1</v>
@@ -6467,7 +6475,7 @@
         <v>123.04150000000001</v>
       </c>
       <c r="E142">
-        <v>500</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="F142">
         <v>1</v>
@@ -6496,7 +6504,7 @@
         <v>161.62200000000001</v>
       </c>
       <c r="E143">
-        <v>500</v>
+        <v>161.62200000000001</v>
       </c>
       <c r="F143">
         <v>1</v>
@@ -6525,7 +6533,7 @@
         <v>455.15499999999997</v>
       </c>
       <c r="E144">
-        <v>500</v>
+        <v>455.15499999999997</v>
       </c>
       <c r="F144">
         <v>1</v>
@@ -6554,7 +6562,7 @@
         <v>351.714</v>
       </c>
       <c r="E145">
-        <v>500</v>
+        <v>351.714</v>
       </c>
       <c r="F145">
         <v>1</v>
@@ -6583,7 +6591,7 @@
         <v>167.75399999999999</v>
       </c>
       <c r="E146">
-        <v>500</v>
+        <v>167.75399999999999</v>
       </c>
       <c r="F146">
         <v>1</v>
@@ -6612,7 +6620,7 @@
         <v>207.5025</v>
       </c>
       <c r="E147">
-        <v>500</v>
+        <v>207.5025</v>
       </c>
       <c r="F147">
         <v>1</v>
@@ -6641,7 +6649,7 @@
         <v>513.19000000000005</v>
       </c>
       <c r="E148">
-        <v>500</v>
+        <v>513.19000000000005</v>
       </c>
       <c r="F148">
         <v>1</v>
@@ -6670,7 +6678,7 @@
         <v>140.52500000000001</v>
       </c>
       <c r="E149">
-        <v>500</v>
+        <v>140.52500000000001</v>
       </c>
       <c r="F149">
         <v>1</v>
@@ -6699,7 +6707,7 @@
         <v>82.927999999999997</v>
       </c>
       <c r="E150">
-        <v>500</v>
+        <v>82.927999999999997</v>
       </c>
       <c r="F150">
         <v>1</v>
@@ -6728,7 +6736,7 @@
         <v>67.451999999999998</v>
       </c>
       <c r="E151">
-        <v>500</v>
+        <v>67.451999999999998</v>
       </c>
       <c r="F151">
         <v>1</v>
@@ -6754,10 +6762,10 @@
         <v>22</v>
       </c>
       <c r="D152">
-        <v>395</v>
+        <v>200.71350000000001</v>
       </c>
       <c r="E152">
-        <v>395</v>
+        <v>200.71350000000001</v>
       </c>
       <c r="F152">
         <v>1</v>
@@ -6783,10 +6791,10 @@
         <v>74</v>
       </c>
       <c r="D153">
-        <v>395</v>
+        <v>200.71350000000001</v>
       </c>
       <c r="E153">
-        <v>395</v>
+        <v>200.71350000000001</v>
       </c>
       <c r="F153">
         <v>1</v>
@@ -6812,10 +6820,10 @@
         <v>20</v>
       </c>
       <c r="D154">
-        <v>395</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="E154">
-        <v>395</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="F154">
         <v>1</v>
@@ -6832,19 +6840,19 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B155" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="C155" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="D155">
-        <v>500</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="E155">
-        <v>500</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="F155">
         <v>1</v>
@@ -6853,7 +6861,7 @@
         <v>10000000</v>
       </c>
       <c r="H155">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I155">
         <v>1</v>
@@ -6864,10 +6872,10 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C156" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D156">
         <v>500</v>
@@ -6893,10 +6901,10 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C157" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D157">
         <v>500</v>
@@ -6922,10 +6930,10 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C158" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D158">
         <v>500</v>
@@ -6951,10 +6959,10 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C159" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D159">
         <v>500</v>
@@ -6980,10 +6988,10 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C160" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D160">
         <v>500</v>
@@ -7009,10 +7017,10 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C161" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D161">
         <v>500</v>
@@ -7038,10 +7046,10 @@
         <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C162" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D162">
         <v>500</v>
@@ -7067,10 +7075,10 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C163" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D163">
         <v>500</v>
@@ -7096,10 +7104,10 @@
         <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C164" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D164">
         <v>500</v>
@@ -7125,10 +7133,10 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C165" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D165">
         <v>500</v>
@@ -7154,10 +7162,10 @@
         <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C166" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D166">
         <v>500</v>
@@ -7183,10 +7191,10 @@
         <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="C167" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="D167">
         <v>500</v>
@@ -7212,10 +7220,10 @@
         <v>12</v>
       </c>
       <c r="B168" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="C168" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="D168">
         <v>500</v>
@@ -7241,10 +7249,10 @@
         <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C169" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D169">
         <v>500</v>
@@ -7270,10 +7278,10 @@
         <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C170" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D170">
         <v>500</v>
@@ -7299,10 +7307,10 @@
         <v>12</v>
       </c>
       <c r="B171" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C171" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D171">
         <v>500</v>
@@ -7328,10 +7336,10 @@
         <v>12</v>
       </c>
       <c r="B172" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C172" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D172">
         <v>500</v>
@@ -7357,10 +7365,10 @@
         <v>12</v>
       </c>
       <c r="B173" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C173" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D173">
         <v>500</v>
@@ -7386,10 +7394,10 @@
         <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C174" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D174">
         <v>500</v>
@@ -7415,10 +7423,10 @@
         <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C175" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="D175">
         <v>500</v>
@@ -7444,10 +7452,10 @@
         <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C176" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D176">
         <v>500</v>
@@ -7473,10 +7481,10 @@
         <v>12</v>
       </c>
       <c r="B177" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C177" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D177">
         <v>500</v>
@@ -7502,10 +7510,10 @@
         <v>12</v>
       </c>
       <c r="B178" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C178" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D178">
         <v>500</v>
@@ -7531,10 +7539,10 @@
         <v>12</v>
       </c>
       <c r="B179" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C179" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D179">
         <v>500</v>
@@ -7560,10 +7568,10 @@
         <v>12</v>
       </c>
       <c r="B180" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C180" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D180">
         <v>500</v>
@@ -7592,7 +7600,7 @@
         <v>38</v>
       </c>
       <c r="C181" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="D181">
         <v>500</v>
@@ -7618,10 +7626,10 @@
         <v>12</v>
       </c>
       <c r="B182" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C182" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D182">
         <v>500</v>
@@ -7650,7 +7658,7 @@
         <v>16</v>
       </c>
       <c r="C183" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D183">
         <v>500</v>
@@ -7679,7 +7687,7 @@
         <v>16</v>
       </c>
       <c r="C184" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D184">
         <v>500</v>
@@ -7708,7 +7716,7 @@
         <v>16</v>
       </c>
       <c r="C185" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D185">
         <v>500</v>
@@ -7734,10 +7742,10 @@
         <v>12</v>
       </c>
       <c r="B186" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C186" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D186">
         <v>500</v>
@@ -7766,7 +7774,7 @@
         <v>28</v>
       </c>
       <c r="C187" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D187">
         <v>500</v>
@@ -7792,10 +7800,10 @@
         <v>12</v>
       </c>
       <c r="B188" t="s">
+        <v>28</v>
+      </c>
+      <c r="C188" t="s">
         <v>42</v>
-      </c>
-      <c r="C188" t="s">
-        <v>16</v>
       </c>
       <c r="D188">
         <v>500</v>
@@ -7824,7 +7832,7 @@
         <v>42</v>
       </c>
       <c r="C189" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D189">
         <v>500</v>
@@ -7853,7 +7861,7 @@
         <v>42</v>
       </c>
       <c r="C190" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="D190">
         <v>500</v>
@@ -7882,7 +7890,7 @@
         <v>42</v>
       </c>
       <c r="C191" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D191">
         <v>500</v>
@@ -7911,7 +7919,7 @@
         <v>42</v>
       </c>
       <c r="C192" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D192">
         <v>500</v>
@@ -7940,7 +7948,7 @@
         <v>42</v>
       </c>
       <c r="C193" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D193">
         <v>500</v>
@@ -7969,7 +7977,7 @@
         <v>42</v>
       </c>
       <c r="C194" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D194">
         <v>500</v>
@@ -7998,7 +8006,7 @@
         <v>42</v>
       </c>
       <c r="C195" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="D195">
         <v>500</v>
@@ -8027,7 +8035,7 @@
         <v>42</v>
       </c>
       <c r="C196" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D196">
         <v>500</v>
@@ -8053,10 +8061,10 @@
         <v>12</v>
       </c>
       <c r="B197" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C197" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D197">
         <v>500</v>
@@ -8085,7 +8093,7 @@
         <v>60</v>
       </c>
       <c r="C198" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D198">
         <v>500</v>
@@ -8114,7 +8122,7 @@
         <v>60</v>
       </c>
       <c r="C199" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="D199">
         <v>500</v>
@@ -8143,7 +8151,7 @@
         <v>60</v>
       </c>
       <c r="C200" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D200">
         <v>500</v>
@@ -8172,7 +8180,7 @@
         <v>60</v>
       </c>
       <c r="C201" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D201">
         <v>500</v>
@@ -8198,10 +8206,10 @@
         <v>12</v>
       </c>
       <c r="B202" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C202" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D202">
         <v>500</v>
@@ -8230,7 +8238,7 @@
         <v>22</v>
       </c>
       <c r="C203" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D203">
         <v>500</v>
@@ -8259,7 +8267,7 @@
         <v>22</v>
       </c>
       <c r="C204" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D204">
         <v>500</v>
@@ -8285,10 +8293,10 @@
         <v>12</v>
       </c>
       <c r="B205" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C205" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D205">
         <v>500</v>
@@ -8317,7 +8325,7 @@
         <v>61</v>
       </c>
       <c r="C206" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D206">
         <v>500</v>
@@ -8346,7 +8354,7 @@
         <v>61</v>
       </c>
       <c r="C207" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D207">
         <v>500</v>
@@ -8372,10 +8380,10 @@
         <v>12</v>
       </c>
       <c r="B208" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C208" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D208">
         <v>500</v>
@@ -8404,7 +8412,7 @@
         <v>64</v>
       </c>
       <c r="C209" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D209">
         <v>500</v>
@@ -8430,10 +8438,10 @@
         <v>12</v>
       </c>
       <c r="B210" t="s">
+        <v>64</v>
+      </c>
+      <c r="C210" t="s">
         <v>24</v>
-      </c>
-      <c r="C210" t="s">
-        <v>64</v>
       </c>
       <c r="D210">
         <v>500</v>
@@ -8462,7 +8470,7 @@
         <v>24</v>
       </c>
       <c r="C211" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D211">
         <v>500</v>
@@ -8488,10 +8496,10 @@
         <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C212" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="D212">
         <v>500</v>
@@ -8520,7 +8528,7 @@
         <v>18</v>
       </c>
       <c r="C213" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="D213">
         <v>500</v>
@@ -8549,7 +8557,7 @@
         <v>18</v>
       </c>
       <c r="C214" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D214">
         <v>500</v>
@@ -8575,10 +8583,10 @@
         <v>12</v>
       </c>
       <c r="B215" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C215" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D215">
         <v>500</v>
@@ -8604,7 +8612,7 @@
         <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C216" t="s">
         <v>42</v>
@@ -8633,7 +8641,7 @@
         <v>12</v>
       </c>
       <c r="B217" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="C217" t="s">
         <v>42</v>
@@ -8665,7 +8673,7 @@
         <v>62</v>
       </c>
       <c r="C218" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D218">
         <v>500</v>
@@ -8694,7 +8702,7 @@
         <v>62</v>
       </c>
       <c r="C219" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D219">
         <v>500</v>
@@ -8720,10 +8728,10 @@
         <v>12</v>
       </c>
       <c r="B220" t="s">
+        <v>62</v>
+      </c>
+      <c r="C220" t="s">
         <v>65</v>
-      </c>
-      <c r="C220" t="s">
-        <v>60</v>
       </c>
       <c r="D220">
         <v>500</v>
@@ -8752,7 +8760,7 @@
         <v>65</v>
       </c>
       <c r="C221" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D221">
         <v>500</v>
@@ -8781,7 +8789,7 @@
         <v>65</v>
       </c>
       <c r="C222" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D222">
         <v>500</v>
@@ -8810,7 +8818,7 @@
         <v>65</v>
       </c>
       <c r="C223" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D223">
         <v>500</v>
@@ -8836,10 +8844,10 @@
         <v>12</v>
       </c>
       <c r="B224" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C224" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="D224">
         <v>500</v>
@@ -8868,7 +8876,7 @@
         <v>66</v>
       </c>
       <c r="C225" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="D225">
         <v>500</v>
@@ -8897,7 +8905,7 @@
         <v>66</v>
       </c>
       <c r="C226" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D226">
         <v>500</v>
@@ -8926,7 +8934,7 @@
         <v>66</v>
       </c>
       <c r="C227" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D227">
         <v>500</v>
@@ -8952,10 +8960,10 @@
         <v>12</v>
       </c>
       <c r="B228" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C228" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D228">
         <v>500</v>
@@ -8984,7 +8992,7 @@
         <v>67</v>
       </c>
       <c r="C229" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D229">
         <v>500</v>
@@ -9010,10 +9018,10 @@
         <v>12</v>
       </c>
       <c r="B230" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C230" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D230">
         <v>500</v>
@@ -9042,7 +9050,7 @@
         <v>68</v>
       </c>
       <c r="C231" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="D231">
         <v>500</v>
@@ -9071,7 +9079,7 @@
         <v>68</v>
       </c>
       <c r="C232" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="D232">
         <v>500</v>
@@ -9100,7 +9108,7 @@
         <v>68</v>
       </c>
       <c r="C233" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="D233">
         <v>500</v>
@@ -9129,7 +9137,7 @@
         <v>68</v>
       </c>
       <c r="C234" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="D234">
         <v>500</v>
@@ -9155,10 +9163,10 @@
         <v>12</v>
       </c>
       <c r="B235" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="C235" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="D235">
         <v>500</v>
@@ -9184,10 +9192,10 @@
         <v>12</v>
       </c>
       <c r="B236" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="C236" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D236">
         <v>500</v>
@@ -9216,7 +9224,7 @@
         <v>51</v>
       </c>
       <c r="C237" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D237">
         <v>500</v>
@@ -9245,7 +9253,7 @@
         <v>51</v>
       </c>
       <c r="C238" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D238">
         <v>500</v>
@@ -9274,7 +9282,7 @@
         <v>51</v>
       </c>
       <c r="C239" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D239">
         <v>500</v>
@@ -9300,10 +9308,10 @@
         <v>12</v>
       </c>
       <c r="B240" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C240" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D240">
         <v>500</v>
@@ -9332,7 +9340,7 @@
         <v>26</v>
       </c>
       <c r="C241" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="D241">
         <v>500</v>
@@ -9358,10 +9366,10 @@
         <v>12</v>
       </c>
       <c r="B242" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="C242" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D242">
         <v>500</v>
@@ -9390,7 +9398,7 @@
         <v>72</v>
       </c>
       <c r="C243" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="D243">
         <v>500</v>
@@ -9416,10 +9424,10 @@
         <v>12</v>
       </c>
       <c r="B244" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C244" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D244">
         <v>500</v>
@@ -9448,7 +9456,7 @@
         <v>34</v>
       </c>
       <c r="C245" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D245">
         <v>500</v>
@@ -9474,10 +9482,10 @@
         <v>12</v>
       </c>
       <c r="B246" t="s">
+        <v>34</v>
+      </c>
+      <c r="C246" t="s">
         <v>32</v>
-      </c>
-      <c r="C246" t="s">
-        <v>34</v>
       </c>
       <c r="D246">
         <v>500</v>
@@ -9503,10 +9511,10 @@
         <v>12</v>
       </c>
       <c r="B247" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C247" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D247">
         <v>500</v>
@@ -9535,7 +9543,7 @@
         <v>58</v>
       </c>
       <c r="C248" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D248">
         <v>500</v>
@@ -9564,7 +9572,7 @@
         <v>58</v>
       </c>
       <c r="C249" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D249">
         <v>500</v>
@@ -9593,7 +9601,7 @@
         <v>58</v>
       </c>
       <c r="C250" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D250">
         <v>500</v>
@@ -9619,7 +9627,7 @@
         <v>12</v>
       </c>
       <c r="B251" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C251" t="s">
         <v>51</v>
@@ -9648,10 +9656,10 @@
         <v>12</v>
       </c>
       <c r="B252" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C252" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D252">
         <v>500</v>
@@ -9680,7 +9688,7 @@
         <v>53</v>
       </c>
       <c r="C253" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="D253">
         <v>500</v>
@@ -9709,7 +9717,7 @@
         <v>53</v>
       </c>
       <c r="C254" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D254">
         <v>500</v>
@@ -9735,10 +9743,10 @@
         <v>12</v>
       </c>
       <c r="B255" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C255" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="D255">
         <v>500</v>
@@ -9764,10 +9772,10 @@
         <v>12</v>
       </c>
       <c r="B256" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C256" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="D256">
         <v>500</v>
@@ -9796,7 +9804,7 @@
         <v>36</v>
       </c>
       <c r="C257" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D257">
         <v>500</v>
@@ -9822,10 +9830,10 @@
         <v>12</v>
       </c>
       <c r="B258" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C258" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D258">
         <v>500</v>
@@ -9854,7 +9862,7 @@
         <v>48</v>
       </c>
       <c r="C259" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D259">
         <v>500</v>
@@ -9883,7 +9891,7 @@
         <v>48</v>
       </c>
       <c r="C260" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D260">
         <v>500</v>
@@ -9912,7 +9920,7 @@
         <v>48</v>
       </c>
       <c r="C261" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D261">
         <v>500</v>
@@ -9938,10 +9946,10 @@
         <v>12</v>
       </c>
       <c r="B262" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C262" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D262">
         <v>500</v>
@@ -9967,10 +9975,10 @@
         <v>12</v>
       </c>
       <c r="B263" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C263" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D263">
         <v>500</v>
@@ -9996,7 +10004,7 @@
         <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C264" t="s">
         <v>22</v>
@@ -10025,10 +10033,10 @@
         <v>12</v>
       </c>
       <c r="B265" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C265" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D265">
         <v>500</v>
@@ -10057,7 +10065,7 @@
         <v>75</v>
       </c>
       <c r="C266" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D266">
         <v>500</v>
@@ -10083,10 +10091,10 @@
         <v>12</v>
       </c>
       <c r="B267" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C267" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="D267">
         <v>500</v>
@@ -10112,10 +10120,10 @@
         <v>12</v>
       </c>
       <c r="B268" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="C268" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="D268">
         <v>500</v>
@@ -10141,10 +10149,10 @@
         <v>12</v>
       </c>
       <c r="B269" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C269" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D269">
         <v>500</v>
@@ -10173,7 +10181,7 @@
         <v>58</v>
       </c>
       <c r="C270" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D270">
         <v>500</v>
@@ -10202,7 +10210,7 @@
         <v>58</v>
       </c>
       <c r="C271" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D271">
         <v>500</v>
@@ -10228,7 +10236,7 @@
         <v>12</v>
       </c>
       <c r="B272" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C272" t="s">
         <v>66</v>
@@ -10257,10 +10265,10 @@
         <v>12</v>
       </c>
       <c r="B273" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C273" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D273">
         <v>500</v>
@@ -10289,7 +10297,7 @@
         <v>68</v>
       </c>
       <c r="C274" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D274">
         <v>500</v>
@@ -10315,10 +10323,10 @@
         <v>12</v>
       </c>
       <c r="B275" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="C275" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D275">
         <v>500</v>
@@ -10344,10 +10352,10 @@
         <v>12</v>
       </c>
       <c r="B276" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C276" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D276">
         <v>500</v>
@@ -10373,10 +10381,10 @@
         <v>12</v>
       </c>
       <c r="B277" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C277" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="D277">
         <v>500</v>
@@ -10402,7 +10410,7 @@
         <v>12</v>
       </c>
       <c r="B278" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C278" t="s">
         <v>22</v>
@@ -10431,10 +10439,10 @@
         <v>12</v>
       </c>
       <c r="B279" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="C279" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D279">
         <v>500</v>
@@ -10460,7 +10468,7 @@
         <v>12</v>
       </c>
       <c r="B280" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C280" t="s">
         <v>34</v>
@@ -10489,10 +10497,10 @@
         <v>12</v>
       </c>
       <c r="B281" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="C281" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D281">
         <v>500</v>
@@ -10521,7 +10529,7 @@
         <v>48</v>
       </c>
       <c r="C282" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D282">
         <v>500</v>
@@ -10550,7 +10558,7 @@
         <v>48</v>
       </c>
       <c r="C283" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D283">
         <v>500</v>
@@ -10579,7 +10587,7 @@
         <v>48</v>
       </c>
       <c r="C284" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D284">
         <v>500</v>
@@ -10608,7 +10616,7 @@
         <v>48</v>
       </c>
       <c r="C285" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="D285">
         <v>500</v>
@@ -10634,10 +10642,10 @@
         <v>12</v>
       </c>
       <c r="B286" t="s">
+        <v>48</v>
+      </c>
+      <c r="C286" t="s">
         <v>38</v>
-      </c>
-      <c r="C286" t="s">
-        <v>79</v>
       </c>
       <c r="D286">
         <v>500</v>
@@ -10666,7 +10674,7 @@
         <v>38</v>
       </c>
       <c r="C287" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="D287">
         <v>500</v>
@@ -10695,7 +10703,7 @@
         <v>38</v>
       </c>
       <c r="C288" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D288">
         <v>500</v>
@@ -10721,10 +10729,10 @@
         <v>12</v>
       </c>
       <c r="B289" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="C289" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D289">
         <v>500</v>
@@ -10750,10 +10758,10 @@
         <v>12</v>
       </c>
       <c r="B290" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="C290" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="D290">
         <v>500</v>
@@ -10779,10 +10787,10 @@
         <v>12</v>
       </c>
       <c r="B291" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="C291" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="D291">
         <v>500</v>
@@ -10808,19 +10816,19 @@
         <v>12</v>
       </c>
       <c r="B292" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C292" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
       <c r="D292">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="E292">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="F292">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G292">
         <v>10000000</v>
@@ -10837,19 +10845,19 @@
         <v>12</v>
       </c>
       <c r="B293" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C293" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D293">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="E293">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="F293">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G293">
         <v>10000000</v>
@@ -10866,10 +10874,10 @@
         <v>12</v>
       </c>
       <c r="B294" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C294" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D294">
         <v>10000</v>
@@ -10895,10 +10903,10 @@
         <v>12</v>
       </c>
       <c r="B295" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C295" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="D295">
         <v>10000</v>
@@ -10924,10 +10932,10 @@
         <v>12</v>
       </c>
       <c r="B296" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C296" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D296">
         <v>10000</v>
@@ -10953,10 +10961,10 @@
         <v>12</v>
       </c>
       <c r="B297" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C297" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D297">
         <v>10000</v>
@@ -10982,10 +10990,10 @@
         <v>12</v>
       </c>
       <c r="B298" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C298" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D298">
         <v>10000</v>
@@ -11011,10 +11019,10 @@
         <v>12</v>
       </c>
       <c r="B299" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C299" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D299">
         <v>10000</v>
@@ -11040,10 +11048,10 @@
         <v>12</v>
       </c>
       <c r="B300" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C300" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="D300">
         <v>10000</v>
@@ -11069,10 +11077,10 @@
         <v>12</v>
       </c>
       <c r="B301" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C301" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="D301">
         <v>10000</v>
@@ -11098,10 +11106,10 @@
         <v>12</v>
       </c>
       <c r="B302" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C302" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="D302">
         <v>10000</v>
@@ -11127,10 +11135,10 @@
         <v>12</v>
       </c>
       <c r="B303" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C303" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D303">
         <v>10000</v>
@@ -11156,10 +11164,10 @@
         <v>12</v>
       </c>
       <c r="B304" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C304" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D304">
         <v>10000</v>
@@ -11185,10 +11193,10 @@
         <v>12</v>
       </c>
       <c r="B305" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C305" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D305">
         <v>10000</v>
@@ -11214,10 +11222,10 @@
         <v>12</v>
       </c>
       <c r="B306" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C306" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="D306">
         <v>10000</v>
@@ -11243,10 +11251,10 @@
         <v>12</v>
       </c>
       <c r="B307" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C307" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="D307">
         <v>10000</v>
@@ -11264,6 +11272,64 @@
         <v>1000</v>
       </c>
       <c r="I307">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>12</v>
+      </c>
+      <c r="B308" t="s">
+        <v>97</v>
+      </c>
+      <c r="C308" t="s">
+        <v>36</v>
+      </c>
+      <c r="D308">
+        <v>10000</v>
+      </c>
+      <c r="E308">
+        <v>10000</v>
+      </c>
+      <c r="F308">
+        <v>100</v>
+      </c>
+      <c r="G308">
+        <v>10000000</v>
+      </c>
+      <c r="H308">
+        <v>1000</v>
+      </c>
+      <c r="I308">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>12</v>
+      </c>
+      <c r="B309" t="s">
+        <v>98</v>
+      </c>
+      <c r="C309" t="s">
+        <v>34</v>
+      </c>
+      <c r="D309">
+        <v>10000</v>
+      </c>
+      <c r="E309">
+        <v>10000</v>
+      </c>
+      <c r="F309">
+        <v>100</v>
+      </c>
+      <c r="G309">
+        <v>10000000</v>
+      </c>
+      <c r="H309">
+        <v>1000</v>
+      </c>
+      <c r="I309">
         <v>1</v>
       </c>
     </row>
@@ -11297,7 +11363,7 @@
         <v>15</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>111.378</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -11308,7 +11374,7 @@
         <v>17</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>322.40999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -11319,7 +11385,7 @@
         <v>19</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>73.274999999999991</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -11330,7 +11396,7 @@
         <v>21</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>155.83149999999998</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -11341,7 +11407,7 @@
         <v>23</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>25.402000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -11352,7 +11418,7 @@
         <v>25</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>39.08</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -11363,7 +11429,7 @@
         <v>27</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>122.125</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -11374,7 +11440,7 @@
         <v>29</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>60.573999999999998</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -11385,7 +11451,7 @@
         <v>31</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>74.251999999999995</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -11396,7 +11462,7 @@
         <v>33</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>655.56699999999989</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -11407,7 +11473,7 @@
         <v>35</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>425.97199999999998</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -11418,7 +11484,7 @@
         <v>37</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>510.97099999999995</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D090723C-22A6-4BFE-BF9A-F2325F44EED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{670EB0CF-6BF9-4B32-A097-98F6C60D675C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="99">
   <si>
     <t>Commodities</t>
   </si>
@@ -1119,7 +1119,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B155"/>
+  <dimension ref="A1:B156"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -2360,6 +2360,14 @@
       </c>
       <c r="B155" t="s">
         <v>78</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>84</v>
+      </c>
+      <c r="B156" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -2369,7 +2377,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
-  <dimension ref="A1:I309"/>
+  <dimension ref="A1:I311"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -6869,19 +6877,19 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B156" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="C156" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="D156">
-        <v>500</v>
+        <v>421.21</v>
       </c>
       <c r="E156">
-        <v>500</v>
+        <v>421.21</v>
       </c>
       <c r="F156">
         <v>1</v>
@@ -6890,7 +6898,7 @@
         <v>10000000</v>
       </c>
       <c r="H156">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I156">
         <v>1</v>
@@ -6901,10 +6909,10 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C157" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D157">
         <v>500</v>
@@ -6930,10 +6938,10 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C158" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D158">
         <v>500</v>
@@ -6959,10 +6967,10 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C159" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D159">
         <v>500</v>
@@ -6988,10 +6996,10 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C160" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D160">
         <v>500</v>
@@ -7017,10 +7025,10 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C161" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D161">
         <v>500</v>
@@ -7046,10 +7054,10 @@
         <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C162" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D162">
         <v>500</v>
@@ -7075,10 +7083,10 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C163" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D163">
         <v>500</v>
@@ -7104,10 +7112,10 @@
         <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C164" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D164">
         <v>500</v>
@@ -7133,10 +7141,10 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C165" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D165">
         <v>500</v>
@@ -7162,10 +7170,10 @@
         <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C166" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D166">
         <v>500</v>
@@ -7191,10 +7199,10 @@
         <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C167" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D167">
         <v>500</v>
@@ -7220,10 +7228,10 @@
         <v>12</v>
       </c>
       <c r="B168" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="C168" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="D168">
         <v>500</v>
@@ -7249,10 +7257,10 @@
         <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="C169" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="D169">
         <v>500</v>
@@ -7278,10 +7286,10 @@
         <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C170" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D170">
         <v>500</v>
@@ -7307,10 +7315,10 @@
         <v>12</v>
       </c>
       <c r="B171" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C171" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D171">
         <v>500</v>
@@ -7336,10 +7344,10 @@
         <v>12</v>
       </c>
       <c r="B172" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C172" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D172">
         <v>500</v>
@@ -7365,10 +7373,10 @@
         <v>12</v>
       </c>
       <c r="B173" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C173" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D173">
         <v>500</v>
@@ -7394,10 +7402,10 @@
         <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C174" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D174">
         <v>500</v>
@@ -7423,10 +7431,10 @@
         <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C175" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D175">
         <v>500</v>
@@ -7452,10 +7460,10 @@
         <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C176" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="D176">
         <v>500</v>
@@ -7481,10 +7489,10 @@
         <v>12</v>
       </c>
       <c r="B177" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C177" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D177">
         <v>500</v>
@@ -7510,10 +7518,10 @@
         <v>12</v>
       </c>
       <c r="B178" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C178" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D178">
         <v>500</v>
@@ -7539,10 +7547,10 @@
         <v>12</v>
       </c>
       <c r="B179" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C179" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D179">
         <v>500</v>
@@ -7568,10 +7576,10 @@
         <v>12</v>
       </c>
       <c r="B180" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C180" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D180">
         <v>500</v>
@@ -7597,10 +7605,10 @@
         <v>12</v>
       </c>
       <c r="B181" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C181" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D181">
         <v>500</v>
@@ -7629,7 +7637,7 @@
         <v>38</v>
       </c>
       <c r="C182" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="D182">
         <v>500</v>
@@ -7655,10 +7663,10 @@
         <v>12</v>
       </c>
       <c r="B183" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C183" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D183">
         <v>500</v>
@@ -7687,7 +7695,7 @@
         <v>16</v>
       </c>
       <c r="C184" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D184">
         <v>500</v>
@@ -7716,7 +7724,7 @@
         <v>16</v>
       </c>
       <c r="C185" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D185">
         <v>500</v>
@@ -7745,7 +7753,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D186">
         <v>500</v>
@@ -7771,10 +7779,10 @@
         <v>12</v>
       </c>
       <c r="B187" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C187" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D187">
         <v>500</v>
@@ -7803,7 +7811,7 @@
         <v>28</v>
       </c>
       <c r="C188" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D188">
         <v>500</v>
@@ -7829,10 +7837,10 @@
         <v>12</v>
       </c>
       <c r="B189" t="s">
+        <v>28</v>
+      </c>
+      <c r="C189" t="s">
         <v>42</v>
-      </c>
-      <c r="C189" t="s">
-        <v>16</v>
       </c>
       <c r="D189">
         <v>500</v>
@@ -7861,7 +7869,7 @@
         <v>42</v>
       </c>
       <c r="C190" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D190">
         <v>500</v>
@@ -7890,7 +7898,7 @@
         <v>42</v>
       </c>
       <c r="C191" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="D191">
         <v>500</v>
@@ -7919,7 +7927,7 @@
         <v>42</v>
       </c>
       <c r="C192" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D192">
         <v>500</v>
@@ -7948,7 +7956,7 @@
         <v>42</v>
       </c>
       <c r="C193" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D193">
         <v>500</v>
@@ -7977,7 +7985,7 @@
         <v>42</v>
       </c>
       <c r="C194" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D194">
         <v>500</v>
@@ -8006,7 +8014,7 @@
         <v>42</v>
       </c>
       <c r="C195" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D195">
         <v>500</v>
@@ -8035,7 +8043,7 @@
         <v>42</v>
       </c>
       <c r="C196" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="D196">
         <v>500</v>
@@ -8064,7 +8072,7 @@
         <v>42</v>
       </c>
       <c r="C197" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D197">
         <v>500</v>
@@ -8090,10 +8098,10 @@
         <v>12</v>
       </c>
       <c r="B198" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C198" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D198">
         <v>500</v>
@@ -8122,7 +8130,7 @@
         <v>60</v>
       </c>
       <c r="C199" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D199">
         <v>500</v>
@@ -8151,7 +8159,7 @@
         <v>60</v>
       </c>
       <c r="C200" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="D200">
         <v>500</v>
@@ -8180,7 +8188,7 @@
         <v>60</v>
       </c>
       <c r="C201" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D201">
         <v>500</v>
@@ -8209,7 +8217,7 @@
         <v>60</v>
       </c>
       <c r="C202" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D202">
         <v>500</v>
@@ -8235,10 +8243,10 @@
         <v>12</v>
       </c>
       <c r="B203" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C203" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D203">
         <v>500</v>
@@ -8267,7 +8275,7 @@
         <v>22</v>
       </c>
       <c r="C204" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D204">
         <v>500</v>
@@ -8296,7 +8304,7 @@
         <v>22</v>
       </c>
       <c r="C205" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D205">
         <v>500</v>
@@ -8322,10 +8330,10 @@
         <v>12</v>
       </c>
       <c r="B206" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C206" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D206">
         <v>500</v>
@@ -8354,7 +8362,7 @@
         <v>61</v>
       </c>
       <c r="C207" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D207">
         <v>500</v>
@@ -8383,7 +8391,7 @@
         <v>61</v>
       </c>
       <c r="C208" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D208">
         <v>500</v>
@@ -8409,10 +8417,10 @@
         <v>12</v>
       </c>
       <c r="B209" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C209" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D209">
         <v>500</v>
@@ -8441,7 +8449,7 @@
         <v>64</v>
       </c>
       <c r="C210" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D210">
         <v>500</v>
@@ -8467,10 +8475,10 @@
         <v>12</v>
       </c>
       <c r="B211" t="s">
+        <v>64</v>
+      </c>
+      <c r="C211" t="s">
         <v>24</v>
-      </c>
-      <c r="C211" t="s">
-        <v>64</v>
       </c>
       <c r="D211">
         <v>500</v>
@@ -8499,7 +8507,7 @@
         <v>24</v>
       </c>
       <c r="C212" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D212">
         <v>500</v>
@@ -8525,10 +8533,10 @@
         <v>12</v>
       </c>
       <c r="B213" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C213" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="D213">
         <v>500</v>
@@ -8557,7 +8565,7 @@
         <v>18</v>
       </c>
       <c r="C214" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="D214">
         <v>500</v>
@@ -8586,7 +8594,7 @@
         <v>18</v>
       </c>
       <c r="C215" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D215">
         <v>500</v>
@@ -8612,10 +8620,10 @@
         <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C216" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D216">
         <v>500</v>
@@ -8641,7 +8649,7 @@
         <v>12</v>
       </c>
       <c r="B217" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C217" t="s">
         <v>42</v>
@@ -8670,7 +8678,7 @@
         <v>12</v>
       </c>
       <c r="B218" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="C218" t="s">
         <v>42</v>
@@ -8702,7 +8710,7 @@
         <v>62</v>
       </c>
       <c r="C219" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D219">
         <v>500</v>
@@ -8731,7 +8739,7 @@
         <v>62</v>
       </c>
       <c r="C220" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D220">
         <v>500</v>
@@ -8757,10 +8765,10 @@
         <v>12</v>
       </c>
       <c r="B221" t="s">
+        <v>62</v>
+      </c>
+      <c r="C221" t="s">
         <v>65</v>
-      </c>
-      <c r="C221" t="s">
-        <v>60</v>
       </c>
       <c r="D221">
         <v>500</v>
@@ -8789,7 +8797,7 @@
         <v>65</v>
       </c>
       <c r="C222" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D222">
         <v>500</v>
@@ -8818,7 +8826,7 @@
         <v>65</v>
       </c>
       <c r="C223" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D223">
         <v>500</v>
@@ -8847,7 +8855,7 @@
         <v>65</v>
       </c>
       <c r="C224" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D224">
         <v>500</v>
@@ -8873,10 +8881,10 @@
         <v>12</v>
       </c>
       <c r="B225" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C225" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="D225">
         <v>500</v>
@@ -8905,7 +8913,7 @@
         <v>66</v>
       </c>
       <c r="C226" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="D226">
         <v>500</v>
@@ -8934,7 +8942,7 @@
         <v>66</v>
       </c>
       <c r="C227" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D227">
         <v>500</v>
@@ -8963,7 +8971,7 @@
         <v>66</v>
       </c>
       <c r="C228" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D228">
         <v>500</v>
@@ -8989,10 +8997,10 @@
         <v>12</v>
       </c>
       <c r="B229" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C229" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D229">
         <v>500</v>
@@ -9021,7 +9029,7 @@
         <v>67</v>
       </c>
       <c r="C230" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D230">
         <v>500</v>
@@ -9047,10 +9055,10 @@
         <v>12</v>
       </c>
       <c r="B231" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C231" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D231">
         <v>500</v>
@@ -9079,7 +9087,7 @@
         <v>68</v>
       </c>
       <c r="C232" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="D232">
         <v>500</v>
@@ -9108,7 +9116,7 @@
         <v>68</v>
       </c>
       <c r="C233" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="D233">
         <v>500</v>
@@ -9137,7 +9145,7 @@
         <v>68</v>
       </c>
       <c r="C234" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="D234">
         <v>500</v>
@@ -9166,7 +9174,7 @@
         <v>68</v>
       </c>
       <c r="C235" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="D235">
         <v>500</v>
@@ -9192,10 +9200,10 @@
         <v>12</v>
       </c>
       <c r="B236" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="C236" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="D236">
         <v>500</v>
@@ -9221,10 +9229,10 @@
         <v>12</v>
       </c>
       <c r="B237" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="C237" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D237">
         <v>500</v>
@@ -9253,7 +9261,7 @@
         <v>51</v>
       </c>
       <c r="C238" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D238">
         <v>500</v>
@@ -9282,7 +9290,7 @@
         <v>51</v>
       </c>
       <c r="C239" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D239">
         <v>500</v>
@@ -9311,7 +9319,7 @@
         <v>51</v>
       </c>
       <c r="C240" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D240">
         <v>500</v>
@@ -9337,10 +9345,10 @@
         <v>12</v>
       </c>
       <c r="B241" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C241" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D241">
         <v>500</v>
@@ -9369,7 +9377,7 @@
         <v>26</v>
       </c>
       <c r="C242" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="D242">
         <v>500</v>
@@ -9395,10 +9403,10 @@
         <v>12</v>
       </c>
       <c r="B243" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="C243" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D243">
         <v>500</v>
@@ -9427,7 +9435,7 @@
         <v>72</v>
       </c>
       <c r="C244" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="D244">
         <v>500</v>
@@ -9453,10 +9461,10 @@
         <v>12</v>
       </c>
       <c r="B245" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C245" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D245">
         <v>500</v>
@@ -9485,7 +9493,7 @@
         <v>34</v>
       </c>
       <c r="C246" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D246">
         <v>500</v>
@@ -9511,10 +9519,10 @@
         <v>12</v>
       </c>
       <c r="B247" t="s">
+        <v>34</v>
+      </c>
+      <c r="C247" t="s">
         <v>32</v>
-      </c>
-      <c r="C247" t="s">
-        <v>34</v>
       </c>
       <c r="D247">
         <v>500</v>
@@ -9540,10 +9548,10 @@
         <v>12</v>
       </c>
       <c r="B248" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C248" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D248">
         <v>500</v>
@@ -9572,7 +9580,7 @@
         <v>58</v>
       </c>
       <c r="C249" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D249">
         <v>500</v>
@@ -9601,7 +9609,7 @@
         <v>58</v>
       </c>
       <c r="C250" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D250">
         <v>500</v>
@@ -9630,7 +9638,7 @@
         <v>58</v>
       </c>
       <c r="C251" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D251">
         <v>500</v>
@@ -9656,7 +9664,7 @@
         <v>12</v>
       </c>
       <c r="B252" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C252" t="s">
         <v>51</v>
@@ -9685,10 +9693,10 @@
         <v>12</v>
       </c>
       <c r="B253" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C253" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D253">
         <v>500</v>
@@ -9717,7 +9725,7 @@
         <v>53</v>
       </c>
       <c r="C254" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="D254">
         <v>500</v>
@@ -9746,7 +9754,7 @@
         <v>53</v>
       </c>
       <c r="C255" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D255">
         <v>500</v>
@@ -9772,10 +9780,10 @@
         <v>12</v>
       </c>
       <c r="B256" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C256" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="D256">
         <v>500</v>
@@ -9801,10 +9809,10 @@
         <v>12</v>
       </c>
       <c r="B257" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C257" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="D257">
         <v>500</v>
@@ -9833,7 +9841,7 @@
         <v>36</v>
       </c>
       <c r="C258" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D258">
         <v>500</v>
@@ -9859,10 +9867,10 @@
         <v>12</v>
       </c>
       <c r="B259" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C259" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D259">
         <v>500</v>
@@ -9891,7 +9899,7 @@
         <v>48</v>
       </c>
       <c r="C260" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D260">
         <v>500</v>
@@ -9920,7 +9928,7 @@
         <v>48</v>
       </c>
       <c r="C261" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D261">
         <v>500</v>
@@ -9949,7 +9957,7 @@
         <v>48</v>
       </c>
       <c r="C262" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D262">
         <v>500</v>
@@ -9975,10 +9983,10 @@
         <v>12</v>
       </c>
       <c r="B263" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C263" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D263">
         <v>500</v>
@@ -10004,10 +10012,10 @@
         <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C264" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D264">
         <v>500</v>
@@ -10033,7 +10041,7 @@
         <v>12</v>
       </c>
       <c r="B265" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C265" t="s">
         <v>22</v>
@@ -10062,10 +10070,10 @@
         <v>12</v>
       </c>
       <c r="B266" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C266" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D266">
         <v>500</v>
@@ -10094,7 +10102,7 @@
         <v>75</v>
       </c>
       <c r="C267" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D267">
         <v>500</v>
@@ -10120,10 +10128,10 @@
         <v>12</v>
       </c>
       <c r="B268" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C268" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="D268">
         <v>500</v>
@@ -10149,10 +10157,10 @@
         <v>12</v>
       </c>
       <c r="B269" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="C269" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="D269">
         <v>500</v>
@@ -10178,10 +10186,10 @@
         <v>12</v>
       </c>
       <c r="B270" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C270" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D270">
         <v>500</v>
@@ -10210,7 +10218,7 @@
         <v>58</v>
       </c>
       <c r="C271" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D271">
         <v>500</v>
@@ -10239,7 +10247,7 @@
         <v>58</v>
       </c>
       <c r="C272" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D272">
         <v>500</v>
@@ -10265,7 +10273,7 @@
         <v>12</v>
       </c>
       <c r="B273" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C273" t="s">
         <v>66</v>
@@ -10294,10 +10302,10 @@
         <v>12</v>
       </c>
       <c r="B274" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C274" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D274">
         <v>500</v>
@@ -10326,7 +10334,7 @@
         <v>68</v>
       </c>
       <c r="C275" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D275">
         <v>500</v>
@@ -10352,10 +10360,10 @@
         <v>12</v>
       </c>
       <c r="B276" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="C276" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D276">
         <v>500</v>
@@ -10381,10 +10389,10 @@
         <v>12</v>
       </c>
       <c r="B277" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C277" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D277">
         <v>500</v>
@@ -10410,10 +10418,10 @@
         <v>12</v>
       </c>
       <c r="B278" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C278" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="D278">
         <v>500</v>
@@ -10439,7 +10447,7 @@
         <v>12</v>
       </c>
       <c r="B279" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C279" t="s">
         <v>22</v>
@@ -10468,10 +10476,10 @@
         <v>12</v>
       </c>
       <c r="B280" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="C280" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D280">
         <v>500</v>
@@ -10497,7 +10505,7 @@
         <v>12</v>
       </c>
       <c r="B281" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C281" t="s">
         <v>34</v>
@@ -10526,10 +10534,10 @@
         <v>12</v>
       </c>
       <c r="B282" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="C282" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D282">
         <v>500</v>
@@ -10558,7 +10566,7 @@
         <v>48</v>
       </c>
       <c r="C283" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D283">
         <v>500</v>
@@ -10587,7 +10595,7 @@
         <v>48</v>
       </c>
       <c r="C284" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D284">
         <v>500</v>
@@ -10616,7 +10624,7 @@
         <v>48</v>
       </c>
       <c r="C285" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D285">
         <v>500</v>
@@ -10645,7 +10653,7 @@
         <v>48</v>
       </c>
       <c r="C286" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="D286">
         <v>500</v>
@@ -10671,10 +10679,10 @@
         <v>12</v>
       </c>
       <c r="B287" t="s">
+        <v>48</v>
+      </c>
+      <c r="C287" t="s">
         <v>38</v>
-      </c>
-      <c r="C287" t="s">
-        <v>79</v>
       </c>
       <c r="D287">
         <v>500</v>
@@ -10703,7 +10711,7 @@
         <v>38</v>
       </c>
       <c r="C288" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="D288">
         <v>500</v>
@@ -10732,7 +10740,7 @@
         <v>38</v>
       </c>
       <c r="C289" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D289">
         <v>500</v>
@@ -10758,10 +10766,10 @@
         <v>12</v>
       </c>
       <c r="B290" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="C290" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D290">
         <v>500</v>
@@ -10787,10 +10795,10 @@
         <v>12</v>
       </c>
       <c r="B291" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="C291" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="D291">
         <v>500</v>
@@ -10816,10 +10824,10 @@
         <v>12</v>
       </c>
       <c r="B292" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="C292" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="D292">
         <v>500</v>
@@ -10845,10 +10853,10 @@
         <v>12</v>
       </c>
       <c r="B293" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C293" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="D293">
         <v>500</v>
@@ -10874,19 +10882,19 @@
         <v>12</v>
       </c>
       <c r="B294" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C294" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D294">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="E294">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="F294">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G294">
         <v>10000000</v>
@@ -10900,22 +10908,22 @@
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B295" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C295" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="D295">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="E295">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="F295">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G295">
         <v>10000000</v>
@@ -10932,10 +10940,10 @@
         <v>12</v>
       </c>
       <c r="B296" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C296" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D296">
         <v>10000</v>
@@ -10961,10 +10969,10 @@
         <v>12</v>
       </c>
       <c r="B297" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C297" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="D297">
         <v>10000</v>
@@ -10990,10 +10998,10 @@
         <v>12</v>
       </c>
       <c r="B298" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C298" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D298">
         <v>10000</v>
@@ -11019,10 +11027,10 @@
         <v>12</v>
       </c>
       <c r="B299" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C299" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D299">
         <v>10000</v>
@@ -11048,10 +11056,10 @@
         <v>12</v>
       </c>
       <c r="B300" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C300" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D300">
         <v>10000</v>
@@ -11077,10 +11085,10 @@
         <v>12</v>
       </c>
       <c r="B301" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C301" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D301">
         <v>10000</v>
@@ -11106,10 +11114,10 @@
         <v>12</v>
       </c>
       <c r="B302" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C302" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="D302">
         <v>10000</v>
@@ -11135,10 +11143,10 @@
         <v>12</v>
       </c>
       <c r="B303" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C303" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="D303">
         <v>10000</v>
@@ -11164,10 +11172,10 @@
         <v>12</v>
       </c>
       <c r="B304" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C304" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="D304">
         <v>10000</v>
@@ -11193,10 +11201,10 @@
         <v>12</v>
       </c>
       <c r="B305" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C305" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D305">
         <v>10000</v>
@@ -11222,10 +11230,10 @@
         <v>12</v>
       </c>
       <c r="B306" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C306" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D306">
         <v>10000</v>
@@ -11251,10 +11259,10 @@
         <v>12</v>
       </c>
       <c r="B307" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C307" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D307">
         <v>10000</v>
@@ -11280,10 +11288,10 @@
         <v>12</v>
       </c>
       <c r="B308" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C308" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="D308">
         <v>10000</v>
@@ -11309,10 +11317,10 @@
         <v>12</v>
       </c>
       <c r="B309" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C309" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="D309">
         <v>10000</v>
@@ -11330,6 +11338,64 @@
         <v>1000</v>
       </c>
       <c r="I309">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>12</v>
+      </c>
+      <c r="B310" t="s">
+        <v>97</v>
+      </c>
+      <c r="C310" t="s">
+        <v>36</v>
+      </c>
+      <c r="D310">
+        <v>10000</v>
+      </c>
+      <c r="E310">
+        <v>10000</v>
+      </c>
+      <c r="F310">
+        <v>100</v>
+      </c>
+      <c r="G310">
+        <v>10000000</v>
+      </c>
+      <c r="H310">
+        <v>1000</v>
+      </c>
+      <c r="I310">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>12</v>
+      </c>
+      <c r="B311" t="s">
+        <v>98</v>
+      </c>
+      <c r="C311" t="s">
+        <v>34</v>
+      </c>
+      <c r="D311">
+        <v>10000</v>
+      </c>
+      <c r="E311">
+        <v>10000</v>
+      </c>
+      <c r="F311">
+        <v>100</v>
+      </c>
+      <c r="G311">
+        <v>10000000</v>
+      </c>
+      <c r="H311">
+        <v>1000</v>
+      </c>
+      <c r="I311">
         <v>1</v>
       </c>
     </row>

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{670EB0CF-6BF9-4B32-A097-98F6C60D675C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640808F7-3D5D-4B0C-932E-02E9AB3AEDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1653" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="99">
   <si>
     <t>Commodities</t>
   </si>
@@ -694,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0CB446-BDDD-415D-AF22-2CEB1FE45CA5}">
-  <dimension ref="A1:A78"/>
+  <dimension ref="A1:A79"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -1085,6 +1085,11 @@
     <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1119,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B156"/>
+  <dimension ref="A1:B157"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -2368,6 +2373,14 @@
       </c>
       <c r="B156" t="s">
         <v>55</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>40</v>
+      </c>
+      <c r="B157" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2377,7 +2390,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
-  <dimension ref="A1:I311"/>
+  <dimension ref="A1:I313"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -5320,10 +5333,10 @@
         <v>71</v>
       </c>
       <c r="D102">
-        <v>5.8765000000000009</v>
+        <v>20.330500000000001</v>
       </c>
       <c r="E102">
-        <v>5.8765000000000009</v>
+        <v>20.330500000000001</v>
       </c>
       <c r="F102">
         <v>1</v>
@@ -6906,19 +6919,19 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B157" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C157" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="D157">
-        <v>500</v>
+        <v>14.965</v>
       </c>
       <c r="E157">
-        <v>500</v>
+        <v>14.965</v>
       </c>
       <c r="F157">
         <v>1</v>
@@ -6927,7 +6940,7 @@
         <v>10000000</v>
       </c>
       <c r="H157">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I157">
         <v>1</v>
@@ -6938,10 +6951,10 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C158" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D158">
         <v>500</v>
@@ -6967,10 +6980,10 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C159" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D159">
         <v>500</v>
@@ -6996,10 +7009,10 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C160" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D160">
         <v>500</v>
@@ -7025,10 +7038,10 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C161" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D161">
         <v>500</v>
@@ -7054,10 +7067,10 @@
         <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C162" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D162">
         <v>500</v>
@@ -7083,10 +7096,10 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C163" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D163">
         <v>500</v>
@@ -7112,10 +7125,10 @@
         <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C164" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D164">
         <v>500</v>
@@ -7141,10 +7154,10 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C165" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D165">
         <v>500</v>
@@ -7170,10 +7183,10 @@
         <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C166" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D166">
         <v>500</v>
@@ -7199,10 +7212,10 @@
         <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C167" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D167">
         <v>500</v>
@@ -7228,10 +7241,10 @@
         <v>12</v>
       </c>
       <c r="B168" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C168" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D168">
         <v>500</v>
@@ -7257,10 +7270,10 @@
         <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="C169" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="D169">
         <v>500</v>
@@ -7286,10 +7299,10 @@
         <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="C170" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="D170">
         <v>500</v>
@@ -7315,10 +7328,10 @@
         <v>12</v>
       </c>
       <c r="B171" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C171" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D171">
         <v>500</v>
@@ -7344,10 +7357,10 @@
         <v>12</v>
       </c>
       <c r="B172" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C172" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D172">
         <v>500</v>
@@ -7373,10 +7386,10 @@
         <v>12</v>
       </c>
       <c r="B173" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C173" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D173">
         <v>500</v>
@@ -7402,10 +7415,10 @@
         <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C174" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D174">
         <v>500</v>
@@ -7431,10 +7444,10 @@
         <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C175" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D175">
         <v>500</v>
@@ -7460,10 +7473,10 @@
         <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C176" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D176">
         <v>500</v>
@@ -7489,10 +7502,10 @@
         <v>12</v>
       </c>
       <c r="B177" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C177" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="D177">
         <v>500</v>
@@ -7518,10 +7531,10 @@
         <v>12</v>
       </c>
       <c r="B178" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C178" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D178">
         <v>500</v>
@@ -7547,10 +7560,10 @@
         <v>12</v>
       </c>
       <c r="B179" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C179" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D179">
         <v>500</v>
@@ -7576,10 +7589,10 @@
         <v>12</v>
       </c>
       <c r="B180" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C180" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D180">
         <v>500</v>
@@ -7605,10 +7618,10 @@
         <v>12</v>
       </c>
       <c r="B181" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C181" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D181">
         <v>500</v>
@@ -7634,10 +7647,10 @@
         <v>12</v>
       </c>
       <c r="B182" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C182" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="D182">
         <v>500</v>
@@ -7666,7 +7679,7 @@
         <v>38</v>
       </c>
       <c r="C183" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="D183">
         <v>500</v>
@@ -7692,10 +7705,10 @@
         <v>12</v>
       </c>
       <c r="B184" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C184" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D184">
         <v>500</v>
@@ -7724,7 +7737,7 @@
         <v>16</v>
       </c>
       <c r="C185" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D185">
         <v>500</v>
@@ -7753,7 +7766,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D186">
         <v>500</v>
@@ -7782,7 +7795,7 @@
         <v>16</v>
       </c>
       <c r="C187" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D187">
         <v>500</v>
@@ -7808,10 +7821,10 @@
         <v>12</v>
       </c>
       <c r="B188" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C188" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D188">
         <v>500</v>
@@ -7840,7 +7853,7 @@
         <v>28</v>
       </c>
       <c r="C189" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D189">
         <v>500</v>
@@ -7866,10 +7879,10 @@
         <v>12</v>
       </c>
       <c r="B190" t="s">
+        <v>28</v>
+      </c>
+      <c r="C190" t="s">
         <v>42</v>
-      </c>
-      <c r="C190" t="s">
-        <v>16</v>
       </c>
       <c r="D190">
         <v>500</v>
@@ -7898,7 +7911,7 @@
         <v>42</v>
       </c>
       <c r="C191" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D191">
         <v>500</v>
@@ -7927,7 +7940,7 @@
         <v>42</v>
       </c>
       <c r="C192" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="D192">
         <v>500</v>
@@ -7956,7 +7969,7 @@
         <v>42</v>
       </c>
       <c r="C193" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D193">
         <v>500</v>
@@ -7985,7 +7998,7 @@
         <v>42</v>
       </c>
       <c r="C194" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D194">
         <v>500</v>
@@ -8014,7 +8027,7 @@
         <v>42</v>
       </c>
       <c r="C195" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D195">
         <v>500</v>
@@ -8043,7 +8056,7 @@
         <v>42</v>
       </c>
       <c r="C196" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D196">
         <v>500</v>
@@ -8072,7 +8085,7 @@
         <v>42</v>
       </c>
       <c r="C197" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="D197">
         <v>500</v>
@@ -8101,7 +8114,7 @@
         <v>42</v>
       </c>
       <c r="C198" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D198">
         <v>500</v>
@@ -8127,10 +8140,10 @@
         <v>12</v>
       </c>
       <c r="B199" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C199" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D199">
         <v>500</v>
@@ -8159,7 +8172,7 @@
         <v>60</v>
       </c>
       <c r="C200" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D200">
         <v>500</v>
@@ -8188,7 +8201,7 @@
         <v>60</v>
       </c>
       <c r="C201" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="D201">
         <v>500</v>
@@ -8217,7 +8230,7 @@
         <v>60</v>
       </c>
       <c r="C202" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D202">
         <v>500</v>
@@ -8246,7 +8259,7 @@
         <v>60</v>
       </c>
       <c r="C203" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D203">
         <v>500</v>
@@ -8272,10 +8285,10 @@
         <v>12</v>
       </c>
       <c r="B204" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C204" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D204">
         <v>500</v>
@@ -8304,7 +8317,7 @@
         <v>22</v>
       </c>
       <c r="C205" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D205">
         <v>500</v>
@@ -8333,7 +8346,7 @@
         <v>22</v>
       </c>
       <c r="C206" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D206">
         <v>500</v>
@@ -8359,10 +8372,10 @@
         <v>12</v>
       </c>
       <c r="B207" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C207" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D207">
         <v>500</v>
@@ -8391,7 +8404,7 @@
         <v>61</v>
       </c>
       <c r="C208" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D208">
         <v>500</v>
@@ -8420,7 +8433,7 @@
         <v>61</v>
       </c>
       <c r="C209" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D209">
         <v>500</v>
@@ -8446,10 +8459,10 @@
         <v>12</v>
       </c>
       <c r="B210" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C210" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D210">
         <v>500</v>
@@ -8478,7 +8491,7 @@
         <v>64</v>
       </c>
       <c r="C211" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D211">
         <v>500</v>
@@ -8504,10 +8517,10 @@
         <v>12</v>
       </c>
       <c r="B212" t="s">
+        <v>64</v>
+      </c>
+      <c r="C212" t="s">
         <v>24</v>
-      </c>
-      <c r="C212" t="s">
-        <v>64</v>
       </c>
       <c r="D212">
         <v>500</v>
@@ -8536,7 +8549,7 @@
         <v>24</v>
       </c>
       <c r="C213" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D213">
         <v>500</v>
@@ -8562,10 +8575,10 @@
         <v>12</v>
       </c>
       <c r="B214" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C214" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c r="D214">
         <v>500</v>
@@ -8594,7 +8607,7 @@
         <v>18</v>
       </c>
       <c r="C215" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="D215">
         <v>500</v>
@@ -8623,7 +8636,7 @@
         <v>18</v>
       </c>
       <c r="C216" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D216">
         <v>500</v>
@@ -8649,10 +8662,10 @@
         <v>12</v>
       </c>
       <c r="B217" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C217" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D217">
         <v>500</v>
@@ -8678,7 +8691,7 @@
         <v>12</v>
       </c>
       <c r="B218" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C218" t="s">
         <v>42</v>
@@ -8707,7 +8720,7 @@
         <v>12</v>
       </c>
       <c r="B219" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="C219" t="s">
         <v>42</v>
@@ -8739,7 +8752,7 @@
         <v>62</v>
       </c>
       <c r="C220" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D220">
         <v>500</v>
@@ -8768,7 +8781,7 @@
         <v>62</v>
       </c>
       <c r="C221" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D221">
         <v>500</v>
@@ -8794,10 +8807,10 @@
         <v>12</v>
       </c>
       <c r="B222" t="s">
+        <v>62</v>
+      </c>
+      <c r="C222" t="s">
         <v>65</v>
-      </c>
-      <c r="C222" t="s">
-        <v>60</v>
       </c>
       <c r="D222">
         <v>500</v>
@@ -8826,7 +8839,7 @@
         <v>65</v>
       </c>
       <c r="C223" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D223">
         <v>500</v>
@@ -8855,7 +8868,7 @@
         <v>65</v>
       </c>
       <c r="C224" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D224">
         <v>500</v>
@@ -8884,7 +8897,7 @@
         <v>65</v>
       </c>
       <c r="C225" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D225">
         <v>500</v>
@@ -8910,10 +8923,10 @@
         <v>12</v>
       </c>
       <c r="B226" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C226" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="D226">
         <v>500</v>
@@ -8942,7 +8955,7 @@
         <v>66</v>
       </c>
       <c r="C227" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="D227">
         <v>500</v>
@@ -8971,7 +8984,7 @@
         <v>66</v>
       </c>
       <c r="C228" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D228">
         <v>500</v>
@@ -9000,7 +9013,7 @@
         <v>66</v>
       </c>
       <c r="C229" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D229">
         <v>500</v>
@@ -9026,10 +9039,10 @@
         <v>12</v>
       </c>
       <c r="B230" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C230" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="D230">
         <v>500</v>
@@ -9058,7 +9071,7 @@
         <v>67</v>
       </c>
       <c r="C231" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D231">
         <v>500</v>
@@ -9084,10 +9097,10 @@
         <v>12</v>
       </c>
       <c r="B232" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C232" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D232">
         <v>500</v>
@@ -9116,7 +9129,7 @@
         <v>68</v>
       </c>
       <c r="C233" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="D233">
         <v>500</v>
@@ -9145,7 +9158,7 @@
         <v>68</v>
       </c>
       <c r="C234" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="D234">
         <v>500</v>
@@ -9174,7 +9187,7 @@
         <v>68</v>
       </c>
       <c r="C235" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="D235">
         <v>500</v>
@@ -9203,7 +9216,7 @@
         <v>68</v>
       </c>
       <c r="C236" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="D236">
         <v>500</v>
@@ -9229,10 +9242,10 @@
         <v>12</v>
       </c>
       <c r="B237" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="C237" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="D237">
         <v>500</v>
@@ -9258,10 +9271,10 @@
         <v>12</v>
       </c>
       <c r="B238" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="C238" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D238">
         <v>500</v>
@@ -9290,7 +9303,7 @@
         <v>51</v>
       </c>
       <c r="C239" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D239">
         <v>500</v>
@@ -9319,7 +9332,7 @@
         <v>51</v>
       </c>
       <c r="C240" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="D240">
         <v>500</v>
@@ -9348,7 +9361,7 @@
         <v>51</v>
       </c>
       <c r="C241" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D241">
         <v>500</v>
@@ -9374,10 +9387,10 @@
         <v>12</v>
       </c>
       <c r="B242" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C242" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D242">
         <v>500</v>
@@ -9406,7 +9419,7 @@
         <v>26</v>
       </c>
       <c r="C243" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="D243">
         <v>500</v>
@@ -9432,10 +9445,10 @@
         <v>12</v>
       </c>
       <c r="B244" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="C244" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D244">
         <v>500</v>
@@ -9464,7 +9477,7 @@
         <v>72</v>
       </c>
       <c r="C245" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="D245">
         <v>500</v>
@@ -9490,10 +9503,10 @@
         <v>12</v>
       </c>
       <c r="B246" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C246" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D246">
         <v>500</v>
@@ -9522,7 +9535,7 @@
         <v>34</v>
       </c>
       <c r="C247" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D247">
         <v>500</v>
@@ -9548,10 +9561,10 @@
         <v>12</v>
       </c>
       <c r="B248" t="s">
+        <v>34</v>
+      </c>
+      <c r="C248" t="s">
         <v>32</v>
-      </c>
-      <c r="C248" t="s">
-        <v>34</v>
       </c>
       <c r="D248">
         <v>500</v>
@@ -9577,10 +9590,10 @@
         <v>12</v>
       </c>
       <c r="B249" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C249" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D249">
         <v>500</v>
@@ -9609,7 +9622,7 @@
         <v>58</v>
       </c>
       <c r="C250" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D250">
         <v>500</v>
@@ -9638,7 +9651,7 @@
         <v>58</v>
       </c>
       <c r="C251" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D251">
         <v>500</v>
@@ -9667,7 +9680,7 @@
         <v>58</v>
       </c>
       <c r="C252" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D252">
         <v>500</v>
@@ -9693,7 +9706,7 @@
         <v>12</v>
       </c>
       <c r="B253" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C253" t="s">
         <v>51</v>
@@ -9722,10 +9735,10 @@
         <v>12</v>
       </c>
       <c r="B254" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C254" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D254">
         <v>500</v>
@@ -9754,7 +9767,7 @@
         <v>53</v>
       </c>
       <c r="C255" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="D255">
         <v>500</v>
@@ -9783,7 +9796,7 @@
         <v>53</v>
       </c>
       <c r="C256" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D256">
         <v>500</v>
@@ -9809,10 +9822,10 @@
         <v>12</v>
       </c>
       <c r="B257" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C257" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="D257">
         <v>500</v>
@@ -9838,10 +9851,10 @@
         <v>12</v>
       </c>
       <c r="B258" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C258" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="D258">
         <v>500</v>
@@ -9870,7 +9883,7 @@
         <v>36</v>
       </c>
       <c r="C259" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="D259">
         <v>500</v>
@@ -9896,10 +9909,10 @@
         <v>12</v>
       </c>
       <c r="B260" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C260" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D260">
         <v>500</v>
@@ -9928,7 +9941,7 @@
         <v>48</v>
       </c>
       <c r="C261" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D261">
         <v>500</v>
@@ -9957,7 +9970,7 @@
         <v>48</v>
       </c>
       <c r="C262" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D262">
         <v>500</v>
@@ -9986,7 +9999,7 @@
         <v>48</v>
       </c>
       <c r="C263" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D263">
         <v>500</v>
@@ -10012,10 +10025,10 @@
         <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C264" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D264">
         <v>500</v>
@@ -10041,10 +10054,10 @@
         <v>12</v>
       </c>
       <c r="B265" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C265" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D265">
         <v>500</v>
@@ -10070,7 +10083,7 @@
         <v>12</v>
       </c>
       <c r="B266" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C266" t="s">
         <v>22</v>
@@ -10099,10 +10112,10 @@
         <v>12</v>
       </c>
       <c r="B267" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C267" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D267">
         <v>500</v>
@@ -10131,7 +10144,7 @@
         <v>75</v>
       </c>
       <c r="C268" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D268">
         <v>500</v>
@@ -10157,10 +10170,10 @@
         <v>12</v>
       </c>
       <c r="B269" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C269" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="D269">
         <v>500</v>
@@ -10186,10 +10199,10 @@
         <v>12</v>
       </c>
       <c r="B270" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="C270" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="D270">
         <v>500</v>
@@ -10215,10 +10228,10 @@
         <v>12</v>
       </c>
       <c r="B271" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C271" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D271">
         <v>500</v>
@@ -10247,7 +10260,7 @@
         <v>58</v>
       </c>
       <c r="C272" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D272">
         <v>500</v>
@@ -10276,7 +10289,7 @@
         <v>58</v>
       </c>
       <c r="C273" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D273">
         <v>500</v>
@@ -10302,7 +10315,7 @@
         <v>12</v>
       </c>
       <c r="B274" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C274" t="s">
         <v>66</v>
@@ -10331,10 +10344,10 @@
         <v>12</v>
       </c>
       <c r="B275" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C275" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D275">
         <v>500</v>
@@ -10363,7 +10376,7 @@
         <v>68</v>
       </c>
       <c r="C276" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D276">
         <v>500</v>
@@ -10389,10 +10402,10 @@
         <v>12</v>
       </c>
       <c r="B277" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="C277" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D277">
         <v>500</v>
@@ -10418,10 +10431,10 @@
         <v>12</v>
       </c>
       <c r="B278" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C278" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D278">
         <v>500</v>
@@ -10447,10 +10460,10 @@
         <v>12</v>
       </c>
       <c r="B279" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C279" t="s">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="D279">
         <v>500</v>
@@ -10476,7 +10489,7 @@
         <v>12</v>
       </c>
       <c r="B280" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C280" t="s">
         <v>22</v>
@@ -10505,10 +10518,10 @@
         <v>12</v>
       </c>
       <c r="B281" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="C281" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D281">
         <v>500</v>
@@ -10534,7 +10547,7 @@
         <v>12</v>
       </c>
       <c r="B282" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C282" t="s">
         <v>34</v>
@@ -10563,10 +10576,10 @@
         <v>12</v>
       </c>
       <c r="B283" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="C283" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D283">
         <v>500</v>
@@ -10595,7 +10608,7 @@
         <v>48</v>
       </c>
       <c r="C284" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D284">
         <v>500</v>
@@ -10624,7 +10637,7 @@
         <v>48</v>
       </c>
       <c r="C285" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D285">
         <v>500</v>
@@ -10653,7 +10666,7 @@
         <v>48</v>
       </c>
       <c r="C286" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D286">
         <v>500</v>
@@ -10682,7 +10695,7 @@
         <v>48</v>
       </c>
       <c r="C287" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="D287">
         <v>500</v>
@@ -10708,10 +10721,10 @@
         <v>12</v>
       </c>
       <c r="B288" t="s">
+        <v>48</v>
+      </c>
+      <c r="C288" t="s">
         <v>38</v>
-      </c>
-      <c r="C288" t="s">
-        <v>79</v>
       </c>
       <c r="D288">
         <v>500</v>
@@ -10740,7 +10753,7 @@
         <v>38</v>
       </c>
       <c r="C289" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="D289">
         <v>500</v>
@@ -10769,7 +10782,7 @@
         <v>38</v>
       </c>
       <c r="C290" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D290">
         <v>500</v>
@@ -10795,10 +10808,10 @@
         <v>12</v>
       </c>
       <c r="B291" t="s">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="C291" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D291">
         <v>500</v>
@@ -10824,10 +10837,10 @@
         <v>12</v>
       </c>
       <c r="B292" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="C292" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="D292">
         <v>500</v>
@@ -10853,10 +10866,10 @@
         <v>12</v>
       </c>
       <c r="B293" t="s">
-        <v>77</v>
+        <v>20</v>
       </c>
       <c r="C293" t="s">
-        <v>20</v>
+        <v>74</v>
       </c>
       <c r="D293">
         <v>500</v>
@@ -10882,10 +10895,10 @@
         <v>12</v>
       </c>
       <c r="B294" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C294" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="D294">
         <v>500</v>
@@ -10908,13 +10921,13 @@
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B295" t="s">
         <v>84</v>
       </c>
       <c r="C295" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="D295">
         <v>500</v>
@@ -10940,19 +10953,19 @@
         <v>12</v>
       </c>
       <c r="B296" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C296" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D296">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="E296">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="F296">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G296">
         <v>10000000</v>
@@ -10969,19 +10982,19 @@
         <v>12</v>
       </c>
       <c r="B297" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="C297" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D297">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="E297">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="F297">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G297">
         <v>10000000</v>
@@ -10998,10 +11011,10 @@
         <v>12</v>
       </c>
       <c r="B298" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C298" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D298">
         <v>10000</v>
@@ -11027,10 +11040,10 @@
         <v>12</v>
       </c>
       <c r="B299" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C299" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="D299">
         <v>10000</v>
@@ -11056,10 +11069,10 @@
         <v>12</v>
       </c>
       <c r="B300" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C300" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D300">
         <v>10000</v>
@@ -11085,10 +11098,10 @@
         <v>12</v>
       </c>
       <c r="B301" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C301" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D301">
         <v>10000</v>
@@ -11114,10 +11127,10 @@
         <v>12</v>
       </c>
       <c r="B302" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C302" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D302">
         <v>10000</v>
@@ -11143,10 +11156,10 @@
         <v>12</v>
       </c>
       <c r="B303" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C303" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D303">
         <v>10000</v>
@@ -11172,10 +11185,10 @@
         <v>12</v>
       </c>
       <c r="B304" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C304" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="D304">
         <v>10000</v>
@@ -11201,10 +11214,10 @@
         <v>12</v>
       </c>
       <c r="B305" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C305" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="D305">
         <v>10000</v>
@@ -11230,10 +11243,10 @@
         <v>12</v>
       </c>
       <c r="B306" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C306" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="D306">
         <v>10000</v>
@@ -11259,10 +11272,10 @@
         <v>12</v>
       </c>
       <c r="B307" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C307" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D307">
         <v>10000</v>
@@ -11288,10 +11301,10 @@
         <v>12</v>
       </c>
       <c r="B308" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C308" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D308">
         <v>10000</v>
@@ -11317,10 +11330,10 @@
         <v>12</v>
       </c>
       <c r="B309" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C309" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D309">
         <v>10000</v>
@@ -11346,10 +11359,10 @@
         <v>12</v>
       </c>
       <c r="B310" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C310" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="D310">
         <v>10000</v>
@@ -11375,10 +11388,10 @@
         <v>12</v>
       </c>
       <c r="B311" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C311" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="D311">
         <v>10000</v>
@@ -11396,6 +11409,64 @@
         <v>1000</v>
       </c>
       <c r="I311">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>12</v>
+      </c>
+      <c r="B312" t="s">
+        <v>97</v>
+      </c>
+      <c r="C312" t="s">
+        <v>36</v>
+      </c>
+      <c r="D312">
+        <v>10000</v>
+      </c>
+      <c r="E312">
+        <v>10000</v>
+      </c>
+      <c r="F312">
+        <v>100</v>
+      </c>
+      <c r="G312">
+        <v>10000000</v>
+      </c>
+      <c r="H312">
+        <v>1000</v>
+      </c>
+      <c r="I312">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>12</v>
+      </c>
+      <c r="B313" t="s">
+        <v>98</v>
+      </c>
+      <c r="C313" t="s">
+        <v>34</v>
+      </c>
+      <c r="D313">
+        <v>10000</v>
+      </c>
+      <c r="E313">
+        <v>10000</v>
+      </c>
+      <c r="F313">
+        <v>100</v>
+      </c>
+      <c r="G313">
+        <v>10000000</v>
+      </c>
+      <c r="H313">
+        <v>1000</v>
+      </c>
+      <c r="I313">
         <v>1</v>
       </c>
     </row>
@@ -11407,7 +11478,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68B577B-1347-43AB-A697-F4519763B965}">
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:C160"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -11938,7 +12009,7 @@
         <v>-661.42899999999997</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>11</v>
       </c>
@@ -11949,7 +12020,7 @@
         <v>-31.263999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>11</v>
       </c>
@@ -11957,10 +12028,10 @@
         <v>64</v>
       </c>
       <c r="C50">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+        <v>-10.498540930309094</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>11</v>
       </c>
@@ -11968,10 +12039,10 @@
         <v>24</v>
       </c>
       <c r="C51">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+        <v>-20.327868125092017</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>11</v>
       </c>
@@ -11982,7 +12053,7 @@
         <v>-397.63900000000001</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>11</v>
       </c>
@@ -11990,10 +12061,10 @@
         <v>40</v>
       </c>
       <c r="C53">
-        <v>-100</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+        <v>-29.166899245671924</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>11</v>
       </c>
@@ -12003,14 +12074,8 @@
       <c r="C54">
         <v>-211.03200000000001</v>
       </c>
-      <c r="F54" t="s">
-        <v>81</v>
-      </c>
-      <c r="G54">
-        <v>-10.747</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>11</v>
       </c>
@@ -12020,14 +12085,8 @@
       <c r="C55">
         <v>-83.045000000000002</v>
       </c>
-      <c r="F55" t="s">
-        <v>77</v>
-      </c>
-      <c r="G55">
-        <v>-453.32799999999997</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>11</v>
       </c>
@@ -12035,10 +12094,10 @@
         <v>65</v>
       </c>
       <c r="C56">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+        <v>-27.339084185091842</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>11</v>
       </c>
@@ -12049,7 +12108,7 @@
         <v>-99.653999999999982</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>11</v>
       </c>
@@ -12057,10 +12116,10 @@
         <v>67</v>
       </c>
       <c r="C58">
-        <v>-30</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
+        <v>-34.696428008002286</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>11</v>
       </c>
@@ -12071,7 +12130,7 @@
         <v>-19.54</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>11</v>
       </c>
@@ -12079,10 +12138,10 @@
         <v>68</v>
       </c>
       <c r="C60">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
+        <v>-34.820653312201756</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>11</v>
       </c>
@@ -12093,7 +12152,7 @@
         <v>-55.689</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>11</v>
       </c>
@@ -12104,7 +12163,7 @@
         <v>-110.401</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>11</v>
       </c>
@@ -12112,10 +12171,10 @@
         <v>26</v>
       </c>
       <c r="C63">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
+        <v>-13.995883970311864</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>11</v>
       </c>
@@ -12123,7 +12182,7 @@
         <v>72</v>
       </c>
       <c r="C64">
-        <v>-20</v>
+        <v>-9.5558311621502252</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
@@ -12167,7 +12226,7 @@
         <v>71</v>
       </c>
       <c r="C68">
-        <v>-10</v>
+        <v>-12.918429819775348</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
@@ -12274,10 +12333,10 @@
         <v>11</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>-10.747</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
@@ -12934,7 +12993,7 @@
         <v>12</v>
       </c>
       <c r="B138" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -12978,7 +13037,7 @@
         <v>12</v>
       </c>
       <c r="B142" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -12989,7 +13048,7 @@
         <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -13000,7 +13059,7 @@
         <v>12</v>
       </c>
       <c r="B144" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -13011,7 +13070,7 @@
         <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -13022,7 +13081,7 @@
         <v>12</v>
       </c>
       <c r="B146" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -13033,7 +13092,7 @@
         <v>12</v>
       </c>
       <c r="B147" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -13044,7 +13103,7 @@
         <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -13055,7 +13114,7 @@
         <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -13066,7 +13125,7 @@
         <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -13077,7 +13136,7 @@
         <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -13088,7 +13147,7 @@
         <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -13099,7 +13158,7 @@
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -13110,7 +13169,7 @@
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -13121,7 +13180,7 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -13132,7 +13191,7 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -13143,7 +13202,7 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -13151,10 +13210,10 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -13162,12 +13221,23 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B159" t="s">
         <v>84</v>
       </c>
       <c r="C159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>12</v>
+      </c>
+      <c r="B160" t="s">
+        <v>84</v>
+      </c>
+      <c r="C160">
         <v>0</v>
       </c>
     </row>

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{640808F7-3D5D-4B0C-932E-02E9AB3AEDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51C345F-A8A2-4127-9B75-711C89601CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1673" uniqueCount="99">
   <si>
     <t>Commodities</t>
   </si>
@@ -694,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0CB446-BDDD-415D-AF22-2CEB1FE45CA5}">
-  <dimension ref="A1:A79"/>
+  <dimension ref="A1:A81"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -1090,6 +1090,16 @@
     <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1124,7 +1134,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B157"/>
+  <dimension ref="A1:B158"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -2381,6 +2391,14 @@
       </c>
       <c r="B157" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>53</v>
+      </c>
+      <c r="B158" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2390,7 +2408,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
-  <dimension ref="A1:I313"/>
+  <dimension ref="A1:I314"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -6110,16 +6128,16 @@
         <v>11</v>
       </c>
       <c r="B129" t="s">
+        <v>53</v>
+      </c>
+      <c r="C129" t="s">
         <v>75</v>
       </c>
-      <c r="C129" t="s">
-        <v>26</v>
-      </c>
       <c r="D129">
-        <v>118.77099999999999</v>
+        <v>439.27749999999992</v>
       </c>
       <c r="E129">
-        <v>118.77099999999999</v>
+        <v>439.27749999999992</v>
       </c>
       <c r="F129">
         <v>1</v>
@@ -6139,16 +6157,16 @@
         <v>11</v>
       </c>
       <c r="B130" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C130" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="D130">
-        <v>486.91</v>
+        <v>118.77099999999999</v>
       </c>
       <c r="E130">
-        <v>486.91</v>
+        <v>118.77099999999999</v>
       </c>
       <c r="F130">
         <v>1</v>
@@ -6168,16 +6186,16 @@
         <v>11</v>
       </c>
       <c r="B131" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="C131" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="D131">
-        <v>144.17500000000001</v>
+        <v>486.91</v>
       </c>
       <c r="E131">
-        <v>144.17500000000001</v>
+        <v>486.91</v>
       </c>
       <c r="F131">
         <v>1</v>
@@ -6197,16 +6215,16 @@
         <v>11</v>
       </c>
       <c r="B132" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C132" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="D132">
-        <v>49.494</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="E132">
-        <v>49.494</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="F132">
         <v>1</v>
@@ -6229,13 +6247,13 @@
         <v>58</v>
       </c>
       <c r="C133" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D133">
-        <v>816.06700000000012</v>
+        <v>49.494</v>
       </c>
       <c r="E133">
-        <v>816.06700000000012</v>
+        <v>49.494</v>
       </c>
       <c r="F133">
         <v>1</v>
@@ -6258,13 +6276,13 @@
         <v>58</v>
       </c>
       <c r="C134" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D134">
-        <v>188.88749999999999</v>
+        <v>816.06700000000012</v>
       </c>
       <c r="E134">
-        <v>188.88749999999999</v>
+        <v>816.06700000000012</v>
       </c>
       <c r="F134">
         <v>1</v>
@@ -6284,16 +6302,16 @@
         <v>11</v>
       </c>
       <c r="B135" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C135" t="s">
         <v>66</v>
       </c>
       <c r="D135">
-        <v>89.716999999999999</v>
+        <v>188.88749999999999</v>
       </c>
       <c r="E135">
-        <v>89.716999999999999</v>
+        <v>188.88749999999999</v>
       </c>
       <c r="F135">
         <v>1</v>
@@ -6313,16 +6331,16 @@
         <v>11</v>
       </c>
       <c r="B136" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C136" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D136">
-        <v>170.63749999999999</v>
+        <v>89.716999999999999</v>
       </c>
       <c r="E136">
-        <v>170.63749999999999</v>
+        <v>89.716999999999999</v>
       </c>
       <c r="F136">
         <v>1</v>
@@ -6345,13 +6363,13 @@
         <v>68</v>
       </c>
       <c r="C137" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D137">
-        <v>12.1837</v>
+        <v>170.63749999999999</v>
       </c>
       <c r="E137">
-        <v>12.1837</v>
+        <v>170.63749999999999</v>
       </c>
       <c r="F137">
         <v>1</v>
@@ -6371,16 +6389,16 @@
         <v>11</v>
       </c>
       <c r="B138" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="C138" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D138">
-        <v>256.15699999999998</v>
+        <v>12.1837</v>
       </c>
       <c r="E138">
-        <v>256.15699999999998</v>
+        <v>12.1837</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -6400,16 +6418,16 @@
         <v>11</v>
       </c>
       <c r="B139" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C139" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D139">
-        <v>61.32</v>
+        <v>256.15699999999998</v>
       </c>
       <c r="E139">
-        <v>61.32</v>
+        <v>256.15699999999998</v>
       </c>
       <c r="F139">
         <v>1</v>
@@ -10460,10 +10478,10 @@
         <v>12</v>
       </c>
       <c r="B279" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C279" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="D279">
         <v>500</v>
@@ -10489,7 +10507,7 @@
         <v>12</v>
       </c>
       <c r="B280" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C280" t="s">
         <v>22</v>
@@ -10518,10 +10536,10 @@
         <v>12</v>
       </c>
       <c r="B281" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="C281" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D281">
         <v>500</v>
@@ -10547,7 +10565,7 @@
         <v>12</v>
       </c>
       <c r="B282" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C282" t="s">
         <v>34</v>
@@ -10576,10 +10594,10 @@
         <v>12</v>
       </c>
       <c r="B283" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C283" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D283">
         <v>500</v>
@@ -10608,7 +10626,7 @@
         <v>48</v>
       </c>
       <c r="C284" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D284">
         <v>500</v>
@@ -10637,7 +10655,7 @@
         <v>48</v>
       </c>
       <c r="C285" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D285">
         <v>500</v>
@@ -10666,7 +10684,7 @@
         <v>48</v>
       </c>
       <c r="C286" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D286">
         <v>500</v>
@@ -10695,7 +10713,7 @@
         <v>48</v>
       </c>
       <c r="C287" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D287">
         <v>500</v>
@@ -10721,10 +10739,10 @@
         <v>12</v>
       </c>
       <c r="B288" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C288" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="D288">
         <v>500</v>
@@ -10753,7 +10771,7 @@
         <v>38</v>
       </c>
       <c r="C289" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="D289">
         <v>500</v>
@@ -10782,7 +10800,7 @@
         <v>38</v>
       </c>
       <c r="C290" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D290">
         <v>500</v>
@@ -10808,10 +10826,10 @@
         <v>12</v>
       </c>
       <c r="B291" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="C291" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D291">
         <v>500</v>
@@ -10837,10 +10855,10 @@
         <v>12</v>
       </c>
       <c r="B292" t="s">
+        <v>20</v>
+      </c>
+      <c r="C292" t="s">
         <v>74</v>
-      </c>
-      <c r="C292" t="s">
-        <v>22</v>
       </c>
       <c r="D292">
         <v>500</v>
@@ -10866,10 +10884,10 @@
         <v>12</v>
       </c>
       <c r="B293" t="s">
+        <v>77</v>
+      </c>
+      <c r="C293" t="s">
         <v>20</v>
-      </c>
-      <c r="C293" t="s">
-        <v>74</v>
       </c>
       <c r="D293">
         <v>500</v>
@@ -10895,10 +10913,10 @@
         <v>12</v>
       </c>
       <c r="B294" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C294" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="D294">
         <v>500</v>
@@ -10927,7 +10945,7 @@
         <v>84</v>
       </c>
       <c r="C295" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="D295">
         <v>500</v>
@@ -10953,10 +10971,10 @@
         <v>12</v>
       </c>
       <c r="B296" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="C296" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="D296">
         <v>500</v>
@@ -10982,19 +11000,19 @@
         <v>12</v>
       </c>
       <c r="B297" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="C297" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D297">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E297">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F297">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G297">
         <v>10000000</v>
@@ -11011,10 +11029,10 @@
         <v>12</v>
       </c>
       <c r="B298" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C298" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="D298">
         <v>10000</v>
@@ -11040,10 +11058,10 @@
         <v>12</v>
       </c>
       <c r="B299" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C299" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="D299">
         <v>10000</v>
@@ -11069,10 +11087,10 @@
         <v>12</v>
       </c>
       <c r="B300" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C300" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="D300">
         <v>10000</v>
@@ -11098,10 +11116,10 @@
         <v>12</v>
       </c>
       <c r="B301" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C301" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="D301">
         <v>10000</v>
@@ -11127,10 +11145,10 @@
         <v>12</v>
       </c>
       <c r="B302" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C302" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="D302">
         <v>10000</v>
@@ -11156,10 +11174,10 @@
         <v>12</v>
       </c>
       <c r="B303" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C303" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="D303">
         <v>10000</v>
@@ -11185,10 +11203,10 @@
         <v>12</v>
       </c>
       <c r="B304" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C304" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="D304">
         <v>10000</v>
@@ -11214,10 +11232,10 @@
         <v>12</v>
       </c>
       <c r="B305" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C305" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D305">
         <v>10000</v>
@@ -11243,10 +11261,10 @@
         <v>12</v>
       </c>
       <c r="B306" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C306" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="D306">
         <v>10000</v>
@@ -11272,10 +11290,10 @@
         <v>12</v>
       </c>
       <c r="B307" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C307" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D307">
         <v>10000</v>
@@ -11301,10 +11319,10 @@
         <v>12</v>
       </c>
       <c r="B308" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C308" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D308">
         <v>10000</v>
@@ -11330,10 +11348,10 @@
         <v>12</v>
       </c>
       <c r="B309" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C309" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D309">
         <v>10000</v>
@@ -11359,10 +11377,10 @@
         <v>12</v>
       </c>
       <c r="B310" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C310" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D310">
         <v>10000</v>
@@ -11388,10 +11406,10 @@
         <v>12</v>
       </c>
       <c r="B311" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C311" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="D311">
         <v>10000</v>
@@ -11417,10 +11435,10 @@
         <v>12</v>
       </c>
       <c r="B312" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C312" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D312">
         <v>10000</v>
@@ -11446,19 +11464,19 @@
         <v>12</v>
       </c>
       <c r="B313" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="C313" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="D313">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="E313">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="F313">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G313">
         <v>10000000</v>
@@ -11467,6 +11485,35 @@
         <v>1000</v>
       </c>
       <c r="I313">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>12</v>
+      </c>
+      <c r="B314" t="s">
+        <v>75</v>
+      </c>
+      <c r="C314" t="s">
+        <v>30</v>
+      </c>
+      <c r="D314">
+        <v>500</v>
+      </c>
+      <c r="E314">
+        <v>500</v>
+      </c>
+      <c r="F314">
+        <v>1</v>
+      </c>
+      <c r="G314">
+        <v>10000000</v>
+      </c>
+      <c r="H314">
+        <v>1000</v>
+      </c>
+      <c r="I314">
         <v>1</v>
       </c>
     </row>
@@ -11478,7 +11525,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68B577B-1347-43AB-A697-F4519763B965}">
-  <dimension ref="A1:C160"/>
+  <dimension ref="A1:C162"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -13007,7 +13054,7 @@
         <v>69</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
@@ -13238,6 +13285,28 @@
         <v>84</v>
       </c>
       <c r="C160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>11</v>
+      </c>
+      <c r="B161" t="s">
+        <v>75</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>12</v>
+      </c>
+      <c r="B162" t="s">
+        <v>75</v>
+      </c>
+      <c r="C162">
         <v>0</v>
       </c>
     </row>

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51C345F-A8A2-4127-9B75-711C89601CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABC4765-BF75-4189-B558-DC82CA74FE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1673" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="98">
   <si>
     <t>Commodities</t>
   </si>
@@ -277,9 +277,6 @@
   </si>
   <si>
     <t>MA</t>
-  </si>
-  <si>
-    <t>IR</t>
   </si>
   <si>
     <t>MA_Prod</t>
@@ -694,7 +691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0CB446-BDDD-415D-AF22-2CEB1FE45CA5}">
-  <dimension ref="A1:A81"/>
+  <dimension ref="A1:A84"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -764,7 +761,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
@@ -1004,92 +1001,92 @@
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.35">
@@ -1100,6 +1097,21 @@
     <row r="81" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>75</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1134,7 +1146,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B158"/>
+  <dimension ref="A1:B152"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -1243,7 +1255,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B14" t="s">
         <v>78</v>
@@ -1971,63 +1983,63 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="B105" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B106" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B107" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="B108" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B109" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B110" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="B111" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B112" t="s">
         <v>30</v>
@@ -2035,135 +2047,135 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B113" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B114" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B115" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B116" t="s">
-        <v>30</v>
+        <v>67</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="B117" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B118" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="B119" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="B120" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="B121" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="B122" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B123" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B124" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B125" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="B126" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="B127" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B128" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B129" t="s">
         <v>28</v>
@@ -2171,233 +2183,185 @@
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B130" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="B131" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B132" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="B133" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="B134" t="s">
-        <v>16</v>
+        <v>83</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="B135" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B136" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="B137" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="B138" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B139" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B140" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B141" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B142" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B143" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B144" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B145" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B146" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B147" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B148" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B149" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B150" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="B151" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="B152" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A153" t="s">
-        <v>97</v>
-      </c>
-      <c r="B153" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A154" t="s">
-        <v>98</v>
-      </c>
-      <c r="B154" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A155" t="s">
-        <v>84</v>
-      </c>
-      <c r="B155" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A156" t="s">
-        <v>84</v>
-      </c>
-      <c r="B156" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A157" t="s">
-        <v>40</v>
-      </c>
-      <c r="B157" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A158" t="s">
-        <v>53</v>
-      </c>
-      <c r="B158" t="s">
         <v>75</v>
       </c>
     </row>
@@ -2408,7 +2372,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
-  <dimension ref="A1:I314"/>
+  <dimension ref="A1:I302"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -2793,7 +2757,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
         <v>74</v>
@@ -2822,10 +2786,10 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" t="s">
         <v>83</v>
-      </c>
-      <c r="C15" t="s">
-        <v>84</v>
       </c>
       <c r="D15">
         <v>10000</v>
@@ -2851,7 +2815,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
         <v>60</v>
@@ -2880,7 +2844,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
         <v>16</v>
@@ -2909,7 +2873,7 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
         <v>68</v>
@@ -2938,7 +2902,7 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C19" t="s">
         <v>24</v>
@@ -2967,7 +2931,7 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C20" t="s">
         <v>62</v>
@@ -2996,7 +2960,7 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
         <v>18</v>
@@ -3025,7 +2989,7 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
         <v>20</v>
@@ -3054,7 +3018,7 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
         <v>66</v>
@@ -3083,7 +3047,7 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
         <v>59</v>
@@ -3112,7 +3076,7 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
         <v>67</v>
@@ -3141,7 +3105,7 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C26" t="s">
         <v>65</v>
@@ -3170,7 +3134,7 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
         <v>64</v>
@@ -3199,7 +3163,7 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C28" t="s">
         <v>36</v>
@@ -3228,7 +3192,7 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C29" t="s">
         <v>34</v>
@@ -3257,7 +3221,7 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
         <v>78</v>
@@ -5174,13 +5138,13 @@
         <v>68</v>
       </c>
       <c r="C96" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="D96">
-        <v>9.9936999999999987</v>
+        <v>181.46340000000004</v>
       </c>
       <c r="E96">
-        <v>9.9936999999999987</v>
+        <v>181.46340000000004</v>
       </c>
       <c r="F96">
         <v>1</v>
@@ -5200,16 +5164,16 @@
         <v>11</v>
       </c>
       <c r="B97" t="s">
+        <v>20</v>
+      </c>
+      <c r="C97" t="s">
         <v>68</v>
       </c>
-      <c r="C97" t="s">
-        <v>36</v>
-      </c>
       <c r="D97">
-        <v>181.46340000000004</v>
+        <v>23.659299999999998</v>
       </c>
       <c r="E97">
-        <v>181.46340000000004</v>
+        <v>23.659299999999998</v>
       </c>
       <c r="F97">
         <v>1</v>
@@ -5229,16 +5193,16 @@
         <v>11</v>
       </c>
       <c r="B98" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C98" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D98">
-        <v>23.659299999999998</v>
+        <v>18.359500000000001</v>
       </c>
       <c r="E98">
-        <v>23.659299999999998</v>
+        <v>18.359500000000001</v>
       </c>
       <c r="F98">
         <v>1</v>
@@ -5261,13 +5225,13 @@
         <v>51</v>
       </c>
       <c r="C99" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D99">
-        <v>18.359500000000001</v>
+        <v>294.09875000000005</v>
       </c>
       <c r="E99">
-        <v>18.359500000000001</v>
+        <v>294.09875000000005</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -5290,13 +5254,13 @@
         <v>51</v>
       </c>
       <c r="C100" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D100">
-        <v>294.09875000000005</v>
+        <v>44.603000000000002</v>
       </c>
       <c r="E100">
-        <v>294.09875000000005</v>
+        <v>44.603000000000002</v>
       </c>
       <c r="F100">
         <v>1</v>
@@ -5319,13 +5283,13 @@
         <v>51</v>
       </c>
       <c r="C101" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D101">
-        <v>44.603000000000002</v>
+        <v>20.330500000000001</v>
       </c>
       <c r="E101">
-        <v>44.603000000000002</v>
+        <v>20.330500000000001</v>
       </c>
       <c r="F101">
         <v>1</v>
@@ -5345,16 +5309,16 @@
         <v>11</v>
       </c>
       <c r="B102" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C102" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D102">
-        <v>20.330500000000001</v>
+        <v>24.673999999999996</v>
       </c>
       <c r="E102">
-        <v>20.330500000000001</v>
+        <v>24.673999999999996</v>
       </c>
       <c r="F102">
         <v>1</v>
@@ -5377,13 +5341,13 @@
         <v>26</v>
       </c>
       <c r="C103" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="D103">
-        <v>24.673999999999996</v>
+        <v>41.683</v>
       </c>
       <c r="E103">
-        <v>24.673999999999996</v>
+        <v>41.683</v>
       </c>
       <c r="F103">
         <v>1</v>
@@ -5403,16 +5367,16 @@
         <v>11</v>
       </c>
       <c r="B104" t="s">
+        <v>72</v>
+      </c>
+      <c r="C104" t="s">
         <v>26</v>
       </c>
-      <c r="C104" t="s">
-        <v>53</v>
-      </c>
       <c r="D104">
-        <v>41.683</v>
+        <v>23.761499999999998</v>
       </c>
       <c r="E104">
-        <v>41.683</v>
+        <v>23.761499999999998</v>
       </c>
       <c r="F104">
         <v>1</v>
@@ -5435,13 +5399,13 @@
         <v>72</v>
       </c>
       <c r="C105" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D105">
-        <v>23.761499999999998</v>
+        <v>31.024999999999999</v>
       </c>
       <c r="E105">
-        <v>23.761499999999998</v>
+        <v>31.024999999999999</v>
       </c>
       <c r="F105">
         <v>1</v>
@@ -5461,16 +5425,16 @@
         <v>11</v>
       </c>
       <c r="B106" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="C106" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D106">
-        <v>31.024999999999999</v>
+        <v>81.906000000000006</v>
       </c>
       <c r="E106">
-        <v>31.024999999999999</v>
+        <v>81.906000000000006</v>
       </c>
       <c r="F106">
         <v>1</v>
@@ -5493,13 +5457,13 @@
         <v>34</v>
       </c>
       <c r="C107" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D107">
-        <v>81.906000000000006</v>
+        <v>52.56</v>
       </c>
       <c r="E107">
-        <v>81.906000000000006</v>
+        <v>52.56</v>
       </c>
       <c r="F107">
         <v>1</v>
@@ -5519,16 +5483,16 @@
         <v>11</v>
       </c>
       <c r="B108" t="s">
+        <v>32</v>
+      </c>
+      <c r="C108" t="s">
         <v>34</v>
       </c>
-      <c r="C108" t="s">
-        <v>32</v>
-      </c>
       <c r="D108">
-        <v>52.56</v>
+        <v>29.2</v>
       </c>
       <c r="E108">
-        <v>52.56</v>
+        <v>29.2</v>
       </c>
       <c r="F108">
         <v>1</v>
@@ -5548,16 +5512,16 @@
         <v>11</v>
       </c>
       <c r="B109" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C109" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D109">
-        <v>29.2</v>
+        <v>49.494</v>
       </c>
       <c r="E109">
-        <v>29.2</v>
+        <v>49.494</v>
       </c>
       <c r="F109">
         <v>1</v>
@@ -5580,13 +5544,13 @@
         <v>58</v>
       </c>
       <c r="C110" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D110">
-        <v>49.494</v>
+        <v>831.32399999999996</v>
       </c>
       <c r="E110">
-        <v>49.494</v>
+        <v>831.32399999999996</v>
       </c>
       <c r="F110">
         <v>1</v>
@@ -5609,13 +5573,13 @@
         <v>58</v>
       </c>
       <c r="C111" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D111">
-        <v>831.32399999999996</v>
+        <v>188.19399999999999</v>
       </c>
       <c r="E111">
-        <v>831.32399999999996</v>
+        <v>188.19399999999999</v>
       </c>
       <c r="F111">
         <v>1</v>
@@ -5638,13 +5602,13 @@
         <v>58</v>
       </c>
       <c r="C112" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="D112">
-        <v>188.19399999999999</v>
+        <v>424.64100000000008</v>
       </c>
       <c r="E112">
-        <v>188.19399999999999</v>
+        <v>424.64100000000008</v>
       </c>
       <c r="F112">
         <v>1</v>
@@ -5664,16 +5628,16 @@
         <v>11</v>
       </c>
       <c r="B113" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="C113" t="s">
         <v>51</v>
       </c>
       <c r="D113">
-        <v>424.64100000000008</v>
+        <v>0.80300000000000016</v>
       </c>
       <c r="E113">
-        <v>424.64100000000008</v>
+        <v>0.80300000000000016</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -5693,16 +5657,16 @@
         <v>11</v>
       </c>
       <c r="B114" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C114" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D114">
-        <v>0.80300000000000016</v>
+        <v>635.83000000000004</v>
       </c>
       <c r="E114">
-        <v>0.80300000000000016</v>
+        <v>635.83000000000004</v>
       </c>
       <c r="F114">
         <v>1</v>
@@ -5725,13 +5689,13 @@
         <v>53</v>
       </c>
       <c r="C115" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D115">
-        <v>635.83000000000004</v>
+        <v>61.32</v>
       </c>
       <c r="E115">
-        <v>635.83000000000004</v>
+        <v>61.32</v>
       </c>
       <c r="F115">
         <v>1</v>
@@ -5754,13 +5718,13 @@
         <v>53</v>
       </c>
       <c r="C116" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D116">
-        <v>61.32</v>
+        <v>80.3</v>
       </c>
       <c r="E116">
-        <v>61.32</v>
+        <v>80.3</v>
       </c>
       <c r="F116">
         <v>1</v>
@@ -5780,16 +5744,16 @@
         <v>11</v>
       </c>
       <c r="B117" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="C117" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="D117">
-        <v>80.3</v>
+        <v>177.79150000000001</v>
       </c>
       <c r="E117">
-        <v>80.3</v>
+        <v>177.79150000000001</v>
       </c>
       <c r="F117">
         <v>1</v>
@@ -5809,16 +5773,16 @@
         <v>11</v>
       </c>
       <c r="B118" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="C118" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D118">
-        <v>177.79150000000001</v>
+        <v>210.25094999999999</v>
       </c>
       <c r="E118">
-        <v>177.79150000000001</v>
+        <v>210.25094999999999</v>
       </c>
       <c r="F118">
         <v>1</v>
@@ -5841,13 +5805,13 @@
         <v>36</v>
       </c>
       <c r="C119" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="D119">
-        <v>210.25094999999999</v>
+        <v>145.489</v>
       </c>
       <c r="E119">
-        <v>210.25094999999999</v>
+        <v>145.489</v>
       </c>
       <c r="F119">
         <v>1</v>
@@ -5867,16 +5831,16 @@
         <v>11</v>
       </c>
       <c r="B120" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="C120" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D120">
-        <v>145.489</v>
+        <v>267.07049999999998</v>
       </c>
       <c r="E120">
-        <v>145.489</v>
+        <v>267.07049999999998</v>
       </c>
       <c r="F120">
         <v>1</v>
@@ -5896,16 +5860,16 @@
         <v>11</v>
       </c>
       <c r="B121" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C121" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D121">
-        <v>547.17150000000004</v>
+        <v>415.40649999999994</v>
       </c>
       <c r="E121">
-        <v>547.17150000000004</v>
+        <v>415.40649999999994</v>
       </c>
       <c r="F121">
         <v>1</v>
@@ -5925,16 +5889,16 @@
         <v>11</v>
       </c>
       <c r="B122" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C122" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D122">
-        <v>178.12</v>
+        <v>173.667</v>
       </c>
       <c r="E122">
-        <v>178.12</v>
+        <v>173.667</v>
       </c>
       <c r="F122">
         <v>1</v>
@@ -5954,16 +5918,16 @@
         <v>11</v>
       </c>
       <c r="B123" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="C123" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D123">
-        <v>806.85586000000001</v>
+        <v>439.27749999999992</v>
       </c>
       <c r="E123">
-        <v>806.85586000000001</v>
+        <v>439.27749999999992</v>
       </c>
       <c r="F123">
         <v>1</v>
@@ -5983,16 +5947,16 @@
         <v>11</v>
       </c>
       <c r="B124" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C124" t="s">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="D124">
-        <v>208.05</v>
+        <v>439.27749999999992</v>
       </c>
       <c r="E124">
-        <v>208.05</v>
+        <v>439.27749999999992</v>
       </c>
       <c r="F124">
         <v>1</v>
@@ -6012,16 +5976,16 @@
         <v>11</v>
       </c>
       <c r="B125" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C125" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D125">
-        <v>267.07049999999998</v>
+        <v>118.77099999999999</v>
       </c>
       <c r="E125">
-        <v>267.07049999999998</v>
+        <v>118.77099999999999</v>
       </c>
       <c r="F125">
         <v>1</v>
@@ -6041,16 +6005,16 @@
         <v>11</v>
       </c>
       <c r="B126" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C126" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="D126">
-        <v>415.40649999999994</v>
+        <v>486.91</v>
       </c>
       <c r="E126">
-        <v>415.40649999999994</v>
+        <v>486.91</v>
       </c>
       <c r="F126">
         <v>1</v>
@@ -6070,16 +6034,16 @@
         <v>11</v>
       </c>
       <c r="B127" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="C127" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="D127">
-        <v>173.667</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="E127">
-        <v>173.667</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="F127">
         <v>1</v>
@@ -6099,16 +6063,16 @@
         <v>11</v>
       </c>
       <c r="B128" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="C128" t="s">
         <v>30</v>
       </c>
       <c r="D128">
-        <v>439.27749999999992</v>
+        <v>49.494</v>
       </c>
       <c r="E128">
-        <v>439.27749999999992</v>
+        <v>49.494</v>
       </c>
       <c r="F128">
         <v>1</v>
@@ -6128,16 +6092,16 @@
         <v>11</v>
       </c>
       <c r="B129" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C129" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D129">
-        <v>439.27749999999992</v>
+        <v>816.06700000000012</v>
       </c>
       <c r="E129">
-        <v>439.27749999999992</v>
+        <v>816.06700000000012</v>
       </c>
       <c r="F129">
         <v>1</v>
@@ -6157,16 +6121,16 @@
         <v>11</v>
       </c>
       <c r="B130" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="C130" t="s">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="D130">
-        <v>118.77099999999999</v>
+        <v>188.88749999999999</v>
       </c>
       <c r="E130">
-        <v>118.77099999999999</v>
+        <v>188.88749999999999</v>
       </c>
       <c r="F130">
         <v>1</v>
@@ -6186,16 +6150,16 @@
         <v>11</v>
       </c>
       <c r="B131" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C131" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D131">
-        <v>486.91</v>
+        <v>89.716999999999999</v>
       </c>
       <c r="E131">
-        <v>486.91</v>
+        <v>89.716999999999999</v>
       </c>
       <c r="F131">
         <v>1</v>
@@ -6215,16 +6179,16 @@
         <v>11</v>
       </c>
       <c r="B132" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C132" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D132">
-        <v>144.17500000000001</v>
+        <v>170.63749999999999</v>
       </c>
       <c r="E132">
-        <v>144.17500000000001</v>
+        <v>170.63749999999999</v>
       </c>
       <c r="F132">
         <v>1</v>
@@ -6244,16 +6208,16 @@
         <v>11</v>
       </c>
       <c r="B133" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C133" t="s">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="D133">
-        <v>49.494</v>
+        <v>12.1837</v>
       </c>
       <c r="E133">
-        <v>49.494</v>
+        <v>12.1837</v>
       </c>
       <c r="F133">
         <v>1</v>
@@ -6273,16 +6237,16 @@
         <v>11</v>
       </c>
       <c r="B134" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="C134" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D134">
-        <v>816.06700000000012</v>
+        <v>256.15699999999998</v>
       </c>
       <c r="E134">
-        <v>816.06700000000012</v>
+        <v>256.15699999999998</v>
       </c>
       <c r="F134">
         <v>1</v>
@@ -6302,16 +6266,16 @@
         <v>11</v>
       </c>
       <c r="B135" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C135" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D135">
-        <v>188.88749999999999</v>
+        <v>180.20050000000001</v>
       </c>
       <c r="E135">
-        <v>188.88749999999999</v>
+        <v>180.20050000000001</v>
       </c>
       <c r="F135">
         <v>1</v>
@@ -6331,16 +6295,16 @@
         <v>11</v>
       </c>
       <c r="B136" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C136" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D136">
-        <v>89.716999999999999</v>
+        <v>421.21</v>
       </c>
       <c r="E136">
-        <v>89.716999999999999</v>
+        <v>421.21</v>
       </c>
       <c r="F136">
         <v>1</v>
@@ -6360,16 +6324,16 @@
         <v>11</v>
       </c>
       <c r="B137" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C137" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="D137">
-        <v>170.63749999999999</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="E137">
-        <v>170.63749999999999</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="F137">
         <v>1</v>
@@ -6389,16 +6353,16 @@
         <v>11</v>
       </c>
       <c r="B138" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C138" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="D138">
-        <v>12.1837</v>
+        <v>161.62200000000001</v>
       </c>
       <c r="E138">
-        <v>12.1837</v>
+        <v>161.62200000000001</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -6418,16 +6382,16 @@
         <v>11</v>
       </c>
       <c r="B139" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C139" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="D139">
-        <v>256.15699999999998</v>
+        <v>455.15499999999997</v>
       </c>
       <c r="E139">
-        <v>256.15699999999998</v>
+        <v>455.15499999999997</v>
       </c>
       <c r="F139">
         <v>1</v>
@@ -6447,16 +6411,16 @@
         <v>11</v>
       </c>
       <c r="B140" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C140" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D140">
-        <v>180.20050000000001</v>
+        <v>351.714</v>
       </c>
       <c r="E140">
-        <v>180.20050000000001</v>
+        <v>351.714</v>
       </c>
       <c r="F140">
         <v>1</v>
@@ -6476,16 +6440,16 @@
         <v>11</v>
       </c>
       <c r="B141" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C141" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D141">
-        <v>421.21</v>
+        <v>167.75399999999999</v>
       </c>
       <c r="E141">
-        <v>421.21</v>
+        <v>167.75399999999999</v>
       </c>
       <c r="F141">
         <v>1</v>
@@ -6505,16 +6469,16 @@
         <v>11</v>
       </c>
       <c r="B142" t="s">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="C142" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D142">
-        <v>123.04150000000001</v>
+        <v>207.5025</v>
       </c>
       <c r="E142">
-        <v>123.04150000000001</v>
+        <v>207.5025</v>
       </c>
       <c r="F142">
         <v>1</v>
@@ -6534,16 +6498,16 @@
         <v>11</v>
       </c>
       <c r="B143" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C143" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D143">
-        <v>161.62200000000001</v>
+        <v>513.19000000000005</v>
       </c>
       <c r="E143">
-        <v>161.62200000000001</v>
+        <v>513.19000000000005</v>
       </c>
       <c r="F143">
         <v>1</v>
@@ -6563,16 +6527,16 @@
         <v>11</v>
       </c>
       <c r="B144" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C144" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D144">
-        <v>455.15499999999997</v>
+        <v>82.927999999999997</v>
       </c>
       <c r="E144">
-        <v>455.15499999999997</v>
+        <v>82.927999999999997</v>
       </c>
       <c r="F144">
         <v>1</v>
@@ -6592,16 +6556,16 @@
         <v>11</v>
       </c>
       <c r="B145" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C145" t="s">
         <v>28</v>
       </c>
       <c r="D145">
-        <v>351.714</v>
+        <v>67.451999999999998</v>
       </c>
       <c r="E145">
-        <v>351.714</v>
+        <v>67.451999999999998</v>
       </c>
       <c r="F145">
         <v>1</v>
@@ -6621,16 +6585,16 @@
         <v>11</v>
       </c>
       <c r="B146" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="C146" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D146">
-        <v>167.75399999999999</v>
+        <v>200.71350000000001</v>
       </c>
       <c r="E146">
-        <v>167.75399999999999</v>
+        <v>200.71350000000001</v>
       </c>
       <c r="F146">
         <v>1</v>
@@ -6650,16 +6614,16 @@
         <v>11</v>
       </c>
       <c r="B147" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="C147" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="D147">
-        <v>207.5025</v>
+        <v>200.71350000000001</v>
       </c>
       <c r="E147">
-        <v>207.5025</v>
+        <v>200.71350000000001</v>
       </c>
       <c r="F147">
         <v>1</v>
@@ -6679,16 +6643,16 @@
         <v>11</v>
       </c>
       <c r="B148" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C148" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D148">
-        <v>513.19000000000005</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="E148">
-        <v>513.19000000000005</v>
+        <v>144.17500000000001</v>
       </c>
       <c r="F148">
         <v>1</v>
@@ -6708,16 +6672,16 @@
         <v>11</v>
       </c>
       <c r="B149" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="C149" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D149">
-        <v>140.52500000000001</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="E149">
-        <v>140.52500000000001</v>
+        <v>123.04150000000001</v>
       </c>
       <c r="F149">
         <v>1</v>
@@ -6737,16 +6701,16 @@
         <v>11</v>
       </c>
       <c r="B150" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="C150" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="D150">
-        <v>82.927999999999997</v>
+        <v>421.21</v>
       </c>
       <c r="E150">
-        <v>82.927999999999997</v>
+        <v>421.21</v>
       </c>
       <c r="F150">
         <v>1</v>
@@ -6766,16 +6730,16 @@
         <v>11</v>
       </c>
       <c r="B151" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C151" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="D151">
-        <v>67.451999999999998</v>
+        <v>14.965</v>
       </c>
       <c r="E151">
-        <v>67.451999999999998</v>
+        <v>14.965</v>
       </c>
       <c r="F151">
         <v>1</v>
@@ -6792,19 +6756,19 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="C152" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D152">
-        <v>200.71350000000001</v>
+        <v>500</v>
       </c>
       <c r="E152">
-        <v>200.71350000000001</v>
+        <v>500</v>
       </c>
       <c r="F152">
         <v>1</v>
@@ -6813,7 +6777,7 @@
         <v>10000000</v>
       </c>
       <c r="H152">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I152">
         <v>1</v>
@@ -6821,19 +6785,19 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C153" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="D153">
-        <v>200.71350000000001</v>
+        <v>500</v>
       </c>
       <c r="E153">
-        <v>200.71350000000001</v>
+        <v>500</v>
       </c>
       <c r="F153">
         <v>1</v>
@@ -6842,7 +6806,7 @@
         <v>10000000</v>
       </c>
       <c r="H153">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I153">
         <v>1</v>
@@ -6850,19 +6814,19 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="C154" t="s">
         <v>20</v>
       </c>
       <c r="D154">
-        <v>144.17500000000001</v>
+        <v>500</v>
       </c>
       <c r="E154">
-        <v>144.17500000000001</v>
+        <v>500</v>
       </c>
       <c r="F154">
         <v>1</v>
@@ -6871,7 +6835,7 @@
         <v>10000000</v>
       </c>
       <c r="H154">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I154">
         <v>1</v>
@@ -6879,19 +6843,19 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="C155" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="D155">
-        <v>123.04150000000001</v>
+        <v>500</v>
       </c>
       <c r="E155">
-        <v>123.04150000000001</v>
+        <v>500</v>
       </c>
       <c r="F155">
         <v>1</v>
@@ -6900,7 +6864,7 @@
         <v>10000000</v>
       </c>
       <c r="H155">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I155">
         <v>1</v>
@@ -6908,19 +6872,19 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="C156" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="D156">
-        <v>421.21</v>
+        <v>500</v>
       </c>
       <c r="E156">
-        <v>421.21</v>
+        <v>500</v>
       </c>
       <c r="F156">
         <v>1</v>
@@ -6929,7 +6893,7 @@
         <v>10000000</v>
       </c>
       <c r="H156">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I156">
         <v>1</v>
@@ -6937,19 +6901,19 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C157" t="s">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="D157">
-        <v>14.965</v>
+        <v>500</v>
       </c>
       <c r="E157">
-        <v>14.965</v>
+        <v>500</v>
       </c>
       <c r="F157">
         <v>1</v>
@@ -6958,7 +6922,7 @@
         <v>10000000</v>
       </c>
       <c r="H157">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I157">
         <v>1</v>
@@ -6969,10 +6933,10 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C158" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D158">
         <v>500</v>
@@ -6998,10 +6962,10 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C159" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D159">
         <v>500</v>
@@ -7027,10 +6991,10 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C160" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D160">
         <v>500</v>
@@ -7056,10 +7020,10 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C161" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D161">
         <v>500</v>
@@ -7085,10 +7049,10 @@
         <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C162" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D162">
         <v>500</v>
@@ -7114,10 +7078,10 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C163" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D163">
         <v>500</v>
@@ -7143,10 +7107,10 @@
         <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="C164" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="D164">
         <v>500</v>
@@ -7172,10 +7136,10 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C165" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D165">
         <v>500</v>
@@ -7201,10 +7165,10 @@
         <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C166" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D166">
         <v>500</v>
@@ -7230,10 +7194,10 @@
         <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C167" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D167">
         <v>500</v>
@@ -7259,10 +7223,10 @@
         <v>12</v>
       </c>
       <c r="B168" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C168" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D168">
         <v>500</v>
@@ -7288,10 +7252,10 @@
         <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C169" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D169">
         <v>500</v>
@@ -7317,10 +7281,10 @@
         <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>80</v>
+        <v>47</v>
       </c>
       <c r="C170" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="D170">
         <v>500</v>
@@ -7346,10 +7310,10 @@
         <v>12</v>
       </c>
       <c r="B171" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C171" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D171">
         <v>500</v>
@@ -7375,10 +7339,10 @@
         <v>12</v>
       </c>
       <c r="B172" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C172" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="D172">
         <v>500</v>
@@ -7404,10 +7368,10 @@
         <v>12</v>
       </c>
       <c r="B173" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C173" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="D173">
         <v>500</v>
@@ -7433,10 +7397,10 @@
         <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C174" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D174">
         <v>500</v>
@@ -7462,10 +7426,10 @@
         <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C175" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D175">
         <v>500</v>
@@ -7491,10 +7455,10 @@
         <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C176" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D176">
         <v>500</v>
@@ -7520,10 +7484,10 @@
         <v>12</v>
       </c>
       <c r="B177" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C177" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D177">
         <v>500</v>
@@ -7549,10 +7513,10 @@
         <v>12</v>
       </c>
       <c r="B178" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C178" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D178">
         <v>500</v>
@@ -7578,10 +7542,10 @@
         <v>12</v>
       </c>
       <c r="B179" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="C179" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D179">
         <v>500</v>
@@ -7607,10 +7571,10 @@
         <v>12</v>
       </c>
       <c r="B180" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="C180" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="D180">
         <v>500</v>
@@ -7636,10 +7600,10 @@
         <v>12</v>
       </c>
       <c r="B181" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="C181" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D181">
         <v>500</v>
@@ -7665,10 +7629,10 @@
         <v>12</v>
       </c>
       <c r="B182" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="C182" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="D182">
         <v>500</v>
@@ -7694,7 +7658,7 @@
         <v>12</v>
       </c>
       <c r="B183" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C183" t="s">
         <v>16</v>
@@ -7723,10 +7687,10 @@
         <v>12</v>
       </c>
       <c r="B184" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C184" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="D184">
         <v>500</v>
@@ -7752,10 +7716,10 @@
         <v>12</v>
       </c>
       <c r="B185" t="s">
+        <v>42</v>
+      </c>
+      <c r="C185" t="s">
         <v>16</v>
-      </c>
-      <c r="C185" t="s">
-        <v>38</v>
       </c>
       <c r="D185">
         <v>500</v>
@@ -7781,7 +7745,7 @@
         <v>12</v>
       </c>
       <c r="B186" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C186" t="s">
         <v>28</v>
@@ -7810,10 +7774,10 @@
         <v>12</v>
       </c>
       <c r="B187" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C187" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="D187">
         <v>500</v>
@@ -7839,10 +7803,10 @@
         <v>12</v>
       </c>
       <c r="B188" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C188" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="D188">
         <v>500</v>
@@ -7868,10 +7832,10 @@
         <v>12</v>
       </c>
       <c r="B189" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C189" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D189">
         <v>500</v>
@@ -7897,10 +7861,10 @@
         <v>12</v>
       </c>
       <c r="B190" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C190" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D190">
         <v>500</v>
@@ -7929,7 +7893,7 @@
         <v>42</v>
       </c>
       <c r="C191" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D191">
         <v>500</v>
@@ -7958,7 +7922,7 @@
         <v>42</v>
       </c>
       <c r="C192" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="D192">
         <v>500</v>
@@ -7987,7 +7951,7 @@
         <v>42</v>
       </c>
       <c r="C193" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D193">
         <v>500</v>
@@ -8013,10 +7977,10 @@
         <v>12</v>
       </c>
       <c r="B194" t="s">
+        <v>60</v>
+      </c>
+      <c r="C194" t="s">
         <v>42</v>
-      </c>
-      <c r="C194" t="s">
-        <v>61</v>
       </c>
       <c r="D194">
         <v>500</v>
@@ -8042,10 +8006,10 @@
         <v>12</v>
       </c>
       <c r="B195" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C195" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D195">
         <v>500</v>
@@ -8071,10 +8035,10 @@
         <v>12</v>
       </c>
       <c r="B196" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C196" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="D196">
         <v>500</v>
@@ -8100,10 +8064,10 @@
         <v>12</v>
       </c>
       <c r="B197" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C197" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D197">
         <v>500</v>
@@ -8129,10 +8093,10 @@
         <v>12</v>
       </c>
       <c r="B198" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C198" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D198">
         <v>500</v>
@@ -8158,10 +8122,10 @@
         <v>12</v>
       </c>
       <c r="B199" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C199" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D199">
         <v>500</v>
@@ -8187,10 +8151,10 @@
         <v>12</v>
       </c>
       <c r="B200" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="C200" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D200">
         <v>500</v>
@@ -8216,10 +8180,10 @@
         <v>12</v>
       </c>
       <c r="B201" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="C201" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="D201">
         <v>500</v>
@@ -8245,10 +8209,10 @@
         <v>12</v>
       </c>
       <c r="B202" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C202" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D202">
         <v>500</v>
@@ -8274,10 +8238,10 @@
         <v>12</v>
       </c>
       <c r="B203" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C203" t="s">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="D203">
         <v>500</v>
@@ -8303,10 +8267,10 @@
         <v>12</v>
       </c>
       <c r="B204" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C204" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="D204">
         <v>500</v>
@@ -8332,10 +8296,10 @@
         <v>12</v>
       </c>
       <c r="B205" t="s">
+        <v>64</v>
+      </c>
+      <c r="C205" t="s">
         <v>22</v>
-      </c>
-      <c r="C205" t="s">
-        <v>60</v>
       </c>
       <c r="D205">
         <v>500</v>
@@ -8361,10 +8325,10 @@
         <v>12</v>
       </c>
       <c r="B206" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="C206" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="D206">
         <v>500</v>
@@ -8390,7 +8354,7 @@
         <v>12</v>
       </c>
       <c r="B207" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C207" t="s">
         <v>64</v>
@@ -8419,10 +8383,10 @@
         <v>12</v>
       </c>
       <c r="B208" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="C208" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D208">
         <v>500</v>
@@ -8448,10 +8412,10 @@
         <v>12</v>
       </c>
       <c r="B209" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="C209" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D209">
         <v>500</v>
@@ -8477,10 +8441,10 @@
         <v>12</v>
       </c>
       <c r="B210" t="s">
+        <v>18</v>
+      </c>
+      <c r="C210" t="s">
         <v>61</v>
-      </c>
-      <c r="C210" t="s">
-        <v>18</v>
       </c>
       <c r="D210">
         <v>500</v>
@@ -8506,10 +8470,10 @@
         <v>12</v>
       </c>
       <c r="B211" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="C211" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D211">
         <v>500</v>
@@ -8535,10 +8499,10 @@
         <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="C212" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D212">
         <v>500</v>
@@ -8564,10 +8528,10 @@
         <v>12</v>
       </c>
       <c r="B213" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C213" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D213">
         <v>500</v>
@@ -8593,10 +8557,10 @@
         <v>12</v>
       </c>
       <c r="B214" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="C214" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="D214">
         <v>500</v>
@@ -8622,10 +8586,10 @@
         <v>12</v>
       </c>
       <c r="B215" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="C215" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D215">
         <v>500</v>
@@ -8651,10 +8615,10 @@
         <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="C216" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D216">
         <v>500</v>
@@ -8680,10 +8644,10 @@
         <v>12</v>
       </c>
       <c r="B217" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C217" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="D217">
         <v>500</v>
@@ -8709,10 +8673,10 @@
         <v>12</v>
       </c>
       <c r="B218" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C218" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D218">
         <v>500</v>
@@ -8738,10 +8702,10 @@
         <v>12</v>
       </c>
       <c r="B219" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="C219" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="D219">
         <v>500</v>
@@ -8767,10 +8731,10 @@
         <v>12</v>
       </c>
       <c r="B220" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C220" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D220">
         <v>500</v>
@@ -8796,10 +8760,10 @@
         <v>12</v>
       </c>
       <c r="B221" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C221" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D221">
         <v>500</v>
@@ -8825,7 +8789,7 @@
         <v>12</v>
       </c>
       <c r="B222" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C222" t="s">
         <v>65</v>
@@ -8854,10 +8818,10 @@
         <v>12</v>
       </c>
       <c r="B223" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C223" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D223">
         <v>500</v>
@@ -8883,10 +8847,10 @@
         <v>12</v>
       </c>
       <c r="B224" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C224" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D224">
         <v>500</v>
@@ -8912,10 +8876,10 @@
         <v>12</v>
       </c>
       <c r="B225" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C225" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D225">
         <v>500</v>
@@ -8941,10 +8905,10 @@
         <v>12</v>
       </c>
       <c r="B226" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C226" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D226">
         <v>500</v>
@@ -8970,10 +8934,10 @@
         <v>12</v>
       </c>
       <c r="B227" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C227" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="D227">
         <v>500</v>
@@ -8999,10 +8963,10 @@
         <v>12</v>
       </c>
       <c r="B228" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C228" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="D228">
         <v>500</v>
@@ -9028,10 +8992,10 @@
         <v>12</v>
       </c>
       <c r="B229" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C229" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="D229">
         <v>500</v>
@@ -9057,10 +9021,10 @@
         <v>12</v>
       </c>
       <c r="B230" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C230" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D230">
         <v>500</v>
@@ -9086,10 +9050,10 @@
         <v>12</v>
       </c>
       <c r="B231" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C231" t="s">
-        <v>68</v>
+        <v>36</v>
       </c>
       <c r="D231">
         <v>500</v>
@@ -9115,10 +9079,10 @@
         <v>12</v>
       </c>
       <c r="B232" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="C232" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D232">
         <v>500</v>
@@ -9144,10 +9108,10 @@
         <v>12</v>
       </c>
       <c r="B233" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C233" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D233">
         <v>500</v>
@@ -9173,10 +9137,10 @@
         <v>12</v>
       </c>
       <c r="B234" t="s">
+        <v>51</v>
+      </c>
+      <c r="C234" t="s">
         <v>68</v>
-      </c>
-      <c r="C234" t="s">
-        <v>20</v>
       </c>
       <c r="D234">
         <v>500</v>
@@ -9202,10 +9166,10 @@
         <v>12</v>
       </c>
       <c r="B235" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C235" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D235">
         <v>500</v>
@@ -9231,10 +9195,10 @@
         <v>12</v>
       </c>
       <c r="B236" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C236" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D236">
         <v>500</v>
@@ -9260,10 +9224,10 @@
         <v>12</v>
       </c>
       <c r="B237" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="C237" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="D237">
         <v>500</v>
@@ -9289,10 +9253,10 @@
         <v>12</v>
       </c>
       <c r="B238" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C238" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D238">
         <v>500</v>
@@ -9318,10 +9282,10 @@
         <v>12</v>
       </c>
       <c r="B239" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="C239" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="D239">
         <v>500</v>
@@ -9347,10 +9311,10 @@
         <v>12</v>
       </c>
       <c r="B240" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="C240" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D240">
         <v>500</v>
@@ -9376,10 +9340,10 @@
         <v>12</v>
       </c>
       <c r="B241" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="C241" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="D241">
         <v>500</v>
@@ -9405,10 +9369,10 @@
         <v>12</v>
       </c>
       <c r="B242" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="C242" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="D242">
         <v>500</v>
@@ -9434,10 +9398,10 @@
         <v>12</v>
       </c>
       <c r="B243" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C243" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="D243">
         <v>500</v>
@@ -9463,10 +9427,10 @@
         <v>12</v>
       </c>
       <c r="B244" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="C244" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="D244">
         <v>500</v>
@@ -9492,10 +9456,10 @@
         <v>12</v>
       </c>
       <c r="B245" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C245" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="D245">
         <v>500</v>
@@ -9521,10 +9485,10 @@
         <v>12</v>
       </c>
       <c r="B246" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C246" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D246">
         <v>500</v>
@@ -9550,10 +9514,10 @@
         <v>12</v>
       </c>
       <c r="B247" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C247" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="D247">
         <v>500</v>
@@ -9579,10 +9543,10 @@
         <v>12</v>
       </c>
       <c r="B248" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C248" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="D248">
         <v>500</v>
@@ -9608,10 +9572,10 @@
         <v>12</v>
       </c>
       <c r="B249" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C249" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D249">
         <v>500</v>
@@ -9637,10 +9601,10 @@
         <v>12</v>
       </c>
       <c r="B250" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C250" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="D250">
         <v>500</v>
@@ -9666,10 +9630,10 @@
         <v>12</v>
       </c>
       <c r="B251" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C251" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D251">
         <v>500</v>
@@ -9695,10 +9659,10 @@
         <v>12</v>
       </c>
       <c r="B252" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="C252" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D252">
         <v>500</v>
@@ -9724,10 +9688,10 @@
         <v>12</v>
       </c>
       <c r="B253" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="C253" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D253">
         <v>500</v>
@@ -9753,10 +9717,10 @@
         <v>12</v>
       </c>
       <c r="B254" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="C254" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="D254">
         <v>500</v>
@@ -9782,10 +9746,10 @@
         <v>12</v>
       </c>
       <c r="B255" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="C255" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D255">
         <v>500</v>
@@ -9811,10 +9775,10 @@
         <v>12</v>
       </c>
       <c r="B256" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C256" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
       <c r="D256">
         <v>500</v>
@@ -9840,10 +9804,10 @@
         <v>12</v>
       </c>
       <c r="B257" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C257" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="D257">
         <v>500</v>
@@ -9869,10 +9833,10 @@
         <v>12</v>
       </c>
       <c r="B258" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C258" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D258">
         <v>500</v>
@@ -9898,10 +9862,10 @@
         <v>12</v>
       </c>
       <c r="B259" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="C259" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="D259">
         <v>500</v>
@@ -9927,10 +9891,10 @@
         <v>12</v>
       </c>
       <c r="B260" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C260" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="D260">
         <v>500</v>
@@ -9956,10 +9920,10 @@
         <v>12</v>
       </c>
       <c r="B261" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="C261" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="D261">
         <v>500</v>
@@ -9985,10 +9949,10 @@
         <v>12</v>
       </c>
       <c r="B262" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C262" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D262">
         <v>500</v>
@@ -10014,10 +9978,10 @@
         <v>12</v>
       </c>
       <c r="B263" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C263" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D263">
         <v>500</v>
@@ -10043,10 +10007,10 @@
         <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C264" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="D264">
         <v>500</v>
@@ -10072,10 +10036,10 @@
         <v>12</v>
       </c>
       <c r="B265" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="C265" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="D265">
         <v>500</v>
@@ -10101,10 +10065,10 @@
         <v>12</v>
       </c>
       <c r="B266" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C266" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="D266">
         <v>500</v>
@@ -10130,10 +10094,10 @@
         <v>12</v>
       </c>
       <c r="B267" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C267" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D267">
         <v>500</v>
@@ -10159,10 +10123,10 @@
         <v>12</v>
       </c>
       <c r="B268" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C268" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D268">
         <v>500</v>
@@ -10188,10 +10152,10 @@
         <v>12</v>
       </c>
       <c r="B269" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C269" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D269">
         <v>500</v>
@@ -10217,10 +10181,10 @@
         <v>12</v>
       </c>
       <c r="B270" t="s">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="C270" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="D270">
         <v>500</v>
@@ -10246,10 +10210,10 @@
         <v>12</v>
       </c>
       <c r="B271" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C271" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="D271">
         <v>500</v>
@@ -10275,10 +10239,10 @@
         <v>12</v>
       </c>
       <c r="B272" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C272" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D272">
         <v>500</v>
@@ -10304,10 +10268,10 @@
         <v>12</v>
       </c>
       <c r="B273" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C273" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="D273">
         <v>500</v>
@@ -10333,10 +10297,10 @@
         <v>12</v>
       </c>
       <c r="B274" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C274" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="D274">
         <v>500</v>
@@ -10362,10 +10326,10 @@
         <v>12</v>
       </c>
       <c r="B275" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="C275" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="D275">
         <v>500</v>
@@ -10391,10 +10355,10 @@
         <v>12</v>
       </c>
       <c r="B276" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="C276" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="D276">
         <v>500</v>
@@ -10420,10 +10384,10 @@
         <v>12</v>
       </c>
       <c r="B277" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C277" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="D277">
         <v>500</v>
@@ -10449,10 +10413,10 @@
         <v>12</v>
       </c>
       <c r="B278" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C278" t="s">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="D278">
         <v>500</v>
@@ -10478,7 +10442,7 @@
         <v>12</v>
       </c>
       <c r="B279" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C279" t="s">
         <v>22</v>
@@ -10507,10 +10471,10 @@
         <v>12</v>
       </c>
       <c r="B280" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="C280" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="D280">
         <v>500</v>
@@ -10536,10 +10500,10 @@
         <v>12</v>
       </c>
       <c r="B281" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C281" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D281">
         <v>500</v>
@@ -10565,10 +10529,10 @@
         <v>12</v>
       </c>
       <c r="B282" t="s">
+        <v>83</v>
+      </c>
+      <c r="C282" t="s">
         <v>78</v>
-      </c>
-      <c r="C282" t="s">
-        <v>34</v>
       </c>
       <c r="D282">
         <v>500</v>
@@ -10594,10 +10558,10 @@
         <v>12</v>
       </c>
       <c r="B283" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="C283" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D283">
         <v>500</v>
@@ -10623,10 +10587,10 @@
         <v>12</v>
       </c>
       <c r="B284" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C284" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="D284">
         <v>500</v>
@@ -10652,19 +10616,19 @@
         <v>12</v>
       </c>
       <c r="B285" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="C285" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="D285">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E285">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F285">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G285">
         <v>10000000</v>
@@ -10681,19 +10645,19 @@
         <v>12</v>
       </c>
       <c r="B286" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="C286" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="D286">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E286">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F286">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G286">
         <v>10000000</v>
@@ -10710,19 +10674,19 @@
         <v>12</v>
       </c>
       <c r="B287" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="C287" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D287">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E287">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F287">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G287">
         <v>10000000</v>
@@ -10739,19 +10703,19 @@
         <v>12</v>
       </c>
       <c r="B288" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="C288" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="D288">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E288">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F288">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G288">
         <v>10000000</v>
@@ -10768,19 +10732,19 @@
         <v>12</v>
       </c>
       <c r="B289" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="C289" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="D289">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E289">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F289">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G289">
         <v>10000000</v>
@@ -10797,19 +10761,19 @@
         <v>12</v>
       </c>
       <c r="B290" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="C290" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D290">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E290">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F290">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G290">
         <v>10000000</v>
@@ -10826,19 +10790,19 @@
         <v>12</v>
       </c>
       <c r="B291" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="C291" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="D291">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E291">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F291">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G291">
         <v>10000000</v>
@@ -10855,19 +10819,19 @@
         <v>12</v>
       </c>
       <c r="B292" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="C292" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="D292">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E292">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F292">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G292">
         <v>10000000</v>
@@ -10884,19 +10848,19 @@
         <v>12</v>
       </c>
       <c r="B293" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C293" t="s">
         <v>20</v>
       </c>
       <c r="D293">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E293">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F293">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G293">
         <v>10000000</v>
@@ -10913,19 +10877,19 @@
         <v>12</v>
       </c>
       <c r="B294" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C294" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D294">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E294">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F294">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G294">
         <v>10000000</v>
@@ -10942,19 +10906,19 @@
         <v>12</v>
       </c>
       <c r="B295" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="C295" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D295">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E295">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F295">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G295">
         <v>10000000</v>
@@ -10971,19 +10935,19 @@
         <v>12</v>
       </c>
       <c r="B296" t="s">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="C296" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="D296">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E296">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F296">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G296">
         <v>10000000</v>
@@ -11000,10 +10964,10 @@
         <v>12</v>
       </c>
       <c r="B297" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C297" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D297">
         <v>10000</v>
@@ -11029,10 +10993,10 @@
         <v>12</v>
       </c>
       <c r="B298" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C298" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="D298">
         <v>10000</v>
@@ -11058,10 +11022,10 @@
         <v>12</v>
       </c>
       <c r="B299" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="C299" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D299">
         <v>10000</v>
@@ -11087,10 +11051,10 @@
         <v>12</v>
       </c>
       <c r="B300" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="C300" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D300">
         <v>10000</v>
@@ -11116,19 +11080,19 @@
         <v>12</v>
       </c>
       <c r="B301" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="C301" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D301">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="E301">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="F301">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G301">
         <v>10000000</v>
@@ -11145,19 +11109,19 @@
         <v>12</v>
       </c>
       <c r="B302" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C302" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D302">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="E302">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="F302">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G302">
         <v>10000000</v>
@@ -11166,354 +11130,6 @@
         <v>1000</v>
       </c>
       <c r="I302">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A303" t="s">
-        <v>12</v>
-      </c>
-      <c r="B303" t="s">
-        <v>89</v>
-      </c>
-      <c r="C303" t="s">
-        <v>62</v>
-      </c>
-      <c r="D303">
-        <v>10000</v>
-      </c>
-      <c r="E303">
-        <v>10000</v>
-      </c>
-      <c r="F303">
-        <v>100</v>
-      </c>
-      <c r="G303">
-        <v>10000000</v>
-      </c>
-      <c r="H303">
-        <v>1000</v>
-      </c>
-      <c r="I303">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A304" t="s">
-        <v>12</v>
-      </c>
-      <c r="B304" t="s">
-        <v>90</v>
-      </c>
-      <c r="C304" t="s">
-        <v>18</v>
-      </c>
-      <c r="D304">
-        <v>10000</v>
-      </c>
-      <c r="E304">
-        <v>10000</v>
-      </c>
-      <c r="F304">
-        <v>100</v>
-      </c>
-      <c r="G304">
-        <v>10000000</v>
-      </c>
-      <c r="H304">
-        <v>1000</v>
-      </c>
-      <c r="I304">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A305" t="s">
-        <v>12</v>
-      </c>
-      <c r="B305" t="s">
-        <v>91</v>
-      </c>
-      <c r="C305" t="s">
-        <v>20</v>
-      </c>
-      <c r="D305">
-        <v>10000</v>
-      </c>
-      <c r="E305">
-        <v>10000</v>
-      </c>
-      <c r="F305">
-        <v>100</v>
-      </c>
-      <c r="G305">
-        <v>10000000</v>
-      </c>
-      <c r="H305">
-        <v>1000</v>
-      </c>
-      <c r="I305">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A306" t="s">
-        <v>12</v>
-      </c>
-      <c r="B306" t="s">
-        <v>92</v>
-      </c>
-      <c r="C306" t="s">
-        <v>66</v>
-      </c>
-      <c r="D306">
-        <v>10000</v>
-      </c>
-      <c r="E306">
-        <v>10000</v>
-      </c>
-      <c r="F306">
-        <v>100</v>
-      </c>
-      <c r="G306">
-        <v>10000000</v>
-      </c>
-      <c r="H306">
-        <v>1000</v>
-      </c>
-      <c r="I306">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A307" t="s">
-        <v>12</v>
-      </c>
-      <c r="B307" t="s">
-        <v>93</v>
-      </c>
-      <c r="C307" t="s">
-        <v>59</v>
-      </c>
-      <c r="D307">
-        <v>10000</v>
-      </c>
-      <c r="E307">
-        <v>10000</v>
-      </c>
-      <c r="F307">
-        <v>100</v>
-      </c>
-      <c r="G307">
-        <v>10000000</v>
-      </c>
-      <c r="H307">
-        <v>1000</v>
-      </c>
-      <c r="I307">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A308" t="s">
-        <v>12</v>
-      </c>
-      <c r="B308" t="s">
-        <v>94</v>
-      </c>
-      <c r="C308" t="s">
-        <v>67</v>
-      </c>
-      <c r="D308">
-        <v>10000</v>
-      </c>
-      <c r="E308">
-        <v>10000</v>
-      </c>
-      <c r="F308">
-        <v>100</v>
-      </c>
-      <c r="G308">
-        <v>10000000</v>
-      </c>
-      <c r="H308">
-        <v>1000</v>
-      </c>
-      <c r="I308">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A309" t="s">
-        <v>12</v>
-      </c>
-      <c r="B309" t="s">
-        <v>95</v>
-      </c>
-      <c r="C309" t="s">
-        <v>65</v>
-      </c>
-      <c r="D309">
-        <v>10000</v>
-      </c>
-      <c r="E309">
-        <v>10000</v>
-      </c>
-      <c r="F309">
-        <v>100</v>
-      </c>
-      <c r="G309">
-        <v>10000000</v>
-      </c>
-      <c r="H309">
-        <v>1000</v>
-      </c>
-      <c r="I309">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A310" t="s">
-        <v>12</v>
-      </c>
-      <c r="B310" t="s">
-        <v>96</v>
-      </c>
-      <c r="C310" t="s">
-        <v>64</v>
-      </c>
-      <c r="D310">
-        <v>10000</v>
-      </c>
-      <c r="E310">
-        <v>10000</v>
-      </c>
-      <c r="F310">
-        <v>100</v>
-      </c>
-      <c r="G310">
-        <v>10000000</v>
-      </c>
-      <c r="H310">
-        <v>1000</v>
-      </c>
-      <c r="I310">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A311" t="s">
-        <v>12</v>
-      </c>
-      <c r="B311" t="s">
-        <v>97</v>
-      </c>
-      <c r="C311" t="s">
-        <v>36</v>
-      </c>
-      <c r="D311">
-        <v>10000</v>
-      </c>
-      <c r="E311">
-        <v>10000</v>
-      </c>
-      <c r="F311">
-        <v>100</v>
-      </c>
-      <c r="G311">
-        <v>10000000</v>
-      </c>
-      <c r="H311">
-        <v>1000</v>
-      </c>
-      <c r="I311">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A312" t="s">
-        <v>12</v>
-      </c>
-      <c r="B312" t="s">
-        <v>98</v>
-      </c>
-      <c r="C312" t="s">
-        <v>34</v>
-      </c>
-      <c r="D312">
-        <v>10000</v>
-      </c>
-      <c r="E312">
-        <v>10000</v>
-      </c>
-      <c r="F312">
-        <v>100</v>
-      </c>
-      <c r="G312">
-        <v>10000000</v>
-      </c>
-      <c r="H312">
-        <v>1000</v>
-      </c>
-      <c r="I312">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A313" t="s">
-        <v>12</v>
-      </c>
-      <c r="B313" t="s">
-        <v>53</v>
-      </c>
-      <c r="C313" t="s">
-        <v>75</v>
-      </c>
-      <c r="D313">
-        <v>500</v>
-      </c>
-      <c r="E313">
-        <v>500</v>
-      </c>
-      <c r="F313">
-        <v>1</v>
-      </c>
-      <c r="G313">
-        <v>10000000</v>
-      </c>
-      <c r="H313">
-        <v>1000</v>
-      </c>
-      <c r="I313">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A314" t="s">
-        <v>12</v>
-      </c>
-      <c r="B314" t="s">
-        <v>75</v>
-      </c>
-      <c r="C314" t="s">
-        <v>30</v>
-      </c>
-      <c r="D314">
-        <v>500</v>
-      </c>
-      <c r="E314">
-        <v>500</v>
-      </c>
-      <c r="F314">
-        <v>1</v>
-      </c>
-      <c r="G314">
-        <v>10000000</v>
-      </c>
-      <c r="H314">
-        <v>1000</v>
-      </c>
-      <c r="I314">
         <v>1</v>
       </c>
     </row>
@@ -11525,7 +11141,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68B577B-1347-43AB-A697-F4519763B965}">
-  <dimension ref="A1:C162"/>
+  <dimension ref="A1:C168"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -11676,7 +11292,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -11687,7 +11303,7 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C15">
         <v>0.55586415</v>
@@ -11698,7 +11314,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C16">
         <v>796.255</v>
@@ -11709,7 +11325,7 @@
         <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C17">
         <v>7.5617455199999997</v>
@@ -11720,7 +11336,7 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C18">
         <v>5.7643000000000007E-2</v>
@@ -11731,7 +11347,7 @@
         <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C19">
         <v>0.53100926999999998</v>
@@ -11742,7 +11358,7 @@
         <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C20">
         <v>8.6795214499999993</v>
@@ -11753,7 +11369,7 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C21">
         <v>1.9156527500000002</v>
@@ -11764,7 +11380,7 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C22">
         <v>0.16949973000000002</v>
@@ -11775,7 +11391,7 @@
         <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C23">
         <v>6.3309600000000021E-2</v>
@@ -11786,7 +11402,7 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C24">
         <v>16.46245</v>
@@ -11797,7 +11413,7 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C25">
         <v>19.829690269999997</v>
@@ -11808,7 +11424,7 @@
         <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C26">
         <v>3.9959299999999995</v>
@@ -11819,7 +11435,7 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C27">
         <v>0.6516687699999999</v>
@@ -11830,7 +11446,7 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C28">
         <v>5.2113180000000002E-2</v>
@@ -11841,7 +11457,7 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C29">
         <v>4.2744726999999996</v>
@@ -11852,7 +11468,7 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C30">
         <v>0.44941999999999999</v>
@@ -12380,7 +11996,7 @@
         <v>11</v>
       </c>
       <c r="B78" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C78">
         <v>-10.747</v>
@@ -12388,13 +12004,13 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>-3.1361880225518983</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.35">
@@ -12402,7 +12018,7 @@
         <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -12413,7 +12029,7 @@
         <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -12424,7 +12040,7 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -12435,7 +12051,7 @@
         <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -12446,7 +12062,7 @@
         <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -12457,7 +12073,7 @@
         <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -12468,7 +12084,7 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -12479,7 +12095,7 @@
         <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -12490,7 +12106,7 @@
         <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -12501,7 +12117,7 @@
         <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -12512,7 +12128,7 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -12523,7 +12139,7 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -12534,7 +12150,7 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -12545,7 +12161,7 @@
         <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -12556,7 +12172,7 @@
         <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -12567,7 +12183,7 @@
         <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -12578,7 +12194,7 @@
         <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -12589,7 +12205,7 @@
         <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -12600,7 +12216,7 @@
         <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -12611,7 +12227,7 @@
         <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -12622,7 +12238,7 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -12633,7 +12249,7 @@
         <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -12644,7 +12260,7 @@
         <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C102">
         <v>0</v>
@@ -12655,7 +12271,7 @@
         <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -12666,7 +12282,7 @@
         <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -12677,7 +12293,7 @@
         <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -12688,7 +12304,7 @@
         <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -12699,7 +12315,7 @@
         <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -12710,7 +12326,7 @@
         <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -12721,7 +12337,7 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -12732,7 +12348,7 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="C110">
         <v>0</v>
@@ -12743,7 +12359,7 @@
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -12754,7 +12370,7 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="C112">
         <v>0</v>
@@ -12765,7 +12381,7 @@
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C113">
         <v>0</v>
@@ -12776,7 +12392,7 @@
         <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -12787,7 +12403,7 @@
         <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -12798,7 +12414,7 @@
         <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -12809,7 +12425,7 @@
         <v>12</v>
       </c>
       <c r="B117" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C117">
         <v>0</v>
@@ -12820,7 +12436,7 @@
         <v>12</v>
       </c>
       <c r="B118" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C118">
         <v>0</v>
@@ -12831,7 +12447,7 @@
         <v>12</v>
       </c>
       <c r="B119" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C119">
         <v>0</v>
@@ -12842,7 +12458,7 @@
         <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C120">
         <v>0</v>
@@ -12853,7 +12469,7 @@
         <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>20</v>
+        <v>68</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -12864,7 +12480,7 @@
         <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="C122">
         <v>0</v>
@@ -12875,7 +12491,7 @@
         <v>12</v>
       </c>
       <c r="B123" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C123">
         <v>0</v>
@@ -12886,7 +12502,7 @@
         <v>12</v>
       </c>
       <c r="B124" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -12897,7 +12513,7 @@
         <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -12908,7 +12524,7 @@
         <v>12</v>
       </c>
       <c r="B126" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -12919,7 +12535,7 @@
         <v>12</v>
       </c>
       <c r="B127" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -12930,7 +12546,7 @@
         <v>12</v>
       </c>
       <c r="B128" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -12941,7 +12557,7 @@
         <v>12</v>
       </c>
       <c r="B129" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -12952,7 +12568,7 @@
         <v>12</v>
       </c>
       <c r="B130" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="C130">
         <v>0</v>
@@ -12963,7 +12579,7 @@
         <v>12</v>
       </c>
       <c r="B131" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -12974,7 +12590,7 @@
         <v>12</v>
       </c>
       <c r="B132" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -12985,7 +12601,7 @@
         <v>12</v>
       </c>
       <c r="B133" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -12996,7 +12612,7 @@
         <v>12</v>
       </c>
       <c r="B134" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -13007,7 +12623,7 @@
         <v>12</v>
       </c>
       <c r="B135" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C135">
         <v>0</v>
@@ -13018,7 +12634,7 @@
         <v>12</v>
       </c>
       <c r="B136" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -13029,7 +12645,7 @@
         <v>12</v>
       </c>
       <c r="B137" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -13040,7 +12656,7 @@
         <v>12</v>
       </c>
       <c r="B138" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -13048,24 +12664,24 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B139" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C139">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B140" t="s">
         <v>69</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.35">
@@ -13073,7 +12689,7 @@
         <v>12</v>
       </c>
       <c r="B141" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -13084,7 +12700,7 @@
         <v>12</v>
       </c>
       <c r="B142" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C142">
         <v>0</v>
@@ -13095,7 +12711,7 @@
         <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -13106,7 +12722,7 @@
         <v>12</v>
       </c>
       <c r="B144" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C144">
         <v>0</v>
@@ -13117,7 +12733,7 @@
         <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -13128,7 +12744,7 @@
         <v>12</v>
       </c>
       <c r="B146" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -13139,7 +12755,7 @@
         <v>12</v>
       </c>
       <c r="B147" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -13150,7 +12766,7 @@
         <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -13161,7 +12777,7 @@
         <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -13172,7 +12788,7 @@
         <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -13183,7 +12799,7 @@
         <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -13194,7 +12810,7 @@
         <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -13205,7 +12821,7 @@
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -13216,7 +12832,7 @@
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -13227,7 +12843,7 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C155">
         <v>0</v>
@@ -13238,7 +12854,7 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -13249,7 +12865,7 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -13260,7 +12876,7 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -13268,10 +12884,10 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -13279,10 +12895,10 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B160" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -13290,10 +12906,10 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -13301,13 +12917,79 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B162" t="s">
         <v>75</v>
       </c>
       <c r="C162">
         <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>12</v>
+      </c>
+      <c r="B163" t="s">
+        <v>75</v>
+      </c>
+      <c r="C163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>12</v>
+      </c>
+      <c r="B164" t="s">
+        <v>63</v>
+      </c>
+      <c r="C164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>12</v>
+      </c>
+      <c r="B165" t="s">
+        <v>59</v>
+      </c>
+      <c r="C165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>11</v>
+      </c>
+      <c r="B166" t="s">
+        <v>59</v>
+      </c>
+      <c r="C166">
+        <v>-24.864095362311311</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>12</v>
+      </c>
+      <c r="B167" t="s">
+        <v>70</v>
+      </c>
+      <c r="C167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>11</v>
+      </c>
+      <c r="B168" t="s">
+        <v>70</v>
+      </c>
+      <c r="C168">
+        <v>-10.40036286731274</v>
       </c>
     </row>
   </sheetData>

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABC4765-BF75-4189-B558-DC82CA74FE35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB750021-E204-4236-87C1-A98FE3E00811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB750021-E204-4236-87C1-A98FE3E00811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C857E544-B57C-4100-98BC-5FB281A38C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1640" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1643" uniqueCount="99">
   <si>
     <t>Commodities</t>
   </si>
@@ -334,6 +334,9 @@
   </si>
   <si>
     <t>ES_Prod</t>
+  </si>
+  <si>
+    <t>RU2</t>
   </si>
 </sst>
 </file>
@@ -691,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B0CB446-BDDD-415D-AF22-2CEB1FE45CA5}">
-  <dimension ref="A1:A84"/>
+  <dimension ref="A1:A83"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
@@ -1107,11 +1110,6 @@
     <row r="83" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1146,7 +1144,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B152"/>
+  <dimension ref="A1:B153"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -2363,6 +2361,14 @@
       </c>
       <c r="B152" t="s">
         <v>75</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>52</v>
+      </c>
+      <c r="B153" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2372,7 +2378,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
-  <dimension ref="A1:I302"/>
+  <dimension ref="A1:I304"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -3604,10 +3610,10 @@
         <v>16</v>
       </c>
       <c r="D43">
-        <v>237.87050000000002</v>
+        <v>10000</v>
       </c>
       <c r="E43">
-        <v>237.87050000000002</v>
+        <v>10000</v>
       </c>
       <c r="F43">
         <v>1</v>
@@ -3633,10 +3639,10 @@
         <v>59</v>
       </c>
       <c r="D44">
-        <v>141.21850000000001</v>
+        <v>10000</v>
       </c>
       <c r="E44">
-        <v>141.21850000000001</v>
+        <v>10000</v>
       </c>
       <c r="F44">
         <v>1</v>
@@ -3662,10 +3668,10 @@
         <v>38</v>
       </c>
       <c r="D45">
-        <v>293.24099999999999</v>
+        <v>10000</v>
       </c>
       <c r="E45">
-        <v>293.24099999999999</v>
+        <v>10000</v>
       </c>
       <c r="F45">
         <v>1</v>
@@ -3691,10 +3697,10 @@
         <v>28</v>
       </c>
       <c r="D46">
-        <v>120.88800000000001</v>
+        <v>10000</v>
       </c>
       <c r="E46">
-        <v>120.88800000000001</v>
+        <v>10000</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -3720,10 +3726,10 @@
         <v>42</v>
       </c>
       <c r="D47">
-        <v>117.81104999999999</v>
+        <v>10000</v>
       </c>
       <c r="E47">
-        <v>117.81104999999999</v>
+        <v>10000</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -3749,10 +3755,10 @@
         <v>18</v>
       </c>
       <c r="D48">
-        <v>317.55</v>
+        <v>10000</v>
       </c>
       <c r="E48">
-        <v>317.55</v>
+        <v>10000</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -3778,10 +3784,10 @@
         <v>16</v>
       </c>
       <c r="D49">
-        <v>509.97800000000001</v>
+        <v>10000</v>
       </c>
       <c r="E49">
-        <v>509.97800000000001</v>
+        <v>10000</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -3807,10 +3813,10 @@
         <v>42</v>
       </c>
       <c r="D50">
-        <v>702.90714500000001</v>
+        <v>10000</v>
       </c>
       <c r="E50">
-        <v>702.90714500000001</v>
+        <v>10000</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -3836,10 +3842,10 @@
         <v>16</v>
       </c>
       <c r="D51">
-        <v>144.59475</v>
+        <v>10000</v>
       </c>
       <c r="E51">
-        <v>144.59475</v>
+        <v>10000</v>
       </c>
       <c r="F51">
         <v>1</v>
@@ -3865,10 +3871,10 @@
         <v>28</v>
       </c>
       <c r="D52">
-        <v>594.33059500000013</v>
+        <v>10000</v>
       </c>
       <c r="E52">
-        <v>594.33059500000013</v>
+        <v>10000</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -3894,10 +3900,10 @@
         <v>60</v>
       </c>
       <c r="D53">
-        <v>125.65051999999997</v>
+        <v>10000</v>
       </c>
       <c r="E53">
-        <v>125.65051999999997</v>
+        <v>10000</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -3923,10 +3929,10 @@
         <v>61</v>
       </c>
       <c r="D54">
-        <v>119.72</v>
+        <v>10000</v>
       </c>
       <c r="E54">
-        <v>119.72</v>
+        <v>10000</v>
       </c>
       <c r="F54">
         <v>1</v>
@@ -3952,10 +3958,10 @@
         <v>18</v>
       </c>
       <c r="D55">
-        <v>224.00633999999999</v>
+        <v>10000</v>
       </c>
       <c r="E55">
-        <v>224.00633999999999</v>
+        <v>10000</v>
       </c>
       <c r="F55">
         <v>1</v>
@@ -3981,10 +3987,10 @@
         <v>40</v>
       </c>
       <c r="D56">
-        <v>49.680879999999995</v>
+        <v>10000</v>
       </c>
       <c r="E56">
-        <v>49.680879999999995</v>
+        <v>10000</v>
       </c>
       <c r="F56">
         <v>1</v>
@@ -4010,10 +4016,10 @@
         <v>30</v>
       </c>
       <c r="D57">
-        <v>85.227500000000006</v>
+        <v>10000</v>
       </c>
       <c r="E57">
-        <v>85.227500000000006</v>
+        <v>10000</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -4039,10 +4045,10 @@
         <v>62</v>
       </c>
       <c r="D58">
-        <v>658.37605000000008</v>
+        <v>10000</v>
       </c>
       <c r="E58">
-        <v>658.37605000000008</v>
+        <v>10000</v>
       </c>
       <c r="F58">
         <v>1</v>
@@ -4068,10 +4074,10 @@
         <v>63</v>
       </c>
       <c r="D59">
-        <v>9.7491500000000002</v>
+        <v>10000</v>
       </c>
       <c r="E59">
-        <v>9.7491500000000002</v>
+        <v>10000</v>
       </c>
       <c r="F59">
         <v>1</v>
@@ -4097,10 +4103,10 @@
         <v>42</v>
       </c>
       <c r="D60">
-        <v>124.08832</v>
+        <v>10000</v>
       </c>
       <c r="E60">
-        <v>124.08832</v>
+        <v>10000</v>
       </c>
       <c r="F60">
         <v>1</v>
@@ -4126,10 +4132,10 @@
         <v>22</v>
       </c>
       <c r="D61">
-        <v>419.75</v>
+        <v>10000</v>
       </c>
       <c r="E61">
-        <v>419.75</v>
+        <v>10000</v>
       </c>
       <c r="F61">
         <v>1</v>
@@ -4155,10 +4161,10 @@
         <v>64</v>
       </c>
       <c r="D62">
-        <v>41.0625</v>
+        <v>10000</v>
       </c>
       <c r="E62">
-        <v>41.0625</v>
+        <v>10000</v>
       </c>
       <c r="F62">
         <v>1</v>
@@ -4184,10 +4190,10 @@
         <v>65</v>
       </c>
       <c r="D63">
-        <v>89.972499999999997</v>
+        <v>10000</v>
       </c>
       <c r="E63">
-        <v>89.972499999999997</v>
+        <v>10000</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -4213,10 +4219,10 @@
         <v>66</v>
       </c>
       <c r="D64">
-        <v>55.881500000000003</v>
+        <v>10000</v>
       </c>
       <c r="E64">
-        <v>55.881500000000003</v>
+        <v>10000</v>
       </c>
       <c r="F64">
         <v>1</v>
@@ -4242,10 +4248,10 @@
         <v>60</v>
       </c>
       <c r="D65">
-        <v>70.627499999999998</v>
+        <v>10000</v>
       </c>
       <c r="E65">
-        <v>70.627499999999998</v>
+        <v>10000</v>
       </c>
       <c r="F65">
         <v>1</v>
@@ -4271,10 +4277,10 @@
         <v>61</v>
       </c>
       <c r="D66">
-        <v>157.46100000000001</v>
+        <v>10000</v>
       </c>
       <c r="E66">
-        <v>157.46100000000001</v>
+        <v>10000</v>
       </c>
       <c r="F66">
         <v>1</v>
@@ -4300,10 +4306,10 @@
         <v>64</v>
       </c>
       <c r="D67">
-        <v>10.4025</v>
+        <v>10000</v>
       </c>
       <c r="E67">
-        <v>10.4025</v>
+        <v>10000</v>
       </c>
       <c r="F67">
         <v>1</v>
@@ -4329,10 +4335,10 @@
         <v>42</v>
       </c>
       <c r="D68">
-        <v>63.07200000000001</v>
+        <v>10000</v>
       </c>
       <c r="E68">
-        <v>63.07200000000001</v>
+        <v>10000</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -4358,10 +4364,10 @@
         <v>22</v>
       </c>
       <c r="D69">
-        <v>233.74600000000001</v>
+        <v>10000</v>
       </c>
       <c r="E69">
-        <v>233.74600000000001</v>
+        <v>10000</v>
       </c>
       <c r="F69">
         <v>1</v>
@@ -4387,10 +4393,10 @@
         <v>18</v>
       </c>
       <c r="D70">
-        <v>36.5</v>
+        <v>10000</v>
       </c>
       <c r="E70">
-        <v>36.5</v>
+        <v>10000</v>
       </c>
       <c r="F70">
         <v>1</v>
@@ -4416,10 +4422,10 @@
         <v>22</v>
       </c>
       <c r="D71">
-        <v>7.8475000000000001</v>
+        <v>10000</v>
       </c>
       <c r="E71">
-        <v>7.8475000000000001</v>
+        <v>10000</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -4445,10 +4451,10 @@
         <v>24</v>
       </c>
       <c r="D72">
-        <v>19.6005</v>
+        <v>10000</v>
       </c>
       <c r="E72">
-        <v>19.6005</v>
+        <v>10000</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -4474,10 +4480,10 @@
         <v>64</v>
       </c>
       <c r="D73">
-        <v>2.8105000000000002</v>
+        <v>10000</v>
       </c>
       <c r="E73">
-        <v>2.8105000000000002</v>
+        <v>10000</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -4503,10 +4509,10 @@
         <v>66</v>
       </c>
       <c r="D74">
-        <v>17.72805</v>
+        <v>10000</v>
       </c>
       <c r="E74">
-        <v>17.72805</v>
+        <v>10000</v>
       </c>
       <c r="F74">
         <v>1</v>
@@ -4532,10 +4538,10 @@
         <v>16</v>
       </c>
       <c r="D75">
-        <v>98.55</v>
+        <v>10000</v>
       </c>
       <c r="E75">
-        <v>98.55</v>
+        <v>10000</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -4561,10 +4567,10 @@
         <v>61</v>
       </c>
       <c r="D76">
-        <v>81.394999999999996</v>
+        <v>10000</v>
       </c>
       <c r="E76">
-        <v>81.394999999999996</v>
+        <v>10000</v>
       </c>
       <c r="F76">
         <v>1</v>
@@ -4590,10 +4596,10 @@
         <v>34</v>
       </c>
       <c r="D77">
-        <v>60.068779999999997</v>
+        <v>10000</v>
       </c>
       <c r="E77">
-        <v>60.068779999999997</v>
+        <v>10000</v>
       </c>
       <c r="F77">
         <v>1</v>
@@ -4619,10 +4625,10 @@
         <v>42</v>
       </c>
       <c r="D78">
-        <v>1.5034349999999999</v>
+        <v>10000</v>
       </c>
       <c r="E78">
-        <v>1.5034349999999999</v>
+        <v>10000</v>
       </c>
       <c r="F78">
         <v>1</v>
@@ -4648,10 +4654,10 @@
         <v>42</v>
       </c>
       <c r="D79">
-        <v>340.03399999999999</v>
+        <v>10000</v>
       </c>
       <c r="E79">
-        <v>340.03399999999999</v>
+        <v>10000</v>
       </c>
       <c r="F79">
         <v>1</v>
@@ -4677,10 +4683,10 @@
         <v>42</v>
       </c>
       <c r="D80">
-        <v>449.59203500000001</v>
+        <v>10000</v>
       </c>
       <c r="E80">
-        <v>449.59203500000001</v>
+        <v>10000</v>
       </c>
       <c r="F80">
         <v>1</v>
@@ -4706,10 +4712,10 @@
         <v>30</v>
       </c>
       <c r="D81">
-        <v>10.220000000000001</v>
+        <v>10000</v>
       </c>
       <c r="E81">
-        <v>10.220000000000001</v>
+        <v>10000</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -4735,10 +4741,10 @@
         <v>65</v>
       </c>
       <c r="D82">
-        <v>454.93600000000004</v>
+        <v>10000</v>
       </c>
       <c r="E82">
-        <v>454.93600000000004</v>
+        <v>10000</v>
       </c>
       <c r="F82">
         <v>1</v>
@@ -4764,10 +4770,10 @@
         <v>60</v>
       </c>
       <c r="D83">
-        <v>573.19600000000003</v>
+        <v>10000</v>
       </c>
       <c r="E83">
-        <v>573.19600000000003</v>
+        <v>10000</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -4793,10 +4799,10 @@
         <v>62</v>
       </c>
       <c r="D84">
-        <v>167.024</v>
+        <v>10000</v>
       </c>
       <c r="E84">
-        <v>167.024</v>
+        <v>10000</v>
       </c>
       <c r="F84">
         <v>1</v>
@@ -4822,10 +4828,10 @@
         <v>66</v>
       </c>
       <c r="D85">
-        <v>47.048499999999997</v>
+        <v>10000</v>
       </c>
       <c r="E85">
-        <v>47.048499999999997</v>
+        <v>10000</v>
       </c>
       <c r="F85">
         <v>1</v>
@@ -4851,10 +4857,10 @@
         <v>58</v>
       </c>
       <c r="D86">
-        <v>151.84</v>
+        <v>10000</v>
       </c>
       <c r="E86">
-        <v>151.84</v>
+        <v>10000</v>
       </c>
       <c r="F86">
         <v>1</v>
@@ -4880,10 +4886,10 @@
         <v>24</v>
       </c>
       <c r="D87">
-        <v>28.251000000000005</v>
+        <v>10000</v>
       </c>
       <c r="E87">
-        <v>28.251000000000005</v>
+        <v>10000</v>
       </c>
       <c r="F87">
         <v>1</v>
@@ -4909,10 +4915,10 @@
         <v>65</v>
       </c>
       <c r="D88">
-        <v>18.572295</v>
+        <v>10000</v>
       </c>
       <c r="E88">
-        <v>18.572295</v>
+        <v>10000</v>
       </c>
       <c r="F88">
         <v>1</v>
@@ -4938,10 +4944,10 @@
         <v>67</v>
       </c>
       <c r="D89">
-        <v>51.83</v>
+        <v>10000</v>
       </c>
       <c r="E89">
-        <v>51.83</v>
+        <v>10000</v>
       </c>
       <c r="F89">
         <v>1</v>
@@ -4967,10 +4973,10 @@
         <v>51</v>
       </c>
       <c r="D90">
-        <v>28.287500000000001</v>
+        <v>10000</v>
       </c>
       <c r="E90">
-        <v>28.287500000000001</v>
+        <v>10000</v>
       </c>
       <c r="F90">
         <v>1</v>
@@ -4996,10 +5002,10 @@
         <v>68</v>
       </c>
       <c r="D91">
-        <v>122.3699</v>
+        <v>10000</v>
       </c>
       <c r="E91">
-        <v>122.3699</v>
+        <v>10000</v>
       </c>
       <c r="F91">
         <v>1</v>
@@ -5025,10 +5031,10 @@
         <v>69</v>
       </c>
       <c r="D92">
-        <v>6.5626999999999995</v>
+        <v>10000</v>
       </c>
       <c r="E92">
-        <v>6.5626999999999995</v>
+        <v>10000</v>
       </c>
       <c r="F92">
         <v>1</v>
@@ -5054,10 +5060,10 @@
         <v>67</v>
       </c>
       <c r="D93">
-        <v>145.31745000000001</v>
+        <v>10000</v>
       </c>
       <c r="E93">
-        <v>145.31745000000001</v>
+        <v>10000</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -5083,10 +5089,10 @@
         <v>20</v>
       </c>
       <c r="D94">
-        <v>42.997</v>
+        <v>10000</v>
       </c>
       <c r="E94">
-        <v>42.997</v>
+        <v>10000</v>
       </c>
       <c r="F94">
         <v>1</v>
@@ -5112,10 +5118,10 @@
         <v>51</v>
       </c>
       <c r="D95">
-        <v>54.074750000000002</v>
+        <v>10000</v>
       </c>
       <c r="E95">
-        <v>54.074750000000002</v>
+        <v>10000</v>
       </c>
       <c r="F95">
         <v>1</v>
@@ -5141,10 +5147,10 @@
         <v>36</v>
       </c>
       <c r="D96">
-        <v>181.46340000000004</v>
+        <v>10000</v>
       </c>
       <c r="E96">
-        <v>181.46340000000004</v>
+        <v>10000</v>
       </c>
       <c r="F96">
         <v>1</v>
@@ -5170,10 +5176,10 @@
         <v>68</v>
       </c>
       <c r="D97">
-        <v>23.659299999999998</v>
+        <v>10000</v>
       </c>
       <c r="E97">
-        <v>23.659299999999998</v>
+        <v>10000</v>
       </c>
       <c r="F97">
         <v>1</v>
@@ -5199,10 +5205,10 @@
         <v>66</v>
       </c>
       <c r="D98">
-        <v>18.359500000000001</v>
+        <v>10000</v>
       </c>
       <c r="E98">
-        <v>18.359500000000001</v>
+        <v>10000</v>
       </c>
       <c r="F98">
         <v>1</v>
@@ -5228,10 +5234,10 @@
         <v>68</v>
       </c>
       <c r="D99">
-        <v>294.09875000000005</v>
+        <v>10000</v>
       </c>
       <c r="E99">
-        <v>294.09875000000005</v>
+        <v>10000</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -5257,10 +5263,10 @@
         <v>58</v>
       </c>
       <c r="D100">
-        <v>44.603000000000002</v>
+        <v>10000</v>
       </c>
       <c r="E100">
-        <v>44.603000000000002</v>
+        <v>10000</v>
       </c>
       <c r="F100">
         <v>1</v>
@@ -5286,10 +5292,10 @@
         <v>71</v>
       </c>
       <c r="D101">
-        <v>20.330500000000001</v>
+        <v>10000</v>
       </c>
       <c r="E101">
-        <v>20.330500000000001</v>
+        <v>10000</v>
       </c>
       <c r="F101">
         <v>1</v>
@@ -5315,10 +5321,10 @@
         <v>72</v>
       </c>
       <c r="D102">
-        <v>24.673999999999996</v>
+        <v>10000</v>
       </c>
       <c r="E102">
-        <v>24.673999999999996</v>
+        <v>10000</v>
       </c>
       <c r="F102">
         <v>1</v>
@@ -5344,10 +5350,10 @@
         <v>53</v>
       </c>
       <c r="D103">
-        <v>41.683</v>
+        <v>10000</v>
       </c>
       <c r="E103">
-        <v>41.683</v>
+        <v>10000</v>
       </c>
       <c r="F103">
         <v>1</v>
@@ -5373,10 +5379,10 @@
         <v>26</v>
       </c>
       <c r="D104">
-        <v>23.761499999999998</v>
+        <v>10000</v>
       </c>
       <c r="E104">
-        <v>23.761499999999998</v>
+        <v>10000</v>
       </c>
       <c r="F104">
         <v>1</v>
@@ -5402,10 +5408,10 @@
         <v>53</v>
       </c>
       <c r="D105">
-        <v>31.024999999999999</v>
+        <v>10000</v>
       </c>
       <c r="E105">
-        <v>31.024999999999999</v>
+        <v>10000</v>
       </c>
       <c r="F105">
         <v>1</v>
@@ -5431,10 +5437,10 @@
         <v>18</v>
       </c>
       <c r="D106">
-        <v>81.906000000000006</v>
+        <v>10000</v>
       </c>
       <c r="E106">
-        <v>81.906000000000006</v>
+        <v>10000</v>
       </c>
       <c r="F106">
         <v>1</v>
@@ -5460,10 +5466,10 @@
         <v>32</v>
       </c>
       <c r="D107">
-        <v>52.56</v>
+        <v>10000</v>
       </c>
       <c r="E107">
-        <v>52.56</v>
+        <v>10000</v>
       </c>
       <c r="F107">
         <v>1</v>
@@ -5489,10 +5495,10 @@
         <v>34</v>
       </c>
       <c r="D108">
-        <v>29.2</v>
+        <v>10000</v>
       </c>
       <c r="E108">
-        <v>29.2</v>
+        <v>10000</v>
       </c>
       <c r="F108">
         <v>1</v>
@@ -5518,10 +5524,10 @@
         <v>30</v>
       </c>
       <c r="D109">
-        <v>49.494</v>
+        <v>10000</v>
       </c>
       <c r="E109">
-        <v>49.494</v>
+        <v>10000</v>
       </c>
       <c r="F109">
         <v>1</v>
@@ -5547,10 +5553,10 @@
         <v>65</v>
       </c>
       <c r="D110">
-        <v>831.32399999999996</v>
+        <v>10000</v>
       </c>
       <c r="E110">
-        <v>831.32399999999996</v>
+        <v>10000</v>
       </c>
       <c r="F110">
         <v>1</v>
@@ -5576,10 +5582,10 @@
         <v>66</v>
       </c>
       <c r="D111">
-        <v>188.19399999999999</v>
+        <v>10000</v>
       </c>
       <c r="E111">
-        <v>188.19399999999999</v>
+        <v>10000</v>
       </c>
       <c r="F111">
         <v>1</v>
@@ -5605,10 +5611,10 @@
         <v>51</v>
       </c>
       <c r="D112">
-        <v>424.64100000000008</v>
+        <v>10000</v>
       </c>
       <c r="E112">
-        <v>424.64100000000008</v>
+        <v>10000</v>
       </c>
       <c r="F112">
         <v>1</v>
@@ -5634,10 +5640,10 @@
         <v>51</v>
       </c>
       <c r="D113">
-        <v>0.80300000000000016</v>
+        <v>10000</v>
       </c>
       <c r="E113">
-        <v>0.80300000000000016</v>
+        <v>10000</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -5663,10 +5669,10 @@
         <v>42</v>
       </c>
       <c r="D114">
-        <v>635.83000000000004</v>
+        <v>10000</v>
       </c>
       <c r="E114">
-        <v>635.83000000000004</v>
+        <v>10000</v>
       </c>
       <c r="F114">
         <v>1</v>
@@ -5692,10 +5698,10 @@
         <v>72</v>
       </c>
       <c r="D115">
-        <v>61.32</v>
+        <v>10000</v>
       </c>
       <c r="E115">
-        <v>61.32</v>
+        <v>10000</v>
       </c>
       <c r="F115">
         <v>1</v>
@@ -5721,10 +5727,10 @@
         <v>73</v>
       </c>
       <c r="D116">
-        <v>80.3</v>
+        <v>10000</v>
       </c>
       <c r="E116">
-        <v>80.3</v>
+        <v>10000</v>
       </c>
       <c r="F116">
         <v>1</v>
@@ -5750,10 +5756,10 @@
         <v>22</v>
       </c>
       <c r="D117">
-        <v>177.79150000000001</v>
+        <v>10000</v>
       </c>
       <c r="E117">
-        <v>177.79150000000001</v>
+        <v>10000</v>
       </c>
       <c r="F117">
         <v>1</v>
@@ -5779,10 +5785,10 @@
         <v>68</v>
       </c>
       <c r="D118">
-        <v>210.25094999999999</v>
+        <v>10000</v>
       </c>
       <c r="E118">
-        <v>210.25094999999999</v>
+        <v>10000</v>
       </c>
       <c r="F118">
         <v>1</v>
@@ -5808,10 +5814,10 @@
         <v>20</v>
       </c>
       <c r="D119">
-        <v>145.489</v>
+        <v>10000</v>
       </c>
       <c r="E119">
-        <v>145.489</v>
+        <v>10000</v>
       </c>
       <c r="F119">
         <v>1</v>
@@ -5837,10 +5843,10 @@
         <v>34</v>
       </c>
       <c r="D120">
-        <v>267.07049999999998</v>
+        <v>10000</v>
       </c>
       <c r="E120">
-        <v>267.07049999999998</v>
+        <v>10000</v>
       </c>
       <c r="F120">
         <v>1</v>
@@ -5866,10 +5872,10 @@
         <v>22</v>
       </c>
       <c r="D121">
-        <v>415.40649999999994</v>
+        <v>10000</v>
       </c>
       <c r="E121">
-        <v>415.40649999999994</v>
+        <v>10000</v>
       </c>
       <c r="F121">
         <v>1</v>
@@ -5895,10 +5901,10 @@
         <v>22</v>
       </c>
       <c r="D122">
-        <v>173.667</v>
+        <v>10000</v>
       </c>
       <c r="E122">
-        <v>173.667</v>
+        <v>10000</v>
       </c>
       <c r="F122">
         <v>1</v>
@@ -5924,10 +5930,10 @@
         <v>30</v>
       </c>
       <c r="D123">
-        <v>439.27749999999992</v>
+        <v>10000</v>
       </c>
       <c r="E123">
-        <v>439.27749999999992</v>
+        <v>10000</v>
       </c>
       <c r="F123">
         <v>1</v>
@@ -5953,10 +5959,10 @@
         <v>75</v>
       </c>
       <c r="D124">
-        <v>439.27749999999992</v>
+        <v>10000</v>
       </c>
       <c r="E124">
-        <v>439.27749999999992</v>
+        <v>10000</v>
       </c>
       <c r="F124">
         <v>1</v>
@@ -5982,10 +5988,10 @@
         <v>26</v>
       </c>
       <c r="D125">
-        <v>118.77099999999999</v>
+        <v>10000</v>
       </c>
       <c r="E125">
-        <v>118.77099999999999</v>
+        <v>10000</v>
       </c>
       <c r="F125">
         <v>1</v>
@@ -6011,10 +6017,10 @@
         <v>58</v>
       </c>
       <c r="D126">
-        <v>486.91</v>
+        <v>10000</v>
       </c>
       <c r="E126">
-        <v>486.91</v>
+        <v>10000</v>
       </c>
       <c r="F126">
         <v>1</v>
@@ -6040,10 +6046,10 @@
         <v>77</v>
       </c>
       <c r="D127">
-        <v>144.17500000000001</v>
+        <v>10000</v>
       </c>
       <c r="E127">
-        <v>144.17500000000001</v>
+        <v>10000</v>
       </c>
       <c r="F127">
         <v>1</v>
@@ -6069,10 +6075,10 @@
         <v>30</v>
       </c>
       <c r="D128">
-        <v>49.494</v>
+        <v>10000</v>
       </c>
       <c r="E128">
-        <v>49.494</v>
+        <v>10000</v>
       </c>
       <c r="F128">
         <v>1</v>
@@ -6098,10 +6104,10 @@
         <v>65</v>
       </c>
       <c r="D129">
-        <v>816.06700000000012</v>
+        <v>10000</v>
       </c>
       <c r="E129">
-        <v>816.06700000000012</v>
+        <v>10000</v>
       </c>
       <c r="F129">
         <v>1</v>
@@ -6127,10 +6133,10 @@
         <v>66</v>
       </c>
       <c r="D130">
-        <v>188.88749999999999</v>
+        <v>10000</v>
       </c>
       <c r="E130">
-        <v>188.88749999999999</v>
+        <v>10000</v>
       </c>
       <c r="F130">
         <v>1</v>
@@ -6156,10 +6162,10 @@
         <v>66</v>
       </c>
       <c r="D131">
-        <v>89.716999999999999</v>
+        <v>10000</v>
       </c>
       <c r="E131">
-        <v>89.716999999999999</v>
+        <v>10000</v>
       </c>
       <c r="F131">
         <v>1</v>
@@ -6185,10 +6191,10 @@
         <v>67</v>
       </c>
       <c r="D132">
-        <v>170.63749999999999</v>
+        <v>10000</v>
       </c>
       <c r="E132">
-        <v>170.63749999999999</v>
+        <v>10000</v>
       </c>
       <c r="F132">
         <v>1</v>
@@ -6214,10 +6220,10 @@
         <v>70</v>
       </c>
       <c r="D133">
-        <v>12.1837</v>
+        <v>10000</v>
       </c>
       <c r="E133">
-        <v>12.1837</v>
+        <v>10000</v>
       </c>
       <c r="F133">
         <v>1</v>
@@ -6243,10 +6249,10 @@
         <v>68</v>
       </c>
       <c r="D134">
-        <v>256.15699999999998</v>
+        <v>10000</v>
       </c>
       <c r="E134">
-        <v>256.15699999999998</v>
+        <v>10000</v>
       </c>
       <c r="F134">
         <v>1</v>
@@ -6272,10 +6278,10 @@
         <v>22</v>
       </c>
       <c r="D135">
-        <v>180.20050000000001</v>
+        <v>10000</v>
       </c>
       <c r="E135">
-        <v>180.20050000000001</v>
+        <v>10000</v>
       </c>
       <c r="F135">
         <v>1</v>
@@ -6301,10 +6307,10 @@
         <v>22</v>
       </c>
       <c r="D136">
-        <v>421.21</v>
+        <v>10000</v>
       </c>
       <c r="E136">
-        <v>421.21</v>
+        <v>10000</v>
       </c>
       <c r="F136">
         <v>1</v>
@@ -6330,10 +6336,10 @@
         <v>34</v>
       </c>
       <c r="D137">
-        <v>123.04150000000001</v>
+        <v>10000</v>
       </c>
       <c r="E137">
-        <v>123.04150000000001</v>
+        <v>10000</v>
       </c>
       <c r="F137">
         <v>1</v>
@@ -6359,10 +6365,10 @@
         <v>34</v>
       </c>
       <c r="D138">
-        <v>161.62200000000001</v>
+        <v>10000</v>
       </c>
       <c r="E138">
-        <v>161.62200000000001</v>
+        <v>10000</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -6388,10 +6394,10 @@
         <v>42</v>
       </c>
       <c r="D139">
-        <v>455.15499999999997</v>
+        <v>10000</v>
       </c>
       <c r="E139">
-        <v>455.15499999999997</v>
+        <v>10000</v>
       </c>
       <c r="F139">
         <v>1</v>
@@ -6417,10 +6423,10 @@
         <v>28</v>
       </c>
       <c r="D140">
-        <v>351.714</v>
+        <v>10000</v>
       </c>
       <c r="E140">
-        <v>351.714</v>
+        <v>10000</v>
       </c>
       <c r="F140">
         <v>1</v>
@@ -6446,10 +6452,10 @@
         <v>16</v>
       </c>
       <c r="D141">
-        <v>167.75399999999999</v>
+        <v>10000</v>
       </c>
       <c r="E141">
-        <v>167.75399999999999</v>
+        <v>10000</v>
       </c>
       <c r="F141">
         <v>1</v>
@@ -6475,10 +6481,10 @@
         <v>18</v>
       </c>
       <c r="D142">
-        <v>207.5025</v>
+        <v>10000</v>
       </c>
       <c r="E142">
-        <v>207.5025</v>
+        <v>10000</v>
       </c>
       <c r="F142">
         <v>1</v>
@@ -6504,10 +6510,10 @@
         <v>38</v>
       </c>
       <c r="D143">
-        <v>513.19000000000005</v>
+        <v>10000</v>
       </c>
       <c r="E143">
-        <v>513.19000000000005</v>
+        <v>10000</v>
       </c>
       <c r="F143">
         <v>1</v>
@@ -6533,10 +6539,10 @@
         <v>16</v>
       </c>
       <c r="D144">
-        <v>82.927999999999997</v>
+        <v>10000</v>
       </c>
       <c r="E144">
-        <v>82.927999999999997</v>
+        <v>10000</v>
       </c>
       <c r="F144">
         <v>1</v>
@@ -6562,10 +6568,10 @@
         <v>28</v>
       </c>
       <c r="D145">
-        <v>67.451999999999998</v>
+        <v>10000</v>
       </c>
       <c r="E145">
-        <v>67.451999999999998</v>
+        <v>10000</v>
       </c>
       <c r="F145">
         <v>1</v>
@@ -6591,10 +6597,10 @@
         <v>22</v>
       </c>
       <c r="D146">
-        <v>200.71350000000001</v>
+        <v>10000</v>
       </c>
       <c r="E146">
-        <v>200.71350000000001</v>
+        <v>10000</v>
       </c>
       <c r="F146">
         <v>1</v>
@@ -6620,10 +6626,10 @@
         <v>74</v>
       </c>
       <c r="D147">
-        <v>200.71350000000001</v>
+        <v>10000</v>
       </c>
       <c r="E147">
-        <v>200.71350000000001</v>
+        <v>10000</v>
       </c>
       <c r="F147">
         <v>1</v>
@@ -6649,10 +6655,10 @@
         <v>20</v>
       </c>
       <c r="D148">
-        <v>144.17500000000001</v>
+        <v>10000</v>
       </c>
       <c r="E148">
-        <v>144.17500000000001</v>
+        <v>10000</v>
       </c>
       <c r="F148">
         <v>1</v>
@@ -6678,10 +6684,10 @@
         <v>78</v>
       </c>
       <c r="D149">
-        <v>123.04150000000001</v>
+        <v>10000</v>
       </c>
       <c r="E149">
-        <v>123.04150000000001</v>
+        <v>10000</v>
       </c>
       <c r="F149">
         <v>1</v>
@@ -6707,10 +6713,10 @@
         <v>55</v>
       </c>
       <c r="D150">
-        <v>421.21</v>
+        <v>10000</v>
       </c>
       <c r="E150">
-        <v>421.21</v>
+        <v>10000</v>
       </c>
       <c r="F150">
         <v>1</v>
@@ -6736,10 +6742,10 @@
         <v>80</v>
       </c>
       <c r="D151">
-        <v>14.965</v>
+        <v>10000</v>
       </c>
       <c r="E151">
-        <v>14.965</v>
+        <v>10000</v>
       </c>
       <c r="F151">
         <v>1</v>
@@ -6765,10 +6771,10 @@
         <v>16</v>
       </c>
       <c r="D152">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E152">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F152">
         <v>1</v>
@@ -6794,10 +6800,10 @@
         <v>18</v>
       </c>
       <c r="D153">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E153">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F153">
         <v>1</v>
@@ -6823,10 +6829,10 @@
         <v>20</v>
       </c>
       <c r="D154">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E154">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F154">
         <v>1</v>
@@ -6852,10 +6858,10 @@
         <v>22</v>
       </c>
       <c r="D155">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E155">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F155">
         <v>1</v>
@@ -6881,10 +6887,10 @@
         <v>24</v>
       </c>
       <c r="D156">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E156">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F156">
         <v>1</v>
@@ -6910,10 +6916,10 @@
         <v>26</v>
       </c>
       <c r="D157">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E157">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F157">
         <v>1</v>
@@ -6939,10 +6945,10 @@
         <v>28</v>
       </c>
       <c r="D158">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E158">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F158">
         <v>1</v>
@@ -6968,10 +6974,10 @@
         <v>30</v>
       </c>
       <c r="D159">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E159">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F159">
         <v>1</v>
@@ -6997,10 +7003,10 @@
         <v>32</v>
       </c>
       <c r="D160">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E160">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F160">
         <v>1</v>
@@ -7026,10 +7032,10 @@
         <v>34</v>
       </c>
       <c r="D161">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E161">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F161">
         <v>1</v>
@@ -7055,10 +7061,10 @@
         <v>36</v>
       </c>
       <c r="D162">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E162">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F162">
         <v>1</v>
@@ -7084,10 +7090,10 @@
         <v>38</v>
       </c>
       <c r="D163">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E163">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F163">
         <v>1</v>
@@ -7113,10 +7119,10 @@
         <v>78</v>
       </c>
       <c r="D164">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E164">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F164">
         <v>1</v>
@@ -7142,10 +7148,10 @@
         <v>40</v>
       </c>
       <c r="D165">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E165">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F165">
         <v>1</v>
@@ -7171,10 +7177,10 @@
         <v>42</v>
       </c>
       <c r="D166">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E166">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F166">
         <v>1</v>
@@ -7200,10 +7206,10 @@
         <v>22</v>
       </c>
       <c r="D167">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E167">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F167">
         <v>1</v>
@@ -7229,10 +7235,10 @@
         <v>45</v>
       </c>
       <c r="D168">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E168">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F168">
         <v>1</v>
@@ -7258,10 +7264,10 @@
         <v>28</v>
       </c>
       <c r="D169">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E169">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F169">
         <v>1</v>
@@ -7287,10 +7293,10 @@
         <v>48</v>
       </c>
       <c r="D170">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E170">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F170">
         <v>1</v>
@@ -7316,10 +7322,10 @@
         <v>30</v>
       </c>
       <c r="D171">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E171">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F171">
         <v>1</v>
@@ -7345,10 +7351,10 @@
         <v>51</v>
       </c>
       <c r="D172">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E172">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F172">
         <v>1</v>
@@ -7374,10 +7380,10 @@
         <v>53</v>
       </c>
       <c r="D173">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E173">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F173">
         <v>1</v>
@@ -7403,10 +7409,10 @@
         <v>55</v>
       </c>
       <c r="D174">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E174">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F174">
         <v>1</v>
@@ -7432,10 +7438,10 @@
         <v>38</v>
       </c>
       <c r="D175">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E175">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F175">
         <v>1</v>
@@ -7461,10 +7467,10 @@
         <v>58</v>
       </c>
       <c r="D176">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E176">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F176">
         <v>1</v>
@@ -7490,10 +7496,10 @@
         <v>16</v>
       </c>
       <c r="D177">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E177">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F177">
         <v>1</v>
@@ -7519,10 +7525,10 @@
         <v>59</v>
       </c>
       <c r="D178">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E178">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F178">
         <v>1</v>
@@ -7548,10 +7554,10 @@
         <v>38</v>
       </c>
       <c r="D179">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E179">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F179">
         <v>1</v>
@@ -7577,10 +7583,10 @@
         <v>28</v>
       </c>
       <c r="D180">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E180">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F180">
         <v>1</v>
@@ -7606,10 +7612,10 @@
         <v>42</v>
       </c>
       <c r="D181">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E181">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F181">
         <v>1</v>
@@ -7635,10 +7641,10 @@
         <v>18</v>
       </c>
       <c r="D182">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E182">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F182">
         <v>1</v>
@@ -7664,10 +7670,10 @@
         <v>16</v>
       </c>
       <c r="D183">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E183">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F183">
         <v>1</v>
@@ -7693,10 +7699,10 @@
         <v>42</v>
       </c>
       <c r="D184">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E184">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F184">
         <v>1</v>
@@ -7722,10 +7728,10 @@
         <v>16</v>
       </c>
       <c r="D185">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E185">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F185">
         <v>1</v>
@@ -7751,10 +7757,10 @@
         <v>28</v>
       </c>
       <c r="D186">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E186">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F186">
         <v>1</v>
@@ -7780,10 +7786,10 @@
         <v>60</v>
       </c>
       <c r="D187">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E187">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F187">
         <v>1</v>
@@ -7809,10 +7815,10 @@
         <v>61</v>
       </c>
       <c r="D188">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E188">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F188">
         <v>1</v>
@@ -7838,10 +7844,10 @@
         <v>18</v>
       </c>
       <c r="D189">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E189">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F189">
         <v>1</v>
@@ -7867,10 +7873,10 @@
         <v>40</v>
       </c>
       <c r="D190">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E190">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F190">
         <v>1</v>
@@ -7896,10 +7902,10 @@
         <v>30</v>
       </c>
       <c r="D191">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E191">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F191">
         <v>1</v>
@@ -7925,10 +7931,10 @@
         <v>62</v>
       </c>
       <c r="D192">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E192">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F192">
         <v>1</v>
@@ -7954,10 +7960,10 @@
         <v>63</v>
       </c>
       <c r="D193">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E193">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F193">
         <v>1</v>
@@ -7983,10 +7989,10 @@
         <v>42</v>
       </c>
       <c r="D194">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E194">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F194">
         <v>1</v>
@@ -8012,10 +8018,10 @@
         <v>22</v>
       </c>
       <c r="D195">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E195">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F195">
         <v>1</v>
@@ -8041,10 +8047,10 @@
         <v>64</v>
       </c>
       <c r="D196">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E196">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F196">
         <v>1</v>
@@ -8070,10 +8076,10 @@
         <v>65</v>
       </c>
       <c r="D197">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E197">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F197">
         <v>1</v>
@@ -8099,10 +8105,10 @@
         <v>66</v>
       </c>
       <c r="D198">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E198">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F198">
         <v>1</v>
@@ -8128,10 +8134,10 @@
         <v>60</v>
       </c>
       <c r="D199">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E199">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F199">
         <v>1</v>
@@ -8157,10 +8163,10 @@
         <v>61</v>
       </c>
       <c r="D200">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E200">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F200">
         <v>1</v>
@@ -8186,10 +8192,10 @@
         <v>64</v>
       </c>
       <c r="D201">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E201">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F201">
         <v>1</v>
@@ -8215,10 +8221,10 @@
         <v>42</v>
       </c>
       <c r="D202">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E202">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F202">
         <v>1</v>
@@ -8244,10 +8250,10 @@
         <v>22</v>
       </c>
       <c r="D203">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E203">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F203">
         <v>1</v>
@@ -8273,10 +8279,10 @@
         <v>18</v>
       </c>
       <c r="D204">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E204">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F204">
         <v>1</v>
@@ -8302,10 +8308,10 @@
         <v>22</v>
       </c>
       <c r="D205">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E205">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F205">
         <v>1</v>
@@ -8331,10 +8337,10 @@
         <v>24</v>
       </c>
       <c r="D206">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E206">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F206">
         <v>1</v>
@@ -8360,10 +8366,10 @@
         <v>64</v>
       </c>
       <c r="D207">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E207">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F207">
         <v>1</v>
@@ -8389,10 +8395,10 @@
         <v>66</v>
       </c>
       <c r="D208">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E208">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F208">
         <v>1</v>
@@ -8418,10 +8424,10 @@
         <v>16</v>
       </c>
       <c r="D209">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E209">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F209">
         <v>1</v>
@@ -8447,10 +8453,10 @@
         <v>61</v>
       </c>
       <c r="D210">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E210">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F210">
         <v>1</v>
@@ -8476,10 +8482,10 @@
         <v>34</v>
       </c>
       <c r="D211">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E211">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F211">
         <v>1</v>
@@ -8505,10 +8511,10 @@
         <v>42</v>
       </c>
       <c r="D212">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E212">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F212">
         <v>1</v>
@@ -8534,10 +8540,10 @@
         <v>42</v>
       </c>
       <c r="D213">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E213">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F213">
         <v>1</v>
@@ -8563,10 +8569,10 @@
         <v>42</v>
       </c>
       <c r="D214">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E214">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F214">
         <v>1</v>
@@ -8592,10 +8598,10 @@
         <v>30</v>
       </c>
       <c r="D215">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E215">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F215">
         <v>1</v>
@@ -8621,10 +8627,10 @@
         <v>65</v>
       </c>
       <c r="D216">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E216">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F216">
         <v>1</v>
@@ -8650,10 +8656,10 @@
         <v>60</v>
       </c>
       <c r="D217">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E217">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F217">
         <v>1</v>
@@ -8679,10 +8685,10 @@
         <v>62</v>
       </c>
       <c r="D218">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E218">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F218">
         <v>1</v>
@@ -8708,10 +8714,10 @@
         <v>66</v>
       </c>
       <c r="D219">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E219">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F219">
         <v>1</v>
@@ -8737,10 +8743,10 @@
         <v>58</v>
       </c>
       <c r="D220">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E220">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F220">
         <v>1</v>
@@ -8766,10 +8772,10 @@
         <v>24</v>
       </c>
       <c r="D221">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E221">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F221">
         <v>1</v>
@@ -8795,10 +8801,10 @@
         <v>65</v>
       </c>
       <c r="D222">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E222">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F222">
         <v>1</v>
@@ -8824,10 +8830,10 @@
         <v>67</v>
       </c>
       <c r="D223">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E223">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F223">
         <v>1</v>
@@ -8853,10 +8859,10 @@
         <v>51</v>
       </c>
       <c r="D224">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E224">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F224">
         <v>1</v>
@@ -8882,10 +8888,10 @@
         <v>68</v>
       </c>
       <c r="D225">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E225">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F225">
         <v>1</v>
@@ -8911,10 +8917,10 @@
         <v>69</v>
       </c>
       <c r="D226">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E226">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F226">
         <v>1</v>
@@ -8940,10 +8946,10 @@
         <v>67</v>
       </c>
       <c r="D227">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E227">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F227">
         <v>1</v>
@@ -8969,10 +8975,10 @@
         <v>20</v>
       </c>
       <c r="D228">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E228">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F228">
         <v>1</v>
@@ -8998,10 +9004,10 @@
         <v>51</v>
       </c>
       <c r="D229">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E229">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F229">
         <v>1</v>
@@ -9027,10 +9033,10 @@
         <v>70</v>
       </c>
       <c r="D230">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E230">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F230">
         <v>1</v>
@@ -9056,10 +9062,10 @@
         <v>36</v>
       </c>
       <c r="D231">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E231">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F231">
         <v>1</v>
@@ -9085,10 +9091,10 @@
         <v>68</v>
       </c>
       <c r="D232">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E232">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F232">
         <v>1</v>
@@ -9114,10 +9120,10 @@
         <v>66</v>
       </c>
       <c r="D233">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E233">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F233">
         <v>1</v>
@@ -9143,10 +9149,10 @@
         <v>68</v>
       </c>
       <c r="D234">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E234">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F234">
         <v>1</v>
@@ -9172,10 +9178,10 @@
         <v>58</v>
       </c>
       <c r="D235">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E235">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F235">
         <v>1</v>
@@ -9201,10 +9207,10 @@
         <v>71</v>
       </c>
       <c r="D236">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E236">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F236">
         <v>1</v>
@@ -9230,10 +9236,10 @@
         <v>72</v>
       </c>
       <c r="D237">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E237">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F237">
         <v>1</v>
@@ -9259,10 +9265,10 @@
         <v>53</v>
       </c>
       <c r="D238">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E238">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F238">
         <v>1</v>
@@ -9288,10 +9294,10 @@
         <v>26</v>
       </c>
       <c r="D239">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E239">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F239">
         <v>1</v>
@@ -9317,10 +9323,10 @@
         <v>53</v>
       </c>
       <c r="D240">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E240">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F240">
         <v>1</v>
@@ -9346,10 +9352,10 @@
         <v>18</v>
       </c>
       <c r="D241">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E241">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F241">
         <v>1</v>
@@ -9375,10 +9381,10 @@
         <v>32</v>
       </c>
       <c r="D242">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E242">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F242">
         <v>1</v>
@@ -9404,10 +9410,10 @@
         <v>34</v>
       </c>
       <c r="D243">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E243">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F243">
         <v>1</v>
@@ -9433,10 +9439,10 @@
         <v>30</v>
       </c>
       <c r="D244">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E244">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F244">
         <v>1</v>
@@ -9462,10 +9468,10 @@
         <v>65</v>
       </c>
       <c r="D245">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E245">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F245">
         <v>1</v>
@@ -9491,10 +9497,10 @@
         <v>66</v>
       </c>
       <c r="D246">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E246">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F246">
         <v>1</v>
@@ -9520,10 +9526,10 @@
         <v>51</v>
       </c>
       <c r="D247">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E247">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F247">
         <v>1</v>
@@ -9549,10 +9555,10 @@
         <v>51</v>
       </c>
       <c r="D248">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E248">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F248">
         <v>1</v>
@@ -9578,10 +9584,10 @@
         <v>42</v>
       </c>
       <c r="D249">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E249">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F249">
         <v>1</v>
@@ -9607,10 +9613,10 @@
         <v>72</v>
       </c>
       <c r="D250">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E250">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F250">
         <v>1</v>
@@ -9636,10 +9642,10 @@
         <v>73</v>
       </c>
       <c r="D251">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E251">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F251">
         <v>1</v>
@@ -9665,10 +9671,10 @@
         <v>22</v>
       </c>
       <c r="D252">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E252">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F252">
         <v>1</v>
@@ -9694,10 +9700,10 @@
         <v>68</v>
       </c>
       <c r="D253">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E253">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F253">
         <v>1</v>
@@ -9723,10 +9729,10 @@
         <v>20</v>
       </c>
       <c r="D254">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E254">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F254">
         <v>1</v>
@@ -9752,10 +9758,10 @@
         <v>34</v>
       </c>
       <c r="D255">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E255">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F255">
         <v>1</v>
@@ -9781,10 +9787,10 @@
         <v>22</v>
       </c>
       <c r="D256">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E256">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F256">
         <v>1</v>
@@ -9810,10 +9816,10 @@
         <v>22</v>
       </c>
       <c r="D257">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E257">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F257">
         <v>1</v>
@@ -9839,10 +9845,10 @@
         <v>30</v>
       </c>
       <c r="D258">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E258">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F258">
         <v>1</v>
@@ -9868,10 +9874,10 @@
         <v>26</v>
       </c>
       <c r="D259">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E259">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F259">
         <v>1</v>
@@ -9897,10 +9903,10 @@
         <v>58</v>
       </c>
       <c r="D260">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E260">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F260">
         <v>1</v>
@@ -9926,10 +9932,10 @@
         <v>77</v>
       </c>
       <c r="D261">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E261">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F261">
         <v>1</v>
@@ -9955,10 +9961,10 @@
         <v>30</v>
       </c>
       <c r="D262">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E262">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F262">
         <v>1</v>
@@ -9984,10 +9990,10 @@
         <v>65</v>
       </c>
       <c r="D263">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E263">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F263">
         <v>1</v>
@@ -10013,10 +10019,10 @@
         <v>66</v>
       </c>
       <c r="D264">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E264">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F264">
         <v>1</v>
@@ -10042,10 +10048,10 @@
         <v>66</v>
       </c>
       <c r="D265">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E265">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F265">
         <v>1</v>
@@ -10071,10 +10077,10 @@
         <v>67</v>
       </c>
       <c r="D266">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E266">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F266">
         <v>1</v>
@@ -10100,10 +10106,10 @@
         <v>68</v>
       </c>
       <c r="D267">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E267">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F267">
         <v>1</v>
@@ -10129,10 +10135,10 @@
         <v>22</v>
       </c>
       <c r="D268">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E268">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F268">
         <v>1</v>
@@ -10158,10 +10164,10 @@
         <v>22</v>
       </c>
       <c r="D269">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E269">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F269">
         <v>1</v>
@@ -10187,10 +10193,10 @@
         <v>34</v>
       </c>
       <c r="D270">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E270">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F270">
         <v>1</v>
@@ -10216,10 +10222,10 @@
         <v>34</v>
       </c>
       <c r="D271">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E271">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F271">
         <v>1</v>
@@ -10245,10 +10251,10 @@
         <v>42</v>
       </c>
       <c r="D272">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E272">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F272">
         <v>1</v>
@@ -10274,10 +10280,10 @@
         <v>28</v>
       </c>
       <c r="D273">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E273">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F273">
         <v>1</v>
@@ -10303,10 +10309,10 @@
         <v>16</v>
       </c>
       <c r="D274">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E274">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F274">
         <v>1</v>
@@ -10332,10 +10338,10 @@
         <v>18</v>
       </c>
       <c r="D275">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E275">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F275">
         <v>1</v>
@@ -10361,10 +10367,10 @@
         <v>38</v>
       </c>
       <c r="D276">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E276">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F276">
         <v>1</v>
@@ -10390,10 +10396,10 @@
         <v>16</v>
       </c>
       <c r="D277">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E277">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F277">
         <v>1</v>
@@ -10419,10 +10425,10 @@
         <v>28</v>
       </c>
       <c r="D278">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E278">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F278">
         <v>1</v>
@@ -10448,10 +10454,10 @@
         <v>22</v>
       </c>
       <c r="D279">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E279">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F279">
         <v>1</v>
@@ -10477,10 +10483,10 @@
         <v>74</v>
       </c>
       <c r="D280">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E280">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F280">
         <v>1</v>
@@ -10506,10 +10512,10 @@
         <v>20</v>
       </c>
       <c r="D281">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E281">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F281">
         <v>1</v>
@@ -10535,10 +10541,10 @@
         <v>78</v>
       </c>
       <c r="D282">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E282">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F282">
         <v>1</v>
@@ -10564,10 +10570,10 @@
         <v>55</v>
       </c>
       <c r="D283">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E283">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F283">
         <v>1</v>
@@ -10593,10 +10599,10 @@
         <v>80</v>
       </c>
       <c r="D284">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E284">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F284">
         <v>1</v>
@@ -11086,10 +11092,10 @@
         <v>75</v>
       </c>
       <c r="D301">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E301">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F301">
         <v>1</v>
@@ -11115,10 +11121,10 @@
         <v>30</v>
       </c>
       <c r="D302">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="E302">
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="F302">
         <v>1</v>
@@ -11130,6 +11136,64 @@
         <v>1000</v>
       </c>
       <c r="I302">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>11</v>
+      </c>
+      <c r="B303" t="s">
+        <v>52</v>
+      </c>
+      <c r="C303" t="s">
+        <v>98</v>
+      </c>
+      <c r="D303">
+        <v>10000</v>
+      </c>
+      <c r="E303">
+        <v>10000</v>
+      </c>
+      <c r="F303">
+        <v>1</v>
+      </c>
+      <c r="G303">
+        <v>10000000</v>
+      </c>
+      <c r="H303">
+        <v>1000</v>
+      </c>
+      <c r="I303">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>12</v>
+      </c>
+      <c r="B304" t="s">
+        <v>52</v>
+      </c>
+      <c r="C304" t="s">
+        <v>98</v>
+      </c>
+      <c r="D304">
+        <v>10000</v>
+      </c>
+      <c r="E304">
+        <v>10000</v>
+      </c>
+      <c r="F304">
+        <v>1</v>
+      </c>
+      <c r="G304">
+        <v>10000000</v>
+      </c>
+      <c r="H304">
+        <v>1000</v>
+      </c>
+      <c r="I304">
         <v>1</v>
       </c>
     </row>
@@ -11141,7 +11205,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68B577B-1347-43AB-A697-F4519763B965}">
-  <dimension ref="A1:C168"/>
+  <dimension ref="A1:C166"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
@@ -12970,28 +13034,6 @@
         <v>-24.864095362311311</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A167" t="s">
-        <v>12</v>
-      </c>
-      <c r="B167" t="s">
-        <v>70</v>
-      </c>
-      <c r="C167">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A168" t="s">
-        <v>11</v>
-      </c>
-      <c r="B168" t="s">
-        <v>70</v>
-      </c>
-      <c r="C168">
-        <v>-10.40036286731274</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C857E544-B57C-4100-98BC-5FB281A38C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC30B68-F149-49D2-9BD4-63DBDE1D0480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC30B68-F149-49D2-9BD4-63DBDE1D0480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76DD410E-E2B9-4E73-A272-4C5B0151C4A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76DD410E-E2B9-4E73-A272-4C5B0151C4A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06798385-13A4-421A-96D7-F1160EEE40FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -11156,7 +11156,7 @@
         <v>10000</v>
       </c>
       <c r="F303">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G303">
         <v>10000000</v>
@@ -11185,7 +11185,7 @@
         <v>10000</v>
       </c>
       <c r="F304">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G304">
         <v>10000000</v>

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06798385-13A4-421A-96D7-F1160EEE40FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17146672-1AAB-43A3-93D8-31D85F8773D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17146672-1AAB-43A3-93D8-31D85F8773D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735C170F-3175-43D2-9C67-62A310F3DD40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1643" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="98">
   <si>
     <t>Commodities</t>
   </si>
@@ -334,9 +334,6 @@
   </si>
   <si>
     <t>ES_Prod</t>
-  </si>
-  <si>
-    <t>RU2</t>
   </si>
 </sst>
 </file>
@@ -1144,7 +1141,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B153"/>
+  <dimension ref="A1:B150"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -2032,7 +2029,7 @@
         <v>76</v>
       </c>
       <c r="B111" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
@@ -2101,15 +2098,15 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="B120" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B121" t="s">
         <v>34</v>
@@ -2117,10 +2114,10 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="B122" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
@@ -2128,7 +2125,7 @@
         <v>48</v>
       </c>
       <c r="B123" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
@@ -2136,7 +2133,7 @@
         <v>48</v>
       </c>
       <c r="B124" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
@@ -2144,7 +2141,7 @@
         <v>48</v>
       </c>
       <c r="B125" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
@@ -2152,15 +2149,15 @@
         <v>48</v>
       </c>
       <c r="B126" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B127" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
@@ -2168,28 +2165,28 @@
         <v>38</v>
       </c>
       <c r="B128" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="B129" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
+        <v>20</v>
+      </c>
+      <c r="B130" t="s">
         <v>74</v>
-      </c>
-      <c r="B130" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="B131" t="s">
         <v>74</v>
@@ -2197,178 +2194,154 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B132" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B133" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B134" t="s">
-        <v>83</v>
+        <v>16</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B135" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B136" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B137" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B138" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B139" t="s">
-        <v>62</v>
+        <v>20</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B140" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B141" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B142" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B143" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B144" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B145" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B146" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B147" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B148" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="B149" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="B150" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A151" t="s">
-        <v>40</v>
-      </c>
-      <c r="B151" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A152" t="s">
-        <v>53</v>
-      </c>
-      <c r="B152" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A153" t="s">
-        <v>52</v>
-      </c>
-      <c r="B153" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2378,7 +2351,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
-  <dimension ref="A1:I304"/>
+  <dimension ref="A1:I299"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -6043,7 +6016,7 @@
         <v>76</v>
       </c>
       <c r="C127" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="D127">
         <v>10000</v>
@@ -6301,10 +6274,10 @@
         <v>11</v>
       </c>
       <c r="B136" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="C136" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D136">
         <v>10000</v>
@@ -6330,7 +6303,7 @@
         <v>11</v>
       </c>
       <c r="B137" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C137" t="s">
         <v>34</v>
@@ -6359,10 +6332,10 @@
         <v>11</v>
       </c>
       <c r="B138" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C138" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D138">
         <v>10000</v>
@@ -6391,7 +6364,7 @@
         <v>48</v>
       </c>
       <c r="C139" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D139">
         <v>10000</v>
@@ -6420,7 +6393,7 @@
         <v>48</v>
       </c>
       <c r="C140" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D140">
         <v>10000</v>
@@ -6449,7 +6422,7 @@
         <v>48</v>
       </c>
       <c r="C141" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D141">
         <v>10000</v>
@@ -6478,7 +6451,7 @@
         <v>48</v>
       </c>
       <c r="C142" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D142">
         <v>10000</v>
@@ -6504,10 +6477,10 @@
         <v>11</v>
       </c>
       <c r="B143" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C143" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D143">
         <v>10000</v>
@@ -6536,7 +6509,7 @@
         <v>38</v>
       </c>
       <c r="C144" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D144">
         <v>10000</v>
@@ -6562,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="B145" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="C145" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D145">
         <v>10000</v>
@@ -6591,10 +6564,10 @@
         <v>11</v>
       </c>
       <c r="B146" t="s">
+        <v>20</v>
+      </c>
+      <c r="C146" t="s">
         <v>74</v>
-      </c>
-      <c r="C146" t="s">
-        <v>22</v>
       </c>
       <c r="D146">
         <v>10000</v>
@@ -6620,10 +6593,10 @@
         <v>11</v>
       </c>
       <c r="B147" t="s">
+        <v>77</v>
+      </c>
+      <c r="C147" t="s">
         <v>20</v>
-      </c>
-      <c r="C147" t="s">
-        <v>74</v>
       </c>
       <c r="D147">
         <v>10000</v>
@@ -6649,10 +6622,10 @@
         <v>11</v>
       </c>
       <c r="B148" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C148" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="D148">
         <v>10000</v>
@@ -6681,7 +6654,7 @@
         <v>83</v>
       </c>
       <c r="C149" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="D149">
         <v>10000</v>
@@ -6707,10 +6680,10 @@
         <v>11</v>
       </c>
       <c r="B150" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="C150" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="D150">
         <v>10000</v>
@@ -6733,13 +6706,13 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C151" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="D151">
         <v>10000</v>
@@ -6754,7 +6727,7 @@
         <v>10000000</v>
       </c>
       <c r="H151">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I151">
         <v>1</v>
@@ -6765,10 +6738,10 @@
         <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C152" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D152">
         <v>10000</v>
@@ -6794,10 +6767,10 @@
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C153" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D153">
         <v>10000</v>
@@ -6823,10 +6796,10 @@
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C154" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D154">
         <v>10000</v>
@@ -6852,10 +6825,10 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C155" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D155">
         <v>10000</v>
@@ -6881,10 +6854,10 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C156" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D156">
         <v>10000</v>
@@ -6910,10 +6883,10 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C157" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D157">
         <v>10000</v>
@@ -6939,10 +6912,10 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C158" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D158">
         <v>10000</v>
@@ -6968,10 +6941,10 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C159" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D159">
         <v>10000</v>
@@ -6997,10 +6970,10 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C160" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D160">
         <v>10000</v>
@@ -7026,10 +6999,10 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C161" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D161">
         <v>10000</v>
@@ -7055,10 +7028,10 @@
         <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C162" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D162">
         <v>10000</v>
@@ -7084,10 +7057,10 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="C163" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="D163">
         <v>10000</v>
@@ -7113,10 +7086,10 @@
         <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="C164" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="D164">
         <v>10000</v>
@@ -7142,10 +7115,10 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C165" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D165">
         <v>10000</v>
@@ -7171,10 +7144,10 @@
         <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C166" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D166">
         <v>10000</v>
@@ -7200,10 +7173,10 @@
         <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C167" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="D167">
         <v>10000</v>
@@ -7229,10 +7202,10 @@
         <v>12</v>
       </c>
       <c r="B168" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C168" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D168">
         <v>10000</v>
@@ -7258,10 +7231,10 @@
         <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C169" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D169">
         <v>10000</v>
@@ -7287,10 +7260,10 @@
         <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C170" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D170">
         <v>10000</v>
@@ -7316,10 +7289,10 @@
         <v>12</v>
       </c>
       <c r="B171" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C171" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="D171">
         <v>10000</v>
@@ -7345,10 +7318,10 @@
         <v>12</v>
       </c>
       <c r="B172" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C172" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D172">
         <v>10000</v>
@@ -7374,10 +7347,10 @@
         <v>12</v>
       </c>
       <c r="B173" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C173" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D173">
         <v>10000</v>
@@ -7403,10 +7376,10 @@
         <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C174" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D174">
         <v>10000</v>
@@ -7432,10 +7405,10 @@
         <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C175" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="D175">
         <v>10000</v>
@@ -7461,10 +7434,10 @@
         <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="C176" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="D176">
         <v>10000</v>
@@ -7493,7 +7466,7 @@
         <v>38</v>
       </c>
       <c r="C177" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D177">
         <v>10000</v>
@@ -7519,10 +7492,10 @@
         <v>12</v>
       </c>
       <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="s">
         <v>38</v>
-      </c>
-      <c r="C178" t="s">
-        <v>59</v>
       </c>
       <c r="D178">
         <v>10000</v>
@@ -7551,7 +7524,7 @@
         <v>16</v>
       </c>
       <c r="C179" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D179">
         <v>10000</v>
@@ -7580,7 +7553,7 @@
         <v>16</v>
       </c>
       <c r="C180" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D180">
         <v>10000</v>
@@ -7609,7 +7582,7 @@
         <v>16</v>
       </c>
       <c r="C181" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="D181">
         <v>10000</v>
@@ -7635,10 +7608,10 @@
         <v>12</v>
       </c>
       <c r="B182" t="s">
+        <v>28</v>
+      </c>
+      <c r="C182" t="s">
         <v>16</v>
-      </c>
-      <c r="C182" t="s">
-        <v>18</v>
       </c>
       <c r="D182">
         <v>10000</v>
@@ -7667,7 +7640,7 @@
         <v>28</v>
       </c>
       <c r="C183" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="D183">
         <v>10000</v>
@@ -7693,10 +7666,10 @@
         <v>12</v>
       </c>
       <c r="B184" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C184" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D184">
         <v>10000</v>
@@ -7725,7 +7698,7 @@
         <v>42</v>
       </c>
       <c r="C185" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D185">
         <v>10000</v>
@@ -7754,7 +7727,7 @@
         <v>42</v>
       </c>
       <c r="C186" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="D186">
         <v>10000</v>
@@ -7783,7 +7756,7 @@
         <v>42</v>
       </c>
       <c r="C187" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D187">
         <v>10000</v>
@@ -7812,7 +7785,7 @@
         <v>42</v>
       </c>
       <c r="C188" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="D188">
         <v>10000</v>
@@ -7841,7 +7814,7 @@
         <v>42</v>
       </c>
       <c r="C189" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D189">
         <v>10000</v>
@@ -7870,7 +7843,7 @@
         <v>42</v>
       </c>
       <c r="C190" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D190">
         <v>10000</v>
@@ -7899,7 +7872,7 @@
         <v>42</v>
       </c>
       <c r="C191" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="D191">
         <v>10000</v>
@@ -7928,7 +7901,7 @@
         <v>42</v>
       </c>
       <c r="C192" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D192">
         <v>10000</v>
@@ -7954,10 +7927,10 @@
         <v>12</v>
       </c>
       <c r="B193" t="s">
+        <v>60</v>
+      </c>
+      <c r="C193" t="s">
         <v>42</v>
-      </c>
-      <c r="C193" t="s">
-        <v>63</v>
       </c>
       <c r="D193">
         <v>10000</v>
@@ -7986,7 +7959,7 @@
         <v>60</v>
       </c>
       <c r="C194" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D194">
         <v>10000</v>
@@ -8015,7 +7988,7 @@
         <v>60</v>
       </c>
       <c r="C195" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="D195">
         <v>10000</v>
@@ -8044,7 +8017,7 @@
         <v>60</v>
       </c>
       <c r="C196" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D196">
         <v>10000</v>
@@ -8073,7 +8046,7 @@
         <v>60</v>
       </c>
       <c r="C197" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D197">
         <v>10000</v>
@@ -8099,10 +8072,10 @@
         <v>12</v>
       </c>
       <c r="B198" t="s">
+        <v>22</v>
+      </c>
+      <c r="C198" t="s">
         <v>60</v>
-      </c>
-      <c r="C198" t="s">
-        <v>66</v>
       </c>
       <c r="D198">
         <v>10000</v>
@@ -8131,7 +8104,7 @@
         <v>22</v>
       </c>
       <c r="C199" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D199">
         <v>10000</v>
@@ -8160,7 +8133,7 @@
         <v>22</v>
       </c>
       <c r="C200" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D200">
         <v>10000</v>
@@ -8186,10 +8159,10 @@
         <v>12</v>
       </c>
       <c r="B201" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="C201" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="D201">
         <v>10000</v>
@@ -8218,7 +8191,7 @@
         <v>61</v>
       </c>
       <c r="C202" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D202">
         <v>10000</v>
@@ -8247,7 +8220,7 @@
         <v>61</v>
       </c>
       <c r="C203" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D203">
         <v>10000</v>
@@ -8273,10 +8246,10 @@
         <v>12</v>
       </c>
       <c r="B204" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C204" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D204">
         <v>10000</v>
@@ -8305,7 +8278,7 @@
         <v>64</v>
       </c>
       <c r="C205" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D205">
         <v>10000</v>
@@ -8331,10 +8304,10 @@
         <v>12</v>
       </c>
       <c r="B206" t="s">
+        <v>24</v>
+      </c>
+      <c r="C206" t="s">
         <v>64</v>
-      </c>
-      <c r="C206" t="s">
-        <v>24</v>
       </c>
       <c r="D206">
         <v>10000</v>
@@ -8363,7 +8336,7 @@
         <v>24</v>
       </c>
       <c r="C207" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D207">
         <v>10000</v>
@@ -8389,10 +8362,10 @@
         <v>12</v>
       </c>
       <c r="B208" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C208" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="D208">
         <v>10000</v>
@@ -8421,7 +8394,7 @@
         <v>18</v>
       </c>
       <c r="C209" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="D209">
         <v>10000</v>
@@ -8450,7 +8423,7 @@
         <v>18</v>
       </c>
       <c r="C210" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D210">
         <v>10000</v>
@@ -8476,10 +8449,10 @@
         <v>12</v>
       </c>
       <c r="B211" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C211" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D211">
         <v>10000</v>
@@ -8505,7 +8478,7 @@
         <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C212" t="s">
         <v>42</v>
@@ -8534,7 +8507,7 @@
         <v>12</v>
       </c>
       <c r="B213" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="C213" t="s">
         <v>42</v>
@@ -8566,7 +8539,7 @@
         <v>62</v>
       </c>
       <c r="C214" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D214">
         <v>10000</v>
@@ -8595,7 +8568,7 @@
         <v>62</v>
       </c>
       <c r="C215" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D215">
         <v>10000</v>
@@ -8621,10 +8594,10 @@
         <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C216" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D216">
         <v>10000</v>
@@ -8653,7 +8626,7 @@
         <v>65</v>
       </c>
       <c r="C217" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D217">
         <v>10000</v>
@@ -8682,7 +8655,7 @@
         <v>65</v>
       </c>
       <c r="C218" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D218">
         <v>10000</v>
@@ -8711,7 +8684,7 @@
         <v>65</v>
       </c>
       <c r="C219" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D219">
         <v>10000</v>
@@ -8737,10 +8710,10 @@
         <v>12</v>
       </c>
       <c r="B220" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C220" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D220">
         <v>10000</v>
@@ -8769,7 +8742,7 @@
         <v>66</v>
       </c>
       <c r="C221" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="D221">
         <v>10000</v>
@@ -8798,7 +8771,7 @@
         <v>66</v>
       </c>
       <c r="C222" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D222">
         <v>10000</v>
@@ -8827,7 +8800,7 @@
         <v>66</v>
       </c>
       <c r="C223" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="D223">
         <v>10000</v>
@@ -8853,10 +8826,10 @@
         <v>12</v>
       </c>
       <c r="B224" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C224" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D224">
         <v>10000</v>
@@ -8885,7 +8858,7 @@
         <v>67</v>
       </c>
       <c r="C225" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D225">
         <v>10000</v>
@@ -8911,10 +8884,10 @@
         <v>12</v>
       </c>
       <c r="B226" t="s">
+        <v>68</v>
+      </c>
+      <c r="C226" t="s">
         <v>67</v>
-      </c>
-      <c r="C226" t="s">
-        <v>69</v>
       </c>
       <c r="D226">
         <v>10000</v>
@@ -8943,7 +8916,7 @@
         <v>68</v>
       </c>
       <c r="C227" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="D227">
         <v>10000</v>
@@ -8972,7 +8945,7 @@
         <v>68</v>
       </c>
       <c r="C228" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D228">
         <v>10000</v>
@@ -9001,7 +8974,7 @@
         <v>68</v>
       </c>
       <c r="C229" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="D229">
         <v>10000</v>
@@ -9030,7 +9003,7 @@
         <v>68</v>
       </c>
       <c r="C230" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="D230">
         <v>10000</v>
@@ -9056,10 +9029,10 @@
         <v>12</v>
       </c>
       <c r="B231" t="s">
+        <v>20</v>
+      </c>
+      <c r="C231" t="s">
         <v>68</v>
-      </c>
-      <c r="C231" t="s">
-        <v>36</v>
       </c>
       <c r="D231">
         <v>10000</v>
@@ -9085,10 +9058,10 @@
         <v>12</v>
       </c>
       <c r="B232" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C232" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D232">
         <v>10000</v>
@@ -9117,7 +9090,7 @@
         <v>51</v>
       </c>
       <c r="C233" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D233">
         <v>10000</v>
@@ -9146,7 +9119,7 @@
         <v>51</v>
       </c>
       <c r="C234" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="D234">
         <v>10000</v>
@@ -9175,7 +9148,7 @@
         <v>51</v>
       </c>
       <c r="C235" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D235">
         <v>10000</v>
@@ -9201,10 +9174,10 @@
         <v>12</v>
       </c>
       <c r="B236" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="C236" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D236">
         <v>10000</v>
@@ -9233,7 +9206,7 @@
         <v>26</v>
       </c>
       <c r="C237" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="D237">
         <v>10000</v>
@@ -9259,10 +9232,10 @@
         <v>12</v>
       </c>
       <c r="B238" t="s">
+        <v>72</v>
+      </c>
+      <c r="C238" t="s">
         <v>26</v>
-      </c>
-      <c r="C238" t="s">
-        <v>53</v>
       </c>
       <c r="D238">
         <v>10000</v>
@@ -9291,7 +9264,7 @@
         <v>72</v>
       </c>
       <c r="C239" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="D239">
         <v>10000</v>
@@ -9317,10 +9290,10 @@
         <v>12</v>
       </c>
       <c r="B240" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="C240" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D240">
         <v>10000</v>
@@ -9349,7 +9322,7 @@
         <v>34</v>
       </c>
       <c r="C241" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D241">
         <v>10000</v>
@@ -9375,10 +9348,10 @@
         <v>12</v>
       </c>
       <c r="B242" t="s">
+        <v>32</v>
+      </c>
+      <c r="C242" t="s">
         <v>34</v>
-      </c>
-      <c r="C242" t="s">
-        <v>32</v>
       </c>
       <c r="D242">
         <v>10000</v>
@@ -9404,10 +9377,10 @@
         <v>12</v>
       </c>
       <c r="B243" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C243" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D243">
         <v>10000</v>
@@ -9436,7 +9409,7 @@
         <v>58</v>
       </c>
       <c r="C244" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D244">
         <v>10000</v>
@@ -9465,7 +9438,7 @@
         <v>58</v>
       </c>
       <c r="C245" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D245">
         <v>10000</v>
@@ -9494,7 +9467,7 @@
         <v>58</v>
       </c>
       <c r="C246" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="D246">
         <v>10000</v>
@@ -9520,7 +9493,7 @@
         <v>12</v>
       </c>
       <c r="B247" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="C247" t="s">
         <v>51</v>
@@ -9549,10 +9522,10 @@
         <v>12</v>
       </c>
       <c r="B248" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C248" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D248">
         <v>10000</v>
@@ -9581,7 +9554,7 @@
         <v>53</v>
       </c>
       <c r="C249" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="D249">
         <v>10000</v>
@@ -9610,7 +9583,7 @@
         <v>53</v>
       </c>
       <c r="C250" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D250">
         <v>10000</v>
@@ -9636,10 +9609,10 @@
         <v>12</v>
       </c>
       <c r="B251" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="C251" t="s">
-        <v>73</v>
+        <v>22</v>
       </c>
       <c r="D251">
         <v>10000</v>
@@ -9665,10 +9638,10 @@
         <v>12</v>
       </c>
       <c r="B252" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="C252" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D252">
         <v>10000</v>
@@ -9697,7 +9670,7 @@
         <v>36</v>
       </c>
       <c r="C253" t="s">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="D253">
         <v>10000</v>
@@ -9723,10 +9696,10 @@
         <v>12</v>
       </c>
       <c r="B254" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="C254" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D254">
         <v>10000</v>
@@ -9752,10 +9725,10 @@
         <v>12</v>
       </c>
       <c r="B255" t="s">
-        <v>78</v>
+        <v>55</v>
       </c>
       <c r="C255" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D255">
         <v>10000</v>
@@ -9781,7 +9754,7 @@
         <v>12</v>
       </c>
       <c r="B256" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C256" t="s">
         <v>22</v>
@@ -9810,10 +9783,10 @@
         <v>12</v>
       </c>
       <c r="B257" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="C257" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D257">
         <v>10000</v>
@@ -9842,7 +9815,7 @@
         <v>75</v>
       </c>
       <c r="C258" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D258">
         <v>10000</v>
@@ -9868,10 +9841,10 @@
         <v>12</v>
       </c>
       <c r="B259" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="C259" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="D259">
         <v>10000</v>
@@ -9897,10 +9870,10 @@
         <v>12</v>
       </c>
       <c r="B260" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="C260" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="D260">
         <v>10000</v>
@@ -9926,10 +9899,10 @@
         <v>12</v>
       </c>
       <c r="B261" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C261" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="D261">
         <v>10000</v>
@@ -9958,7 +9931,7 @@
         <v>58</v>
       </c>
       <c r="C262" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D262">
         <v>10000</v>
@@ -9987,7 +9960,7 @@
         <v>58</v>
       </c>
       <c r="C263" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D263">
         <v>10000</v>
@@ -10013,7 +9986,7 @@
         <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C264" t="s">
         <v>66</v>
@@ -10042,10 +10015,10 @@
         <v>12</v>
       </c>
       <c r="B265" t="s">
+        <v>68</v>
+      </c>
+      <c r="C265" t="s">
         <v>67</v>
-      </c>
-      <c r="C265" t="s">
-        <v>66</v>
       </c>
       <c r="D265">
         <v>10000</v>
@@ -10071,10 +10044,10 @@
         <v>12</v>
       </c>
       <c r="B266" t="s">
+        <v>36</v>
+      </c>
+      <c r="C266" t="s">
         <v>68</v>
-      </c>
-      <c r="C266" t="s">
-        <v>67</v>
       </c>
       <c r="D266">
         <v>10000</v>
@@ -10100,10 +10073,10 @@
         <v>12</v>
       </c>
       <c r="B267" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C267" t="s">
-        <v>68</v>
+        <v>22</v>
       </c>
       <c r="D267">
         <v>10000</v>
@@ -10129,10 +10102,10 @@
         <v>12</v>
       </c>
       <c r="B268" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="C268" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D268">
         <v>10000</v>
@@ -10158,10 +10131,10 @@
         <v>12</v>
       </c>
       <c r="B269" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C269" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D269">
         <v>10000</v>
@@ -10187,10 +10160,10 @@
         <v>12</v>
       </c>
       <c r="B270" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="C270" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D270">
         <v>10000</v>
@@ -10216,10 +10189,10 @@
         <v>12</v>
       </c>
       <c r="B271" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C271" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D271">
         <v>10000</v>
@@ -10248,7 +10221,7 @@
         <v>48</v>
       </c>
       <c r="C272" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D272">
         <v>10000</v>
@@ -10277,7 +10250,7 @@
         <v>48</v>
       </c>
       <c r="C273" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D273">
         <v>10000</v>
@@ -10306,7 +10279,7 @@
         <v>48</v>
       </c>
       <c r="C274" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D274">
         <v>10000</v>
@@ -10332,10 +10305,10 @@
         <v>12</v>
       </c>
       <c r="B275" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C275" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D275">
         <v>10000</v>
@@ -10361,10 +10334,10 @@
         <v>12</v>
       </c>
       <c r="B276" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C276" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D276">
         <v>10000</v>
@@ -10390,10 +10363,10 @@
         <v>12</v>
       </c>
       <c r="B277" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="C277" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D277">
         <v>10000</v>
@@ -10419,10 +10392,10 @@
         <v>12</v>
       </c>
       <c r="B278" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="C278" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="D278">
         <v>10000</v>
@@ -10448,10 +10421,10 @@
         <v>12</v>
       </c>
       <c r="B279" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C279" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="D279">
         <v>10000</v>
@@ -10477,10 +10450,10 @@
         <v>12</v>
       </c>
       <c r="B280" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="C280" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="D280">
         <v>10000</v>
@@ -10506,10 +10479,10 @@
         <v>12</v>
       </c>
       <c r="B281" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="C281" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D281">
         <v>10000</v>
@@ -10535,10 +10508,10 @@
         <v>12</v>
       </c>
       <c r="B282" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C282" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D282">
         <v>10000</v>
@@ -10547,7 +10520,7 @@
         <v>10000</v>
       </c>
       <c r="F282">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G282">
         <v>10000000</v>
@@ -10564,11 +10537,11 @@
         <v>12</v>
       </c>
       <c r="B283" t="s">
+        <v>82</v>
+      </c>
+      <c r="C283" t="s">
         <v>83</v>
       </c>
-      <c r="C283" t="s">
-        <v>55</v>
-      </c>
       <c r="D283">
         <v>10000</v>
       </c>
@@ -10576,7 +10549,7 @@
         <v>10000</v>
       </c>
       <c r="F283">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G283">
         <v>10000000</v>
@@ -10593,10 +10566,10 @@
         <v>12</v>
       </c>
       <c r="B284" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="C284" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="D284">
         <v>10000</v>
@@ -10605,7 +10578,7 @@
         <v>10000</v>
       </c>
       <c r="F284">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G284">
         <v>10000000</v>
@@ -10622,10 +10595,10 @@
         <v>12</v>
       </c>
       <c r="B285" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C285" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="D285">
         <v>10000</v>
@@ -10651,10 +10624,10 @@
         <v>12</v>
       </c>
       <c r="B286" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C286" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="D286">
         <v>10000</v>
@@ -10680,10 +10653,10 @@
         <v>12</v>
       </c>
       <c r="B287" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C287" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D287">
         <v>10000</v>
@@ -10709,10 +10682,10 @@
         <v>12</v>
       </c>
       <c r="B288" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C288" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="D288">
         <v>10000</v>
@@ -10738,10 +10711,10 @@
         <v>12</v>
       </c>
       <c r="B289" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C289" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="D289">
         <v>10000</v>
@@ -10767,10 +10740,10 @@
         <v>12</v>
       </c>
       <c r="B290" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C290" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D290">
         <v>10000</v>
@@ -10796,10 +10769,10 @@
         <v>12</v>
       </c>
       <c r="B291" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C291" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D291">
         <v>10000</v>
@@ -10825,10 +10798,10 @@
         <v>12</v>
       </c>
       <c r="B292" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C292" t="s">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="D292">
         <v>10000</v>
@@ -10854,10 +10827,10 @@
         <v>12</v>
       </c>
       <c r="B293" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C293" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="D293">
         <v>10000</v>
@@ -10883,10 +10856,10 @@
         <v>12</v>
       </c>
       <c r="B294" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C294" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D294">
         <v>10000</v>
@@ -10912,10 +10885,10 @@
         <v>12</v>
       </c>
       <c r="B295" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C295" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D295">
         <v>10000</v>
@@ -10941,10 +10914,10 @@
         <v>12</v>
       </c>
       <c r="B296" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C296" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="D296">
         <v>10000</v>
@@ -10970,10 +10943,10 @@
         <v>12</v>
       </c>
       <c r="B297" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C297" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="D297">
         <v>10000</v>
@@ -10999,10 +10972,10 @@
         <v>12</v>
       </c>
       <c r="B298" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="C298" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D298">
         <v>10000</v>
@@ -11011,7 +10984,7 @@
         <v>10000</v>
       </c>
       <c r="F298">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G298">
         <v>10000000</v>
@@ -11028,10 +11001,10 @@
         <v>12</v>
       </c>
       <c r="B299" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C299" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D299">
         <v>10000</v>
@@ -11040,7 +11013,7 @@
         <v>10000</v>
       </c>
       <c r="F299">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G299">
         <v>10000000</v>
@@ -11049,151 +11022,6 @@
         <v>1000</v>
       </c>
       <c r="I299">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A300" t="s">
-        <v>12</v>
-      </c>
-      <c r="B300" t="s">
-        <v>97</v>
-      </c>
-      <c r="C300" t="s">
-        <v>34</v>
-      </c>
-      <c r="D300">
-        <v>10000</v>
-      </c>
-      <c r="E300">
-        <v>10000</v>
-      </c>
-      <c r="F300">
-        <v>100</v>
-      </c>
-      <c r="G300">
-        <v>10000000</v>
-      </c>
-      <c r="H300">
-        <v>1000</v>
-      </c>
-      <c r="I300">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A301" t="s">
-        <v>12</v>
-      </c>
-      <c r="B301" t="s">
-        <v>53</v>
-      </c>
-      <c r="C301" t="s">
-        <v>75</v>
-      </c>
-      <c r="D301">
-        <v>10000</v>
-      </c>
-      <c r="E301">
-        <v>10000</v>
-      </c>
-      <c r="F301">
-        <v>1</v>
-      </c>
-      <c r="G301">
-        <v>10000000</v>
-      </c>
-      <c r="H301">
-        <v>1000</v>
-      </c>
-      <c r="I301">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A302" t="s">
-        <v>12</v>
-      </c>
-      <c r="B302" t="s">
-        <v>75</v>
-      </c>
-      <c r="C302" t="s">
-        <v>30</v>
-      </c>
-      <c r="D302">
-        <v>10000</v>
-      </c>
-      <c r="E302">
-        <v>10000</v>
-      </c>
-      <c r="F302">
-        <v>1</v>
-      </c>
-      <c r="G302">
-        <v>10000000</v>
-      </c>
-      <c r="H302">
-        <v>1000</v>
-      </c>
-      <c r="I302">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A303" t="s">
-        <v>11</v>
-      </c>
-      <c r="B303" t="s">
-        <v>52</v>
-      </c>
-      <c r="C303" t="s">
-        <v>98</v>
-      </c>
-      <c r="D303">
-        <v>10000</v>
-      </c>
-      <c r="E303">
-        <v>10000</v>
-      </c>
-      <c r="F303">
-        <v>10</v>
-      </c>
-      <c r="G303">
-        <v>10000000</v>
-      </c>
-      <c r="H303">
-        <v>1000</v>
-      </c>
-      <c r="I303">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A304" t="s">
-        <v>12</v>
-      </c>
-      <c r="B304" t="s">
-        <v>52</v>
-      </c>
-      <c r="C304" t="s">
-        <v>98</v>
-      </c>
-      <c r="D304">
-        <v>10000</v>
-      </c>
-      <c r="E304">
-        <v>10000</v>
-      </c>
-      <c r="F304">
-        <v>10</v>
-      </c>
-      <c r="G304">
-        <v>10000000</v>
-      </c>
-      <c r="H304">
-        <v>1000</v>
-      </c>
-      <c r="I304">
         <v>1</v>
       </c>
     </row>

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735C170F-3175-43D2-9C67-62A310F3DD40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30517978-7F32-4007-8902-0E1155DB3DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
     <sheet name="Commodities" sheetId="2" r:id="rId2"/>
     <sheet name="Edges" sheetId="3" r:id="rId3"/>
-    <sheet name="Parameters" sheetId="4" r:id="rId4"/>
-    <sheet name="Supply" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId4"/>
+    <sheet name="Parameters" sheetId="4" r:id="rId5"/>
+    <sheet name="Supply" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1622" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="196">
   <si>
     <t>Commodities</t>
   </si>
@@ -334,6 +335,300 @@
   </si>
   <si>
     <t>ES_Prod</t>
+  </si>
+  <si>
+    <t>UKBE</t>
+  </si>
+  <si>
+    <t>UKIE</t>
+  </si>
+  <si>
+    <t>BEUK</t>
+  </si>
+  <si>
+    <t>BENL</t>
+  </si>
+  <si>
+    <t>BEDE</t>
+  </si>
+  <si>
+    <t>BEFR</t>
+  </si>
+  <si>
+    <t>NLBE</t>
+  </si>
+  <si>
+    <t>NLDE</t>
+  </si>
+  <si>
+    <t>DEBE</t>
+  </si>
+  <si>
+    <t>DENL</t>
+  </si>
+  <si>
+    <t>DEAT</t>
+  </si>
+  <si>
+    <t>DECH</t>
+  </si>
+  <si>
+    <t>DEFR</t>
+  </si>
+  <si>
+    <t>DEDK</t>
+  </si>
+  <si>
+    <t>DEPL</t>
+  </si>
+  <si>
+    <t>DECZ</t>
+  </si>
+  <si>
+    <t>DELU</t>
+  </si>
+  <si>
+    <t>ATDE</t>
+  </si>
+  <si>
+    <t>ATIT</t>
+  </si>
+  <si>
+    <t>ATSI</t>
+  </si>
+  <si>
+    <t>ATSK</t>
+  </si>
+  <si>
+    <t>ATHU</t>
+  </si>
+  <si>
+    <t>ITAT</t>
+  </si>
+  <si>
+    <t>ITCH</t>
+  </si>
+  <si>
+    <t>ITSI</t>
+  </si>
+  <si>
+    <t>CHDE</t>
+  </si>
+  <si>
+    <t>CHIT</t>
+  </si>
+  <si>
+    <t>CHFR</t>
+  </si>
+  <si>
+    <t>SIIT</t>
+  </si>
+  <si>
+    <t>SIHR</t>
+  </si>
+  <si>
+    <t>HRSI</t>
+  </si>
+  <si>
+    <t>HRHU</t>
+  </si>
+  <si>
+    <t>FRBE</t>
+  </si>
+  <si>
+    <t>FRCH</t>
+  </si>
+  <si>
+    <t>FRES</t>
+  </si>
+  <si>
+    <t>DKDE</t>
+  </si>
+  <si>
+    <t>PLDE</t>
+  </si>
+  <si>
+    <t>CZDE</t>
+  </si>
+  <si>
+    <t>CZPL</t>
+  </si>
+  <si>
+    <t>CZSK</t>
+  </si>
+  <si>
+    <t>SKAT</t>
+  </si>
+  <si>
+    <t>SKCZ</t>
+  </si>
+  <si>
+    <t>SKHU</t>
+  </si>
+  <si>
+    <t>SKUA</t>
+  </si>
+  <si>
+    <t>HUHR</t>
+  </si>
+  <si>
+    <t>HUSK</t>
+  </si>
+  <si>
+    <t>HURS</t>
+  </si>
+  <si>
+    <t>HURO</t>
+  </si>
+  <si>
+    <t>RSBG</t>
+  </si>
+  <si>
+    <t>RSBA</t>
+  </si>
+  <si>
+    <t>BGRS</t>
+  </si>
+  <si>
+    <t>BGGR</t>
+  </si>
+  <si>
+    <t>BGRO</t>
+  </si>
+  <si>
+    <t>BGMK</t>
+  </si>
+  <si>
+    <t>BGTR</t>
+  </si>
+  <si>
+    <t>GRBG</t>
+  </si>
+  <si>
+    <t>ROHU</t>
+  </si>
+  <si>
+    <t>ROBG</t>
+  </si>
+  <si>
+    <t>ROUA</t>
+  </si>
+  <si>
+    <t>ROMD</t>
+  </si>
+  <si>
+    <t>LTLV</t>
+  </si>
+  <si>
+    <t>LTRU</t>
+  </si>
+  <si>
+    <t>LVLT</t>
+  </si>
+  <si>
+    <t>LVRU</t>
+  </si>
+  <si>
+    <t>ESFR</t>
+  </si>
+  <si>
+    <t>ESPT</t>
+  </si>
+  <si>
+    <t>PTES</t>
+  </si>
+  <si>
+    <t>UAPL</t>
+  </si>
+  <si>
+    <t>UASK</t>
+  </si>
+  <si>
+    <t>UAHU</t>
+  </si>
+  <si>
+    <t>UARO</t>
+  </si>
+  <si>
+    <t>MDRO</t>
+  </si>
+  <si>
+    <t>RUDE</t>
+  </si>
+  <si>
+    <t>RULV</t>
+  </si>
+  <si>
+    <t>RUFI</t>
+  </si>
+  <si>
+    <t>ALIT</t>
+  </si>
+  <si>
+    <t>TRBG</t>
+  </si>
+  <si>
+    <t>TRGR</t>
+  </si>
+  <si>
+    <t>MAES</t>
+  </si>
+  <si>
+    <t>TNIT</t>
+  </si>
+  <si>
+    <t>LYIT</t>
+  </si>
+  <si>
+    <t>BYPL</t>
+  </si>
+  <si>
+    <t>BYLT</t>
+  </si>
+  <si>
+    <t>RUUA</t>
+  </si>
+  <si>
+    <t>AZTR</t>
+  </si>
+  <si>
+    <t>RSHU</t>
+  </si>
+  <si>
+    <t>DZES</t>
+  </si>
+  <si>
+    <t>NODE</t>
+  </si>
+  <si>
+    <t>NONL</t>
+  </si>
+  <si>
+    <t>NOBE</t>
+  </si>
+  <si>
+    <t>NOFR</t>
+  </si>
+  <si>
+    <t>NOUK</t>
+  </si>
+  <si>
+    <t>UKNL</t>
+  </si>
+  <si>
+    <t>GRAL</t>
+  </si>
+  <si>
+    <t>DZMA</t>
+  </si>
+  <si>
+    <t>DZTN</t>
+  </si>
+  <si>
+    <t>DKSE</t>
+  </si>
+  <si>
+    <t>RUBY</t>
   </si>
 </sst>
 </file>
@@ -1141,7 +1436,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA366CBE-E84C-4E05-9B58-54F3A95EEAB7}">
-  <dimension ref="A1:B150"/>
+  <dimension ref="A1:B140"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -2034,314 +2329,234 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B112" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="B113" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B114" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="B115" t="s">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="B116" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B117" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B118" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B119" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="B120" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
+        <v>83</v>
+      </c>
+      <c r="B121" t="s">
         <v>78</v>
-      </c>
-      <c r="B121" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B122" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B123" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B124" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="B125" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="B126" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="B127" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="B128" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="B129" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>20</v>
+        <v>87</v>
       </c>
       <c r="B130" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B131" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B132" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B133" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B134" t="s">
-        <v>16</v>
+        <v>66</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B135" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B136" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B137" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B138" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B139" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B140" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
-        <v>92</v>
-      </c>
-      <c r="B141" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A142" t="s">
-        <v>93</v>
-      </c>
-      <c r="B142" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A143" t="s">
-        <v>94</v>
-      </c>
-      <c r="B143" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A144" t="s">
-        <v>95</v>
-      </c>
-      <c r="B144" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A145" t="s">
-        <v>96</v>
-      </c>
-      <c r="B145" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A146" t="s">
-        <v>97</v>
-      </c>
-      <c r="B146" t="s">
         <v>34</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A147" t="s">
-        <v>83</v>
-      </c>
-      <c r="B147" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
-        <v>83</v>
-      </c>
-      <c r="B148" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A149" t="s">
-        <v>40</v>
-      </c>
-      <c r="B149" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A150" t="s">
-        <v>53</v>
-      </c>
-      <c r="B150" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2350,8 +2565,2070 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E70C3ED-3ED5-4BEB-AFBD-5D4B07BA3767}">
+  <dimension ref="A1:I108"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="str">
+        <f>_xlfn.TEXTJOIN(,TRUE,A1,B1)</f>
+        <v>UKBE</v>
+      </c>
+      <c r="E1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1" t="b">
+        <f>EXACT(C1,E1)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" t="str">
+        <f t="shared" ref="C2:C65" si="0">_xlfn.TEXTJOIN(,TRUE,A2,B2)</f>
+        <v>UKIE</v>
+      </c>
+      <c r="E2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" t="b">
+        <f t="shared" ref="F2:F65" si="1">EXACT(C2,E2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="str">
+        <f t="shared" si="0"/>
+        <v>BEUK</v>
+      </c>
+      <c r="E3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F3" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="str">
+        <f t="shared" si="0"/>
+        <v>BENL</v>
+      </c>
+      <c r="E4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" si="0"/>
+        <v>BEDE</v>
+      </c>
+      <c r="E5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v>BEFR</v>
+      </c>
+      <c r="E6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" si="0"/>
+        <v>NLBE</v>
+      </c>
+      <c r="E7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F7" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="0"/>
+        <v>NLDE</v>
+      </c>
+      <c r="E8" t="s">
+        <v>105</v>
+      </c>
+      <c r="F8" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="0"/>
+        <v>DEBE</v>
+      </c>
+      <c r="E9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F9" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="str">
+        <f t="shared" si="0"/>
+        <v>DENL</v>
+      </c>
+      <c r="E10" t="s">
+        <v>107</v>
+      </c>
+      <c r="F10" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="0"/>
+        <v>DEAT</v>
+      </c>
+      <c r="E11" t="s">
+        <v>108</v>
+      </c>
+      <c r="F11" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="str">
+        <f t="shared" si="0"/>
+        <v>DECH</v>
+      </c>
+      <c r="E12" t="s">
+        <v>109</v>
+      </c>
+      <c r="F12" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" si="0"/>
+        <v>DEFR</v>
+      </c>
+      <c r="E13" t="s">
+        <v>110</v>
+      </c>
+      <c r="F13" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" t="str">
+        <f t="shared" si="0"/>
+        <v>DEDK</v>
+      </c>
+      <c r="E14" t="s">
+        <v>111</v>
+      </c>
+      <c r="F14" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" t="str">
+        <f t="shared" si="0"/>
+        <v>DEPL</v>
+      </c>
+      <c r="E15" t="s">
+        <v>112</v>
+      </c>
+      <c r="F15" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" t="str">
+        <f t="shared" si="0"/>
+        <v>DECZ</v>
+      </c>
+      <c r="E16" t="s">
+        <v>113</v>
+      </c>
+      <c r="F16" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" t="str">
+        <f t="shared" si="0"/>
+        <v>DELU</v>
+      </c>
+      <c r="E17" t="s">
+        <v>114</v>
+      </c>
+      <c r="F17" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" t="str">
+        <f t="shared" si="0"/>
+        <v>ATDE</v>
+      </c>
+      <c r="E18" t="s">
+        <v>115</v>
+      </c>
+      <c r="F18" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" t="str">
+        <f t="shared" si="0"/>
+        <v>ATIT</v>
+      </c>
+      <c r="E19" t="s">
+        <v>116</v>
+      </c>
+      <c r="F19" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" t="str">
+        <f t="shared" si="0"/>
+        <v>ATSI</v>
+      </c>
+      <c r="E20" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" t="str">
+        <f t="shared" si="0"/>
+        <v>ATSK</v>
+      </c>
+      <c r="E21" t="s">
+        <v>118</v>
+      </c>
+      <c r="F21" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" t="str">
+        <f t="shared" si="0"/>
+        <v>ATHU</v>
+      </c>
+      <c r="E22" t="s">
+        <v>119</v>
+      </c>
+      <c r="F22" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" t="str">
+        <f t="shared" si="0"/>
+        <v>ITAT</v>
+      </c>
+      <c r="E23" t="s">
+        <v>120</v>
+      </c>
+      <c r="F23" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" t="str">
+        <f t="shared" si="0"/>
+        <v>ITCH</v>
+      </c>
+      <c r="E24" t="s">
+        <v>121</v>
+      </c>
+      <c r="F24" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C25" t="str">
+        <f t="shared" si="0"/>
+        <v>ITSI</v>
+      </c>
+      <c r="E25" t="s">
+        <v>122</v>
+      </c>
+      <c r="F25" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="str">
+        <f t="shared" si="0"/>
+        <v>CHDE</v>
+      </c>
+      <c r="E26" t="s">
+        <v>123</v>
+      </c>
+      <c r="F26" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" t="str">
+        <f t="shared" si="0"/>
+        <v>CHIT</v>
+      </c>
+      <c r="E27" t="s">
+        <v>124</v>
+      </c>
+      <c r="F27" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" t="str">
+        <f t="shared" si="0"/>
+        <v>CHFR</v>
+      </c>
+      <c r="E28" t="s">
+        <v>125</v>
+      </c>
+      <c r="F28" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" t="str">
+        <f t="shared" si="0"/>
+        <v>SIIT</v>
+      </c>
+      <c r="E29" t="s">
+        <v>126</v>
+      </c>
+      <c r="F29" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" t="str">
+        <f t="shared" si="0"/>
+        <v>SIHR</v>
+      </c>
+      <c r="E30" t="s">
+        <v>127</v>
+      </c>
+      <c r="F30" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31" t="s">
+        <v>64</v>
+      </c>
+      <c r="C31" t="str">
+        <f t="shared" si="0"/>
+        <v>HRSI</v>
+      </c>
+      <c r="E31" t="s">
+        <v>128</v>
+      </c>
+      <c r="F31" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" t="str">
+        <f t="shared" si="0"/>
+        <v>HRHU</v>
+      </c>
+      <c r="E32" t="s">
+        <v>129</v>
+      </c>
+      <c r="F32" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="str">
+        <f t="shared" si="0"/>
+        <v>FRBE</v>
+      </c>
+      <c r="E33" t="s">
+        <v>130</v>
+      </c>
+      <c r="F33" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" t="s">
+        <v>61</v>
+      </c>
+      <c r="C34" t="str">
+        <f t="shared" si="0"/>
+        <v>FRCH</v>
+      </c>
+      <c r="E34" t="s">
+        <v>131</v>
+      </c>
+      <c r="F34" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" t="str">
+        <f t="shared" si="0"/>
+        <v>FRES</v>
+      </c>
+      <c r="E35" t="s">
+        <v>132</v>
+      </c>
+      <c r="F35" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" t="str">
+        <f t="shared" si="0"/>
+        <v>DKDE</v>
+      </c>
+      <c r="E36" t="s">
+        <v>133</v>
+      </c>
+      <c r="F36" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" t="str">
+        <f t="shared" si="0"/>
+        <v>PLDE</v>
+      </c>
+      <c r="E37" t="s">
+        <v>134</v>
+      </c>
+      <c r="F37" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" t="str">
+        <f t="shared" si="0"/>
+        <v>CZDE</v>
+      </c>
+      <c r="E38" t="s">
+        <v>135</v>
+      </c>
+      <c r="F38" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>62</v>
+      </c>
+      <c r="B39" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" t="str">
+        <f t="shared" si="0"/>
+        <v>CZPL</v>
+      </c>
+      <c r="E39" t="s">
+        <v>136</v>
+      </c>
+      <c r="F39" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40" t="s">
+        <v>65</v>
+      </c>
+      <c r="C40" t="str">
+        <f t="shared" si="0"/>
+        <v>CZSK</v>
+      </c>
+      <c r="E40" t="s">
+        <v>137</v>
+      </c>
+      <c r="F40" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>65</v>
+      </c>
+      <c r="B41" t="s">
+        <v>60</v>
+      </c>
+      <c r="C41" t="str">
+        <f t="shared" si="0"/>
+        <v>SKAT</v>
+      </c>
+      <c r="E41" t="s">
+        <v>138</v>
+      </c>
+      <c r="F41" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>65</v>
+      </c>
+      <c r="B42" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" t="str">
+        <f t="shared" si="0"/>
+        <v>SKCZ</v>
+      </c>
+      <c r="E42" t="s">
+        <v>139</v>
+      </c>
+      <c r="F42" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>65</v>
+      </c>
+      <c r="B43" t="s">
+        <v>66</v>
+      </c>
+      <c r="C43" t="str">
+        <f t="shared" si="0"/>
+        <v>SKHU</v>
+      </c>
+      <c r="E43" t="s">
+        <v>140</v>
+      </c>
+      <c r="F43" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>65</v>
+      </c>
+      <c r="B44" t="s">
+        <v>58</v>
+      </c>
+      <c r="C44" t="str">
+        <f t="shared" si="0"/>
+        <v>SKUA</v>
+      </c>
+      <c r="E44" t="s">
+        <v>141</v>
+      </c>
+      <c r="F44" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>66</v>
+      </c>
+      <c r="B45" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" t="str">
+        <f t="shared" si="0"/>
+        <v>HUHR</v>
+      </c>
+      <c r="E45" t="s">
+        <v>142</v>
+      </c>
+      <c r="F45" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>66</v>
+      </c>
+      <c r="B46" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46" t="str">
+        <f t="shared" si="0"/>
+        <v>HUSK</v>
+      </c>
+      <c r="E46" t="s">
+        <v>143</v>
+      </c>
+      <c r="F46" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>66</v>
+      </c>
+      <c r="B47" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" t="str">
+        <f t="shared" si="0"/>
+        <v>HURS</v>
+      </c>
+      <c r="E47" t="s">
+        <v>144</v>
+      </c>
+      <c r="F47" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>66</v>
+      </c>
+      <c r="B48" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" t="str">
+        <f t="shared" si="0"/>
+        <v>HURO</v>
+      </c>
+      <c r="E48" t="s">
+        <v>145</v>
+      </c>
+      <c r="F48" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>67</v>
+      </c>
+      <c r="B49" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49" t="str">
+        <f t="shared" si="0"/>
+        <v>RSBG</v>
+      </c>
+      <c r="E49" t="s">
+        <v>146</v>
+      </c>
+      <c r="F49" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>67</v>
+      </c>
+      <c r="B50" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" t="str">
+        <f t="shared" si="0"/>
+        <v>RSBA</v>
+      </c>
+      <c r="E50" t="s">
+        <v>147</v>
+      </c>
+      <c r="F50" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" t="s">
+        <v>67</v>
+      </c>
+      <c r="C51" t="str">
+        <f t="shared" si="0"/>
+        <v>BGRS</v>
+      </c>
+      <c r="E51" t="s">
+        <v>148</v>
+      </c>
+      <c r="F51" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>68</v>
+      </c>
+      <c r="B52" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" t="str">
+        <f t="shared" si="0"/>
+        <v>BGGR</v>
+      </c>
+      <c r="E52" t="s">
+        <v>149</v>
+      </c>
+      <c r="F52" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>68</v>
+      </c>
+      <c r="B53" t="s">
+        <v>51</v>
+      </c>
+      <c r="C53" t="str">
+        <f t="shared" si="0"/>
+        <v>BGRO</v>
+      </c>
+      <c r="E53" t="s">
+        <v>150</v>
+      </c>
+      <c r="F53" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>68</v>
+      </c>
+      <c r="B54" t="s">
+        <v>70</v>
+      </c>
+      <c r="C54" t="str">
+        <f t="shared" si="0"/>
+        <v>BGMK</v>
+      </c>
+      <c r="E54" t="s">
+        <v>151</v>
+      </c>
+      <c r="F54" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>68</v>
+      </c>
+      <c r="B55" t="s">
+        <v>36</v>
+      </c>
+      <c r="C55" t="str">
+        <f t="shared" si="0"/>
+        <v>BGTR</v>
+      </c>
+      <c r="E55" t="s">
+        <v>152</v>
+      </c>
+      <c r="F55" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>20</v>
+      </c>
+      <c r="B56" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" t="str">
+        <f t="shared" si="0"/>
+        <v>GRBG</v>
+      </c>
+      <c r="E56" t="s">
+        <v>153</v>
+      </c>
+      <c r="F56" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>51</v>
+      </c>
+      <c r="B57" t="s">
+        <v>66</v>
+      </c>
+      <c r="C57" t="str">
+        <f t="shared" si="0"/>
+        <v>ROHU</v>
+      </c>
+      <c r="E57" t="s">
+        <v>154</v>
+      </c>
+      <c r="F57" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>51</v>
+      </c>
+      <c r="B58" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58" t="str">
+        <f t="shared" si="0"/>
+        <v>ROBG</v>
+      </c>
+      <c r="E58" t="s">
+        <v>155</v>
+      </c>
+      <c r="F58" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>51</v>
+      </c>
+      <c r="B59" t="s">
+        <v>58</v>
+      </c>
+      <c r="C59" t="str">
+        <f t="shared" si="0"/>
+        <v>ROUA</v>
+      </c>
+      <c r="E59" t="s">
+        <v>156</v>
+      </c>
+      <c r="F59" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>51</v>
+      </c>
+      <c r="B60" t="s">
+        <v>71</v>
+      </c>
+      <c r="C60" t="str">
+        <f t="shared" si="0"/>
+        <v>ROMD</v>
+      </c>
+      <c r="E60" t="s">
+        <v>157</v>
+      </c>
+      <c r="F60" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>26</v>
+      </c>
+      <c r="B61" t="s">
+        <v>72</v>
+      </c>
+      <c r="C61" t="str">
+        <f t="shared" si="0"/>
+        <v>LTLV</v>
+      </c>
+      <c r="E61" t="s">
+        <v>158</v>
+      </c>
+      <c r="F61" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>26</v>
+      </c>
+      <c r="B62" t="s">
+        <v>53</v>
+      </c>
+      <c r="C62" t="str">
+        <f t="shared" si="0"/>
+        <v>LTRU</v>
+      </c>
+      <c r="E62" t="s">
+        <v>159</v>
+      </c>
+      <c r="F62" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>72</v>
+      </c>
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" t="str">
+        <f t="shared" si="0"/>
+        <v>LVLT</v>
+      </c>
+      <c r="E63" t="s">
+        <v>160</v>
+      </c>
+      <c r="F63" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>72</v>
+      </c>
+      <c r="B64" t="s">
+        <v>53</v>
+      </c>
+      <c r="C64" t="str">
+        <f t="shared" si="0"/>
+        <v>LVRU</v>
+      </c>
+      <c r="E64" t="s">
+        <v>161</v>
+      </c>
+      <c r="F64" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>34</v>
+      </c>
+      <c r="B65" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" t="str">
+        <f t="shared" si="0"/>
+        <v>ESFR</v>
+      </c>
+      <c r="E65" t="s">
+        <v>162</v>
+      </c>
+      <c r="F65" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>34</v>
+      </c>
+      <c r="B66" t="s">
+        <v>32</v>
+      </c>
+      <c r="C66" t="str">
+        <f t="shared" ref="C66:C108" si="2">_xlfn.TEXTJOIN(,TRUE,A66,B66)</f>
+        <v>ESPT</v>
+      </c>
+      <c r="E66" t="s">
+        <v>163</v>
+      </c>
+      <c r="F66" t="b">
+        <f t="shared" ref="F66:F108" si="3">EXACT(C66,E66)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>32</v>
+      </c>
+      <c r="B67" t="s">
+        <v>34</v>
+      </c>
+      <c r="C67" t="str">
+        <f t="shared" si="2"/>
+        <v>PTES</v>
+      </c>
+      <c r="E67" t="s">
+        <v>164</v>
+      </c>
+      <c r="F67" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>58</v>
+      </c>
+      <c r="B68" t="s">
+        <v>30</v>
+      </c>
+      <c r="C68" t="str">
+        <f t="shared" si="2"/>
+        <v>UAPL</v>
+      </c>
+      <c r="E68" t="s">
+        <v>165</v>
+      </c>
+      <c r="F68" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>58</v>
+      </c>
+      <c r="B69" t="s">
+        <v>65</v>
+      </c>
+      <c r="C69" t="str">
+        <f t="shared" si="2"/>
+        <v>UASK</v>
+      </c>
+      <c r="E69" t="s">
+        <v>166</v>
+      </c>
+      <c r="F69" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>58</v>
+      </c>
+      <c r="B70" t="s">
+        <v>66</v>
+      </c>
+      <c r="C70" t="str">
+        <f t="shared" si="2"/>
+        <v>UAHU</v>
+      </c>
+      <c r="E70" t="s">
+        <v>167</v>
+      </c>
+      <c r="F70" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>58</v>
+      </c>
+      <c r="B71" t="s">
+        <v>51</v>
+      </c>
+      <c r="C71" t="str">
+        <f t="shared" si="2"/>
+        <v>UARO</v>
+      </c>
+      <c r="E71" t="s">
+        <v>168</v>
+      </c>
+      <c r="F71" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>51</v>
+      </c>
+      <c r="C72" t="str">
+        <f t="shared" si="2"/>
+        <v>MDRO</v>
+      </c>
+      <c r="E72" t="s">
+        <v>169</v>
+      </c>
+      <c r="F72" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>53</v>
+      </c>
+      <c r="B73" t="s">
+        <v>42</v>
+      </c>
+      <c r="C73" t="str">
+        <f t="shared" si="2"/>
+        <v>RUDE</v>
+      </c>
+      <c r="E73" t="s">
+        <v>170</v>
+      </c>
+      <c r="F73" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>53</v>
+      </c>
+      <c r="B74" t="s">
+        <v>72</v>
+      </c>
+      <c r="C74" t="str">
+        <f t="shared" si="2"/>
+        <v>RULV</v>
+      </c>
+      <c r="E74" t="s">
+        <v>171</v>
+      </c>
+      <c r="F74" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>53</v>
+      </c>
+      <c r="B75" t="s">
+        <v>73</v>
+      </c>
+      <c r="C75" t="str">
+        <f t="shared" si="2"/>
+        <v>RUFI</v>
+      </c>
+      <c r="E75" t="s">
+        <v>172</v>
+      </c>
+      <c r="F75" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>74</v>
+      </c>
+      <c r="B76" t="s">
+        <v>22</v>
+      </c>
+      <c r="C76" t="str">
+        <f t="shared" si="2"/>
+        <v>ALIT</v>
+      </c>
+      <c r="E76" t="s">
+        <v>173</v>
+      </c>
+      <c r="F76" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>36</v>
+      </c>
+      <c r="B77" t="s">
+        <v>68</v>
+      </c>
+      <c r="C77" t="str">
+        <f t="shared" si="2"/>
+        <v>TRBG</v>
+      </c>
+      <c r="E77" t="s">
+        <v>174</v>
+      </c>
+      <c r="F77" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>36</v>
+      </c>
+      <c r="B78" t="s">
+        <v>20</v>
+      </c>
+      <c r="C78" t="str">
+        <f t="shared" si="2"/>
+        <v>TRGR</v>
+      </c>
+      <c r="E78" t="s">
+        <v>175</v>
+      </c>
+      <c r="F78" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>34</v>
+      </c>
+      <c r="C79" t="str">
+        <f t="shared" si="2"/>
+        <v>MAES</v>
+      </c>
+      <c r="E79" t="s">
+        <v>176</v>
+      </c>
+      <c r="F79" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>55</v>
+      </c>
+      <c r="B80" t="s">
+        <v>22</v>
+      </c>
+      <c r="C80" t="str">
+        <f t="shared" si="2"/>
+        <v>TNIT</v>
+      </c>
+      <c r="E80" t="s">
+        <v>177</v>
+      </c>
+      <c r="F80" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>45</v>
+      </c>
+      <c r="B81" t="s">
+        <v>22</v>
+      </c>
+      <c r="C81" t="str">
+        <f t="shared" si="2"/>
+        <v>LYIT</v>
+      </c>
+      <c r="E81" t="s">
+        <v>178</v>
+      </c>
+      <c r="F81" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>75</v>
+      </c>
+      <c r="B82" t="s">
+        <v>30</v>
+      </c>
+      <c r="C82" t="str">
+        <f t="shared" si="2"/>
+        <v>BYPL</v>
+      </c>
+      <c r="E82" t="s">
+        <v>179</v>
+      </c>
+      <c r="F82" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>75</v>
+      </c>
+      <c r="B83" t="s">
+        <v>26</v>
+      </c>
+      <c r="C83" t="str">
+        <f t="shared" si="2"/>
+        <v>BYLT</v>
+      </c>
+      <c r="E83" t="s">
+        <v>180</v>
+      </c>
+      <c r="F83" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>53</v>
+      </c>
+      <c r="B84" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" t="str">
+        <f t="shared" si="2"/>
+        <v>RUUA</v>
+      </c>
+      <c r="E84" t="s">
+        <v>181</v>
+      </c>
+      <c r="F84" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>76</v>
+      </c>
+      <c r="B85" t="s">
+        <v>36</v>
+      </c>
+      <c r="C85" t="str">
+        <f t="shared" si="2"/>
+        <v>AZTR</v>
+      </c>
+      <c r="E85" t="s">
+        <v>182</v>
+      </c>
+      <c r="F85" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>58</v>
+      </c>
+      <c r="B86" t="s">
+        <v>30</v>
+      </c>
+      <c r="C86" t="str">
+        <f t="shared" si="2"/>
+        <v>UAPL</v>
+      </c>
+      <c r="F86" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I86" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>58</v>
+      </c>
+      <c r="B87" t="s">
+        <v>65</v>
+      </c>
+      <c r="C87" t="str">
+        <f t="shared" si="2"/>
+        <v>UASK</v>
+      </c>
+      <c r="F87" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I87" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>58</v>
+      </c>
+      <c r="B88" t="s">
+        <v>66</v>
+      </c>
+      <c r="C88" t="str">
+        <f t="shared" si="2"/>
+        <v>UAHU</v>
+      </c>
+      <c r="F88" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I88" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>67</v>
+      </c>
+      <c r="B89" t="s">
+        <v>66</v>
+      </c>
+      <c r="C89" t="str">
+        <f t="shared" si="2"/>
+        <v>RSHU</v>
+      </c>
+      <c r="E89" t="s">
+        <v>183</v>
+      </c>
+      <c r="F89" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="I89" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>68</v>
+      </c>
+      <c r="B90" t="s">
+        <v>67</v>
+      </c>
+      <c r="C90" t="str">
+        <f t="shared" si="2"/>
+        <v>BGRS</v>
+      </c>
+      <c r="F90" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I90" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>36</v>
+      </c>
+      <c r="B91" t="s">
+        <v>68</v>
+      </c>
+      <c r="C91" t="str">
+        <f t="shared" si="2"/>
+        <v>TRBG</v>
+      </c>
+      <c r="F91" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I91" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>53</v>
+      </c>
+      <c r="B92" t="s">
+        <v>72</v>
+      </c>
+      <c r="C92" t="str">
+        <f t="shared" si="2"/>
+        <v>RULV</v>
+      </c>
+      <c r="F92" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I92" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>45</v>
+      </c>
+      <c r="B93" t="s">
+        <v>22</v>
+      </c>
+      <c r="C93" t="str">
+        <f t="shared" si="2"/>
+        <v>LYIT</v>
+      </c>
+      <c r="F93" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I93" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>83</v>
+      </c>
+      <c r="B94" t="s">
+        <v>34</v>
+      </c>
+      <c r="C94" t="str">
+        <f t="shared" si="2"/>
+        <v>DZES</v>
+      </c>
+      <c r="E94" t="s">
+        <v>184</v>
+      </c>
+      <c r="F94" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="I94" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>78</v>
+      </c>
+      <c r="B95" t="s">
+        <v>34</v>
+      </c>
+      <c r="C95" t="str">
+        <f t="shared" si="2"/>
+        <v>MAES</v>
+      </c>
+      <c r="F95" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I95" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>48</v>
+      </c>
+      <c r="B96" t="s">
+        <v>42</v>
+      </c>
+      <c r="C96" t="str">
+        <f t="shared" si="2"/>
+        <v>NODE</v>
+      </c>
+      <c r="E96" t="s">
+        <v>185</v>
+      </c>
+      <c r="F96" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>48</v>
+      </c>
+      <c r="B97" t="s">
+        <v>28</v>
+      </c>
+      <c r="C97" t="str">
+        <f t="shared" si="2"/>
+        <v>NONL</v>
+      </c>
+      <c r="E97" t="s">
+        <v>186</v>
+      </c>
+      <c r="F97" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>48</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="str">
+        <f t="shared" si="2"/>
+        <v>NOBE</v>
+      </c>
+      <c r="E98" t="s">
+        <v>187</v>
+      </c>
+      <c r="F98" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>48</v>
+      </c>
+      <c r="B99" t="s">
+        <v>18</v>
+      </c>
+      <c r="C99" t="str">
+        <f t="shared" si="2"/>
+        <v>NOFR</v>
+      </c>
+      <c r="E99" t="s">
+        <v>188</v>
+      </c>
+      <c r="F99" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>48</v>
+      </c>
+      <c r="B100" t="s">
+        <v>38</v>
+      </c>
+      <c r="C100" t="str">
+        <f t="shared" si="2"/>
+        <v>NOUK</v>
+      </c>
+      <c r="E100" t="s">
+        <v>189</v>
+      </c>
+      <c r="F100" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>38</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="str">
+        <f t="shared" si="2"/>
+        <v>UKBE</v>
+      </c>
+      <c r="F101" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>38</v>
+      </c>
+      <c r="B102" t="s">
+        <v>28</v>
+      </c>
+      <c r="C102" t="str">
+        <f t="shared" si="2"/>
+        <v>UKNL</v>
+      </c>
+      <c r="E102" t="s">
+        <v>190</v>
+      </c>
+      <c r="F102" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>74</v>
+      </c>
+      <c r="B103" t="s">
+        <v>22</v>
+      </c>
+      <c r="C103" t="str">
+        <f t="shared" si="2"/>
+        <v>ALIT</v>
+      </c>
+      <c r="F103" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>20</v>
+      </c>
+      <c r="B104" t="s">
+        <v>74</v>
+      </c>
+      <c r="C104" t="str">
+        <f t="shared" si="2"/>
+        <v>GRAL</v>
+      </c>
+      <c r="E104" t="s">
+        <v>191</v>
+      </c>
+      <c r="F104" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>83</v>
+      </c>
+      <c r="B105" t="s">
+        <v>78</v>
+      </c>
+      <c r="C105" t="str">
+        <f t="shared" si="2"/>
+        <v>DZMA</v>
+      </c>
+      <c r="E105" t="s">
+        <v>192</v>
+      </c>
+      <c r="F105" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>83</v>
+      </c>
+      <c r="B106" t="s">
+        <v>55</v>
+      </c>
+      <c r="C106" t="str">
+        <f t="shared" si="2"/>
+        <v>DZTN</v>
+      </c>
+      <c r="E106" t="s">
+        <v>193</v>
+      </c>
+      <c r="F106" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>40</v>
+      </c>
+      <c r="B107" t="s">
+        <v>80</v>
+      </c>
+      <c r="C107" t="str">
+        <f t="shared" si="2"/>
+        <v>DKSE</v>
+      </c>
+      <c r="E107" t="s">
+        <v>194</v>
+      </c>
+      <c r="F107" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>53</v>
+      </c>
+      <c r="B108" t="s">
+        <v>75</v>
+      </c>
+      <c r="C108" t="str">
+        <f t="shared" si="2"/>
+        <v>RUBY</v>
+      </c>
+      <c r="E108" t="s">
+        <v>195</v>
+      </c>
+      <c r="F108" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
-  <dimension ref="A1:I299"/>
+  <dimension ref="A1:I281"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -6042,10 +8319,10 @@
         <v>11</v>
       </c>
       <c r="B128" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C128" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="D128">
         <v>10000</v>
@@ -6071,10 +8348,10 @@
         <v>11</v>
       </c>
       <c r="B129" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C129" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D129">
         <v>10000</v>
@@ -6100,10 +8377,10 @@
         <v>11</v>
       </c>
       <c r="B130" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="C130" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="D130">
         <v>10000</v>
@@ -6129,10 +8406,10 @@
         <v>11</v>
       </c>
       <c r="B131" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="C131" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="D131">
         <v>10000</v>
@@ -6158,10 +8435,10 @@
         <v>11</v>
       </c>
       <c r="B132" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="C132" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="D132">
         <v>10000</v>
@@ -6187,10 +8464,10 @@
         <v>11</v>
       </c>
       <c r="B133" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="C133" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="D133">
         <v>10000</v>
@@ -6216,10 +8493,10 @@
         <v>11</v>
       </c>
       <c r="B134" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C134" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="D134">
         <v>10000</v>
@@ -6245,10 +8522,10 @@
         <v>11</v>
       </c>
       <c r="B135" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C135" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D135">
         <v>10000</v>
@@ -6274,10 +8551,10 @@
         <v>11</v>
       </c>
       <c r="B136" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="C136" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D136">
         <v>10000</v>
@@ -6303,10 +8580,10 @@
         <v>11</v>
       </c>
       <c r="B137" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="C137" t="s">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="D137">
         <v>10000</v>
@@ -6332,10 +8609,10 @@
         <v>11</v>
       </c>
       <c r="B138" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="C138" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D138">
         <v>10000</v>
@@ -6361,10 +8638,10 @@
         <v>11</v>
       </c>
       <c r="B139" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="C139" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="D139">
         <v>10000</v>
@@ -6390,10 +8667,10 @@
         <v>11</v>
       </c>
       <c r="B140" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="C140" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="D140">
         <v>10000</v>
@@ -6419,10 +8696,10 @@
         <v>11</v>
       </c>
       <c r="B141" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C141" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="D141">
         <v>10000</v>
@@ -6445,13 +8722,13 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B142" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C142" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D142">
         <v>10000</v>
@@ -6466,7 +8743,7 @@
         <v>10000000</v>
       </c>
       <c r="H142">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I142">
         <v>1</v>
@@ -6474,13 +8751,13 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B143" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="C143" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D143">
         <v>10000</v>
@@ -6495,7 +8772,7 @@
         <v>10000000</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I143">
         <v>1</v>
@@ -6503,13 +8780,13 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B144" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="C144" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D144">
         <v>10000</v>
@@ -6524,7 +8801,7 @@
         <v>10000000</v>
       </c>
       <c r="H144">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I144">
         <v>1</v>
@@ -6532,10 +8809,10 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B145" t="s">
-        <v>74</v>
+        <v>21</v>
       </c>
       <c r="C145" t="s">
         <v>22</v>
@@ -6553,7 +8830,7 @@
         <v>10000000</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I145">
         <v>1</v>
@@ -6561,13 +8838,13 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B146" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C146" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="D146">
         <v>10000</v>
@@ -6582,7 +8859,7 @@
         <v>10000000</v>
       </c>
       <c r="H146">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I146">
         <v>1</v>
@@ -6590,13 +8867,13 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B147" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="C147" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D147">
         <v>10000</v>
@@ -6611,7 +8888,7 @@
         <v>10000000</v>
       </c>
       <c r="H147">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I147">
         <v>1</v>
@@ -6619,13 +8896,13 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B148" t="s">
-        <v>83</v>
+        <v>27</v>
       </c>
       <c r="C148" t="s">
-        <v>78</v>
+        <v>28</v>
       </c>
       <c r="D148">
         <v>10000</v>
@@ -6640,7 +8917,7 @@
         <v>10000000</v>
       </c>
       <c r="H148">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I148">
         <v>1</v>
@@ -6648,13 +8925,13 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B149" t="s">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="C149" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="D149">
         <v>10000</v>
@@ -6669,7 +8946,7 @@
         <v>10000000</v>
       </c>
       <c r="H149">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I149">
         <v>1</v>
@@ -6677,13 +8954,13 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B150" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C150" t="s">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="D150">
         <v>10000</v>
@@ -6698,7 +8975,7 @@
         <v>10000000</v>
       </c>
       <c r="H150">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I150">
         <v>1</v>
@@ -6709,10 +8986,10 @@
         <v>12</v>
       </c>
       <c r="B151" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="C151" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D151">
         <v>10000</v>
@@ -6738,10 +9015,10 @@
         <v>12</v>
       </c>
       <c r="B152" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C152" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D152">
         <v>10000</v>
@@ -6767,10 +9044,10 @@
         <v>12</v>
       </c>
       <c r="B153" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="C153" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D153">
         <v>10000</v>
@@ -6796,10 +9073,10 @@
         <v>12</v>
       </c>
       <c r="B154" t="s">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="C154" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="D154">
         <v>10000</v>
@@ -6825,10 +9102,10 @@
         <v>12</v>
       </c>
       <c r="B155" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C155" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D155">
         <v>10000</v>
@@ -6854,10 +9131,10 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="C156" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D156">
         <v>10000</v>
@@ -6883,10 +9160,10 @@
         <v>12</v>
       </c>
       <c r="B157" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C157" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D157">
         <v>10000</v>
@@ -6912,10 +9189,10 @@
         <v>12</v>
       </c>
       <c r="B158" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="C158" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D158">
         <v>10000</v>
@@ -6941,10 +9218,10 @@
         <v>12</v>
       </c>
       <c r="B159" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C159" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D159">
         <v>10000</v>
@@ -6970,10 +9247,10 @@
         <v>12</v>
       </c>
       <c r="B160" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C160" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D160">
         <v>10000</v>
@@ -6999,10 +9276,10 @@
         <v>12</v>
       </c>
       <c r="B161" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C161" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D161">
         <v>10000</v>
@@ -7028,10 +9305,10 @@
         <v>12</v>
       </c>
       <c r="B162" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C162" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D162">
         <v>10000</v>
@@ -7057,10 +9334,10 @@
         <v>12</v>
       </c>
       <c r="B163" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="C163" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="D163">
         <v>10000</v>
@@ -7086,10 +9363,10 @@
         <v>12</v>
       </c>
       <c r="B164" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="C164" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D164">
         <v>10000</v>
@@ -7115,10 +9392,10 @@
         <v>12</v>
       </c>
       <c r="B165" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="C165" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D165">
         <v>10000</v>
@@ -7144,10 +9421,10 @@
         <v>12</v>
       </c>
       <c r="B166" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C166" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="D166">
         <v>10000</v>
@@ -7173,10 +9450,10 @@
         <v>12</v>
       </c>
       <c r="B167" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C167" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="D167">
         <v>10000</v>
@@ -7202,10 +9479,10 @@
         <v>12</v>
       </c>
       <c r="B168" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C168" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="D168">
         <v>10000</v>
@@ -7231,10 +9508,10 @@
         <v>12</v>
       </c>
       <c r="B169" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="C169" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D169">
         <v>10000</v>
@@ -7260,10 +9537,10 @@
         <v>12</v>
       </c>
       <c r="B170" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C170" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D170">
         <v>10000</v>
@@ -7289,10 +9566,10 @@
         <v>12</v>
       </c>
       <c r="B171" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="C171" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D171">
         <v>10000</v>
@@ -7318,10 +9595,10 @@
         <v>12</v>
       </c>
       <c r="B172" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="C172" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="D172">
         <v>10000</v>
@@ -7347,10 +9624,10 @@
         <v>12</v>
       </c>
       <c r="B173" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C173" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="D173">
         <v>10000</v>
@@ -7376,10 +9653,10 @@
         <v>12</v>
       </c>
       <c r="B174" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="C174" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D174">
         <v>10000</v>
@@ -7405,10 +9682,10 @@
         <v>12</v>
       </c>
       <c r="B175" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C175" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="D175">
         <v>10000</v>
@@ -7434,10 +9711,10 @@
         <v>12</v>
       </c>
       <c r="B176" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C176" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="D176">
         <v>10000</v>
@@ -7463,10 +9740,10 @@
         <v>12</v>
       </c>
       <c r="B177" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C177" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D177">
         <v>10000</v>
@@ -7492,10 +9769,10 @@
         <v>12</v>
       </c>
       <c r="B178" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C178" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D178">
         <v>10000</v>
@@ -7521,10 +9798,10 @@
         <v>12</v>
       </c>
       <c r="B179" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C179" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D179">
         <v>10000</v>
@@ -7550,10 +9827,10 @@
         <v>12</v>
       </c>
       <c r="B180" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C180" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D180">
         <v>10000</v>
@@ -7579,10 +9856,10 @@
         <v>12</v>
       </c>
       <c r="B181" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C181" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D181">
         <v>10000</v>
@@ -7608,10 +9885,10 @@
         <v>12</v>
       </c>
       <c r="B182" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C182" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="D182">
         <v>10000</v>
@@ -7637,10 +9914,10 @@
         <v>12</v>
       </c>
       <c r="B183" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C183" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D183">
         <v>10000</v>
@@ -7666,10 +9943,10 @@
         <v>12</v>
       </c>
       <c r="B184" t="s">
+        <v>60</v>
+      </c>
+      <c r="C184" t="s">
         <v>42</v>
-      </c>
-      <c r="C184" t="s">
-        <v>16</v>
       </c>
       <c r="D184">
         <v>10000</v>
@@ -7695,10 +9972,10 @@
         <v>12</v>
       </c>
       <c r="B185" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C185" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D185">
         <v>10000</v>
@@ -7724,10 +10001,10 @@
         <v>12</v>
       </c>
       <c r="B186" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C186" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D186">
         <v>10000</v>
@@ -7753,10 +10030,10 @@
         <v>12</v>
       </c>
       <c r="B187" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C187" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D187">
         <v>10000</v>
@@ -7782,10 +10059,10 @@
         <v>12</v>
       </c>
       <c r="B188" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C188" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="D188">
         <v>10000</v>
@@ -7811,10 +10088,10 @@
         <v>12</v>
       </c>
       <c r="B189" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C189" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D189">
         <v>10000</v>
@@ -7840,10 +10117,10 @@
         <v>12</v>
       </c>
       <c r="B190" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C190" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="D190">
         <v>10000</v>
@@ -7869,10 +10146,10 @@
         <v>12</v>
       </c>
       <c r="B191" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C191" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D191">
         <v>10000</v>
@@ -7898,10 +10175,10 @@
         <v>12</v>
       </c>
       <c r="B192" t="s">
+        <v>61</v>
+      </c>
+      <c r="C192" t="s">
         <v>42</v>
-      </c>
-      <c r="C192" t="s">
-        <v>63</v>
       </c>
       <c r="D192">
         <v>10000</v>
@@ -7927,10 +10204,10 @@
         <v>12</v>
       </c>
       <c r="B193" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C193" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D193">
         <v>10000</v>
@@ -7956,10 +10233,10 @@
         <v>12</v>
       </c>
       <c r="B194" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C194" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D194">
         <v>10000</v>
@@ -7985,10 +10262,10 @@
         <v>12</v>
       </c>
       <c r="B195" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C195" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="D195">
         <v>10000</v>
@@ -8014,10 +10291,10 @@
         <v>12</v>
       </c>
       <c r="B196" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C196" t="s">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="D196">
         <v>10000</v>
@@ -8043,10 +10320,10 @@
         <v>12</v>
       </c>
       <c r="B197" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="C197" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D197">
         <v>10000</v>
@@ -8072,10 +10349,10 @@
         <v>12</v>
       </c>
       <c r="B198" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C198" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D198">
         <v>10000</v>
@@ -8101,10 +10378,10 @@
         <v>12</v>
       </c>
       <c r="B199" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C199" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
       <c r="D199">
         <v>10000</v>
@@ -8130,10 +10407,10 @@
         <v>12</v>
       </c>
       <c r="B200" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C200" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D200">
         <v>10000</v>
@@ -8159,10 +10436,10 @@
         <v>12</v>
       </c>
       <c r="B201" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="C201" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D201">
         <v>10000</v>
@@ -8188,10 +10465,10 @@
         <v>12</v>
       </c>
       <c r="B202" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="C202" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D202">
         <v>10000</v>
@@ -8217,10 +10494,10 @@
         <v>12</v>
       </c>
       <c r="B203" t="s">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="C203" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D203">
         <v>10000</v>
@@ -8246,10 +10523,10 @@
         <v>12</v>
       </c>
       <c r="B204" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C204" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D204">
         <v>10000</v>
@@ -8275,10 +10552,10 @@
         <v>12</v>
       </c>
       <c r="B205" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C205" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D205">
         <v>10000</v>
@@ -8304,10 +10581,10 @@
         <v>12</v>
       </c>
       <c r="B206" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="C206" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D206">
         <v>10000</v>
@@ -8333,10 +10610,10 @@
         <v>12</v>
       </c>
       <c r="B207" t="s">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="C207" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D207">
         <v>10000</v>
@@ -8362,10 +10639,10 @@
         <v>12</v>
       </c>
       <c r="B208" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C208" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="D208">
         <v>10000</v>
@@ -8391,10 +10668,10 @@
         <v>12</v>
       </c>
       <c r="B209" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C209" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D209">
         <v>10000</v>
@@ -8420,10 +10697,10 @@
         <v>12</v>
       </c>
       <c r="B210" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C210" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="D210">
         <v>10000</v>
@@ -8449,10 +10726,10 @@
         <v>12</v>
       </c>
       <c r="B211" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C211" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D211">
         <v>10000</v>
@@ -8478,10 +10755,10 @@
         <v>12</v>
       </c>
       <c r="B212" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="C212" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="D212">
         <v>10000</v>
@@ -8507,10 +10784,10 @@
         <v>12</v>
       </c>
       <c r="B213" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C213" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D213">
         <v>10000</v>
@@ -8536,10 +10813,10 @@
         <v>12</v>
       </c>
       <c r="B214" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C214" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="D214">
         <v>10000</v>
@@ -8565,10 +10842,10 @@
         <v>12</v>
       </c>
       <c r="B215" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C215" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D215">
         <v>10000</v>
@@ -8594,10 +10871,10 @@
         <v>12</v>
       </c>
       <c r="B216" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C216" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D216">
         <v>10000</v>
@@ -8623,10 +10900,10 @@
         <v>12</v>
       </c>
       <c r="B217" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C217" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D217">
         <v>10000</v>
@@ -8652,10 +10929,10 @@
         <v>12</v>
       </c>
       <c r="B218" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C218" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="D218">
         <v>10000</v>
@@ -8681,10 +10958,10 @@
         <v>12</v>
       </c>
       <c r="B219" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C219" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D219">
         <v>10000</v>
@@ -8710,10 +10987,10 @@
         <v>12</v>
       </c>
       <c r="B220" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C220" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D220">
         <v>10000</v>
@@ -8739,10 +11016,10 @@
         <v>12</v>
       </c>
       <c r="B221" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C221" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="D221">
         <v>10000</v>
@@ -8768,10 +11045,10 @@
         <v>12</v>
       </c>
       <c r="B222" t="s">
-        <v>66</v>
+        <v>20</v>
       </c>
       <c r="C222" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D222">
         <v>10000</v>
@@ -8797,10 +11074,10 @@
         <v>12</v>
       </c>
       <c r="B223" t="s">
+        <v>51</v>
+      </c>
+      <c r="C223" t="s">
         <v>66</v>
-      </c>
-      <c r="C223" t="s">
-        <v>51</v>
       </c>
       <c r="D223">
         <v>10000</v>
@@ -8826,7 +11103,7 @@
         <v>12</v>
       </c>
       <c r="B224" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C224" t="s">
         <v>68</v>
@@ -8855,10 +11132,10 @@
         <v>12</v>
       </c>
       <c r="B225" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C225" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D225">
         <v>10000</v>
@@ -8884,10 +11161,10 @@
         <v>12</v>
       </c>
       <c r="B226" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C226" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D226">
         <v>10000</v>
@@ -8913,10 +11190,10 @@
         <v>12</v>
       </c>
       <c r="B227" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="C227" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="D227">
         <v>10000</v>
@@ -8942,10 +11219,10 @@
         <v>12</v>
       </c>
       <c r="B228" t="s">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="C228" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D228">
         <v>10000</v>
@@ -8971,10 +11248,10 @@
         <v>12</v>
       </c>
       <c r="B229" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C229" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="D229">
         <v>10000</v>
@@ -9000,10 +11277,10 @@
         <v>12</v>
       </c>
       <c r="B230" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C230" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D230">
         <v>10000</v>
@@ -9029,10 +11306,10 @@
         <v>12</v>
       </c>
       <c r="B231" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="C231" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="D231">
         <v>10000</v>
@@ -9058,10 +11335,10 @@
         <v>12</v>
       </c>
       <c r="B232" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="C232" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="D232">
         <v>10000</v>
@@ -9087,10 +11364,10 @@
         <v>12</v>
       </c>
       <c r="B233" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="C233" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="D233">
         <v>10000</v>
@@ -9116,10 +11393,10 @@
         <v>12</v>
       </c>
       <c r="B234" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C234" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="D234">
         <v>10000</v>
@@ -9145,10 +11422,10 @@
         <v>12</v>
       </c>
       <c r="B235" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C235" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D235">
         <v>10000</v>
@@ -9174,10 +11451,10 @@
         <v>12</v>
       </c>
       <c r="B236" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="C236" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D236">
         <v>10000</v>
@@ -9203,10 +11480,10 @@
         <v>12</v>
       </c>
       <c r="B237" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="C237" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D237">
         <v>10000</v>
@@ -9232,10 +11509,10 @@
         <v>12</v>
       </c>
       <c r="B238" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C238" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="D238">
         <v>10000</v>
@@ -9261,10 +11538,10 @@
         <v>12</v>
       </c>
       <c r="B239" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="C239" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D239">
         <v>10000</v>
@@ -9290,10 +11567,10 @@
         <v>12</v>
       </c>
       <c r="B240" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C240" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="D240">
         <v>10000</v>
@@ -9319,10 +11596,10 @@
         <v>12</v>
       </c>
       <c r="B241" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C241" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="D241">
         <v>10000</v>
@@ -9348,10 +11625,10 @@
         <v>12</v>
       </c>
       <c r="B242" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="C242" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D242">
         <v>10000</v>
@@ -9377,10 +11654,10 @@
         <v>12</v>
       </c>
       <c r="B243" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="C243" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="D243">
         <v>10000</v>
@@ -9406,10 +11683,10 @@
         <v>12</v>
       </c>
       <c r="B244" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="C244" t="s">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="D244">
         <v>10000</v>
@@ -9435,10 +11712,10 @@
         <v>12</v>
       </c>
       <c r="B245" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="C245" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="D245">
         <v>10000</v>
@@ -9464,10 +11741,10 @@
         <v>12</v>
       </c>
       <c r="B246" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C246" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="D246">
         <v>10000</v>
@@ -9493,10 +11770,10 @@
         <v>12</v>
       </c>
       <c r="B247" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="C247" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="D247">
         <v>10000</v>
@@ -9522,10 +11799,10 @@
         <v>12</v>
       </c>
       <c r="B248" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C248" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D248">
         <v>10000</v>
@@ -9551,10 +11828,10 @@
         <v>12</v>
       </c>
       <c r="B249" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C249" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="D249">
         <v>10000</v>
@@ -9583,7 +11860,7 @@
         <v>53</v>
       </c>
       <c r="C250" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="D250">
         <v>10000</v>
@@ -9609,10 +11886,10 @@
         <v>12</v>
       </c>
       <c r="B251" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C251" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D251">
         <v>10000</v>
@@ -9638,10 +11915,10 @@
         <v>12</v>
       </c>
       <c r="B252" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="C252" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D252">
         <v>10000</v>
@@ -9667,10 +11944,10 @@
         <v>12</v>
       </c>
       <c r="B253" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="C253" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D253">
         <v>10000</v>
@@ -9696,10 +11973,10 @@
         <v>12</v>
       </c>
       <c r="B254" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="C254" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D254">
         <v>10000</v>
@@ -9725,10 +12002,10 @@
         <v>12</v>
       </c>
       <c r="B255" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C255" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D255">
         <v>10000</v>
@@ -9754,10 +12031,10 @@
         <v>12</v>
       </c>
       <c r="B256" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C256" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D256">
         <v>10000</v>
@@ -9783,10 +12060,10 @@
         <v>12</v>
       </c>
       <c r="B257" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="C257" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D257">
         <v>10000</v>
@@ -9812,10 +12089,10 @@
         <v>12</v>
       </c>
       <c r="B258" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="C258" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D258">
         <v>10000</v>
@@ -9841,10 +12118,10 @@
         <v>12</v>
       </c>
       <c r="B259" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C259" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="D259">
         <v>10000</v>
@@ -9870,10 +12147,10 @@
         <v>12</v>
       </c>
       <c r="B260" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="C260" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="D260">
         <v>10000</v>
@@ -9899,10 +12176,10 @@
         <v>12</v>
       </c>
       <c r="B261" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="C261" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="D261">
         <v>10000</v>
@@ -9928,10 +12205,10 @@
         <v>12</v>
       </c>
       <c r="B262" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="C262" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D262">
         <v>10000</v>
@@ -9957,10 +12234,10 @@
         <v>12</v>
       </c>
       <c r="B263" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C263" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="D263">
         <v>10000</v>
@@ -9986,10 +12263,10 @@
         <v>12</v>
       </c>
       <c r="B264" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="C264" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D264">
         <v>10000</v>
@@ -9998,7 +12275,7 @@
         <v>10000</v>
       </c>
       <c r="F264">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G264">
         <v>10000000</v>
@@ -10015,10 +12292,10 @@
         <v>12</v>
       </c>
       <c r="B265" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C265" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="D265">
         <v>10000</v>
@@ -10027,7 +12304,7 @@
         <v>10000</v>
       </c>
       <c r="F265">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G265">
         <v>10000000</v>
@@ -10044,10 +12321,10 @@
         <v>12</v>
       </c>
       <c r="B266" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="C266" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D266">
         <v>10000</v>
@@ -10056,7 +12333,7 @@
         <v>10000</v>
       </c>
       <c r="F266">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G266">
         <v>10000000</v>
@@ -10073,10 +12350,10 @@
         <v>12</v>
       </c>
       <c r="B267" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="C267" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D267">
         <v>10000</v>
@@ -10085,7 +12362,7 @@
         <v>10000</v>
       </c>
       <c r="F267">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G267">
         <v>10000000</v>
@@ -10102,10 +12379,10 @@
         <v>12</v>
       </c>
       <c r="B268" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C268" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="D268">
         <v>10000</v>
@@ -10114,7 +12391,7 @@
         <v>10000</v>
       </c>
       <c r="F268">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G268">
         <v>10000000</v>
@@ -10131,10 +12408,10 @@
         <v>12</v>
       </c>
       <c r="B269" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C269" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D269">
         <v>10000</v>
@@ -10143,7 +12420,7 @@
         <v>10000</v>
       </c>
       <c r="F269">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G269">
         <v>10000000</v>
@@ -10160,10 +12437,10 @@
         <v>12</v>
       </c>
       <c r="B270" t="s">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="C270" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="D270">
         <v>10000</v>
@@ -10172,7 +12449,7 @@
         <v>10000</v>
       </c>
       <c r="F270">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G270">
         <v>10000000</v>
@@ -10189,10 +12466,10 @@
         <v>12</v>
       </c>
       <c r="B271" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="C271" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D271">
         <v>10000</v>
@@ -10201,7 +12478,7 @@
         <v>10000</v>
       </c>
       <c r="F271">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G271">
         <v>10000000</v>
@@ -10218,10 +12495,10 @@
         <v>12</v>
       </c>
       <c r="B272" t="s">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="C272" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D272">
         <v>10000</v>
@@ -10230,7 +12507,7 @@
         <v>10000</v>
       </c>
       <c r="F272">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G272">
         <v>10000000</v>
@@ -10247,10 +12524,10 @@
         <v>12</v>
       </c>
       <c r="B273" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="C273" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="D273">
         <v>10000</v>
@@ -10259,7 +12536,7 @@
         <v>10000</v>
       </c>
       <c r="F273">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G273">
         <v>10000000</v>
@@ -10276,10 +12553,10 @@
         <v>12</v>
       </c>
       <c r="B274" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="C274" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D274">
         <v>10000</v>
@@ -10288,7 +12565,7 @@
         <v>10000</v>
       </c>
       <c r="F274">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G274">
         <v>10000000</v>
@@ -10305,10 +12582,10 @@
         <v>12</v>
       </c>
       <c r="B275" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="C275" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="D275">
         <v>10000</v>
@@ -10317,7 +12594,7 @@
         <v>10000</v>
       </c>
       <c r="F275">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G275">
         <v>10000000</v>
@@ -10334,10 +12611,10 @@
         <v>12</v>
       </c>
       <c r="B276" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="C276" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="D276">
         <v>10000</v>
@@ -10346,7 +12623,7 @@
         <v>10000</v>
       </c>
       <c r="F276">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G276">
         <v>10000000</v>
@@ -10363,10 +12640,10 @@
         <v>12</v>
       </c>
       <c r="B277" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="C277" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="D277">
         <v>10000</v>
@@ -10375,7 +12652,7 @@
         <v>10000</v>
       </c>
       <c r="F277">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G277">
         <v>10000000</v>
@@ -10392,10 +12669,10 @@
         <v>12</v>
       </c>
       <c r="B278" t="s">
-        <v>20</v>
+        <v>96</v>
       </c>
       <c r="C278" t="s">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="D278">
         <v>10000</v>
@@ -10404,7 +12681,7 @@
         <v>10000</v>
       </c>
       <c r="F278">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G278">
         <v>10000000</v>
@@ -10421,10 +12698,10 @@
         <v>12</v>
       </c>
       <c r="B279" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="C279" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="D279">
         <v>10000</v>
@@ -10433,7 +12710,7 @@
         <v>10000</v>
       </c>
       <c r="F279">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G279">
         <v>10000000</v>
@@ -10450,10 +12727,10 @@
         <v>12</v>
       </c>
       <c r="B280" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="C280" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="D280">
         <v>10000</v>
@@ -10479,10 +12756,10 @@
         <v>12</v>
       </c>
       <c r="B281" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="C281" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="D281">
         <v>10000</v>
@@ -10500,528 +12777,6 @@
         <v>1000</v>
       </c>
       <c r="I281">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A282" t="s">
-        <v>12</v>
-      </c>
-      <c r="B282" t="s">
-        <v>81</v>
-      </c>
-      <c r="C282" t="s">
-        <v>74</v>
-      </c>
-      <c r="D282">
-        <v>10000</v>
-      </c>
-      <c r="E282">
-        <v>10000</v>
-      </c>
-      <c r="F282">
-        <v>100</v>
-      </c>
-      <c r="G282">
-        <v>10000000</v>
-      </c>
-      <c r="H282">
-        <v>1000</v>
-      </c>
-      <c r="I282">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A283" t="s">
-        <v>12</v>
-      </c>
-      <c r="B283" t="s">
-        <v>82</v>
-      </c>
-      <c r="C283" t="s">
-        <v>83</v>
-      </c>
-      <c r="D283">
-        <v>10000</v>
-      </c>
-      <c r="E283">
-        <v>10000</v>
-      </c>
-      <c r="F283">
-        <v>100</v>
-      </c>
-      <c r="G283">
-        <v>10000000</v>
-      </c>
-      <c r="H283">
-        <v>1000</v>
-      </c>
-      <c r="I283">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A284" t="s">
-        <v>12</v>
-      </c>
-      <c r="B284" t="s">
-        <v>84</v>
-      </c>
-      <c r="C284" t="s">
-        <v>60</v>
-      </c>
-      <c r="D284">
-        <v>10000</v>
-      </c>
-      <c r="E284">
-        <v>10000</v>
-      </c>
-      <c r="F284">
-        <v>100</v>
-      </c>
-      <c r="G284">
-        <v>10000000</v>
-      </c>
-      <c r="H284">
-        <v>1000</v>
-      </c>
-      <c r="I284">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A285" t="s">
-        <v>12</v>
-      </c>
-      <c r="B285" t="s">
-        <v>85</v>
-      </c>
-      <c r="C285" t="s">
-        <v>16</v>
-      </c>
-      <c r="D285">
-        <v>10000</v>
-      </c>
-      <c r="E285">
-        <v>10000</v>
-      </c>
-      <c r="F285">
-        <v>100</v>
-      </c>
-      <c r="G285">
-        <v>10000000</v>
-      </c>
-      <c r="H285">
-        <v>1000</v>
-      </c>
-      <c r="I285">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A286" t="s">
-        <v>12</v>
-      </c>
-      <c r="B286" t="s">
-        <v>86</v>
-      </c>
-      <c r="C286" t="s">
-        <v>68</v>
-      </c>
-      <c r="D286">
-        <v>10000</v>
-      </c>
-      <c r="E286">
-        <v>10000</v>
-      </c>
-      <c r="F286">
-        <v>100</v>
-      </c>
-      <c r="G286">
-        <v>10000000</v>
-      </c>
-      <c r="H286">
-        <v>1000</v>
-      </c>
-      <c r="I286">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A287" t="s">
-        <v>12</v>
-      </c>
-      <c r="B287" t="s">
-        <v>87</v>
-      </c>
-      <c r="C287" t="s">
-        <v>24</v>
-      </c>
-      <c r="D287">
-        <v>10000</v>
-      </c>
-      <c r="E287">
-        <v>10000</v>
-      </c>
-      <c r="F287">
-        <v>100</v>
-      </c>
-      <c r="G287">
-        <v>10000000</v>
-      </c>
-      <c r="H287">
-        <v>1000</v>
-      </c>
-      <c r="I287">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A288" t="s">
-        <v>12</v>
-      </c>
-      <c r="B288" t="s">
-        <v>88</v>
-      </c>
-      <c r="C288" t="s">
-        <v>62</v>
-      </c>
-      <c r="D288">
-        <v>10000</v>
-      </c>
-      <c r="E288">
-        <v>10000</v>
-      </c>
-      <c r="F288">
-        <v>100</v>
-      </c>
-      <c r="G288">
-        <v>10000000</v>
-      </c>
-      <c r="H288">
-        <v>1000</v>
-      </c>
-      <c r="I288">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A289" t="s">
-        <v>12</v>
-      </c>
-      <c r="B289" t="s">
-        <v>89</v>
-      </c>
-      <c r="C289" t="s">
-        <v>18</v>
-      </c>
-      <c r="D289">
-        <v>10000</v>
-      </c>
-      <c r="E289">
-        <v>10000</v>
-      </c>
-      <c r="F289">
-        <v>100</v>
-      </c>
-      <c r="G289">
-        <v>10000000</v>
-      </c>
-      <c r="H289">
-        <v>1000</v>
-      </c>
-      <c r="I289">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A290" t="s">
-        <v>12</v>
-      </c>
-      <c r="B290" t="s">
-        <v>90</v>
-      </c>
-      <c r="C290" t="s">
-        <v>20</v>
-      </c>
-      <c r="D290">
-        <v>10000</v>
-      </c>
-      <c r="E290">
-        <v>10000</v>
-      </c>
-      <c r="F290">
-        <v>100</v>
-      </c>
-      <c r="G290">
-        <v>10000000</v>
-      </c>
-      <c r="H290">
-        <v>1000</v>
-      </c>
-      <c r="I290">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A291" t="s">
-        <v>12</v>
-      </c>
-      <c r="B291" t="s">
-        <v>91</v>
-      </c>
-      <c r="C291" t="s">
-        <v>66</v>
-      </c>
-      <c r="D291">
-        <v>10000</v>
-      </c>
-      <c r="E291">
-        <v>10000</v>
-      </c>
-      <c r="F291">
-        <v>100</v>
-      </c>
-      <c r="G291">
-        <v>10000000</v>
-      </c>
-      <c r="H291">
-        <v>1000</v>
-      </c>
-      <c r="I291">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A292" t="s">
-        <v>12</v>
-      </c>
-      <c r="B292" t="s">
-        <v>92</v>
-      </c>
-      <c r="C292" t="s">
-        <v>59</v>
-      </c>
-      <c r="D292">
-        <v>10000</v>
-      </c>
-      <c r="E292">
-        <v>10000</v>
-      </c>
-      <c r="F292">
-        <v>100</v>
-      </c>
-      <c r="G292">
-        <v>10000000</v>
-      </c>
-      <c r="H292">
-        <v>1000</v>
-      </c>
-      <c r="I292">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A293" t="s">
-        <v>12</v>
-      </c>
-      <c r="B293" t="s">
-        <v>93</v>
-      </c>
-      <c r="C293" t="s">
-        <v>67</v>
-      </c>
-      <c r="D293">
-        <v>10000</v>
-      </c>
-      <c r="E293">
-        <v>10000</v>
-      </c>
-      <c r="F293">
-        <v>100</v>
-      </c>
-      <c r="G293">
-        <v>10000000</v>
-      </c>
-      <c r="H293">
-        <v>1000</v>
-      </c>
-      <c r="I293">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A294" t="s">
-        <v>12</v>
-      </c>
-      <c r="B294" t="s">
-        <v>94</v>
-      </c>
-      <c r="C294" t="s">
-        <v>65</v>
-      </c>
-      <c r="D294">
-        <v>10000</v>
-      </c>
-      <c r="E294">
-        <v>10000</v>
-      </c>
-      <c r="F294">
-        <v>100</v>
-      </c>
-      <c r="G294">
-        <v>10000000</v>
-      </c>
-      <c r="H294">
-        <v>1000</v>
-      </c>
-      <c r="I294">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A295" t="s">
-        <v>12</v>
-      </c>
-      <c r="B295" t="s">
-        <v>95</v>
-      </c>
-      <c r="C295" t="s">
-        <v>64</v>
-      </c>
-      <c r="D295">
-        <v>10000</v>
-      </c>
-      <c r="E295">
-        <v>10000</v>
-      </c>
-      <c r="F295">
-        <v>100</v>
-      </c>
-      <c r="G295">
-        <v>10000000</v>
-      </c>
-      <c r="H295">
-        <v>1000</v>
-      </c>
-      <c r="I295">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A296" t="s">
-        <v>12</v>
-      </c>
-      <c r="B296" t="s">
-        <v>96</v>
-      </c>
-      <c r="C296" t="s">
-        <v>36</v>
-      </c>
-      <c r="D296">
-        <v>10000</v>
-      </c>
-      <c r="E296">
-        <v>10000</v>
-      </c>
-      <c r="F296">
-        <v>100</v>
-      </c>
-      <c r="G296">
-        <v>10000000</v>
-      </c>
-      <c r="H296">
-        <v>1000</v>
-      </c>
-      <c r="I296">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A297" t="s">
-        <v>12</v>
-      </c>
-      <c r="B297" t="s">
-        <v>97</v>
-      </c>
-      <c r="C297" t="s">
-        <v>34</v>
-      </c>
-      <c r="D297">
-        <v>10000</v>
-      </c>
-      <c r="E297">
-        <v>10000</v>
-      </c>
-      <c r="F297">
-        <v>100</v>
-      </c>
-      <c r="G297">
-        <v>10000000</v>
-      </c>
-      <c r="H297">
-        <v>1000</v>
-      </c>
-      <c r="I297">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A298" t="s">
-        <v>12</v>
-      </c>
-      <c r="B298" t="s">
-        <v>53</v>
-      </c>
-      <c r="C298" t="s">
-        <v>75</v>
-      </c>
-      <c r="D298">
-        <v>10000</v>
-      </c>
-      <c r="E298">
-        <v>10000</v>
-      </c>
-      <c r="F298">
-        <v>1</v>
-      </c>
-      <c r="G298">
-        <v>10000000</v>
-      </c>
-      <c r="H298">
-        <v>1000</v>
-      </c>
-      <c r="I298">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A299" t="s">
-        <v>12</v>
-      </c>
-      <c r="B299" t="s">
-        <v>75</v>
-      </c>
-      <c r="C299" t="s">
-        <v>30</v>
-      </c>
-      <c r="D299">
-        <v>10000</v>
-      </c>
-      <c r="E299">
-        <v>10000</v>
-      </c>
-      <c r="F299">
-        <v>1</v>
-      </c>
-      <c r="G299">
-        <v>10000000</v>
-      </c>
-      <c r="H299">
-        <v>1000</v>
-      </c>
-      <c r="I299">
         <v>1</v>
       </c>
     </row>
@@ -11031,7 +12786,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68B577B-1347-43AB-A697-F4519763B965}">
   <dimension ref="A1:C166"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
+++ b/01_data/01_input_data/02_processed/Data_update_methane_LNG_test.xlsx
@@ -8,17 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\01_input_data\02_processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30517978-7F32-4007-8902-0E1155DB3DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFCE738F-3301-40E6-BB8D-6603DFF94A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{C00DA6F8-F36F-4C24-9869-33AD338893F6}"/>
   </bookViews>
   <sheets>
     <sheet name="Nodes" sheetId="1" r:id="rId1"/>
     <sheet name="Commodities" sheetId="2" r:id="rId2"/>
     <sheet name="Edges" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId4"/>
-    <sheet name="Parameters" sheetId="4" r:id="rId5"/>
-    <sheet name="Supply" sheetId="5" r:id="rId6"/>
+    <sheet name="Parameters" sheetId="4" r:id="rId4"/>
+    <sheet name="Supply" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1872" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1548" uniqueCount="98">
   <si>
     <t>Commodities</t>
   </si>
@@ -335,300 +334,6 @@
   </si>
   <si>
     <t>ES_Prod</t>
-  </si>
-  <si>
-    <t>UKBE</t>
-  </si>
-  <si>
-    <t>UKIE</t>
-  </si>
-  <si>
-    <t>BEUK</t>
-  </si>
-  <si>
-    <t>BENL</t>
-  </si>
-  <si>
-    <t>BEDE</t>
-  </si>
-  <si>
-    <t>BEFR</t>
-  </si>
-  <si>
-    <t>NLBE</t>
-  </si>
-  <si>
-    <t>NLDE</t>
-  </si>
-  <si>
-    <t>DEBE</t>
-  </si>
-  <si>
-    <t>DENL</t>
-  </si>
-  <si>
-    <t>DEAT</t>
-  </si>
-  <si>
-    <t>DECH</t>
-  </si>
-  <si>
-    <t>DEFR</t>
-  </si>
-  <si>
-    <t>DEDK</t>
-  </si>
-  <si>
-    <t>DEPL</t>
-  </si>
-  <si>
-    <t>DECZ</t>
-  </si>
-  <si>
-    <t>DELU</t>
-  </si>
-  <si>
-    <t>ATDE</t>
-  </si>
-  <si>
-    <t>ATIT</t>
-  </si>
-  <si>
-    <t>ATSI</t>
-  </si>
-  <si>
-    <t>ATSK</t>
-  </si>
-  <si>
-    <t>ATHU</t>
-  </si>
-  <si>
-    <t>ITAT</t>
-  </si>
-  <si>
-    <t>ITCH</t>
-  </si>
-  <si>
-    <t>ITSI</t>
-  </si>
-  <si>
-    <t>CHDE</t>
-  </si>
-  <si>
-    <t>CHIT</t>
-  </si>
-  <si>
-    <t>CHFR</t>
-  </si>
-  <si>
-    <t>SIIT</t>
-  </si>
-  <si>
-    <t>SIHR</t>
-  </si>
-  <si>
-    <t>HRSI</t>
-  </si>
-  <si>
-    <t>HRHU</t>
-  </si>
-  <si>
-    <t>FRBE</t>
-  </si>
-  <si>
-    <t>FRCH</t>
-  </si>
-  <si>
-    <t>FRES</t>
-  </si>
-  <si>
-    <t>DKDE</t>
-  </si>
-  <si>
-    <t>PLDE</t>
-  </si>
-  <si>
-    <t>CZDE</t>
-  </si>
-  <si>
-    <t>CZPL</t>
-  </si>
-  <si>
-    <t>CZSK</t>
-  </si>
-  <si>
-    <t>SKAT</t>
-  </si>
-  <si>
-    <t>SKCZ</t>
-  </si>
-  <si>
-    <t>SKHU</t>
-  </si>
-  <si>
-    <t>SKUA</t>
-  </si>
-  <si>
-    <t>HUHR</t>
-  </si>
-  <si>
-    <t>HUSK</t>
-  </si>
-  <si>
-    <t>HURS</t>
-  </si>
-  <si>
-    <t>HURO</t>
-  </si>
-  <si>
-    <t>RSBG</t>
-  </si>
-  <si>
-    <t>RSBA</t>
-  </si>
-  <si>
-    <t>BGRS</t>
-  </si>
-  <si>
-    <t>BGGR</t>
-  </si>
-  <si>
-    <t>BGRO</t>
-  </si>
-  <si>
-    <t>BGMK</t>
-  </si>
-  <si>
-    <t>BGTR</t>
-  </si>
-  <si>
-    <t>GRBG</t>
-  </si>
-  <si>
-    <t>ROHU</t>
-  </si>
-  <si>
-    <t>ROBG</t>
-  </si>
-  <si>
-    <t>ROUA</t>
-  </si>
-  <si>
-    <t>ROMD</t>
-  </si>
-  <si>
-    <t>LTLV</t>
-  </si>
-  <si>
-    <t>LTRU</t>
-  </si>
-  <si>
-    <t>LVLT</t>
-  </si>
-  <si>
-    <t>LVRU</t>
-  </si>
-  <si>
-    <t>ESFR</t>
-  </si>
-  <si>
-    <t>ESPT</t>
-  </si>
-  <si>
-    <t>PTES</t>
-  </si>
-  <si>
-    <t>UAPL</t>
-  </si>
-  <si>
-    <t>UASK</t>
-  </si>
-  <si>
-    <t>UAHU</t>
-  </si>
-  <si>
-    <t>UARO</t>
-  </si>
-  <si>
-    <t>MDRO</t>
-  </si>
-  <si>
-    <t>RUDE</t>
-  </si>
-  <si>
-    <t>RULV</t>
-  </si>
-  <si>
-    <t>RUFI</t>
-  </si>
-  <si>
-    <t>ALIT</t>
-  </si>
-  <si>
-    <t>TRBG</t>
-  </si>
-  <si>
-    <t>TRGR</t>
-  </si>
-  <si>
-    <t>MAES</t>
-  </si>
-  <si>
-    <t>TNIT</t>
-  </si>
-  <si>
-    <t>LYIT</t>
-  </si>
-  <si>
-    <t>BYPL</t>
-  </si>
-  <si>
-    <t>BYLT</t>
-  </si>
-  <si>
-    <t>RUUA</t>
-  </si>
-  <si>
-    <t>AZTR</t>
-  </si>
-  <si>
-    <t>RSHU</t>
-  </si>
-  <si>
-    <t>DZES</t>
-  </si>
-  <si>
-    <t>NODE</t>
-  </si>
-  <si>
-    <t>NONL</t>
-  </si>
-  <si>
-    <t>NOBE</t>
-  </si>
-  <si>
-    <t>NOFR</t>
-  </si>
-  <si>
-    <t>NOUK</t>
-  </si>
-  <si>
-    <t>UKNL</t>
-  </si>
-  <si>
-    <t>GRAL</t>
-  </si>
-  <si>
-    <t>DZMA</t>
-  </si>
-  <si>
-    <t>DZTN</t>
-  </si>
-  <si>
-    <t>DKSE</t>
-  </si>
-  <si>
-    <t>RUBY</t>
   </si>
 </sst>
 </file>
@@ -2565,2068 +2270,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E70C3ED-3ED5-4BEB-AFBD-5D4B07BA3767}">
-  <dimension ref="A1:I108"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" t="str">
-        <f>_xlfn.TEXTJOIN(,TRUE,A1,B1)</f>
-        <v>UKBE</v>
-      </c>
-      <c r="E1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F1" t="b">
-        <f>EXACT(C1,E1)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" t="str">
-        <f t="shared" ref="C2:C65" si="0">_xlfn.TEXTJOIN(,TRUE,A2,B2)</f>
-        <v>UKIE</v>
-      </c>
-      <c r="E2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F2" t="b">
-        <f t="shared" ref="F2:F65" si="1">EXACT(C2,E2)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" t="str">
-        <f t="shared" si="0"/>
-        <v>BEUK</v>
-      </c>
-      <c r="E3" t="s">
-        <v>100</v>
-      </c>
-      <c r="F3" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" t="str">
-        <f t="shared" si="0"/>
-        <v>BENL</v>
-      </c>
-      <c r="E4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F4" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" t="str">
-        <f t="shared" si="0"/>
-        <v>BEDE</v>
-      </c>
-      <c r="E5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" t="str">
-        <f t="shared" si="0"/>
-        <v>BEFR</v>
-      </c>
-      <c r="E6" t="s">
-        <v>103</v>
-      </c>
-      <c r="F6" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="str">
-        <f t="shared" si="0"/>
-        <v>NLBE</v>
-      </c>
-      <c r="E7" t="s">
-        <v>104</v>
-      </c>
-      <c r="F7" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" t="str">
-        <f t="shared" si="0"/>
-        <v>NLDE</v>
-      </c>
-      <c r="E8" t="s">
-        <v>105</v>
-      </c>
-      <c r="F8" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="str">
-        <f t="shared" si="0"/>
-        <v>DEBE</v>
-      </c>
-      <c r="E9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F9" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="str">
-        <f t="shared" si="0"/>
-        <v>DENL</v>
-      </c>
-      <c r="E10" t="s">
-        <v>107</v>
-      </c>
-      <c r="F10" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" t="str">
-        <f t="shared" si="0"/>
-        <v>DEAT</v>
-      </c>
-      <c r="E11" t="s">
-        <v>108</v>
-      </c>
-      <c r="F11" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" t="str">
-        <f t="shared" si="0"/>
-        <v>DECH</v>
-      </c>
-      <c r="E12" t="s">
-        <v>109</v>
-      </c>
-      <c r="F12" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" t="str">
-        <f t="shared" si="0"/>
-        <v>DEFR</v>
-      </c>
-      <c r="E13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F13" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" t="str">
-        <f t="shared" si="0"/>
-        <v>DEDK</v>
-      </c>
-      <c r="E14" t="s">
-        <v>111</v>
-      </c>
-      <c r="F14" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" t="str">
-        <f t="shared" si="0"/>
-        <v>DEPL</v>
-      </c>
-      <c r="E15" t="s">
-        <v>112</v>
-      </c>
-      <c r="F15" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" t="str">
-        <f t="shared" si="0"/>
-        <v>DECZ</v>
-      </c>
-      <c r="E16" t="s">
-        <v>113</v>
-      </c>
-      <c r="F16" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" t="str">
-        <f t="shared" si="0"/>
-        <v>DELU</v>
-      </c>
-      <c r="E17" t="s">
-        <v>114</v>
-      </c>
-      <c r="F17" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>60</v>
-      </c>
-      <c r="B18" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" t="str">
-        <f t="shared" si="0"/>
-        <v>ATDE</v>
-      </c>
-      <c r="E18" t="s">
-        <v>115</v>
-      </c>
-      <c r="F18" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" t="str">
-        <f t="shared" si="0"/>
-        <v>ATIT</v>
-      </c>
-      <c r="E19" t="s">
-        <v>116</v>
-      </c>
-      <c r="F19" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>60</v>
-      </c>
-      <c r="B20" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" t="str">
-        <f t="shared" si="0"/>
-        <v>ATSI</v>
-      </c>
-      <c r="E20" t="s">
-        <v>117</v>
-      </c>
-      <c r="F20" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" t="str">
-        <f t="shared" si="0"/>
-        <v>ATSK</v>
-      </c>
-      <c r="E21" t="s">
-        <v>118</v>
-      </c>
-      <c r="F21" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>60</v>
-      </c>
-      <c r="B22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" t="str">
-        <f t="shared" si="0"/>
-        <v>ATHU</v>
-      </c>
-      <c r="E22" t="s">
-        <v>119</v>
-      </c>
-      <c r="F22" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>60</v>
-      </c>
-      <c r="C23" t="str">
-        <f t="shared" si="0"/>
-        <v>ITAT</v>
-      </c>
-      <c r="E23" t="s">
-        <v>120</v>
-      </c>
-      <c r="F23" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" t="s">
-        <v>61</v>
-      </c>
-      <c r="C24" t="str">
-        <f t="shared" si="0"/>
-        <v>ITCH</v>
-      </c>
-      <c r="E24" t="s">
-        <v>121</v>
-      </c>
-      <c r="F24" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" t="str">
-        <f t="shared" si="0"/>
-        <v>ITSI</v>
-      </c>
-      <c r="E25" t="s">
-        <v>122</v>
-      </c>
-      <c r="F25" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>61</v>
-      </c>
-      <c r="B26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C26" t="str">
-        <f t="shared" si="0"/>
-        <v>CHDE</v>
-      </c>
-      <c r="E26" t="s">
-        <v>123</v>
-      </c>
-      <c r="F26" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" t="str">
-        <f t="shared" si="0"/>
-        <v>CHIT</v>
-      </c>
-      <c r="E27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F27" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>61</v>
-      </c>
-      <c r="B28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" t="str">
-        <f t="shared" si="0"/>
-        <v>CHFR</v>
-      </c>
-      <c r="E28" t="s">
-        <v>125</v>
-      </c>
-      <c r="F28" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>64</v>
-      </c>
-      <c r="B29" t="s">
-        <v>22</v>
-      </c>
-      <c r="C29" t="str">
-        <f t="shared" si="0"/>
-        <v>SIIT</v>
-      </c>
-      <c r="E29" t="s">
-        <v>126</v>
-      </c>
-      <c r="F29" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" t="s">
-        <v>24</v>
-      </c>
-      <c r="C30" t="str">
-        <f t="shared" si="0"/>
-        <v>SIHR</v>
-      </c>
-      <c r="E30" t="s">
-        <v>127</v>
-      </c>
-      <c r="F30" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" t="str">
-        <f t="shared" si="0"/>
-        <v>HRSI</v>
-      </c>
-      <c r="E31" t="s">
-        <v>128</v>
-      </c>
-      <c r="F31" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>24</v>
-      </c>
-      <c r="B32" t="s">
-        <v>66</v>
-      </c>
-      <c r="C32" t="str">
-        <f t="shared" si="0"/>
-        <v>HRHU</v>
-      </c>
-      <c r="E32" t="s">
-        <v>129</v>
-      </c>
-      <c r="F32" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>18</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="str">
-        <f t="shared" si="0"/>
-        <v>FRBE</v>
-      </c>
-      <c r="E33" t="s">
-        <v>130</v>
-      </c>
-      <c r="F33" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>18</v>
-      </c>
-      <c r="B34" t="s">
-        <v>61</v>
-      </c>
-      <c r="C34" t="str">
-        <f t="shared" si="0"/>
-        <v>FRCH</v>
-      </c>
-      <c r="E34" t="s">
-        <v>131</v>
-      </c>
-      <c r="F34" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>18</v>
-      </c>
-      <c r="B35" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" t="str">
-        <f t="shared" si="0"/>
-        <v>FRES</v>
-      </c>
-      <c r="E35" t="s">
-        <v>132</v>
-      </c>
-      <c r="F35" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" t="s">
-        <v>42</v>
-      </c>
-      <c r="C36" t="str">
-        <f t="shared" si="0"/>
-        <v>DKDE</v>
-      </c>
-      <c r="E36" t="s">
-        <v>133</v>
-      </c>
-      <c r="F36" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B37" t="s">
-        <v>42</v>
-      </c>
-      <c r="C37" t="str">
-        <f t="shared" si="0"/>
-        <v>PLDE</v>
-      </c>
-      <c r="E37" t="s">
-        <v>134</v>
-      </c>
-      <c r="F37" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>62</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" t="str">
-        <f t="shared" si="0"/>
-        <v>CZDE</v>
-      </c>
-      <c r="E38" t="s">
-        <v>135</v>
-      </c>
-      <c r="F38" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>62</v>
-      </c>
-      <c r="B39" t="s">
-        <v>30</v>
-      </c>
-      <c r="C39" t="str">
-        <f t="shared" si="0"/>
-        <v>CZPL</v>
-      </c>
-      <c r="E39" t="s">
-        <v>136</v>
-      </c>
-      <c r="F39" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>62</v>
-      </c>
-      <c r="B40" t="s">
-        <v>65</v>
-      </c>
-      <c r="C40" t="str">
-        <f t="shared" si="0"/>
-        <v>CZSK</v>
-      </c>
-      <c r="E40" t="s">
-        <v>137</v>
-      </c>
-      <c r="F40" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>65</v>
-      </c>
-      <c r="B41" t="s">
-        <v>60</v>
-      </c>
-      <c r="C41" t="str">
-        <f t="shared" si="0"/>
-        <v>SKAT</v>
-      </c>
-      <c r="E41" t="s">
-        <v>138</v>
-      </c>
-      <c r="F41" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>65</v>
-      </c>
-      <c r="B42" t="s">
-        <v>62</v>
-      </c>
-      <c r="C42" t="str">
-        <f t="shared" si="0"/>
-        <v>SKCZ</v>
-      </c>
-      <c r="E42" t="s">
-        <v>139</v>
-      </c>
-      <c r="F42" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43" t="s">
-        <v>66</v>
-      </c>
-      <c r="C43" t="str">
-        <f t="shared" si="0"/>
-        <v>SKHU</v>
-      </c>
-      <c r="E43" t="s">
-        <v>140</v>
-      </c>
-      <c r="F43" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>65</v>
-      </c>
-      <c r="B44" t="s">
-        <v>58</v>
-      </c>
-      <c r="C44" t="str">
-        <f t="shared" si="0"/>
-        <v>SKUA</v>
-      </c>
-      <c r="E44" t="s">
-        <v>141</v>
-      </c>
-      <c r="F44" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>66</v>
-      </c>
-      <c r="B45" t="s">
-        <v>24</v>
-      </c>
-      <c r="C45" t="str">
-        <f t="shared" si="0"/>
-        <v>HUHR</v>
-      </c>
-      <c r="E45" t="s">
-        <v>142</v>
-      </c>
-      <c r="F45" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>66</v>
-      </c>
-      <c r="B46" t="s">
-        <v>65</v>
-      </c>
-      <c r="C46" t="str">
-        <f t="shared" si="0"/>
-        <v>HUSK</v>
-      </c>
-      <c r="E46" t="s">
-        <v>143</v>
-      </c>
-      <c r="F46" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>66</v>
-      </c>
-      <c r="B47" t="s">
-        <v>67</v>
-      </c>
-      <c r="C47" t="str">
-        <f t="shared" si="0"/>
-        <v>HURS</v>
-      </c>
-      <c r="E47" t="s">
-        <v>144</v>
-      </c>
-      <c r="F47" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>66</v>
-      </c>
-      <c r="B48" t="s">
-        <v>51</v>
-      </c>
-      <c r="C48" t="str">
-        <f t="shared" si="0"/>
-        <v>HURO</v>
-      </c>
-      <c r="E48" t="s">
-        <v>145</v>
-      </c>
-      <c r="F48" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>67</v>
-      </c>
-      <c r="B49" t="s">
-        <v>68</v>
-      </c>
-      <c r="C49" t="str">
-        <f t="shared" si="0"/>
-        <v>RSBG</v>
-      </c>
-      <c r="E49" t="s">
-        <v>146</v>
-      </c>
-      <c r="F49" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>67</v>
-      </c>
-      <c r="B50" t="s">
-        <v>69</v>
-      </c>
-      <c r="C50" t="str">
-        <f t="shared" si="0"/>
-        <v>RSBA</v>
-      </c>
-      <c r="E50" t="s">
-        <v>147</v>
-      </c>
-      <c r="F50" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>68</v>
-      </c>
-      <c r="B51" t="s">
-        <v>67</v>
-      </c>
-      <c r="C51" t="str">
-        <f t="shared" si="0"/>
-        <v>BGRS</v>
-      </c>
-      <c r="E51" t="s">
-        <v>148</v>
-      </c>
-      <c r="F51" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>68</v>
-      </c>
-      <c r="B52" t="s">
-        <v>20</v>
-      </c>
-      <c r="C52" t="str">
-        <f t="shared" si="0"/>
-        <v>BGGR</v>
-      </c>
-      <c r="E52" t="s">
-        <v>149</v>
-      </c>
-      <c r="F52" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>68</v>
-      </c>
-      <c r="B53" t="s">
-        <v>51</v>
-      </c>
-      <c r="C53" t="str">
-        <f t="shared" si="0"/>
-        <v>BGRO</v>
-      </c>
-      <c r="E53" t="s">
-        <v>150</v>
-      </c>
-      <c r="F53" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>68</v>
-      </c>
-      <c r="B54" t="s">
-        <v>70</v>
-      </c>
-      <c r="C54" t="str">
-        <f t="shared" si="0"/>
-        <v>BGMK</v>
-      </c>
-      <c r="E54" t="s">
-        <v>151</v>
-      </c>
-      <c r="F54" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>68</v>
-      </c>
-      <c r="B55" t="s">
-        <v>36</v>
-      </c>
-      <c r="C55" t="str">
-        <f t="shared" si="0"/>
-        <v>BGTR</v>
-      </c>
-      <c r="E55" t="s">
-        <v>152</v>
-      </c>
-      <c r="F55" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>20</v>
-      </c>
-      <c r="B56" t="s">
-        <v>68</v>
-      </c>
-      <c r="C56" t="str">
-        <f t="shared" si="0"/>
-        <v>GRBG</v>
-      </c>
-      <c r="E56" t="s">
-        <v>153</v>
-      </c>
-      <c r="F56" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>51</v>
-      </c>
-      <c r="B57" t="s">
-        <v>66</v>
-      </c>
-      <c r="C57" t="str">
-        <f t="shared" si="0"/>
-        <v>ROHU</v>
-      </c>
-      <c r="E57" t="s">
-        <v>154</v>
-      </c>
-      <c r="F57" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>51</v>
-      </c>
-      <c r="B58" t="s">
-        <v>68</v>
-      </c>
-      <c r="C58" t="str">
-        <f t="shared" si="0"/>
-        <v>ROBG</v>
-      </c>
-      <c r="E58" t="s">
-        <v>155</v>
-      </c>
-      <c r="F58" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>51</v>
-      </c>
-      <c r="B59" t="s">
-        <v>58</v>
-      </c>
-      <c r="C59" t="str">
-        <f t="shared" si="0"/>
-        <v>ROUA</v>
-      </c>
-      <c r="E59" t="s">
-        <v>156</v>
-      </c>
-      <c r="F59" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>51</v>
-      </c>
-      <c r="B60" t="s">
-        <v>71</v>
-      </c>
-      <c r="C60" t="str">
-        <f t="shared" si="0"/>
-        <v>ROMD</v>
-      </c>
-      <c r="E60" t="s">
-        <v>157</v>
-      </c>
-      <c r="F60" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>26</v>
-      </c>
-      <c r="B61" t="s">
-        <v>72</v>
-      </c>
-      <c r="C61" t="str">
-        <f t="shared" si="0"/>
-        <v>LTLV</v>
-      </c>
-      <c r="E61" t="s">
-        <v>158</v>
-      </c>
-      <c r="F61" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>26</v>
-      </c>
-      <c r="B62" t="s">
-        <v>53</v>
-      </c>
-      <c r="C62" t="str">
-        <f t="shared" si="0"/>
-        <v>LTRU</v>
-      </c>
-      <c r="E62" t="s">
-        <v>159</v>
-      </c>
-      <c r="F62" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>72</v>
-      </c>
-      <c r="B63" t="s">
-        <v>26</v>
-      </c>
-      <c r="C63" t="str">
-        <f t="shared" si="0"/>
-        <v>LVLT</v>
-      </c>
-      <c r="E63" t="s">
-        <v>160</v>
-      </c>
-      <c r="F63" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>72</v>
-      </c>
-      <c r="B64" t="s">
-        <v>53</v>
-      </c>
-      <c r="C64" t="str">
-        <f t="shared" si="0"/>
-        <v>LVRU</v>
-      </c>
-      <c r="E64" t="s">
-        <v>161</v>
-      </c>
-      <c r="F64" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>34</v>
-      </c>
-      <c r="B65" t="s">
-        <v>18</v>
-      </c>
-      <c r="C65" t="str">
-        <f t="shared" si="0"/>
-        <v>ESFR</v>
-      </c>
-      <c r="E65" t="s">
-        <v>162</v>
-      </c>
-      <c r="F65" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>34</v>
-      </c>
-      <c r="B66" t="s">
-        <v>32</v>
-      </c>
-      <c r="C66" t="str">
-        <f t="shared" ref="C66:C108" si="2">_xlfn.TEXTJOIN(,TRUE,A66,B66)</f>
-        <v>ESPT</v>
-      </c>
-      <c r="E66" t="s">
-        <v>163</v>
-      </c>
-      <c r="F66" t="b">
-        <f t="shared" ref="F66:F108" si="3">EXACT(C66,E66)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>32</v>
-      </c>
-      <c r="B67" t="s">
-        <v>34</v>
-      </c>
-      <c r="C67" t="str">
-        <f t="shared" si="2"/>
-        <v>PTES</v>
-      </c>
-      <c r="E67" t="s">
-        <v>164</v>
-      </c>
-      <c r="F67" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>58</v>
-      </c>
-      <c r="B68" t="s">
-        <v>30</v>
-      </c>
-      <c r="C68" t="str">
-        <f t="shared" si="2"/>
-        <v>UAPL</v>
-      </c>
-      <c r="E68" t="s">
-        <v>165</v>
-      </c>
-      <c r="F68" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>58</v>
-      </c>
-      <c r="B69" t="s">
-        <v>65</v>
-      </c>
-      <c r="C69" t="str">
-        <f t="shared" si="2"/>
-        <v>UASK</v>
-      </c>
-      <c r="E69" t="s">
-        <v>166</v>
-      </c>
-      <c r="F69" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>58</v>
-      </c>
-      <c r="B70" t="s">
-        <v>66</v>
-      </c>
-      <c r="C70" t="str">
-        <f t="shared" si="2"/>
-        <v>UAHU</v>
-      </c>
-      <c r="E70" t="s">
-        <v>167</v>
-      </c>
-      <c r="F70" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A71" t="s">
-        <v>58</v>
-      </c>
-      <c r="B71" t="s">
-        <v>51</v>
-      </c>
-      <c r="C71" t="str">
-        <f t="shared" si="2"/>
-        <v>UARO</v>
-      </c>
-      <c r="E71" t="s">
-        <v>168</v>
-      </c>
-      <c r="F71" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A72" t="s">
-        <v>71</v>
-      </c>
-      <c r="B72" t="s">
-        <v>51</v>
-      </c>
-      <c r="C72" t="str">
-        <f t="shared" si="2"/>
-        <v>MDRO</v>
-      </c>
-      <c r="E72" t="s">
-        <v>169</v>
-      </c>
-      <c r="F72" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A73" t="s">
-        <v>53</v>
-      </c>
-      <c r="B73" t="s">
-        <v>42</v>
-      </c>
-      <c r="C73" t="str">
-        <f t="shared" si="2"/>
-        <v>RUDE</v>
-      </c>
-      <c r="E73" t="s">
-        <v>170</v>
-      </c>
-      <c r="F73" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
-        <v>53</v>
-      </c>
-      <c r="B74" t="s">
-        <v>72</v>
-      </c>
-      <c r="C74" t="str">
-        <f t="shared" si="2"/>
-        <v>RULV</v>
-      </c>
-      <c r="E74" t="s">
-        <v>171</v>
-      </c>
-      <c r="F74" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
-        <v>53</v>
-      </c>
-      <c r="B75" t="s">
-        <v>73</v>
-      </c>
-      <c r="C75" t="str">
-        <f t="shared" si="2"/>
-        <v>RUFI</v>
-      </c>
-      <c r="E75" t="s">
-        <v>172</v>
-      </c>
-      <c r="F75" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A76" t="s">
-        <v>74</v>
-      </c>
-      <c r="B76" t="s">
-        <v>22</v>
-      </c>
-      <c r="C76" t="str">
-        <f t="shared" si="2"/>
-        <v>ALIT</v>
-      </c>
-      <c r="E76" t="s">
-        <v>173</v>
-      </c>
-      <c r="F76" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A77" t="s">
-        <v>36</v>
-      </c>
-      <c r="B77" t="s">
-        <v>68</v>
-      </c>
-      <c r="C77" t="str">
-        <f t="shared" si="2"/>
-        <v>TRBG</v>
-      </c>
-      <c r="E77" t="s">
-        <v>174</v>
-      </c>
-      <c r="F77" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A78" t="s">
-        <v>36</v>
-      </c>
-      <c r="B78" t="s">
-        <v>20</v>
-      </c>
-      <c r="C78" t="str">
-        <f t="shared" si="2"/>
-        <v>TRGR</v>
-      </c>
-      <c r="E78" t="s">
-        <v>175</v>
-      </c>
-      <c r="F78" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" t="s">
-        <v>78</v>
-      </c>
-      <c r="B79" t="s">
-        <v>34</v>
-      </c>
-      <c r="C79" t="str">
-        <f t="shared" si="2"/>
-        <v>MAES</v>
-      </c>
-      <c r="E79" t="s">
-        <v>176</v>
-      </c>
-      <c r="F79" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A80" t="s">
-        <v>55</v>
-      </c>
-      <c r="B80" t="s">
-        <v>22</v>
-      </c>
-      <c r="C80" t="str">
-        <f t="shared" si="2"/>
-        <v>TNIT</v>
-      </c>
-      <c r="E80" t="s">
-        <v>177</v>
-      </c>
-      <c r="F80" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
-        <v>45</v>
-      </c>
-      <c r="B81" t="s">
-        <v>22</v>
-      </c>
-      <c r="C81" t="str">
-        <f t="shared" si="2"/>
-        <v>LYIT</v>
-      </c>
-      <c r="E81" t="s">
-        <v>178</v>
-      </c>
-      <c r="F81" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
-        <v>75</v>
-      </c>
-      <c r="B82" t="s">
-        <v>30</v>
-      </c>
-      <c r="C82" t="str">
-        <f t="shared" si="2"/>
-        <v>BYPL</v>
-      </c>
-      <c r="E82" t="s">
-        <v>179</v>
-      </c>
-      <c r="F82" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
-        <v>75</v>
-      </c>
-      <c r="B83" t="s">
-        <v>26</v>
-      </c>
-      <c r="C83" t="str">
-        <f t="shared" si="2"/>
-        <v>BYLT</v>
-      </c>
-      <c r="E83" t="s">
-        <v>180</v>
-      </c>
-      <c r="F83" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
-        <v>53</v>
-      </c>
-      <c r="B84" t="s">
-        <v>58</v>
-      </c>
-      <c r="C84" t="str">
-        <f t="shared" si="2"/>
-        <v>RUUA</v>
-      </c>
-      <c r="E84" t="s">
-        <v>181</v>
-      </c>
-      <c r="F84" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
-        <v>76</v>
-      </c>
-      <c r="B85" t="s">
-        <v>36</v>
-      </c>
-      <c r="C85" t="str">
-        <f t="shared" si="2"/>
-        <v>AZTR</v>
-      </c>
-      <c r="E85" t="s">
-        <v>182</v>
-      </c>
-      <c r="F85" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>58</v>
-      </c>
-      <c r="B86" t="s">
-        <v>30</v>
-      </c>
-      <c r="C86" t="str">
-        <f t="shared" si="2"/>
-        <v>UAPL</v>
-      </c>
-      <c r="F86" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I86" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>58</v>
-      </c>
-      <c r="B87" t="s">
-        <v>65</v>
-      </c>
-      <c r="C87" t="str">
-        <f t="shared" si="2"/>
-        <v>UASK</v>
-      </c>
-      <c r="F87" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I87" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>58</v>
-      </c>
-      <c r="B88" t="s">
-        <v>66</v>
-      </c>
-      <c r="C88" t="str">
-        <f t="shared" si="2"/>
-        <v>UAHU</v>
-      </c>
-      <c r="F88" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I88" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>67</v>
-      </c>
-      <c r="B89" t="s">
-        <v>66</v>
-      </c>
-      <c r="C89" t="str">
-        <f t="shared" si="2"/>
-        <v>RSHU</v>
-      </c>
-      <c r="E89" t="s">
-        <v>183</v>
-      </c>
-      <c r="F89" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="I89" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>68</v>
-      </c>
-      <c r="B90" t="s">
-        <v>67</v>
-      </c>
-      <c r="C90" t="str">
-        <f t="shared" si="2"/>
-        <v>BGRS</v>
-      </c>
-      <c r="F90" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I90" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>36</v>
-      </c>
-      <c r="B91" t="s">
-        <v>68</v>
-      </c>
-      <c r="C91" t="str">
-        <f t="shared" si="2"/>
-        <v>TRBG</v>
-      </c>
-      <c r="F91" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I91" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>53</v>
-      </c>
-      <c r="B92" t="s">
-        <v>72</v>
-      </c>
-      <c r="C92" t="str">
-        <f t="shared" si="2"/>
-        <v>RULV</v>
-      </c>
-      <c r="F92" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I92" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>45</v>
-      </c>
-      <c r="B93" t="s">
-        <v>22</v>
-      </c>
-      <c r="C93" t="str">
-        <f t="shared" si="2"/>
-        <v>LYIT</v>
-      </c>
-      <c r="F93" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I93" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>83</v>
-      </c>
-      <c r="B94" t="s">
-        <v>34</v>
-      </c>
-      <c r="C94" t="str">
-        <f t="shared" si="2"/>
-        <v>DZES</v>
-      </c>
-      <c r="E94" t="s">
-        <v>184</v>
-      </c>
-      <c r="F94" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="I94" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>78</v>
-      </c>
-      <c r="B95" t="s">
-        <v>34</v>
-      </c>
-      <c r="C95" t="str">
-        <f t="shared" si="2"/>
-        <v>MAES</v>
-      </c>
-      <c r="F95" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I95" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>48</v>
-      </c>
-      <c r="B96" t="s">
-        <v>42</v>
-      </c>
-      <c r="C96" t="str">
-        <f t="shared" si="2"/>
-        <v>NODE</v>
-      </c>
-      <c r="E96" t="s">
-        <v>185</v>
-      </c>
-      <c r="F96" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
-        <v>48</v>
-      </c>
-      <c r="B97" t="s">
-        <v>28</v>
-      </c>
-      <c r="C97" t="str">
-        <f t="shared" si="2"/>
-        <v>NONL</v>
-      </c>
-      <c r="E97" t="s">
-        <v>186</v>
-      </c>
-      <c r="F97" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
-        <v>48</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="str">
-        <f t="shared" si="2"/>
-        <v>NOBE</v>
-      </c>
-      <c r="E98" t="s">
-        <v>187</v>
-      </c>
-      <c r="F98" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>48</v>
-      </c>
-      <c r="B99" t="s">
-        <v>18</v>
-      </c>
-      <c r="C99" t="str">
-        <f t="shared" si="2"/>
-        <v>NOFR</v>
-      </c>
-      <c r="E99" t="s">
-        <v>188</v>
-      </c>
-      <c r="F99" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>48</v>
-      </c>
-      <c r="B100" t="s">
-        <v>38</v>
-      </c>
-      <c r="C100" t="str">
-        <f t="shared" si="2"/>
-        <v>NOUK</v>
-      </c>
-      <c r="E100" t="s">
-        <v>189</v>
-      </c>
-      <c r="F100" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>38</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="str">
-        <f t="shared" si="2"/>
-        <v>UKBE</v>
-      </c>
-      <c r="F101" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A102" t="s">
-        <v>38</v>
-      </c>
-      <c r="B102" t="s">
-        <v>28</v>
-      </c>
-      <c r="C102" t="str">
-        <f t="shared" si="2"/>
-        <v>UKNL</v>
-      </c>
-      <c r="E102" t="s">
-        <v>190</v>
-      </c>
-      <c r="F102" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A103" t="s">
-        <v>74</v>
-      </c>
-      <c r="B103" t="s">
-        <v>22</v>
-      </c>
-      <c r="C103" t="str">
-        <f t="shared" si="2"/>
-        <v>ALIT</v>
-      </c>
-      <c r="F103" t="b">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A104" t="s">
-        <v>20</v>
-      </c>
-      <c r="B104" t="s">
-        <v>74</v>
-      </c>
-      <c r="C104" t="str">
-        <f t="shared" si="2"/>
-        <v>GRAL</v>
-      </c>
-      <c r="E104" t="s">
-        <v>191</v>
-      </c>
-      <c r="F104" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A105" t="s">
-        <v>83</v>
-      </c>
-      <c r="B105" t="s">
-        <v>78</v>
-      </c>
-      <c r="C105" t="str">
-        <f t="shared" si="2"/>
-        <v>DZMA</v>
-      </c>
-      <c r="E105" t="s">
-        <v>192</v>
-      </c>
-      <c r="F105" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A106" t="s">
-        <v>83</v>
-      </c>
-      <c r="B106" t="s">
-        <v>55</v>
-      </c>
-      <c r="C106" t="str">
-        <f t="shared" si="2"/>
-        <v>DZTN</v>
-      </c>
-      <c r="E106" t="s">
-        <v>193</v>
-      </c>
-      <c r="F106" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A107" t="s">
-        <v>40</v>
-      </c>
-      <c r="B107" t="s">
-        <v>80</v>
-      </c>
-      <c r="C107" t="str">
-        <f t="shared" si="2"/>
-        <v>DKSE</v>
-      </c>
-      <c r="E107" t="s">
-        <v>194</v>
-      </c>
-      <c r="F107" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A108" t="s">
-        <v>53</v>
-      </c>
-      <c r="B108" t="s">
-        <v>75</v>
-      </c>
-      <c r="C108" t="str">
-        <f t="shared" si="2"/>
-        <v>RUBY</v>
-      </c>
-      <c r="E108" t="s">
-        <v>195</v>
-      </c>
-      <c r="F108" t="b">
-        <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C781A78E-EFEC-4F2E-A496-3B44BD173FD3}">
   <dimension ref="A1:I281"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -12786,7 +10429,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68B577B-1347-43AB-A697-F4519763B965}">
   <dimension ref="A1:C166"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
